--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -220,12 +220,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+游戏中，【左侧列表】不能打开对应界面时的提示</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -257,6 +279,9 @@
     <t>开启状态</t>
   </si>
   <si>
+    <t>提示文本ID</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -294,6 +319,9 @@
   </si>
   <si>
     <t>isOpen</t>
+  </si>
+  <si>
+    <t>tips</t>
   </si>
   <si>
     <t>小游戏</t>
@@ -1494,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="3" customWidth="1"/>
@@ -1507,11 +1535,12 @@
     <col min="8" max="8" width="19.7" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.875" style="3" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="26" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="11" max="11" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="26" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1542,71 +1571,80 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1617,33 +1655,35 @@
       <c r="H4" s="9"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J5" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" s="10"/>
+      <c r="L5" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -1652,25 +1692,26 @@
         <v>3</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="10">
         <v>3</v>
       </c>
@@ -1679,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1688,16 +1729,17 @@
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J7" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" s="10"/>
+      <c r="L7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="10">
         <v>4</v>
       </c>
@@ -1706,10 +1748,10 @@
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" s="10">
         <v>3</v>
@@ -1719,16 +1761,17 @@
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J8" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="10"/>
+      <c r="L8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="10">
         <v>5</v>
       </c>
@@ -1737,7 +1780,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1746,52 +1789,52 @@
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="10"/>
+      <c r="L9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="10">
         <v>6</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="11">
         <v>1</v>
       </c>
-      <c r="H10" s="11">
-        <v>3</v>
-      </c>
+      <c r="H10" s="11"/>
       <c r="I10" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J10" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="10"/>
+      <c r="L10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="10">
         <v>7</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -1800,23 +1843,24 @@
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J11" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="10"/>
+      <c r="L11" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -1825,41 +1869,43 @@
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J12" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="10"/>
+      <c r="L12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="10">
         <v>9</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="10">
         <v>10</v>
       </c>
@@ -1868,7 +1914,7 @@
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10">
@@ -1879,16 +1925,17 @@
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="10"/>
+      <c r="L14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="12">
         <v>101</v>
       </c>
@@ -1897,31 +1944,34 @@
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="12">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H15" s="13">
         <v>1</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="12">
+        <v>47061</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="12">
         <v>102</v>
       </c>
@@ -1932,10 +1982,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" s="12">
         <v>2</v>
@@ -1945,16 +1995,17 @@
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" s="12"/>
+      <c r="L16" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="12">
         <v>103</v>
       </c>
@@ -1965,31 +2016,32 @@
         <v>5</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="12">
         <v>9</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="13">
         <v>2</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" s="12"/>
+      <c r="L17" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="12">
         <v>104</v>
       </c>
@@ -2000,29 +2052,30 @@
         <v>4</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F18" s="12">
         <v>5</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="K18" s="12"/>
+      <c r="L18" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="12">
         <v>105</v>
       </c>
@@ -2031,29 +2084,30 @@
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F19" s="12">
         <v>6</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J19" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="K19" s="12"/>
+      <c r="L19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="12">
         <v>106</v>
       </c>
@@ -2064,10 +2118,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F20" s="12">
         <v>7</v>
@@ -2077,16 +2131,17 @@
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J20" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" s="12"/>
+      <c r="L20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="12">
         <v>107</v>
       </c>
@@ -2097,10 +2152,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F21" s="12">
         <v>8</v>
@@ -2110,16 +2165,17 @@
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J21" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" s="12"/>
+      <c r="L21" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="12">
         <v>108</v>
       </c>
@@ -2130,10 +2186,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F22" s="12">
         <v>10</v>
@@ -2143,16 +2199,17 @@
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J22" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="K22" s="12"/>
+      <c r="L22" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="12">
         <v>109</v>
       </c>
@@ -2161,10 +2218,10 @@
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F23" s="12">
         <v>11</v>
@@ -2174,16 +2231,17 @@
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J23" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="K23" s="12"/>
+      <c r="L23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="12">
         <v>110</v>
       </c>
@@ -2192,10 +2250,10 @@
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F24" s="12">
         <v>12</v>
@@ -2205,16 +2263,17 @@
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J24" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="K24" s="12"/>
+      <c r="L24" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="12">
         <v>111</v>
       </c>
@@ -2223,29 +2282,30 @@
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F25" s="12">
         <v>13</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J25" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="K25" s="12"/>
+      <c r="L25" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="12">
         <v>112</v>
       </c>
@@ -2254,10 +2314,10 @@
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F26" s="12">
         <v>14</v>
@@ -2267,16 +2327,17 @@
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J26" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:11">
+      <c r="K26" s="12"/>
+      <c r="L26" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:12">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2285,29 +2346,29 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F27" s="2">
         <v>15</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:11">
+      <c r="L27" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:12">
       <c r="A28" s="2">
         <v>114</v>
       </c>
@@ -2316,10 +2377,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -2329,16 +2390,16 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:11">
+      <c r="L28" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:12">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2347,10 +2408,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -2360,16 +2421,16 @@
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:11">
+      <c r="L29" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:12">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2378,10 +2439,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -2391,16 +2452,16 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:11">
+      <c r="L30" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:12">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2409,10 +2470,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F31" s="2">
         <v>18</v>
@@ -2422,16 +2483,16 @@
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:11">
+      <c r="L31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:12">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2440,10 +2501,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -2453,13 +2514,13 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>30</v>
+      <c r="L32" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -216,7 +216,31 @@
           </rPr>
           <t xml:space="preserve">
 条件类型_条件参数
-condition表中条件类型</t>
+condition表中条件类型
+注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
         </r>
       </text>
     </comment>
@@ -247,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>id</t>
   </si>
@@ -330,7 +354,7 @@
     <t>1_2</t>
   </si>
   <si>
-    <t>1_20</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>显示位置：大厅 + 各游戏区</t>
@@ -339,7 +363,7 @@
     <t>摇钱树</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_5</t>
   </si>
   <si>
     <t>官方派奖</t>
@@ -366,9 +390,6 @@
     <t>公告</t>
   </si>
   <si>
-    <t>1_1</t>
-  </si>
-  <si>
     <t>私人房间</t>
   </si>
   <si>
@@ -378,6 +399,9 @@
     <t>幸运夺宝</t>
   </si>
   <si>
+    <t>Grid (21)</t>
+  </si>
+  <si>
     <t>我的赌场</t>
   </si>
   <si>
@@ -408,9 +432,6 @@
     <t>Grid (2)</t>
   </si>
   <si>
-    <t>1_5</t>
-  </si>
-  <si>
     <t>首充礼包</t>
   </si>
   <si>
@@ -439,9 +460,6 @@
   </si>
   <si>
     <t>Grid (5)</t>
-  </si>
-  <si>
-    <t>1_30</t>
   </si>
   <si>
     <t>客服</t>
@@ -1578,7 +1596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -1611,7 +1629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1675,8 +1693,8 @@
       <c r="I5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="10" t="b">
-        <v>1</v>
+      <c r="J5" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="3" t="s">
@@ -1729,7 +1747,7 @@
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J7" s="10" t="b">
         <v>1</v>
@@ -1754,14 +1772,14 @@
         <v>34</v>
       </c>
       <c r="F8" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="11">
         <v>1</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J8" s="10" t="b">
         <v>1</v>
@@ -1789,7 +1807,7 @@
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J9" s="10" t="b">
         <v>1</v>
@@ -1817,7 +1835,7 @@
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J10" s="10" t="b">
         <v>1</v>
@@ -1843,7 +1861,7 @@
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J11" s="10" t="b">
         <v>1</v>
@@ -1860,7 +1878,7 @@
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -1886,7 +1904,7 @@
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1895,7 +1913,7 @@
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J13" s="10" t="b">
         <v>1</v>
@@ -1914,9 +1932,11 @@
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="10"/>
       <c r="F14" s="10">
         <v>4</v>
       </c>
@@ -1925,7 +1945,7 @@
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J14" s="10" t="b">
         <v>1</v>
@@ -1995,7 +2015,7 @@
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J16" s="12" t="b">
         <v>1</v>
@@ -2058,7 +2078,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>26</v>
@@ -2097,7 +2117,7 @@
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="J19" s="12" t="b">
         <v>1</v>
@@ -2118,10 +2138,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>54</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>55</v>
       </c>
       <c r="F20" s="12">
         <v>7</v>
@@ -2152,10 +2172,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="F21" s="12">
         <v>8</v>
@@ -2186,10 +2206,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>58</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>59</v>
       </c>
       <c r="F22" s="12">
         <v>10</v>
@@ -2199,7 +2219,7 @@
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J22" s="12" t="b">
         <v>1</v>
@@ -2218,10 +2238,10 @@
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>61</v>
       </c>
       <c r="F23" s="12">
         <v>11</v>
@@ -2231,7 +2251,7 @@
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J23" s="12" t="b">
         <v>1</v>
@@ -2250,10 +2270,10 @@
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>63</v>
       </c>
       <c r="F24" s="12">
         <v>12</v>
@@ -2263,7 +2283,7 @@
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="J24" s="12" t="b">
         <v>1</v>
@@ -2282,27 +2302,27 @@
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F25" s="12">
         <v>13</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J25" s="12" t="b">
         <v>1</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2314,10 +2334,10 @@
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F26" s="12">
         <v>14</v>
@@ -2327,7 +2347,7 @@
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J26" s="12" t="b">
         <v>1</v>
@@ -2346,10 +2366,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" s="2">
         <v>15</v>
@@ -2359,7 +2379,7 @@
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2377,10 +2397,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -2390,7 +2410,7 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J28" s="2" t="b">
         <v>0</v>
@@ -2408,10 +2428,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -2421,7 +2441,7 @@
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2439,10 +2459,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -2452,7 +2472,7 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2470,10 +2490,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F31" s="2">
         <v>18</v>
@@ -2483,7 +2503,7 @@
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2501,10 +2521,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -2514,7 +2534,7 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -713,12 +713,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1947,8 +1947,8 @@
       <c r="I14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="10" t="b">
-        <v>1</v>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -713,12 +713,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1947,8 +1947,8 @@
       <c r="I14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
+      <c r="J14" s="10" t="b">
+        <v>1</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -517,6 +517,15 @@
   </si>
   <si>
     <t>Grid (18)</t>
+  </si>
+  <si>
+    <t>限时礼包</t>
+  </si>
+  <si>
+    <t>Grid (22)</t>
+  </si>
+  <si>
+    <t>财富轮盘</t>
   </si>
 </sst>
 </file>
@@ -529,7 +538,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +556,11 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.35"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -713,12 +727,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1050,137 +1064,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1191,43 +1205,52 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1540,56 +1563,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="26" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="26" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1597,763 +1620,763 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="10">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="11">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="12"/>
+      <c r="I5" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="11"/>
+      <c r="L5" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11">
         <v>3</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="10" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="3" t="s">
+      <c r="J6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>3</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11">
         <v>9</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11">
-        <v>1</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="3" t="s">
+      <c r="J7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <v>4</v>
       </c>
-      <c r="B8" s="10">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10" t="s">
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>5</v>
       </c>
-      <c r="G8" s="11">
-        <v>1</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10" t="s">
+      <c r="G8" s="12">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="3" t="s">
+      <c r="J8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <v>5</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11">
         <v>6</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11">
-        <v>1</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="3" t="s">
+      <c r="J9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>6</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11">
-        <v>1</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="10" t="s">
+      <c r="F10" s="11"/>
+      <c r="G10" s="12">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="3" t="s">
+      <c r="J10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>7</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="10" t="s">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="3" t="s">
+      <c r="J11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <v>8</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="10" t="s">
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="3" t="s">
+      <c r="J12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <v>9</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11" t="s">
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="10" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="3" t="s">
+      <c r="J13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <v>10</v>
       </c>
-      <c r="B14" s="10">
-        <v>1</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10" t="s">
+      <c r="B14" s="11">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>4</v>
       </c>
-      <c r="G14" s="11">
-        <v>1</v>
-      </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="10" t="s">
+      <c r="G14" s="12">
+        <v>1</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="3" t="s">
+      <c r="J14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>101</v>
       </c>
-      <c r="B15" s="12">
-        <v>1</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12" t="s">
+      <c r="B15" s="13">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="12">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="F15" s="13">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="13">
-        <v>1</v>
-      </c>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="14">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="12">
+      <c r="J15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="13">
         <v>47061</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>102</v>
       </c>
-      <c r="B16" s="12">
-        <v>1</v>
-      </c>
-      <c r="C16" s="12">
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13">
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>2</v>
       </c>
-      <c r="G16" s="13">
-        <v>1</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="12" t="s">
+      <c r="G16" s="14">
+        <v>1</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="3" t="s">
+      <c r="J16" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="13"/>
+      <c r="L16" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>103</v>
       </c>
-      <c r="B17" s="12">
-        <v>1</v>
-      </c>
-      <c r="C17" s="12">
+      <c r="B17" s="13">
+        <v>1</v>
+      </c>
+      <c r="C17" s="13">
         <v>5</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>9</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <v>2</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="3" t="s">
+      <c r="J17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>104</v>
       </c>
-      <c r="B18" s="12">
-        <v>1</v>
-      </c>
-      <c r="C18" s="12">
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13">
         <v>4</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <v>3</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="12" t="s">
+      <c r="H18" s="14"/>
+      <c r="I18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="3" t="s">
+      <c r="J18" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>105</v>
       </c>
-      <c r="B19" s="12">
-        <v>1</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12" t="s">
+      <c r="B19" s="13">
+        <v>1</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>6</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="12" t="s">
+      <c r="H19" s="14"/>
+      <c r="I19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J19" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="3" t="s">
+      <c r="J19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13"/>
+      <c r="L19" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>106</v>
       </c>
-      <c r="B20" s="12">
-        <v>1</v>
-      </c>
-      <c r="C20" s="12">
+      <c r="B20" s="13">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13">
         <v>11</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>7</v>
       </c>
-      <c r="G20" s="13">
-        <v>1</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="12" t="s">
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="3" t="s">
+      <c r="J20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>107</v>
       </c>
-      <c r="B21" s="12">
-        <v>1</v>
-      </c>
-      <c r="C21" s="12">
+      <c r="B21" s="13">
+        <v>1</v>
+      </c>
+      <c r="C21" s="13">
         <v>15</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>8</v>
       </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="12" t="s">
+      <c r="G21" s="14">
+        <v>1</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="3" t="s">
+      <c r="J21" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>108</v>
       </c>
-      <c r="B22" s="12">
-        <v>1</v>
-      </c>
-      <c r="C22" s="12">
+      <c r="B22" s="13">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13">
         <v>10</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <v>10</v>
       </c>
-      <c r="G22" s="13">
-        <v>1</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="12" t="s">
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="3" t="s">
+      <c r="J22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="13"/>
+      <c r="L22" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>109</v>
       </c>
-      <c r="B23" s="12">
-        <v>1</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12" t="s">
+      <c r="B23" s="13">
+        <v>1</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>11</v>
       </c>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="12" t="s">
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="3" t="s">
+      <c r="J23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="13"/>
+      <c r="L23" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>110</v>
       </c>
-      <c r="B24" s="12">
-        <v>1</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12" t="s">
+      <c r="B24" s="13">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="13">
         <v>12</v>
       </c>
-      <c r="G24" s="13">
-        <v>1</v>
-      </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="12" t="s">
+      <c r="G24" s="14">
+        <v>1</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="3" t="s">
+      <c r="J24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="13"/>
+      <c r="L24" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>111</v>
       </c>
-      <c r="B25" s="12">
-        <v>1</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="B25" s="13">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="13">
         <v>13</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="12" t="s">
+      <c r="H25" s="14"/>
+      <c r="I25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="3" t="s">
+      <c r="J25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>112</v>
       </c>
-      <c r="B26" s="12">
-        <v>1</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12" t="s">
+      <c r="B26" s="13">
+        <v>1</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="13">
         <v>14</v>
       </c>
-      <c r="G26" s="13">
-        <v>1</v>
-      </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="12" t="s">
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J26" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="3" t="s">
+      <c r="J26" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="13"/>
+      <c r="L26" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2374,10 +2397,10 @@
       <c r="F27" s="2">
         <v>15</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="14"/>
+      <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
         <v>71</v>
       </c>
@@ -2399,16 +2422,16 @@
       <c r="D28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15"/>
       <c r="I28" s="2" t="s">
         <v>71</v>
       </c>
@@ -2430,16 +2453,16 @@
       <c r="D29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
         <v>71</v>
       </c>
@@ -2461,16 +2484,16 @@
       <c r="D30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="16" t="s">
         <v>77</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
         <v>71</v>
       </c>
@@ -2492,16 +2515,16 @@
       <c r="D31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="16" t="s">
         <v>79</v>
       </c>
       <c r="F31" s="2">
         <v>18</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
         <v>71</v>
       </c>
@@ -2523,16 +2546,16 @@
       <c r="D32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>81</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
       </c>
-      <c r="G32" s="14">
-        <v>1</v>
-      </c>
-      <c r="H32" s="14"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
         <v>71</v>
       </c>
@@ -2540,6 +2563,62 @@
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:12">
+      <c r="A33" s="3">
+        <v>119</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="3">
+        <v>20</v>
+      </c>
+      <c r="G33" s="18">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="3">
+        <v>120</v>
+      </c>
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="4">
+        <v>21</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -523,9 +523,6 @@
   </si>
   <si>
     <t>Grid (22)</t>
-  </si>
-  <si>
-    <t>财富轮盘</t>
   </si>
 </sst>
 </file>
@@ -727,12 +724,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2580,7 +2577,7 @@
         <v>83</v>
       </c>
       <c r="F33" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" s="18">
         <v>1</v>
@@ -2597,30 +2594,10 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="3">
-        <v>120</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" s="4">
-        <v>21</v>
-      </c>
-      <c r="G34" s="5">
-        <v>1</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J34" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="2"/>
+      <c r="L34" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -1967,8 +1967,8 @@
       <c r="I14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="11" t="b">
-        <v>1</v>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2586,8 +2586,8 @@
       <c r="I33" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J33" s="13" t="b">
-        <v>1</v>
+      <c r="J33" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>32</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -523,6 +523,9 @@
   </si>
   <si>
     <t>Grid (22)</t>
+  </si>
+  <si>
+    <t>财富轮盘</t>
   </si>
 </sst>
 </file>
@@ -2594,10 +2597,34 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="3"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="2"/>
-      <c r="L34" s="3"/>
+      <c r="A34" s="2">
+        <v>120</v>
+      </c>
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="2">
+        <v>22</v>
+      </c>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -526,6 +526,12 @@
   </si>
   <si>
     <t>财富轮盘</t>
+  </si>
+  <si>
+    <t>Grid (23)</t>
+  </si>
+  <si>
+    <t>买一送七</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1200,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1248,6 +1254,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1563,7 +1572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -2597,32 +2606,61 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>120</v>
       </c>
-      <c r="B34" s="2">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="2">
+      <c r="E34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="3">
         <v>22</v>
       </c>
-      <c r="G34" s="15">
-        <v>1</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="2" t="b">
+      <c r="G34" s="19">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="4">
+        <v>121</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="4">
+        <v>23</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2" t="s">
+      <c r="K35" s="2"/>
+      <c r="L35" s="2" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -369,6 +369,9 @@
     <t>官方派奖</t>
   </si>
   <si>
+    <t>1_10</t>
+  </si>
+  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -393,6 +396,9 @@
     <t>私人房间</t>
   </si>
   <si>
+    <t>1_15</t>
+  </si>
+  <si>
     <t>商城界面</t>
   </si>
   <si>
@@ -408,6 +414,9 @@
     <t>Grid (8)</t>
   </si>
   <si>
+    <t>1_20</t>
+  </si>
+  <si>
     <t>每日奖金</t>
   </si>
   <si>
@@ -420,6 +429,9 @@
     <t>Grid (10)</t>
   </si>
   <si>
+    <t>1_25</t>
+  </si>
+  <si>
     <t>储钱罐</t>
   </si>
   <si>
@@ -430,6 +442,9 @@
   </si>
   <si>
     <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
   </si>
   <si>
     <t>首充礼包</t>
@@ -1200,7 +1215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1254,9 +1269,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1779,14 +1791,14 @@
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1798,10 +1810,10 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="11">
         <v>5</v>
@@ -1818,7 +1830,7 @@
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1830,7 +1842,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -1846,7 +1858,7 @@
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1856,10 +1868,10 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="12">
@@ -1874,7 +1886,7 @@
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1884,7 +1896,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -1900,7 +1912,7 @@
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1910,7 +1922,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -1919,14 +1931,14 @@
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J12" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1936,7 +1948,7 @@
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
@@ -1964,10 +1976,10 @@
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="11">
         <v>4</v>
@@ -1984,7 +1996,7 @@
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1996,10 +2008,10 @@
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
@@ -2011,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J15" s="13" t="b">
         <v>1</v>
@@ -2034,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F16" s="13">
         <v>2</v>
@@ -2054,7 +2066,7 @@
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2068,10 +2080,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F17" s="13">
         <v>9</v>
@@ -2083,7 +2095,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J17" s="13" t="b">
         <v>1</v>
@@ -2104,10 +2116,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
@@ -2136,10 +2148,10 @@
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F19" s="13">
         <v>6</v>
@@ -2149,7 +2161,7 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="J19" s="13" t="b">
         <v>1</v>
@@ -2170,10 +2182,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F20" s="13">
         <v>7</v>
@@ -2190,7 +2202,7 @@
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2204,10 +2216,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F21" s="13">
         <v>8</v>
@@ -2217,14 +2229,14 @@
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J21" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K21" s="13"/>
       <c r="L21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2238,10 +2250,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F22" s="13">
         <v>10</v>
@@ -2258,7 +2270,7 @@
       </c>
       <c r="K22" s="13"/>
       <c r="L22" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2270,10 +2282,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F23" s="13">
         <v>11</v>
@@ -2290,7 +2302,7 @@
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2302,10 +2314,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F24" s="13">
         <v>12</v>
@@ -2322,7 +2334,7 @@
       </c>
       <c r="K24" s="13"/>
       <c r="L24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2334,16 +2346,16 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F25" s="13">
         <v>13</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
@@ -2354,7 +2366,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2366,10 +2378,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F26" s="13">
         <v>14</v>
@@ -2386,7 +2398,7 @@
       </c>
       <c r="K26" s="13"/>
       <c r="L26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:12">
@@ -2398,10 +2410,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F27" s="2">
         <v>15</v>
@@ -2411,7 +2423,7 @@
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2429,10 +2441,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -2442,13 +2454,13 @@
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:12">
@@ -2460,10 +2472,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -2473,13 +2485,13 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:12">
@@ -2491,10 +2503,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -2504,13 +2516,13 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:12">
@@ -2522,10 +2534,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F31" s="2">
         <v>18</v>
@@ -2535,13 +2547,13 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:12">
@@ -2553,10 +2565,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -2566,13 +2578,13 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:12">
@@ -2583,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F33" s="3">
         <v>21</v>
@@ -2602,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2614,15 +2626,15 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F34" s="3">
         <v>22</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="18">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
@@ -2634,7 +2646,7 @@
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2645,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2661,7 +2673,7 @@
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -1991,8 +1991,8 @@
       <c r="I14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
+      <c r="J14" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -1264,14 +1264,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1584,7 +1584,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:XFD35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1934,7 +1934,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">
@@ -1992,7 +1992,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
@@ -2069,7 +2069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A17" s="13">
         <v>103</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A18" s="13">
         <v>104</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A19" s="13">
         <v>105</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A20" s="13">
         <v>106</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A21" s="13">
         <v>107</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A22" s="13">
         <v>108</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A23" s="13">
         <v>109</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A24" s="13">
         <v>110</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A25" s="13">
         <v>111</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A26" s="13">
         <v>112</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:12">
+    <row r="27" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2432,38 +2432,7479 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:12">
-      <c r="A28" s="2">
+    <row r="28" s="3" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+      <c r="A28" s="3">
         <v>114</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>1</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>16</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28" s="2" t="b">
+      <c r="H28" s="17"/>
+      <c r="I28" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="P28" s="16"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="2"/>
+      <c r="AA28" s="16"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="2"/>
+      <c r="AL28" s="16"/>
+      <c r="AN28" s="17"/>
+      <c r="AO28" s="17"/>
+      <c r="AP28" s="13"/>
+      <c r="AQ28" s="2"/>
+      <c r="AW28" s="16"/>
+      <c r="AY28" s="17"/>
+      <c r="AZ28" s="17"/>
+      <c r="BA28" s="13"/>
+      <c r="BB28" s="2"/>
+      <c r="BH28" s="16"/>
+      <c r="BJ28" s="17"/>
+      <c r="BK28" s="17"/>
+      <c r="BL28" s="13"/>
+      <c r="BM28" s="2"/>
+      <c r="BS28" s="16"/>
+      <c r="BU28" s="17"/>
+      <c r="BV28" s="17"/>
+      <c r="BW28" s="13"/>
+      <c r="BX28" s="2"/>
+      <c r="CD28" s="16"/>
+      <c r="CF28" s="17"/>
+      <c r="CG28" s="17"/>
+      <c r="CH28" s="13"/>
+      <c r="CI28" s="2"/>
+      <c r="CO28" s="16"/>
+      <c r="CQ28" s="17"/>
+      <c r="CR28" s="17"/>
+      <c r="CS28" s="13"/>
+      <c r="CT28" s="2"/>
+      <c r="CZ28" s="16"/>
+      <c r="DB28" s="17"/>
+      <c r="DC28" s="17"/>
+      <c r="DD28" s="13"/>
+      <c r="DE28" s="2"/>
+      <c r="DK28" s="16"/>
+      <c r="DM28" s="17"/>
+      <c r="DN28" s="17"/>
+      <c r="DO28" s="13"/>
+      <c r="DP28" s="2"/>
+      <c r="DV28" s="16"/>
+      <c r="DX28" s="17"/>
+      <c r="DY28" s="17"/>
+      <c r="DZ28" s="13"/>
+      <c r="EA28" s="2"/>
+      <c r="EG28" s="16"/>
+      <c r="EI28" s="17"/>
+      <c r="EJ28" s="17"/>
+      <c r="EK28" s="13"/>
+      <c r="EL28" s="2"/>
+      <c r="ER28" s="16"/>
+      <c r="ET28" s="17"/>
+      <c r="EU28" s="17"/>
+      <c r="EV28" s="13"/>
+      <c r="EW28" s="2"/>
+      <c r="FC28" s="16"/>
+      <c r="FE28" s="17"/>
+      <c r="FF28" s="17"/>
+      <c r="FG28" s="13"/>
+      <c r="FH28" s="2"/>
+      <c r="FN28" s="16"/>
+      <c r="FP28" s="17"/>
+      <c r="FQ28" s="17"/>
+      <c r="FR28" s="13"/>
+      <c r="FS28" s="2"/>
+      <c r="FY28" s="16"/>
+      <c r="GA28" s="17"/>
+      <c r="GB28" s="17"/>
+      <c r="GC28" s="13"/>
+      <c r="GD28" s="2"/>
+      <c r="GJ28" s="16"/>
+      <c r="GL28" s="17"/>
+      <c r="GM28" s="17"/>
+      <c r="GN28" s="13"/>
+      <c r="GO28" s="2"/>
+      <c r="GU28" s="16"/>
+      <c r="GW28" s="17"/>
+      <c r="GX28" s="17"/>
+      <c r="GY28" s="13"/>
+      <c r="GZ28" s="2"/>
+      <c r="HF28" s="16"/>
+      <c r="HH28" s="17"/>
+      <c r="HI28" s="17"/>
+      <c r="HJ28" s="13"/>
+      <c r="HK28" s="2"/>
+      <c r="HQ28" s="16"/>
+      <c r="HS28" s="17"/>
+      <c r="HT28" s="17"/>
+      <c r="HU28" s="13"/>
+      <c r="HV28" s="2"/>
+      <c r="IB28" s="16"/>
+      <c r="ID28" s="17"/>
+      <c r="IE28" s="17"/>
+      <c r="IF28" s="13"/>
+      <c r="IG28" s="2"/>
+      <c r="IM28" s="16"/>
+      <c r="IO28" s="17"/>
+      <c r="IP28" s="17"/>
+      <c r="IQ28" s="13"/>
+      <c r="IR28" s="2"/>
+      <c r="IX28" s="16"/>
+      <c r="IZ28" s="17"/>
+      <c r="JA28" s="17"/>
+      <c r="JB28" s="13"/>
+      <c r="JC28" s="2"/>
+      <c r="JI28" s="16"/>
+      <c r="JK28" s="17"/>
+      <c r="JL28" s="17"/>
+      <c r="JM28" s="13"/>
+      <c r="JN28" s="2"/>
+      <c r="JT28" s="16"/>
+      <c r="JV28" s="17"/>
+      <c r="JW28" s="17"/>
+      <c r="JX28" s="13"/>
+      <c r="JY28" s="2"/>
+      <c r="KE28" s="16"/>
+      <c r="KG28" s="17"/>
+      <c r="KH28" s="17"/>
+      <c r="KI28" s="13"/>
+      <c r="KJ28" s="2"/>
+      <c r="KP28" s="16"/>
+      <c r="KR28" s="17"/>
+      <c r="KS28" s="17"/>
+      <c r="KT28" s="13"/>
+      <c r="KU28" s="2"/>
+      <c r="LA28" s="16"/>
+      <c r="LC28" s="17"/>
+      <c r="LD28" s="17"/>
+      <c r="LE28" s="13"/>
+      <c r="LF28" s="2"/>
+      <c r="LL28" s="16"/>
+      <c r="LN28" s="17"/>
+      <c r="LO28" s="17"/>
+      <c r="LP28" s="13"/>
+      <c r="LQ28" s="2"/>
+      <c r="LW28" s="16"/>
+      <c r="LY28" s="17"/>
+      <c r="LZ28" s="17"/>
+      <c r="MA28" s="13"/>
+      <c r="MB28" s="2"/>
+      <c r="MH28" s="16"/>
+      <c r="MJ28" s="17"/>
+      <c r="MK28" s="17"/>
+      <c r="ML28" s="13"/>
+      <c r="MM28" s="2"/>
+      <c r="MS28" s="16"/>
+      <c r="MU28" s="17"/>
+      <c r="MV28" s="17"/>
+      <c r="MW28" s="13"/>
+      <c r="MX28" s="2"/>
+      <c r="ND28" s="16"/>
+      <c r="NF28" s="17"/>
+      <c r="NG28" s="17"/>
+      <c r="NH28" s="13"/>
+      <c r="NI28" s="2"/>
+      <c r="NO28" s="16"/>
+      <c r="NQ28" s="17"/>
+      <c r="NR28" s="17"/>
+      <c r="NS28" s="13"/>
+      <c r="NT28" s="2"/>
+      <c r="NZ28" s="16"/>
+      <c r="OB28" s="17"/>
+      <c r="OC28" s="17"/>
+      <c r="OD28" s="13"/>
+      <c r="OE28" s="2"/>
+      <c r="OK28" s="16"/>
+      <c r="OM28" s="17"/>
+      <c r="ON28" s="17"/>
+      <c r="OO28" s="13"/>
+      <c r="OP28" s="2"/>
+      <c r="OV28" s="16"/>
+      <c r="OX28" s="17"/>
+      <c r="OY28" s="17"/>
+      <c r="OZ28" s="13"/>
+      <c r="PA28" s="2"/>
+      <c r="PG28" s="16"/>
+      <c r="PI28" s="17"/>
+      <c r="PJ28" s="17"/>
+      <c r="PK28" s="13"/>
+      <c r="PL28" s="2"/>
+      <c r="PR28" s="16"/>
+      <c r="PT28" s="17"/>
+      <c r="PU28" s="17"/>
+      <c r="PV28" s="13"/>
+      <c r="PW28" s="2"/>
+      <c r="QC28" s="16"/>
+      <c r="QE28" s="17"/>
+      <c r="QF28" s="17"/>
+      <c r="QG28" s="13"/>
+      <c r="QH28" s="2"/>
+      <c r="QN28" s="16"/>
+      <c r="QP28" s="17"/>
+      <c r="QQ28" s="17"/>
+      <c r="QR28" s="13"/>
+      <c r="QS28" s="2"/>
+      <c r="QY28" s="16"/>
+      <c r="RA28" s="17"/>
+      <c r="RB28" s="17"/>
+      <c r="RC28" s="13"/>
+      <c r="RD28" s="2"/>
+      <c r="RJ28" s="16"/>
+      <c r="RL28" s="17"/>
+      <c r="RM28" s="17"/>
+      <c r="RN28" s="13"/>
+      <c r="RO28" s="2"/>
+      <c r="RU28" s="16"/>
+      <c r="RW28" s="17"/>
+      <c r="RX28" s="17"/>
+      <c r="RY28" s="13"/>
+      <c r="RZ28" s="2"/>
+      <c r="SF28" s="16"/>
+      <c r="SH28" s="17"/>
+      <c r="SI28" s="17"/>
+      <c r="SJ28" s="13"/>
+      <c r="SK28" s="2"/>
+      <c r="SQ28" s="16"/>
+      <c r="SS28" s="17"/>
+      <c r="ST28" s="17"/>
+      <c r="SU28" s="13"/>
+      <c r="SV28" s="2"/>
+      <c r="TB28" s="16"/>
+      <c r="TD28" s="17"/>
+      <c r="TE28" s="17"/>
+      <c r="TF28" s="13"/>
+      <c r="TG28" s="2"/>
+      <c r="TM28" s="16"/>
+      <c r="TO28" s="17"/>
+      <c r="TP28" s="17"/>
+      <c r="TQ28" s="13"/>
+      <c r="TR28" s="2"/>
+      <c r="TX28" s="16"/>
+      <c r="TZ28" s="17"/>
+      <c r="UA28" s="17"/>
+      <c r="UB28" s="13"/>
+      <c r="UC28" s="2"/>
+      <c r="UI28" s="16"/>
+      <c r="UK28" s="17"/>
+      <c r="UL28" s="17"/>
+      <c r="UM28" s="13"/>
+      <c r="UN28" s="2"/>
+      <c r="UT28" s="16"/>
+      <c r="UV28" s="17"/>
+      <c r="UW28" s="17"/>
+      <c r="UX28" s="13"/>
+      <c r="UY28" s="2"/>
+      <c r="VE28" s="16"/>
+      <c r="VG28" s="17"/>
+      <c r="VH28" s="17"/>
+      <c r="VI28" s="13"/>
+      <c r="VJ28" s="2"/>
+      <c r="VP28" s="16"/>
+      <c r="VR28" s="17"/>
+      <c r="VS28" s="17"/>
+      <c r="VT28" s="13"/>
+      <c r="VU28" s="2"/>
+      <c r="WA28" s="16"/>
+      <c r="WC28" s="17"/>
+      <c r="WD28" s="17"/>
+      <c r="WE28" s="13"/>
+      <c r="WF28" s="2"/>
+      <c r="WL28" s="16"/>
+      <c r="WN28" s="17"/>
+      <c r="WO28" s="17"/>
+      <c r="WP28" s="13"/>
+      <c r="WQ28" s="2"/>
+      <c r="WW28" s="16"/>
+      <c r="WY28" s="17"/>
+      <c r="WZ28" s="17"/>
+      <c r="XA28" s="13"/>
+      <c r="XB28" s="2"/>
+      <c r="XH28" s="16"/>
+      <c r="XJ28" s="17"/>
+      <c r="XK28" s="17"/>
+      <c r="XL28" s="13"/>
+      <c r="XM28" s="2"/>
+      <c r="XS28" s="16"/>
+      <c r="XU28" s="17"/>
+      <c r="XV28" s="17"/>
+      <c r="XW28" s="13"/>
+      <c r="XX28" s="2"/>
+      <c r="YD28" s="16"/>
+      <c r="YF28" s="17"/>
+      <c r="YG28" s="17"/>
+      <c r="YH28" s="13"/>
+      <c r="YI28" s="2"/>
+      <c r="YO28" s="16"/>
+      <c r="YQ28" s="17"/>
+      <c r="YR28" s="17"/>
+      <c r="YS28" s="13"/>
+      <c r="YT28" s="2"/>
+      <c r="YZ28" s="16"/>
+      <c r="ZB28" s="17"/>
+      <c r="ZC28" s="17"/>
+      <c r="ZD28" s="13"/>
+      <c r="ZE28" s="2"/>
+      <c r="ZK28" s="16"/>
+      <c r="ZM28" s="17"/>
+      <c r="ZN28" s="17"/>
+      <c r="ZO28" s="13"/>
+      <c r="ZP28" s="2"/>
+      <c r="ZV28" s="16"/>
+      <c r="ZX28" s="17"/>
+      <c r="ZY28" s="17"/>
+      <c r="ZZ28" s="13"/>
+      <c r="AAA28" s="2"/>
+      <c r="AAG28" s="16"/>
+      <c r="AAI28" s="17"/>
+      <c r="AAJ28" s="17"/>
+      <c r="AAK28" s="13"/>
+      <c r="AAL28" s="2"/>
+      <c r="AAR28" s="16"/>
+      <c r="AAT28" s="17"/>
+      <c r="AAU28" s="17"/>
+      <c r="AAV28" s="13"/>
+      <c r="AAW28" s="2"/>
+      <c r="ABC28" s="16"/>
+      <c r="ABE28" s="17"/>
+      <c r="ABF28" s="17"/>
+      <c r="ABG28" s="13"/>
+      <c r="ABH28" s="2"/>
+      <c r="ABN28" s="16"/>
+      <c r="ABP28" s="17"/>
+      <c r="ABQ28" s="17"/>
+      <c r="ABR28" s="13"/>
+      <c r="ABS28" s="2"/>
+      <c r="ABY28" s="16"/>
+      <c r="ACA28" s="17"/>
+      <c r="ACB28" s="17"/>
+      <c r="ACC28" s="13"/>
+      <c r="ACD28" s="2"/>
+      <c r="ACJ28" s="16"/>
+      <c r="ACL28" s="17"/>
+      <c r="ACM28" s="17"/>
+      <c r="ACN28" s="13"/>
+      <c r="ACO28" s="2"/>
+      <c r="ACU28" s="16"/>
+      <c r="ACW28" s="17"/>
+      <c r="ACX28" s="17"/>
+      <c r="ACY28" s="13"/>
+      <c r="ACZ28" s="2"/>
+      <c r="ADF28" s="16"/>
+      <c r="ADH28" s="17"/>
+      <c r="ADI28" s="17"/>
+      <c r="ADJ28" s="13"/>
+      <c r="ADK28" s="2"/>
+      <c r="ADQ28" s="16"/>
+      <c r="ADS28" s="17"/>
+      <c r="ADT28" s="17"/>
+      <c r="ADU28" s="13"/>
+      <c r="ADV28" s="2"/>
+      <c r="AEB28" s="16"/>
+      <c r="AED28" s="17"/>
+      <c r="AEE28" s="17"/>
+      <c r="AEF28" s="13"/>
+      <c r="AEG28" s="2"/>
+      <c r="AEM28" s="16"/>
+      <c r="AEO28" s="17"/>
+      <c r="AEP28" s="17"/>
+      <c r="AEQ28" s="13"/>
+      <c r="AER28" s="2"/>
+      <c r="AEX28" s="16"/>
+      <c r="AEZ28" s="17"/>
+      <c r="AFA28" s="17"/>
+      <c r="AFB28" s="13"/>
+      <c r="AFC28" s="2"/>
+      <c r="AFI28" s="16"/>
+      <c r="AFK28" s="17"/>
+      <c r="AFL28" s="17"/>
+      <c r="AFM28" s="13"/>
+      <c r="AFN28" s="2"/>
+      <c r="AFT28" s="16"/>
+      <c r="AFV28" s="17"/>
+      <c r="AFW28" s="17"/>
+      <c r="AFX28" s="13"/>
+      <c r="AFY28" s="2"/>
+      <c r="AGE28" s="16"/>
+      <c r="AGG28" s="17"/>
+      <c r="AGH28" s="17"/>
+      <c r="AGI28" s="13"/>
+      <c r="AGJ28" s="2"/>
+      <c r="AGP28" s="16"/>
+      <c r="AGR28" s="17"/>
+      <c r="AGS28" s="17"/>
+      <c r="AGT28" s="13"/>
+      <c r="AGU28" s="2"/>
+      <c r="AHA28" s="16"/>
+      <c r="AHC28" s="17"/>
+      <c r="AHD28" s="17"/>
+      <c r="AHE28" s="13"/>
+      <c r="AHF28" s="2"/>
+      <c r="AHL28" s="16"/>
+      <c r="AHN28" s="17"/>
+      <c r="AHO28" s="17"/>
+      <c r="AHP28" s="13"/>
+      <c r="AHQ28" s="2"/>
+      <c r="AHW28" s="16"/>
+      <c r="AHY28" s="17"/>
+      <c r="AHZ28" s="17"/>
+      <c r="AIA28" s="13"/>
+      <c r="AIB28" s="2"/>
+      <c r="AIH28" s="16"/>
+      <c r="AIJ28" s="17"/>
+      <c r="AIK28" s="17"/>
+      <c r="AIL28" s="13"/>
+      <c r="AIM28" s="2"/>
+      <c r="AIS28" s="16"/>
+      <c r="AIU28" s="17"/>
+      <c r="AIV28" s="17"/>
+      <c r="AIW28" s="13"/>
+      <c r="AIX28" s="2"/>
+      <c r="AJD28" s="16"/>
+      <c r="AJF28" s="17"/>
+      <c r="AJG28" s="17"/>
+      <c r="AJH28" s="13"/>
+      <c r="AJI28" s="2"/>
+      <c r="AJO28" s="16"/>
+      <c r="AJQ28" s="17"/>
+      <c r="AJR28" s="17"/>
+      <c r="AJS28" s="13"/>
+      <c r="AJT28" s="2"/>
+      <c r="AJZ28" s="16"/>
+      <c r="AKB28" s="17"/>
+      <c r="AKC28" s="17"/>
+      <c r="AKD28" s="13"/>
+      <c r="AKE28" s="2"/>
+      <c r="AKK28" s="16"/>
+      <c r="AKM28" s="17"/>
+      <c r="AKN28" s="17"/>
+      <c r="AKO28" s="13"/>
+      <c r="AKP28" s="2"/>
+      <c r="AKV28" s="16"/>
+      <c r="AKX28" s="17"/>
+      <c r="AKY28" s="17"/>
+      <c r="AKZ28" s="13"/>
+      <c r="ALA28" s="2"/>
+      <c r="ALG28" s="16"/>
+      <c r="ALI28" s="17"/>
+      <c r="ALJ28" s="17"/>
+      <c r="ALK28" s="13"/>
+      <c r="ALL28" s="2"/>
+      <c r="ALR28" s="16"/>
+      <c r="ALT28" s="17"/>
+      <c r="ALU28" s="17"/>
+      <c r="ALV28" s="13"/>
+      <c r="ALW28" s="2"/>
+      <c r="AMC28" s="16"/>
+      <c r="AME28" s="17"/>
+      <c r="AMF28" s="17"/>
+      <c r="AMG28" s="13"/>
+      <c r="AMH28" s="2"/>
+      <c r="AMN28" s="16"/>
+      <c r="AMP28" s="17"/>
+      <c r="AMQ28" s="17"/>
+      <c r="AMR28" s="13"/>
+      <c r="AMS28" s="2"/>
+      <c r="AMY28" s="16"/>
+      <c r="ANA28" s="17"/>
+      <c r="ANB28" s="17"/>
+      <c r="ANC28" s="13"/>
+      <c r="AND28" s="2"/>
+      <c r="ANJ28" s="16"/>
+      <c r="ANL28" s="17"/>
+      <c r="ANM28" s="17"/>
+      <c r="ANN28" s="13"/>
+      <c r="ANO28" s="2"/>
+      <c r="ANU28" s="16"/>
+      <c r="ANW28" s="17"/>
+      <c r="ANX28" s="17"/>
+      <c r="ANY28" s="13"/>
+      <c r="ANZ28" s="2"/>
+      <c r="AOF28" s="16"/>
+      <c r="AOH28" s="17"/>
+      <c r="AOI28" s="17"/>
+      <c r="AOJ28" s="13"/>
+      <c r="AOK28" s="2"/>
+      <c r="AOQ28" s="16"/>
+      <c r="AOS28" s="17"/>
+      <c r="AOT28" s="17"/>
+      <c r="AOU28" s="13"/>
+      <c r="AOV28" s="2"/>
+      <c r="APB28" s="16"/>
+      <c r="APD28" s="17"/>
+      <c r="APE28" s="17"/>
+      <c r="APF28" s="13"/>
+      <c r="APG28" s="2"/>
+      <c r="APM28" s="16"/>
+      <c r="APO28" s="17"/>
+      <c r="APP28" s="17"/>
+      <c r="APQ28" s="13"/>
+      <c r="APR28" s="2"/>
+      <c r="APX28" s="16"/>
+      <c r="APZ28" s="17"/>
+      <c r="AQA28" s="17"/>
+      <c r="AQB28" s="13"/>
+      <c r="AQC28" s="2"/>
+      <c r="AQI28" s="16"/>
+      <c r="AQK28" s="17"/>
+      <c r="AQL28" s="17"/>
+      <c r="AQM28" s="13"/>
+      <c r="AQN28" s="2"/>
+      <c r="AQT28" s="16"/>
+      <c r="AQV28" s="17"/>
+      <c r="AQW28" s="17"/>
+      <c r="AQX28" s="13"/>
+      <c r="AQY28" s="2"/>
+      <c r="ARE28" s="16"/>
+      <c r="ARG28" s="17"/>
+      <c r="ARH28" s="17"/>
+      <c r="ARI28" s="13"/>
+      <c r="ARJ28" s="2"/>
+      <c r="ARP28" s="16"/>
+      <c r="ARR28" s="17"/>
+      <c r="ARS28" s="17"/>
+      <c r="ART28" s="13"/>
+      <c r="ARU28" s="2"/>
+      <c r="ASA28" s="16"/>
+      <c r="ASC28" s="17"/>
+      <c r="ASD28" s="17"/>
+      <c r="ASE28" s="13"/>
+      <c r="ASF28" s="2"/>
+      <c r="ASL28" s="16"/>
+      <c r="ASN28" s="17"/>
+      <c r="ASO28" s="17"/>
+      <c r="ASP28" s="13"/>
+      <c r="ASQ28" s="2"/>
+      <c r="ASW28" s="16"/>
+      <c r="ASY28" s="17"/>
+      <c r="ASZ28" s="17"/>
+      <c r="ATA28" s="13"/>
+      <c r="ATB28" s="2"/>
+      <c r="ATH28" s="16"/>
+      <c r="ATJ28" s="17"/>
+      <c r="ATK28" s="17"/>
+      <c r="ATL28" s="13"/>
+      <c r="ATM28" s="2"/>
+      <c r="ATS28" s="16"/>
+      <c r="ATU28" s="17"/>
+      <c r="ATV28" s="17"/>
+      <c r="ATW28" s="13"/>
+      <c r="ATX28" s="2"/>
+      <c r="AUD28" s="16"/>
+      <c r="AUF28" s="17"/>
+      <c r="AUG28" s="17"/>
+      <c r="AUH28" s="13"/>
+      <c r="AUI28" s="2"/>
+      <c r="AUO28" s="16"/>
+      <c r="AUQ28" s="17"/>
+      <c r="AUR28" s="17"/>
+      <c r="AUS28" s="13"/>
+      <c r="AUT28" s="2"/>
+      <c r="AUZ28" s="16"/>
+      <c r="AVB28" s="17"/>
+      <c r="AVC28" s="17"/>
+      <c r="AVD28" s="13"/>
+      <c r="AVE28" s="2"/>
+      <c r="AVK28" s="16"/>
+      <c r="AVM28" s="17"/>
+      <c r="AVN28" s="17"/>
+      <c r="AVO28" s="13"/>
+      <c r="AVP28" s="2"/>
+      <c r="AVV28" s="16"/>
+      <c r="AVX28" s="17"/>
+      <c r="AVY28" s="17"/>
+      <c r="AVZ28" s="13"/>
+      <c r="AWA28" s="2"/>
+      <c r="AWG28" s="16"/>
+      <c r="AWI28" s="17"/>
+      <c r="AWJ28" s="17"/>
+      <c r="AWK28" s="13"/>
+      <c r="AWL28" s="2"/>
+      <c r="AWR28" s="16"/>
+      <c r="AWT28" s="17"/>
+      <c r="AWU28" s="17"/>
+      <c r="AWV28" s="13"/>
+      <c r="AWW28" s="2"/>
+      <c r="AXC28" s="16"/>
+      <c r="AXE28" s="17"/>
+      <c r="AXF28" s="17"/>
+      <c r="AXG28" s="13"/>
+      <c r="AXH28" s="2"/>
+      <c r="AXN28" s="16"/>
+      <c r="AXP28" s="17"/>
+      <c r="AXQ28" s="17"/>
+      <c r="AXR28" s="13"/>
+      <c r="AXS28" s="2"/>
+      <c r="AXY28" s="16"/>
+      <c r="AYA28" s="17"/>
+      <c r="AYB28" s="17"/>
+      <c r="AYC28" s="13"/>
+      <c r="AYD28" s="2"/>
+      <c r="AYJ28" s="16"/>
+      <c r="AYL28" s="17"/>
+      <c r="AYM28" s="17"/>
+      <c r="AYN28" s="13"/>
+      <c r="AYO28" s="2"/>
+      <c r="AYU28" s="16"/>
+      <c r="AYW28" s="17"/>
+      <c r="AYX28" s="17"/>
+      <c r="AYY28" s="13"/>
+      <c r="AYZ28" s="2"/>
+      <c r="AZF28" s="16"/>
+      <c r="AZH28" s="17"/>
+      <c r="AZI28" s="17"/>
+      <c r="AZJ28" s="13"/>
+      <c r="AZK28" s="2"/>
+      <c r="AZQ28" s="16"/>
+      <c r="AZS28" s="17"/>
+      <c r="AZT28" s="17"/>
+      <c r="AZU28" s="13"/>
+      <c r="AZV28" s="2"/>
+      <c r="BAB28" s="16"/>
+      <c r="BAD28" s="17"/>
+      <c r="BAE28" s="17"/>
+      <c r="BAF28" s="13"/>
+      <c r="BAG28" s="2"/>
+      <c r="BAM28" s="16"/>
+      <c r="BAO28" s="17"/>
+      <c r="BAP28" s="17"/>
+      <c r="BAQ28" s="13"/>
+      <c r="BAR28" s="2"/>
+      <c r="BAX28" s="16"/>
+      <c r="BAZ28" s="17"/>
+      <c r="BBA28" s="17"/>
+      <c r="BBB28" s="13"/>
+      <c r="BBC28" s="2"/>
+      <c r="BBI28" s="16"/>
+      <c r="BBK28" s="17"/>
+      <c r="BBL28" s="17"/>
+      <c r="BBM28" s="13"/>
+      <c r="BBN28" s="2"/>
+      <c r="BBT28" s="16"/>
+      <c r="BBV28" s="17"/>
+      <c r="BBW28" s="17"/>
+      <c r="BBX28" s="13"/>
+      <c r="BBY28" s="2"/>
+      <c r="BCE28" s="16"/>
+      <c r="BCG28" s="17"/>
+      <c r="BCH28" s="17"/>
+      <c r="BCI28" s="13"/>
+      <c r="BCJ28" s="2"/>
+      <c r="BCP28" s="16"/>
+      <c r="BCR28" s="17"/>
+      <c r="BCS28" s="17"/>
+      <c r="BCT28" s="13"/>
+      <c r="BCU28" s="2"/>
+      <c r="BDA28" s="16"/>
+      <c r="BDC28" s="17"/>
+      <c r="BDD28" s="17"/>
+      <c r="BDE28" s="13"/>
+      <c r="BDF28" s="2"/>
+      <c r="BDL28" s="16"/>
+      <c r="BDN28" s="17"/>
+      <c r="BDO28" s="17"/>
+      <c r="BDP28" s="13"/>
+      <c r="BDQ28" s="2"/>
+      <c r="BDW28" s="16"/>
+      <c r="BDY28" s="17"/>
+      <c r="BDZ28" s="17"/>
+      <c r="BEA28" s="13"/>
+      <c r="BEB28" s="2"/>
+      <c r="BEH28" s="16"/>
+      <c r="BEJ28" s="17"/>
+      <c r="BEK28" s="17"/>
+      <c r="BEL28" s="13"/>
+      <c r="BEM28" s="2"/>
+      <c r="BES28" s="16"/>
+      <c r="BEU28" s="17"/>
+      <c r="BEV28" s="17"/>
+      <c r="BEW28" s="13"/>
+      <c r="BEX28" s="2"/>
+      <c r="BFD28" s="16"/>
+      <c r="BFF28" s="17"/>
+      <c r="BFG28" s="17"/>
+      <c r="BFH28" s="13"/>
+      <c r="BFI28" s="2"/>
+      <c r="BFO28" s="16"/>
+      <c r="BFQ28" s="17"/>
+      <c r="BFR28" s="17"/>
+      <c r="BFS28" s="13"/>
+      <c r="BFT28" s="2"/>
+      <c r="BFZ28" s="16"/>
+      <c r="BGB28" s="17"/>
+      <c r="BGC28" s="17"/>
+      <c r="BGD28" s="13"/>
+      <c r="BGE28" s="2"/>
+      <c r="BGK28" s="16"/>
+      <c r="BGM28" s="17"/>
+      <c r="BGN28" s="17"/>
+      <c r="BGO28" s="13"/>
+      <c r="BGP28" s="2"/>
+      <c r="BGV28" s="16"/>
+      <c r="BGX28" s="17"/>
+      <c r="BGY28" s="17"/>
+      <c r="BGZ28" s="13"/>
+      <c r="BHA28" s="2"/>
+      <c r="BHG28" s="16"/>
+      <c r="BHI28" s="17"/>
+      <c r="BHJ28" s="17"/>
+      <c r="BHK28" s="13"/>
+      <c r="BHL28" s="2"/>
+      <c r="BHR28" s="16"/>
+      <c r="BHT28" s="17"/>
+      <c r="BHU28" s="17"/>
+      <c r="BHV28" s="13"/>
+      <c r="BHW28" s="2"/>
+      <c r="BIC28" s="16"/>
+      <c r="BIE28" s="17"/>
+      <c r="BIF28" s="17"/>
+      <c r="BIG28" s="13"/>
+      <c r="BIH28" s="2"/>
+      <c r="BIN28" s="16"/>
+      <c r="BIP28" s="17"/>
+      <c r="BIQ28" s="17"/>
+      <c r="BIR28" s="13"/>
+      <c r="BIS28" s="2"/>
+      <c r="BIY28" s="16"/>
+      <c r="BJA28" s="17"/>
+      <c r="BJB28" s="17"/>
+      <c r="BJC28" s="13"/>
+      <c r="BJD28" s="2"/>
+      <c r="BJJ28" s="16"/>
+      <c r="BJL28" s="17"/>
+      <c r="BJM28" s="17"/>
+      <c r="BJN28" s="13"/>
+      <c r="BJO28" s="2"/>
+      <c r="BJU28" s="16"/>
+      <c r="BJW28" s="17"/>
+      <c r="BJX28" s="17"/>
+      <c r="BJY28" s="13"/>
+      <c r="BJZ28" s="2"/>
+      <c r="BKF28" s="16"/>
+      <c r="BKH28" s="17"/>
+      <c r="BKI28" s="17"/>
+      <c r="BKJ28" s="13"/>
+      <c r="BKK28" s="2"/>
+      <c r="BKQ28" s="16"/>
+      <c r="BKS28" s="17"/>
+      <c r="BKT28" s="17"/>
+      <c r="BKU28" s="13"/>
+      <c r="BKV28" s="2"/>
+      <c r="BLB28" s="16"/>
+      <c r="BLD28" s="17"/>
+      <c r="BLE28" s="17"/>
+      <c r="BLF28" s="13"/>
+      <c r="BLG28" s="2"/>
+      <c r="BLM28" s="16"/>
+      <c r="BLO28" s="17"/>
+      <c r="BLP28" s="17"/>
+      <c r="BLQ28" s="13"/>
+      <c r="BLR28" s="2"/>
+      <c r="BLX28" s="16"/>
+      <c r="BLZ28" s="17"/>
+      <c r="BMA28" s="17"/>
+      <c r="BMB28" s="13"/>
+      <c r="BMC28" s="2"/>
+      <c r="BMI28" s="16"/>
+      <c r="BMK28" s="17"/>
+      <c r="BML28" s="17"/>
+      <c r="BMM28" s="13"/>
+      <c r="BMN28" s="2"/>
+      <c r="BMT28" s="16"/>
+      <c r="BMV28" s="17"/>
+      <c r="BMW28" s="17"/>
+      <c r="BMX28" s="13"/>
+      <c r="BMY28" s="2"/>
+      <c r="BNE28" s="16"/>
+      <c r="BNG28" s="17"/>
+      <c r="BNH28" s="17"/>
+      <c r="BNI28" s="13"/>
+      <c r="BNJ28" s="2"/>
+      <c r="BNP28" s="16"/>
+      <c r="BNR28" s="17"/>
+      <c r="BNS28" s="17"/>
+      <c r="BNT28" s="13"/>
+      <c r="BNU28" s="2"/>
+      <c r="BOA28" s="16"/>
+      <c r="BOC28" s="17"/>
+      <c r="BOD28" s="17"/>
+      <c r="BOE28" s="13"/>
+      <c r="BOF28" s="2"/>
+      <c r="BOL28" s="16"/>
+      <c r="BON28" s="17"/>
+      <c r="BOO28" s="17"/>
+      <c r="BOP28" s="13"/>
+      <c r="BOQ28" s="2"/>
+      <c r="BOW28" s="16"/>
+      <c r="BOY28" s="17"/>
+      <c r="BOZ28" s="17"/>
+      <c r="BPA28" s="13"/>
+      <c r="BPB28" s="2"/>
+      <c r="BPH28" s="16"/>
+      <c r="BPJ28" s="17"/>
+      <c r="BPK28" s="17"/>
+      <c r="BPL28" s="13"/>
+      <c r="BPM28" s="2"/>
+      <c r="BPS28" s="16"/>
+      <c r="BPU28" s="17"/>
+      <c r="BPV28" s="17"/>
+      <c r="BPW28" s="13"/>
+      <c r="BPX28" s="2"/>
+      <c r="BQD28" s="16"/>
+      <c r="BQF28" s="17"/>
+      <c r="BQG28" s="17"/>
+      <c r="BQH28" s="13"/>
+      <c r="BQI28" s="2"/>
+      <c r="BQO28" s="16"/>
+      <c r="BQQ28" s="17"/>
+      <c r="BQR28" s="17"/>
+      <c r="BQS28" s="13"/>
+      <c r="BQT28" s="2"/>
+      <c r="BQZ28" s="16"/>
+      <c r="BRB28" s="17"/>
+      <c r="BRC28" s="17"/>
+      <c r="BRD28" s="13"/>
+      <c r="BRE28" s="2"/>
+      <c r="BRK28" s="16"/>
+      <c r="BRM28" s="17"/>
+      <c r="BRN28" s="17"/>
+      <c r="BRO28" s="13"/>
+      <c r="BRP28" s="2"/>
+      <c r="BRV28" s="16"/>
+      <c r="BRX28" s="17"/>
+      <c r="BRY28" s="17"/>
+      <c r="BRZ28" s="13"/>
+      <c r="BSA28" s="2"/>
+      <c r="BSG28" s="16"/>
+      <c r="BSI28" s="17"/>
+      <c r="BSJ28" s="17"/>
+      <c r="BSK28" s="13"/>
+      <c r="BSL28" s="2"/>
+      <c r="BSR28" s="16"/>
+      <c r="BST28" s="17"/>
+      <c r="BSU28" s="17"/>
+      <c r="BSV28" s="13"/>
+      <c r="BSW28" s="2"/>
+      <c r="BTC28" s="16"/>
+      <c r="BTE28" s="17"/>
+      <c r="BTF28" s="17"/>
+      <c r="BTG28" s="13"/>
+      <c r="BTH28" s="2"/>
+      <c r="BTN28" s="16"/>
+      <c r="BTP28" s="17"/>
+      <c r="BTQ28" s="17"/>
+      <c r="BTR28" s="13"/>
+      <c r="BTS28" s="2"/>
+      <c r="BTY28" s="16"/>
+      <c r="BUA28" s="17"/>
+      <c r="BUB28" s="17"/>
+      <c r="BUC28" s="13"/>
+      <c r="BUD28" s="2"/>
+      <c r="BUJ28" s="16"/>
+      <c r="BUL28" s="17"/>
+      <c r="BUM28" s="17"/>
+      <c r="BUN28" s="13"/>
+      <c r="BUO28" s="2"/>
+      <c r="BUU28" s="16"/>
+      <c r="BUW28" s="17"/>
+      <c r="BUX28" s="17"/>
+      <c r="BUY28" s="13"/>
+      <c r="BUZ28" s="2"/>
+      <c r="BVF28" s="16"/>
+      <c r="BVH28" s="17"/>
+      <c r="BVI28" s="17"/>
+      <c r="BVJ28" s="13"/>
+      <c r="BVK28" s="2"/>
+      <c r="BVQ28" s="16"/>
+      <c r="BVS28" s="17"/>
+      <c r="BVT28" s="17"/>
+      <c r="BVU28" s="13"/>
+      <c r="BVV28" s="2"/>
+      <c r="BWB28" s="16"/>
+      <c r="BWD28" s="17"/>
+      <c r="BWE28" s="17"/>
+      <c r="BWF28" s="13"/>
+      <c r="BWG28" s="2"/>
+      <c r="BWM28" s="16"/>
+      <c r="BWO28" s="17"/>
+      <c r="BWP28" s="17"/>
+      <c r="BWQ28" s="13"/>
+      <c r="BWR28" s="2"/>
+      <c r="BWX28" s="16"/>
+      <c r="BWZ28" s="17"/>
+      <c r="BXA28" s="17"/>
+      <c r="BXB28" s="13"/>
+      <c r="BXC28" s="2"/>
+      <c r="BXI28" s="16"/>
+      <c r="BXK28" s="17"/>
+      <c r="BXL28" s="17"/>
+      <c r="BXM28" s="13"/>
+      <c r="BXN28" s="2"/>
+      <c r="BXT28" s="16"/>
+      <c r="BXV28" s="17"/>
+      <c r="BXW28" s="17"/>
+      <c r="BXX28" s="13"/>
+      <c r="BXY28" s="2"/>
+      <c r="BYE28" s="16"/>
+      <c r="BYG28" s="17"/>
+      <c r="BYH28" s="17"/>
+      <c r="BYI28" s="13"/>
+      <c r="BYJ28" s="2"/>
+      <c r="BYP28" s="16"/>
+      <c r="BYR28" s="17"/>
+      <c r="BYS28" s="17"/>
+      <c r="BYT28" s="13"/>
+      <c r="BYU28" s="2"/>
+      <c r="BZA28" s="16"/>
+      <c r="BZC28" s="17"/>
+      <c r="BZD28" s="17"/>
+      <c r="BZE28" s="13"/>
+      <c r="BZF28" s="2"/>
+      <c r="BZL28" s="16"/>
+      <c r="BZN28" s="17"/>
+      <c r="BZO28" s="17"/>
+      <c r="BZP28" s="13"/>
+      <c r="BZQ28" s="2"/>
+      <c r="BZW28" s="16"/>
+      <c r="BZY28" s="17"/>
+      <c r="BZZ28" s="17"/>
+      <c r="CAA28" s="13"/>
+      <c r="CAB28" s="2"/>
+      <c r="CAH28" s="16"/>
+      <c r="CAJ28" s="17"/>
+      <c r="CAK28" s="17"/>
+      <c r="CAL28" s="13"/>
+      <c r="CAM28" s="2"/>
+      <c r="CAS28" s="16"/>
+      <c r="CAU28" s="17"/>
+      <c r="CAV28" s="17"/>
+      <c r="CAW28" s="13"/>
+      <c r="CAX28" s="2"/>
+      <c r="CBD28" s="16"/>
+      <c r="CBF28" s="17"/>
+      <c r="CBG28" s="17"/>
+      <c r="CBH28" s="13"/>
+      <c r="CBI28" s="2"/>
+      <c r="CBO28" s="16"/>
+      <c r="CBQ28" s="17"/>
+      <c r="CBR28" s="17"/>
+      <c r="CBS28" s="13"/>
+      <c r="CBT28" s="2"/>
+      <c r="CBZ28" s="16"/>
+      <c r="CCB28" s="17"/>
+      <c r="CCC28" s="17"/>
+      <c r="CCD28" s="13"/>
+      <c r="CCE28" s="2"/>
+      <c r="CCK28" s="16"/>
+      <c r="CCM28" s="17"/>
+      <c r="CCN28" s="17"/>
+      <c r="CCO28" s="13"/>
+      <c r="CCP28" s="2"/>
+      <c r="CCV28" s="16"/>
+      <c r="CCX28" s="17"/>
+      <c r="CCY28" s="17"/>
+      <c r="CCZ28" s="13"/>
+      <c r="CDA28" s="2"/>
+      <c r="CDG28" s="16"/>
+      <c r="CDI28" s="17"/>
+      <c r="CDJ28" s="17"/>
+      <c r="CDK28" s="13"/>
+      <c r="CDL28" s="2"/>
+      <c r="CDR28" s="16"/>
+      <c r="CDT28" s="17"/>
+      <c r="CDU28" s="17"/>
+      <c r="CDV28" s="13"/>
+      <c r="CDW28" s="2"/>
+      <c r="CEC28" s="16"/>
+      <c r="CEE28" s="17"/>
+      <c r="CEF28" s="17"/>
+      <c r="CEG28" s="13"/>
+      <c r="CEH28" s="2"/>
+      <c r="CEN28" s="16"/>
+      <c r="CEP28" s="17"/>
+      <c r="CEQ28" s="17"/>
+      <c r="CER28" s="13"/>
+      <c r="CES28" s="2"/>
+      <c r="CEY28" s="16"/>
+      <c r="CFA28" s="17"/>
+      <c r="CFB28" s="17"/>
+      <c r="CFC28" s="13"/>
+      <c r="CFD28" s="2"/>
+      <c r="CFJ28" s="16"/>
+      <c r="CFL28" s="17"/>
+      <c r="CFM28" s="17"/>
+      <c r="CFN28" s="13"/>
+      <c r="CFO28" s="2"/>
+      <c r="CFU28" s="16"/>
+      <c r="CFW28" s="17"/>
+      <c r="CFX28" s="17"/>
+      <c r="CFY28" s="13"/>
+      <c r="CFZ28" s="2"/>
+      <c r="CGF28" s="16"/>
+      <c r="CGH28" s="17"/>
+      <c r="CGI28" s="17"/>
+      <c r="CGJ28" s="13"/>
+      <c r="CGK28" s="2"/>
+      <c r="CGQ28" s="16"/>
+      <c r="CGS28" s="17"/>
+      <c r="CGT28" s="17"/>
+      <c r="CGU28" s="13"/>
+      <c r="CGV28" s="2"/>
+      <c r="CHB28" s="16"/>
+      <c r="CHD28" s="17"/>
+      <c r="CHE28" s="17"/>
+      <c r="CHF28" s="13"/>
+      <c r="CHG28" s="2"/>
+      <c r="CHM28" s="16"/>
+      <c r="CHO28" s="17"/>
+      <c r="CHP28" s="17"/>
+      <c r="CHQ28" s="13"/>
+      <c r="CHR28" s="2"/>
+      <c r="CHX28" s="16"/>
+      <c r="CHZ28" s="17"/>
+      <c r="CIA28" s="17"/>
+      <c r="CIB28" s="13"/>
+      <c r="CIC28" s="2"/>
+      <c r="CII28" s="16"/>
+      <c r="CIK28" s="17"/>
+      <c r="CIL28" s="17"/>
+      <c r="CIM28" s="13"/>
+      <c r="CIN28" s="2"/>
+      <c r="CIT28" s="16"/>
+      <c r="CIV28" s="17"/>
+      <c r="CIW28" s="17"/>
+      <c r="CIX28" s="13"/>
+      <c r="CIY28" s="2"/>
+      <c r="CJE28" s="16"/>
+      <c r="CJG28" s="17"/>
+      <c r="CJH28" s="17"/>
+      <c r="CJI28" s="13"/>
+      <c r="CJJ28" s="2"/>
+      <c r="CJP28" s="16"/>
+      <c r="CJR28" s="17"/>
+      <c r="CJS28" s="17"/>
+      <c r="CJT28" s="13"/>
+      <c r="CJU28" s="2"/>
+      <c r="CKA28" s="16"/>
+      <c r="CKC28" s="17"/>
+      <c r="CKD28" s="17"/>
+      <c r="CKE28" s="13"/>
+      <c r="CKF28" s="2"/>
+      <c r="CKL28" s="16"/>
+      <c r="CKN28" s="17"/>
+      <c r="CKO28" s="17"/>
+      <c r="CKP28" s="13"/>
+      <c r="CKQ28" s="2"/>
+      <c r="CKW28" s="16"/>
+      <c r="CKY28" s="17"/>
+      <c r="CKZ28" s="17"/>
+      <c r="CLA28" s="13"/>
+      <c r="CLB28" s="2"/>
+      <c r="CLH28" s="16"/>
+      <c r="CLJ28" s="17"/>
+      <c r="CLK28" s="17"/>
+      <c r="CLL28" s="13"/>
+      <c r="CLM28" s="2"/>
+      <c r="CLS28" s="16"/>
+      <c r="CLU28" s="17"/>
+      <c r="CLV28" s="17"/>
+      <c r="CLW28" s="13"/>
+      <c r="CLX28" s="2"/>
+      <c r="CMD28" s="16"/>
+      <c r="CMF28" s="17"/>
+      <c r="CMG28" s="17"/>
+      <c r="CMH28" s="13"/>
+      <c r="CMI28" s="2"/>
+      <c r="CMO28" s="16"/>
+      <c r="CMQ28" s="17"/>
+      <c r="CMR28" s="17"/>
+      <c r="CMS28" s="13"/>
+      <c r="CMT28" s="2"/>
+      <c r="CMZ28" s="16"/>
+      <c r="CNB28" s="17"/>
+      <c r="CNC28" s="17"/>
+      <c r="CND28" s="13"/>
+      <c r="CNE28" s="2"/>
+      <c r="CNK28" s="16"/>
+      <c r="CNM28" s="17"/>
+      <c r="CNN28" s="17"/>
+      <c r="CNO28" s="13"/>
+      <c r="CNP28" s="2"/>
+      <c r="CNV28" s="16"/>
+      <c r="CNX28" s="17"/>
+      <c r="CNY28" s="17"/>
+      <c r="CNZ28" s="13"/>
+      <c r="COA28" s="2"/>
+      <c r="COG28" s="16"/>
+      <c r="COI28" s="17"/>
+      <c r="COJ28" s="17"/>
+      <c r="COK28" s="13"/>
+      <c r="COL28" s="2"/>
+      <c r="COR28" s="16"/>
+      <c r="COT28" s="17"/>
+      <c r="COU28" s="17"/>
+      <c r="COV28" s="13"/>
+      <c r="COW28" s="2"/>
+      <c r="CPC28" s="16"/>
+      <c r="CPE28" s="17"/>
+      <c r="CPF28" s="17"/>
+      <c r="CPG28" s="13"/>
+      <c r="CPH28" s="2"/>
+      <c r="CPN28" s="16"/>
+      <c r="CPP28" s="17"/>
+      <c r="CPQ28" s="17"/>
+      <c r="CPR28" s="13"/>
+      <c r="CPS28" s="2"/>
+      <c r="CPY28" s="16"/>
+      <c r="CQA28" s="17"/>
+      <c r="CQB28" s="17"/>
+      <c r="CQC28" s="13"/>
+      <c r="CQD28" s="2"/>
+      <c r="CQJ28" s="16"/>
+      <c r="CQL28" s="17"/>
+      <c r="CQM28" s="17"/>
+      <c r="CQN28" s="13"/>
+      <c r="CQO28" s="2"/>
+      <c r="CQU28" s="16"/>
+      <c r="CQW28" s="17"/>
+      <c r="CQX28" s="17"/>
+      <c r="CQY28" s="13"/>
+      <c r="CQZ28" s="2"/>
+      <c r="CRF28" s="16"/>
+      <c r="CRH28" s="17"/>
+      <c r="CRI28" s="17"/>
+      <c r="CRJ28" s="13"/>
+      <c r="CRK28" s="2"/>
+      <c r="CRQ28" s="16"/>
+      <c r="CRS28" s="17"/>
+      <c r="CRT28" s="17"/>
+      <c r="CRU28" s="13"/>
+      <c r="CRV28" s="2"/>
+      <c r="CSB28" s="16"/>
+      <c r="CSD28" s="17"/>
+      <c r="CSE28" s="17"/>
+      <c r="CSF28" s="13"/>
+      <c r="CSG28" s="2"/>
+      <c r="CSM28" s="16"/>
+      <c r="CSO28" s="17"/>
+      <c r="CSP28" s="17"/>
+      <c r="CSQ28" s="13"/>
+      <c r="CSR28" s="2"/>
+      <c r="CSX28" s="16"/>
+      <c r="CSZ28" s="17"/>
+      <c r="CTA28" s="17"/>
+      <c r="CTB28" s="13"/>
+      <c r="CTC28" s="2"/>
+      <c r="CTI28" s="16"/>
+      <c r="CTK28" s="17"/>
+      <c r="CTL28" s="17"/>
+      <c r="CTM28" s="13"/>
+      <c r="CTN28" s="2"/>
+      <c r="CTT28" s="16"/>
+      <c r="CTV28" s="17"/>
+      <c r="CTW28" s="17"/>
+      <c r="CTX28" s="13"/>
+      <c r="CTY28" s="2"/>
+      <c r="CUE28" s="16"/>
+      <c r="CUG28" s="17"/>
+      <c r="CUH28" s="17"/>
+      <c r="CUI28" s="13"/>
+      <c r="CUJ28" s="2"/>
+      <c r="CUP28" s="16"/>
+      <c r="CUR28" s="17"/>
+      <c r="CUS28" s="17"/>
+      <c r="CUT28" s="13"/>
+      <c r="CUU28" s="2"/>
+      <c r="CVA28" s="16"/>
+      <c r="CVC28" s="17"/>
+      <c r="CVD28" s="17"/>
+      <c r="CVE28" s="13"/>
+      <c r="CVF28" s="2"/>
+      <c r="CVL28" s="16"/>
+      <c r="CVN28" s="17"/>
+      <c r="CVO28" s="17"/>
+      <c r="CVP28" s="13"/>
+      <c r="CVQ28" s="2"/>
+      <c r="CVW28" s="16"/>
+      <c r="CVY28" s="17"/>
+      <c r="CVZ28" s="17"/>
+      <c r="CWA28" s="13"/>
+      <c r="CWB28" s="2"/>
+      <c r="CWH28" s="16"/>
+      <c r="CWJ28" s="17"/>
+      <c r="CWK28" s="17"/>
+      <c r="CWL28" s="13"/>
+      <c r="CWM28" s="2"/>
+      <c r="CWS28" s="16"/>
+      <c r="CWU28" s="17"/>
+      <c r="CWV28" s="17"/>
+      <c r="CWW28" s="13"/>
+      <c r="CWX28" s="2"/>
+      <c r="CXD28" s="16"/>
+      <c r="CXF28" s="17"/>
+      <c r="CXG28" s="17"/>
+      <c r="CXH28" s="13"/>
+      <c r="CXI28" s="2"/>
+      <c r="CXO28" s="16"/>
+      <c r="CXQ28" s="17"/>
+      <c r="CXR28" s="17"/>
+      <c r="CXS28" s="13"/>
+      <c r="CXT28" s="2"/>
+      <c r="CXZ28" s="16"/>
+      <c r="CYB28" s="17"/>
+      <c r="CYC28" s="17"/>
+      <c r="CYD28" s="13"/>
+      <c r="CYE28" s="2"/>
+      <c r="CYK28" s="16"/>
+      <c r="CYM28" s="17"/>
+      <c r="CYN28" s="17"/>
+      <c r="CYO28" s="13"/>
+      <c r="CYP28" s="2"/>
+      <c r="CYV28" s="16"/>
+      <c r="CYX28" s="17"/>
+      <c r="CYY28" s="17"/>
+      <c r="CYZ28" s="13"/>
+      <c r="CZA28" s="2"/>
+      <c r="CZG28" s="16"/>
+      <c r="CZI28" s="17"/>
+      <c r="CZJ28" s="17"/>
+      <c r="CZK28" s="13"/>
+      <c r="CZL28" s="2"/>
+      <c r="CZR28" s="16"/>
+      <c r="CZT28" s="17"/>
+      <c r="CZU28" s="17"/>
+      <c r="CZV28" s="13"/>
+      <c r="CZW28" s="2"/>
+      <c r="DAC28" s="16"/>
+      <c r="DAE28" s="17"/>
+      <c r="DAF28" s="17"/>
+      <c r="DAG28" s="13"/>
+      <c r="DAH28" s="2"/>
+      <c r="DAN28" s="16"/>
+      <c r="DAP28" s="17"/>
+      <c r="DAQ28" s="17"/>
+      <c r="DAR28" s="13"/>
+      <c r="DAS28" s="2"/>
+      <c r="DAY28" s="16"/>
+      <c r="DBA28" s="17"/>
+      <c r="DBB28" s="17"/>
+      <c r="DBC28" s="13"/>
+      <c r="DBD28" s="2"/>
+      <c r="DBJ28" s="16"/>
+      <c r="DBL28" s="17"/>
+      <c r="DBM28" s="17"/>
+      <c r="DBN28" s="13"/>
+      <c r="DBO28" s="2"/>
+      <c r="DBU28" s="16"/>
+      <c r="DBW28" s="17"/>
+      <c r="DBX28" s="17"/>
+      <c r="DBY28" s="13"/>
+      <c r="DBZ28" s="2"/>
+      <c r="DCF28" s="16"/>
+      <c r="DCH28" s="17"/>
+      <c r="DCI28" s="17"/>
+      <c r="DCJ28" s="13"/>
+      <c r="DCK28" s="2"/>
+      <c r="DCQ28" s="16"/>
+      <c r="DCS28" s="17"/>
+      <c r="DCT28" s="17"/>
+      <c r="DCU28" s="13"/>
+      <c r="DCV28" s="2"/>
+      <c r="DDB28" s="16"/>
+      <c r="DDD28" s="17"/>
+      <c r="DDE28" s="17"/>
+      <c r="DDF28" s="13"/>
+      <c r="DDG28" s="2"/>
+      <c r="DDM28" s="16"/>
+      <c r="DDO28" s="17"/>
+      <c r="DDP28" s="17"/>
+      <c r="DDQ28" s="13"/>
+      <c r="DDR28" s="2"/>
+      <c r="DDX28" s="16"/>
+      <c r="DDZ28" s="17"/>
+      <c r="DEA28" s="17"/>
+      <c r="DEB28" s="13"/>
+      <c r="DEC28" s="2"/>
+      <c r="DEI28" s="16"/>
+      <c r="DEK28" s="17"/>
+      <c r="DEL28" s="17"/>
+      <c r="DEM28" s="13"/>
+      <c r="DEN28" s="2"/>
+      <c r="DET28" s="16"/>
+      <c r="DEV28" s="17"/>
+      <c r="DEW28" s="17"/>
+      <c r="DEX28" s="13"/>
+      <c r="DEY28" s="2"/>
+      <c r="DFE28" s="16"/>
+      <c r="DFG28" s="17"/>
+      <c r="DFH28" s="17"/>
+      <c r="DFI28" s="13"/>
+      <c r="DFJ28" s="2"/>
+      <c r="DFP28" s="16"/>
+      <c r="DFR28" s="17"/>
+      <c r="DFS28" s="17"/>
+      <c r="DFT28" s="13"/>
+      <c r="DFU28" s="2"/>
+      <c r="DGA28" s="16"/>
+      <c r="DGC28" s="17"/>
+      <c r="DGD28" s="17"/>
+      <c r="DGE28" s="13"/>
+      <c r="DGF28" s="2"/>
+      <c r="DGL28" s="16"/>
+      <c r="DGN28" s="17"/>
+      <c r="DGO28" s="17"/>
+      <c r="DGP28" s="13"/>
+      <c r="DGQ28" s="2"/>
+      <c r="DGW28" s="16"/>
+      <c r="DGY28" s="17"/>
+      <c r="DGZ28" s="17"/>
+      <c r="DHA28" s="13"/>
+      <c r="DHB28" s="2"/>
+      <c r="DHH28" s="16"/>
+      <c r="DHJ28" s="17"/>
+      <c r="DHK28" s="17"/>
+      <c r="DHL28" s="13"/>
+      <c r="DHM28" s="2"/>
+      <c r="DHS28" s="16"/>
+      <c r="DHU28" s="17"/>
+      <c r="DHV28" s="17"/>
+      <c r="DHW28" s="13"/>
+      <c r="DHX28" s="2"/>
+      <c r="DID28" s="16"/>
+      <c r="DIF28" s="17"/>
+      <c r="DIG28" s="17"/>
+      <c r="DIH28" s="13"/>
+      <c r="DII28" s="2"/>
+      <c r="DIO28" s="16"/>
+      <c r="DIQ28" s="17"/>
+      <c r="DIR28" s="17"/>
+      <c r="DIS28" s="13"/>
+      <c r="DIT28" s="2"/>
+      <c r="DIZ28" s="16"/>
+      <c r="DJB28" s="17"/>
+      <c r="DJC28" s="17"/>
+      <c r="DJD28" s="13"/>
+      <c r="DJE28" s="2"/>
+      <c r="DJK28" s="16"/>
+      <c r="DJM28" s="17"/>
+      <c r="DJN28" s="17"/>
+      <c r="DJO28" s="13"/>
+      <c r="DJP28" s="2"/>
+      <c r="DJV28" s="16"/>
+      <c r="DJX28" s="17"/>
+      <c r="DJY28" s="17"/>
+      <c r="DJZ28" s="13"/>
+      <c r="DKA28" s="2"/>
+      <c r="DKG28" s="16"/>
+      <c r="DKI28" s="17"/>
+      <c r="DKJ28" s="17"/>
+      <c r="DKK28" s="13"/>
+      <c r="DKL28" s="2"/>
+      <c r="DKR28" s="16"/>
+      <c r="DKT28" s="17"/>
+      <c r="DKU28" s="17"/>
+      <c r="DKV28" s="13"/>
+      <c r="DKW28" s="2"/>
+      <c r="DLC28" s="16"/>
+      <c r="DLE28" s="17"/>
+      <c r="DLF28" s="17"/>
+      <c r="DLG28" s="13"/>
+      <c r="DLH28" s="2"/>
+      <c r="DLN28" s="16"/>
+      <c r="DLP28" s="17"/>
+      <c r="DLQ28" s="17"/>
+      <c r="DLR28" s="13"/>
+      <c r="DLS28" s="2"/>
+      <c r="DLY28" s="16"/>
+      <c r="DMA28" s="17"/>
+      <c r="DMB28" s="17"/>
+      <c r="DMC28" s="13"/>
+      <c r="DMD28" s="2"/>
+      <c r="DMJ28" s="16"/>
+      <c r="DML28" s="17"/>
+      <c r="DMM28" s="17"/>
+      <c r="DMN28" s="13"/>
+      <c r="DMO28" s="2"/>
+      <c r="DMU28" s="16"/>
+      <c r="DMW28" s="17"/>
+      <c r="DMX28" s="17"/>
+      <c r="DMY28" s="13"/>
+      <c r="DMZ28" s="2"/>
+      <c r="DNF28" s="16"/>
+      <c r="DNH28" s="17"/>
+      <c r="DNI28" s="17"/>
+      <c r="DNJ28" s="13"/>
+      <c r="DNK28" s="2"/>
+      <c r="DNQ28" s="16"/>
+      <c r="DNS28" s="17"/>
+      <c r="DNT28" s="17"/>
+      <c r="DNU28" s="13"/>
+      <c r="DNV28" s="2"/>
+      <c r="DOB28" s="16"/>
+      <c r="DOD28" s="17"/>
+      <c r="DOE28" s="17"/>
+      <c r="DOF28" s="13"/>
+      <c r="DOG28" s="2"/>
+      <c r="DOM28" s="16"/>
+      <c r="DOO28" s="17"/>
+      <c r="DOP28" s="17"/>
+      <c r="DOQ28" s="13"/>
+      <c r="DOR28" s="2"/>
+      <c r="DOX28" s="16"/>
+      <c r="DOZ28" s="17"/>
+      <c r="DPA28" s="17"/>
+      <c r="DPB28" s="13"/>
+      <c r="DPC28" s="2"/>
+      <c r="DPI28" s="16"/>
+      <c r="DPK28" s="17"/>
+      <c r="DPL28" s="17"/>
+      <c r="DPM28" s="13"/>
+      <c r="DPN28" s="2"/>
+      <c r="DPT28" s="16"/>
+      <c r="DPV28" s="17"/>
+      <c r="DPW28" s="17"/>
+      <c r="DPX28" s="13"/>
+      <c r="DPY28" s="2"/>
+      <c r="DQE28" s="16"/>
+      <c r="DQG28" s="17"/>
+      <c r="DQH28" s="17"/>
+      <c r="DQI28" s="13"/>
+      <c r="DQJ28" s="2"/>
+      <c r="DQP28" s="16"/>
+      <c r="DQR28" s="17"/>
+      <c r="DQS28" s="17"/>
+      <c r="DQT28" s="13"/>
+      <c r="DQU28" s="2"/>
+      <c r="DRA28" s="16"/>
+      <c r="DRC28" s="17"/>
+      <c r="DRD28" s="17"/>
+      <c r="DRE28" s="13"/>
+      <c r="DRF28" s="2"/>
+      <c r="DRL28" s="16"/>
+      <c r="DRN28" s="17"/>
+      <c r="DRO28" s="17"/>
+      <c r="DRP28" s="13"/>
+      <c r="DRQ28" s="2"/>
+      <c r="DRW28" s="16"/>
+      <c r="DRY28" s="17"/>
+      <c r="DRZ28" s="17"/>
+      <c r="DSA28" s="13"/>
+      <c r="DSB28" s="2"/>
+      <c r="DSH28" s="16"/>
+      <c r="DSJ28" s="17"/>
+      <c r="DSK28" s="17"/>
+      <c r="DSL28" s="13"/>
+      <c r="DSM28" s="2"/>
+      <c r="DSS28" s="16"/>
+      <c r="DSU28" s="17"/>
+      <c r="DSV28" s="17"/>
+      <c r="DSW28" s="13"/>
+      <c r="DSX28" s="2"/>
+      <c r="DTD28" s="16"/>
+      <c r="DTF28" s="17"/>
+      <c r="DTG28" s="17"/>
+      <c r="DTH28" s="13"/>
+      <c r="DTI28" s="2"/>
+      <c r="DTO28" s="16"/>
+      <c r="DTQ28" s="17"/>
+      <c r="DTR28" s="17"/>
+      <c r="DTS28" s="13"/>
+      <c r="DTT28" s="2"/>
+      <c r="DTZ28" s="16"/>
+      <c r="DUB28" s="17"/>
+      <c r="DUC28" s="17"/>
+      <c r="DUD28" s="13"/>
+      <c r="DUE28" s="2"/>
+      <c r="DUK28" s="16"/>
+      <c r="DUM28" s="17"/>
+      <c r="DUN28" s="17"/>
+      <c r="DUO28" s="13"/>
+      <c r="DUP28" s="2"/>
+      <c r="DUV28" s="16"/>
+      <c r="DUX28" s="17"/>
+      <c r="DUY28" s="17"/>
+      <c r="DUZ28" s="13"/>
+      <c r="DVA28" s="2"/>
+      <c r="DVG28" s="16"/>
+      <c r="DVI28" s="17"/>
+      <c r="DVJ28" s="17"/>
+      <c r="DVK28" s="13"/>
+      <c r="DVL28" s="2"/>
+      <c r="DVR28" s="16"/>
+      <c r="DVT28" s="17"/>
+      <c r="DVU28" s="17"/>
+      <c r="DVV28" s="13"/>
+      <c r="DVW28" s="2"/>
+      <c r="DWC28" s="16"/>
+      <c r="DWE28" s="17"/>
+      <c r="DWF28" s="17"/>
+      <c r="DWG28" s="13"/>
+      <c r="DWH28" s="2"/>
+      <c r="DWN28" s="16"/>
+      <c r="DWP28" s="17"/>
+      <c r="DWQ28" s="17"/>
+      <c r="DWR28" s="13"/>
+      <c r="DWS28" s="2"/>
+      <c r="DWY28" s="16"/>
+      <c r="DXA28" s="17"/>
+      <c r="DXB28" s="17"/>
+      <c r="DXC28" s="13"/>
+      <c r="DXD28" s="2"/>
+      <c r="DXJ28" s="16"/>
+      <c r="DXL28" s="17"/>
+      <c r="DXM28" s="17"/>
+      <c r="DXN28" s="13"/>
+      <c r="DXO28" s="2"/>
+      <c r="DXU28" s="16"/>
+      <c r="DXW28" s="17"/>
+      <c r="DXX28" s="17"/>
+      <c r="DXY28" s="13"/>
+      <c r="DXZ28" s="2"/>
+      <c r="DYF28" s="16"/>
+      <c r="DYH28" s="17"/>
+      <c r="DYI28" s="17"/>
+      <c r="DYJ28" s="13"/>
+      <c r="DYK28" s="2"/>
+      <c r="DYQ28" s="16"/>
+      <c r="DYS28" s="17"/>
+      <c r="DYT28" s="17"/>
+      <c r="DYU28" s="13"/>
+      <c r="DYV28" s="2"/>
+      <c r="DZB28" s="16"/>
+      <c r="DZD28" s="17"/>
+      <c r="DZE28" s="17"/>
+      <c r="DZF28" s="13"/>
+      <c r="DZG28" s="2"/>
+      <c r="DZM28" s="16"/>
+      <c r="DZO28" s="17"/>
+      <c r="DZP28" s="17"/>
+      <c r="DZQ28" s="13"/>
+      <c r="DZR28" s="2"/>
+      <c r="DZX28" s="16"/>
+      <c r="DZZ28" s="17"/>
+      <c r="EAA28" s="17"/>
+      <c r="EAB28" s="13"/>
+      <c r="EAC28" s="2"/>
+      <c r="EAI28" s="16"/>
+      <c r="EAK28" s="17"/>
+      <c r="EAL28" s="17"/>
+      <c r="EAM28" s="13"/>
+      <c r="EAN28" s="2"/>
+      <c r="EAT28" s="16"/>
+      <c r="EAV28" s="17"/>
+      <c r="EAW28" s="17"/>
+      <c r="EAX28" s="13"/>
+      <c r="EAY28" s="2"/>
+      <c r="EBE28" s="16"/>
+      <c r="EBG28" s="17"/>
+      <c r="EBH28" s="17"/>
+      <c r="EBI28" s="13"/>
+      <c r="EBJ28" s="2"/>
+      <c r="EBP28" s="16"/>
+      <c r="EBR28" s="17"/>
+      <c r="EBS28" s="17"/>
+      <c r="EBT28" s="13"/>
+      <c r="EBU28" s="2"/>
+      <c r="ECA28" s="16"/>
+      <c r="ECC28" s="17"/>
+      <c r="ECD28" s="17"/>
+      <c r="ECE28" s="13"/>
+      <c r="ECF28" s="2"/>
+      <c r="ECL28" s="16"/>
+      <c r="ECN28" s="17"/>
+      <c r="ECO28" s="17"/>
+      <c r="ECP28" s="13"/>
+      <c r="ECQ28" s="2"/>
+      <c r="ECW28" s="16"/>
+      <c r="ECY28" s="17"/>
+      <c r="ECZ28" s="17"/>
+      <c r="EDA28" s="13"/>
+      <c r="EDB28" s="2"/>
+      <c r="EDH28" s="16"/>
+      <c r="EDJ28" s="17"/>
+      <c r="EDK28" s="17"/>
+      <c r="EDL28" s="13"/>
+      <c r="EDM28" s="2"/>
+      <c r="EDS28" s="16"/>
+      <c r="EDU28" s="17"/>
+      <c r="EDV28" s="17"/>
+      <c r="EDW28" s="13"/>
+      <c r="EDX28" s="2"/>
+      <c r="EED28" s="16"/>
+      <c r="EEF28" s="17"/>
+      <c r="EEG28" s="17"/>
+      <c r="EEH28" s="13"/>
+      <c r="EEI28" s="2"/>
+      <c r="EEO28" s="16"/>
+      <c r="EEQ28" s="17"/>
+      <c r="EER28" s="17"/>
+      <c r="EES28" s="13"/>
+      <c r="EET28" s="2"/>
+      <c r="EEZ28" s="16"/>
+      <c r="EFB28" s="17"/>
+      <c r="EFC28" s="17"/>
+      <c r="EFD28" s="13"/>
+      <c r="EFE28" s="2"/>
+      <c r="EFK28" s="16"/>
+      <c r="EFM28" s="17"/>
+      <c r="EFN28" s="17"/>
+      <c r="EFO28" s="13"/>
+      <c r="EFP28" s="2"/>
+      <c r="EFV28" s="16"/>
+      <c r="EFX28" s="17"/>
+      <c r="EFY28" s="17"/>
+      <c r="EFZ28" s="13"/>
+      <c r="EGA28" s="2"/>
+      <c r="EGG28" s="16"/>
+      <c r="EGI28" s="17"/>
+      <c r="EGJ28" s="17"/>
+      <c r="EGK28" s="13"/>
+      <c r="EGL28" s="2"/>
+      <c r="EGR28" s="16"/>
+      <c r="EGT28" s="17"/>
+      <c r="EGU28" s="17"/>
+      <c r="EGV28" s="13"/>
+      <c r="EGW28" s="2"/>
+      <c r="EHC28" s="16"/>
+      <c r="EHE28" s="17"/>
+      <c r="EHF28" s="17"/>
+      <c r="EHG28" s="13"/>
+      <c r="EHH28" s="2"/>
+      <c r="EHN28" s="16"/>
+      <c r="EHP28" s="17"/>
+      <c r="EHQ28" s="17"/>
+      <c r="EHR28" s="13"/>
+      <c r="EHS28" s="2"/>
+      <c r="EHY28" s="16"/>
+      <c r="EIA28" s="17"/>
+      <c r="EIB28" s="17"/>
+      <c r="EIC28" s="13"/>
+      <c r="EID28" s="2"/>
+      <c r="EIJ28" s="16"/>
+      <c r="EIL28" s="17"/>
+      <c r="EIM28" s="17"/>
+      <c r="EIN28" s="13"/>
+      <c r="EIO28" s="2"/>
+      <c r="EIU28" s="16"/>
+      <c r="EIW28" s="17"/>
+      <c r="EIX28" s="17"/>
+      <c r="EIY28" s="13"/>
+      <c r="EIZ28" s="2"/>
+      <c r="EJF28" s="16"/>
+      <c r="EJH28" s="17"/>
+      <c r="EJI28" s="17"/>
+      <c r="EJJ28" s="13"/>
+      <c r="EJK28" s="2"/>
+      <c r="EJQ28" s="16"/>
+      <c r="EJS28" s="17"/>
+      <c r="EJT28" s="17"/>
+      <c r="EJU28" s="13"/>
+      <c r="EJV28" s="2"/>
+      <c r="EKB28" s="16"/>
+      <c r="EKD28" s="17"/>
+      <c r="EKE28" s="17"/>
+      <c r="EKF28" s="13"/>
+      <c r="EKG28" s="2"/>
+      <c r="EKM28" s="16"/>
+      <c r="EKO28" s="17"/>
+      <c r="EKP28" s="17"/>
+      <c r="EKQ28" s="13"/>
+      <c r="EKR28" s="2"/>
+      <c r="EKX28" s="16"/>
+      <c r="EKZ28" s="17"/>
+      <c r="ELA28" s="17"/>
+      <c r="ELB28" s="13"/>
+      <c r="ELC28" s="2"/>
+      <c r="ELI28" s="16"/>
+      <c r="ELK28" s="17"/>
+      <c r="ELL28" s="17"/>
+      <c r="ELM28" s="13"/>
+      <c r="ELN28" s="2"/>
+      <c r="ELT28" s="16"/>
+      <c r="ELV28" s="17"/>
+      <c r="ELW28" s="17"/>
+      <c r="ELX28" s="13"/>
+      <c r="ELY28" s="2"/>
+      <c r="EME28" s="16"/>
+      <c r="EMG28" s="17"/>
+      <c r="EMH28" s="17"/>
+      <c r="EMI28" s="13"/>
+      <c r="EMJ28" s="2"/>
+      <c r="EMP28" s="16"/>
+      <c r="EMR28" s="17"/>
+      <c r="EMS28" s="17"/>
+      <c r="EMT28" s="13"/>
+      <c r="EMU28" s="2"/>
+      <c r="ENA28" s="16"/>
+      <c r="ENC28" s="17"/>
+      <c r="END28" s="17"/>
+      <c r="ENE28" s="13"/>
+      <c r="ENF28" s="2"/>
+      <c r="ENL28" s="16"/>
+      <c r="ENN28" s="17"/>
+      <c r="ENO28" s="17"/>
+      <c r="ENP28" s="13"/>
+      <c r="ENQ28" s="2"/>
+      <c r="ENW28" s="16"/>
+      <c r="ENY28" s="17"/>
+      <c r="ENZ28" s="17"/>
+      <c r="EOA28" s="13"/>
+      <c r="EOB28" s="2"/>
+      <c r="EOH28" s="16"/>
+      <c r="EOJ28" s="17"/>
+      <c r="EOK28" s="17"/>
+      <c r="EOL28" s="13"/>
+      <c r="EOM28" s="2"/>
+      <c r="EOS28" s="16"/>
+      <c r="EOU28" s="17"/>
+      <c r="EOV28" s="17"/>
+      <c r="EOW28" s="13"/>
+      <c r="EOX28" s="2"/>
+      <c r="EPD28" s="16"/>
+      <c r="EPF28" s="17"/>
+      <c r="EPG28" s="17"/>
+      <c r="EPH28" s="13"/>
+      <c r="EPI28" s="2"/>
+      <c r="EPO28" s="16"/>
+      <c r="EPQ28" s="17"/>
+      <c r="EPR28" s="17"/>
+      <c r="EPS28" s="13"/>
+      <c r="EPT28" s="2"/>
+      <c r="EPZ28" s="16"/>
+      <c r="EQB28" s="17"/>
+      <c r="EQC28" s="17"/>
+      <c r="EQD28" s="13"/>
+      <c r="EQE28" s="2"/>
+      <c r="EQK28" s="16"/>
+      <c r="EQM28" s="17"/>
+      <c r="EQN28" s="17"/>
+      <c r="EQO28" s="13"/>
+      <c r="EQP28" s="2"/>
+      <c r="EQV28" s="16"/>
+      <c r="EQX28" s="17"/>
+      <c r="EQY28" s="17"/>
+      <c r="EQZ28" s="13"/>
+      <c r="ERA28" s="2"/>
+      <c r="ERG28" s="16"/>
+      <c r="ERI28" s="17"/>
+      <c r="ERJ28" s="17"/>
+      <c r="ERK28" s="13"/>
+      <c r="ERL28" s="2"/>
+      <c r="ERR28" s="16"/>
+      <c r="ERT28" s="17"/>
+      <c r="ERU28" s="17"/>
+      <c r="ERV28" s="13"/>
+      <c r="ERW28" s="2"/>
+      <c r="ESC28" s="16"/>
+      <c r="ESE28" s="17"/>
+      <c r="ESF28" s="17"/>
+      <c r="ESG28" s="13"/>
+      <c r="ESH28" s="2"/>
+      <c r="ESN28" s="16"/>
+      <c r="ESP28" s="17"/>
+      <c r="ESQ28" s="17"/>
+      <c r="ESR28" s="13"/>
+      <c r="ESS28" s="2"/>
+      <c r="ESY28" s="16"/>
+      <c r="ETA28" s="17"/>
+      <c r="ETB28" s="17"/>
+      <c r="ETC28" s="13"/>
+      <c r="ETD28" s="2"/>
+      <c r="ETJ28" s="16"/>
+      <c r="ETL28" s="17"/>
+      <c r="ETM28" s="17"/>
+      <c r="ETN28" s="13"/>
+      <c r="ETO28" s="2"/>
+      <c r="ETU28" s="16"/>
+      <c r="ETW28" s="17"/>
+      <c r="ETX28" s="17"/>
+      <c r="ETY28" s="13"/>
+      <c r="ETZ28" s="2"/>
+      <c r="EUF28" s="16"/>
+      <c r="EUH28" s="17"/>
+      <c r="EUI28" s="17"/>
+      <c r="EUJ28" s="13"/>
+      <c r="EUK28" s="2"/>
+      <c r="EUQ28" s="16"/>
+      <c r="EUS28" s="17"/>
+      <c r="EUT28" s="17"/>
+      <c r="EUU28" s="13"/>
+      <c r="EUV28" s="2"/>
+      <c r="EVB28" s="16"/>
+      <c r="EVD28" s="17"/>
+      <c r="EVE28" s="17"/>
+      <c r="EVF28" s="13"/>
+      <c r="EVG28" s="2"/>
+      <c r="EVM28" s="16"/>
+      <c r="EVO28" s="17"/>
+      <c r="EVP28" s="17"/>
+      <c r="EVQ28" s="13"/>
+      <c r="EVR28" s="2"/>
+      <c r="EVX28" s="16"/>
+      <c r="EVZ28" s="17"/>
+      <c r="EWA28" s="17"/>
+      <c r="EWB28" s="13"/>
+      <c r="EWC28" s="2"/>
+      <c r="EWI28" s="16"/>
+      <c r="EWK28" s="17"/>
+      <c r="EWL28" s="17"/>
+      <c r="EWM28" s="13"/>
+      <c r="EWN28" s="2"/>
+      <c r="EWT28" s="16"/>
+      <c r="EWV28" s="17"/>
+      <c r="EWW28" s="17"/>
+      <c r="EWX28" s="13"/>
+      <c r="EWY28" s="2"/>
+      <c r="EXE28" s="16"/>
+      <c r="EXG28" s="17"/>
+      <c r="EXH28" s="17"/>
+      <c r="EXI28" s="13"/>
+      <c r="EXJ28" s="2"/>
+      <c r="EXP28" s="16"/>
+      <c r="EXR28" s="17"/>
+      <c r="EXS28" s="17"/>
+      <c r="EXT28" s="13"/>
+      <c r="EXU28" s="2"/>
+      <c r="EYA28" s="16"/>
+      <c r="EYC28" s="17"/>
+      <c r="EYD28" s="17"/>
+      <c r="EYE28" s="13"/>
+      <c r="EYF28" s="2"/>
+      <c r="EYL28" s="16"/>
+      <c r="EYN28" s="17"/>
+      <c r="EYO28" s="17"/>
+      <c r="EYP28" s="13"/>
+      <c r="EYQ28" s="2"/>
+      <c r="EYW28" s="16"/>
+      <c r="EYY28" s="17"/>
+      <c r="EYZ28" s="17"/>
+      <c r="EZA28" s="13"/>
+      <c r="EZB28" s="2"/>
+      <c r="EZH28" s="16"/>
+      <c r="EZJ28" s="17"/>
+      <c r="EZK28" s="17"/>
+      <c r="EZL28" s="13"/>
+      <c r="EZM28" s="2"/>
+      <c r="EZS28" s="16"/>
+      <c r="EZU28" s="17"/>
+      <c r="EZV28" s="17"/>
+      <c r="EZW28" s="13"/>
+      <c r="EZX28" s="2"/>
+      <c r="FAD28" s="16"/>
+      <c r="FAF28" s="17"/>
+      <c r="FAG28" s="17"/>
+      <c r="FAH28" s="13"/>
+      <c r="FAI28" s="2"/>
+      <c r="FAO28" s="16"/>
+      <c r="FAQ28" s="17"/>
+      <c r="FAR28" s="17"/>
+      <c r="FAS28" s="13"/>
+      <c r="FAT28" s="2"/>
+      <c r="FAZ28" s="16"/>
+      <c r="FBB28" s="17"/>
+      <c r="FBC28" s="17"/>
+      <c r="FBD28" s="13"/>
+      <c r="FBE28" s="2"/>
+      <c r="FBK28" s="16"/>
+      <c r="FBM28" s="17"/>
+      <c r="FBN28" s="17"/>
+      <c r="FBO28" s="13"/>
+      <c r="FBP28" s="2"/>
+      <c r="FBV28" s="16"/>
+      <c r="FBX28" s="17"/>
+      <c r="FBY28" s="17"/>
+      <c r="FBZ28" s="13"/>
+      <c r="FCA28" s="2"/>
+      <c r="FCG28" s="16"/>
+      <c r="FCI28" s="17"/>
+      <c r="FCJ28" s="17"/>
+      <c r="FCK28" s="13"/>
+      <c r="FCL28" s="2"/>
+      <c r="FCR28" s="16"/>
+      <c r="FCT28" s="17"/>
+      <c r="FCU28" s="17"/>
+      <c r="FCV28" s="13"/>
+      <c r="FCW28" s="2"/>
+      <c r="FDC28" s="16"/>
+      <c r="FDE28" s="17"/>
+      <c r="FDF28" s="17"/>
+      <c r="FDG28" s="13"/>
+      <c r="FDH28" s="2"/>
+      <c r="FDN28" s="16"/>
+      <c r="FDP28" s="17"/>
+      <c r="FDQ28" s="17"/>
+      <c r="FDR28" s="13"/>
+      <c r="FDS28" s="2"/>
+      <c r="FDY28" s="16"/>
+      <c r="FEA28" s="17"/>
+      <c r="FEB28" s="17"/>
+      <c r="FEC28" s="13"/>
+      <c r="FED28" s="2"/>
+      <c r="FEJ28" s="16"/>
+      <c r="FEL28" s="17"/>
+      <c r="FEM28" s="17"/>
+      <c r="FEN28" s="13"/>
+      <c r="FEO28" s="2"/>
+      <c r="FEU28" s="16"/>
+      <c r="FEW28" s="17"/>
+      <c r="FEX28" s="17"/>
+      <c r="FEY28" s="13"/>
+      <c r="FEZ28" s="2"/>
+      <c r="FFF28" s="16"/>
+      <c r="FFH28" s="17"/>
+      <c r="FFI28" s="17"/>
+      <c r="FFJ28" s="13"/>
+      <c r="FFK28" s="2"/>
+      <c r="FFQ28" s="16"/>
+      <c r="FFS28" s="17"/>
+      <c r="FFT28" s="17"/>
+      <c r="FFU28" s="13"/>
+      <c r="FFV28" s="2"/>
+      <c r="FGB28" s="16"/>
+      <c r="FGD28" s="17"/>
+      <c r="FGE28" s="17"/>
+      <c r="FGF28" s="13"/>
+      <c r="FGG28" s="2"/>
+      <c r="FGM28" s="16"/>
+      <c r="FGO28" s="17"/>
+      <c r="FGP28" s="17"/>
+      <c r="FGQ28" s="13"/>
+      <c r="FGR28" s="2"/>
+      <c r="FGX28" s="16"/>
+      <c r="FGZ28" s="17"/>
+      <c r="FHA28" s="17"/>
+      <c r="FHB28" s="13"/>
+      <c r="FHC28" s="2"/>
+      <c r="FHI28" s="16"/>
+      <c r="FHK28" s="17"/>
+      <c r="FHL28" s="17"/>
+      <c r="FHM28" s="13"/>
+      <c r="FHN28" s="2"/>
+      <c r="FHT28" s="16"/>
+      <c r="FHV28" s="17"/>
+      <c r="FHW28" s="17"/>
+      <c r="FHX28" s="13"/>
+      <c r="FHY28" s="2"/>
+      <c r="FIE28" s="16"/>
+      <c r="FIG28" s="17"/>
+      <c r="FIH28" s="17"/>
+      <c r="FII28" s="13"/>
+      <c r="FIJ28" s="2"/>
+      <c r="FIP28" s="16"/>
+      <c r="FIR28" s="17"/>
+      <c r="FIS28" s="17"/>
+      <c r="FIT28" s="13"/>
+      <c r="FIU28" s="2"/>
+      <c r="FJA28" s="16"/>
+      <c r="FJC28" s="17"/>
+      <c r="FJD28" s="17"/>
+      <c r="FJE28" s="13"/>
+      <c r="FJF28" s="2"/>
+      <c r="FJL28" s="16"/>
+      <c r="FJN28" s="17"/>
+      <c r="FJO28" s="17"/>
+      <c r="FJP28" s="13"/>
+      <c r="FJQ28" s="2"/>
+      <c r="FJW28" s="16"/>
+      <c r="FJY28" s="17"/>
+      <c r="FJZ28" s="17"/>
+      <c r="FKA28" s="13"/>
+      <c r="FKB28" s="2"/>
+      <c r="FKH28" s="16"/>
+      <c r="FKJ28" s="17"/>
+      <c r="FKK28" s="17"/>
+      <c r="FKL28" s="13"/>
+      <c r="FKM28" s="2"/>
+      <c r="FKS28" s="16"/>
+      <c r="FKU28" s="17"/>
+      <c r="FKV28" s="17"/>
+      <c r="FKW28" s="13"/>
+      <c r="FKX28" s="2"/>
+      <c r="FLD28" s="16"/>
+      <c r="FLF28" s="17"/>
+      <c r="FLG28" s="17"/>
+      <c r="FLH28" s="13"/>
+      <c r="FLI28" s="2"/>
+      <c r="FLO28" s="16"/>
+      <c r="FLQ28" s="17"/>
+      <c r="FLR28" s="17"/>
+      <c r="FLS28" s="13"/>
+      <c r="FLT28" s="2"/>
+      <c r="FLZ28" s="16"/>
+      <c r="FMB28" s="17"/>
+      <c r="FMC28" s="17"/>
+      <c r="FMD28" s="13"/>
+      <c r="FME28" s="2"/>
+      <c r="FMK28" s="16"/>
+      <c r="FMM28" s="17"/>
+      <c r="FMN28" s="17"/>
+      <c r="FMO28" s="13"/>
+      <c r="FMP28" s="2"/>
+      <c r="FMV28" s="16"/>
+      <c r="FMX28" s="17"/>
+      <c r="FMY28" s="17"/>
+      <c r="FMZ28" s="13"/>
+      <c r="FNA28" s="2"/>
+      <c r="FNG28" s="16"/>
+      <c r="FNI28" s="17"/>
+      <c r="FNJ28" s="17"/>
+      <c r="FNK28" s="13"/>
+      <c r="FNL28" s="2"/>
+      <c r="FNR28" s="16"/>
+      <c r="FNT28" s="17"/>
+      <c r="FNU28" s="17"/>
+      <c r="FNV28" s="13"/>
+      <c r="FNW28" s="2"/>
+      <c r="FOC28" s="16"/>
+      <c r="FOE28" s="17"/>
+      <c r="FOF28" s="17"/>
+      <c r="FOG28" s="13"/>
+      <c r="FOH28" s="2"/>
+      <c r="FON28" s="16"/>
+      <c r="FOP28" s="17"/>
+      <c r="FOQ28" s="17"/>
+      <c r="FOR28" s="13"/>
+      <c r="FOS28" s="2"/>
+      <c r="FOY28" s="16"/>
+      <c r="FPA28" s="17"/>
+      <c r="FPB28" s="17"/>
+      <c r="FPC28" s="13"/>
+      <c r="FPD28" s="2"/>
+      <c r="FPJ28" s="16"/>
+      <c r="FPL28" s="17"/>
+      <c r="FPM28" s="17"/>
+      <c r="FPN28" s="13"/>
+      <c r="FPO28" s="2"/>
+      <c r="FPU28" s="16"/>
+      <c r="FPW28" s="17"/>
+      <c r="FPX28" s="17"/>
+      <c r="FPY28" s="13"/>
+      <c r="FPZ28" s="2"/>
+      <c r="FQF28" s="16"/>
+      <c r="FQH28" s="17"/>
+      <c r="FQI28" s="17"/>
+      <c r="FQJ28" s="13"/>
+      <c r="FQK28" s="2"/>
+      <c r="FQQ28" s="16"/>
+      <c r="FQS28" s="17"/>
+      <c r="FQT28" s="17"/>
+      <c r="FQU28" s="13"/>
+      <c r="FQV28" s="2"/>
+      <c r="FRB28" s="16"/>
+      <c r="FRD28" s="17"/>
+      <c r="FRE28" s="17"/>
+      <c r="FRF28" s="13"/>
+      <c r="FRG28" s="2"/>
+      <c r="FRM28" s="16"/>
+      <c r="FRO28" s="17"/>
+      <c r="FRP28" s="17"/>
+      <c r="FRQ28" s="13"/>
+      <c r="FRR28" s="2"/>
+      <c r="FRX28" s="16"/>
+      <c r="FRZ28" s="17"/>
+      <c r="FSA28" s="17"/>
+      <c r="FSB28" s="13"/>
+      <c r="FSC28" s="2"/>
+      <c r="FSI28" s="16"/>
+      <c r="FSK28" s="17"/>
+      <c r="FSL28" s="17"/>
+      <c r="FSM28" s="13"/>
+      <c r="FSN28" s="2"/>
+      <c r="FST28" s="16"/>
+      <c r="FSV28" s="17"/>
+      <c r="FSW28" s="17"/>
+      <c r="FSX28" s="13"/>
+      <c r="FSY28" s="2"/>
+      <c r="FTE28" s="16"/>
+      <c r="FTG28" s="17"/>
+      <c r="FTH28" s="17"/>
+      <c r="FTI28" s="13"/>
+      <c r="FTJ28" s="2"/>
+      <c r="FTP28" s="16"/>
+      <c r="FTR28" s="17"/>
+      <c r="FTS28" s="17"/>
+      <c r="FTT28" s="13"/>
+      <c r="FTU28" s="2"/>
+      <c r="FUA28" s="16"/>
+      <c r="FUC28" s="17"/>
+      <c r="FUD28" s="17"/>
+      <c r="FUE28" s="13"/>
+      <c r="FUF28" s="2"/>
+      <c r="FUL28" s="16"/>
+      <c r="FUN28" s="17"/>
+      <c r="FUO28" s="17"/>
+      <c r="FUP28" s="13"/>
+      <c r="FUQ28" s="2"/>
+      <c r="FUW28" s="16"/>
+      <c r="FUY28" s="17"/>
+      <c r="FUZ28" s="17"/>
+      <c r="FVA28" s="13"/>
+      <c r="FVB28" s="2"/>
+      <c r="FVH28" s="16"/>
+      <c r="FVJ28" s="17"/>
+      <c r="FVK28" s="17"/>
+      <c r="FVL28" s="13"/>
+      <c r="FVM28" s="2"/>
+      <c r="FVS28" s="16"/>
+      <c r="FVU28" s="17"/>
+      <c r="FVV28" s="17"/>
+      <c r="FVW28" s="13"/>
+      <c r="FVX28" s="2"/>
+      <c r="FWD28" s="16"/>
+      <c r="FWF28" s="17"/>
+      <c r="FWG28" s="17"/>
+      <c r="FWH28" s="13"/>
+      <c r="FWI28" s="2"/>
+      <c r="FWO28" s="16"/>
+      <c r="FWQ28" s="17"/>
+      <c r="FWR28" s="17"/>
+      <c r="FWS28" s="13"/>
+      <c r="FWT28" s="2"/>
+      <c r="FWZ28" s="16"/>
+      <c r="FXB28" s="17"/>
+      <c r="FXC28" s="17"/>
+      <c r="FXD28" s="13"/>
+      <c r="FXE28" s="2"/>
+      <c r="FXK28" s="16"/>
+      <c r="FXM28" s="17"/>
+      <c r="FXN28" s="17"/>
+      <c r="FXO28" s="13"/>
+      <c r="FXP28" s="2"/>
+      <c r="FXV28" s="16"/>
+      <c r="FXX28" s="17"/>
+      <c r="FXY28" s="17"/>
+      <c r="FXZ28" s="13"/>
+      <c r="FYA28" s="2"/>
+      <c r="FYG28" s="16"/>
+      <c r="FYI28" s="17"/>
+      <c r="FYJ28" s="17"/>
+      <c r="FYK28" s="13"/>
+      <c r="FYL28" s="2"/>
+      <c r="FYR28" s="16"/>
+      <c r="FYT28" s="17"/>
+      <c r="FYU28" s="17"/>
+      <c r="FYV28" s="13"/>
+      <c r="FYW28" s="2"/>
+      <c r="FZC28" s="16"/>
+      <c r="FZE28" s="17"/>
+      <c r="FZF28" s="17"/>
+      <c r="FZG28" s="13"/>
+      <c r="FZH28" s="2"/>
+      <c r="FZN28" s="16"/>
+      <c r="FZP28" s="17"/>
+      <c r="FZQ28" s="17"/>
+      <c r="FZR28" s="13"/>
+      <c r="FZS28" s="2"/>
+      <c r="FZY28" s="16"/>
+      <c r="GAA28" s="17"/>
+      <c r="GAB28" s="17"/>
+      <c r="GAC28" s="13"/>
+      <c r="GAD28" s="2"/>
+      <c r="GAJ28" s="16"/>
+      <c r="GAL28" s="17"/>
+      <c r="GAM28" s="17"/>
+      <c r="GAN28" s="13"/>
+      <c r="GAO28" s="2"/>
+      <c r="GAU28" s="16"/>
+      <c r="GAW28" s="17"/>
+      <c r="GAX28" s="17"/>
+      <c r="GAY28" s="13"/>
+      <c r="GAZ28" s="2"/>
+      <c r="GBF28" s="16"/>
+      <c r="GBH28" s="17"/>
+      <c r="GBI28" s="17"/>
+      <c r="GBJ28" s="13"/>
+      <c r="GBK28" s="2"/>
+      <c r="GBQ28" s="16"/>
+      <c r="GBS28" s="17"/>
+      <c r="GBT28" s="17"/>
+      <c r="GBU28" s="13"/>
+      <c r="GBV28" s="2"/>
+      <c r="GCB28" s="16"/>
+      <c r="GCD28" s="17"/>
+      <c r="GCE28" s="17"/>
+      <c r="GCF28" s="13"/>
+      <c r="GCG28" s="2"/>
+      <c r="GCM28" s="16"/>
+      <c r="GCO28" s="17"/>
+      <c r="GCP28" s="17"/>
+      <c r="GCQ28" s="13"/>
+      <c r="GCR28" s="2"/>
+      <c r="GCX28" s="16"/>
+      <c r="GCZ28" s="17"/>
+      <c r="GDA28" s="17"/>
+      <c r="GDB28" s="13"/>
+      <c r="GDC28" s="2"/>
+      <c r="GDI28" s="16"/>
+      <c r="GDK28" s="17"/>
+      <c r="GDL28" s="17"/>
+      <c r="GDM28" s="13"/>
+      <c r="GDN28" s="2"/>
+      <c r="GDT28" s="16"/>
+      <c r="GDV28" s="17"/>
+      <c r="GDW28" s="17"/>
+      <c r="GDX28" s="13"/>
+      <c r="GDY28" s="2"/>
+      <c r="GEE28" s="16"/>
+      <c r="GEG28" s="17"/>
+      <c r="GEH28" s="17"/>
+      <c r="GEI28" s="13"/>
+      <c r="GEJ28" s="2"/>
+      <c r="GEP28" s="16"/>
+      <c r="GER28" s="17"/>
+      <c r="GES28" s="17"/>
+      <c r="GET28" s="13"/>
+      <c r="GEU28" s="2"/>
+      <c r="GFA28" s="16"/>
+      <c r="GFC28" s="17"/>
+      <c r="GFD28" s="17"/>
+      <c r="GFE28" s="13"/>
+      <c r="GFF28" s="2"/>
+      <c r="GFL28" s="16"/>
+      <c r="GFN28" s="17"/>
+      <c r="GFO28" s="17"/>
+      <c r="GFP28" s="13"/>
+      <c r="GFQ28" s="2"/>
+      <c r="GFW28" s="16"/>
+      <c r="GFY28" s="17"/>
+      <c r="GFZ28" s="17"/>
+      <c r="GGA28" s="13"/>
+      <c r="GGB28" s="2"/>
+      <c r="GGH28" s="16"/>
+      <c r="GGJ28" s="17"/>
+      <c r="GGK28" s="17"/>
+      <c r="GGL28" s="13"/>
+      <c r="GGM28" s="2"/>
+      <c r="GGS28" s="16"/>
+      <c r="GGU28" s="17"/>
+      <c r="GGV28" s="17"/>
+      <c r="GGW28" s="13"/>
+      <c r="GGX28" s="2"/>
+      <c r="GHD28" s="16"/>
+      <c r="GHF28" s="17"/>
+      <c r="GHG28" s="17"/>
+      <c r="GHH28" s="13"/>
+      <c r="GHI28" s="2"/>
+      <c r="GHO28" s="16"/>
+      <c r="GHQ28" s="17"/>
+      <c r="GHR28" s="17"/>
+      <c r="GHS28" s="13"/>
+      <c r="GHT28" s="2"/>
+      <c r="GHZ28" s="16"/>
+      <c r="GIB28" s="17"/>
+      <c r="GIC28" s="17"/>
+      <c r="GID28" s="13"/>
+      <c r="GIE28" s="2"/>
+      <c r="GIK28" s="16"/>
+      <c r="GIM28" s="17"/>
+      <c r="GIN28" s="17"/>
+      <c r="GIO28" s="13"/>
+      <c r="GIP28" s="2"/>
+      <c r="GIV28" s="16"/>
+      <c r="GIX28" s="17"/>
+      <c r="GIY28" s="17"/>
+      <c r="GIZ28" s="13"/>
+      <c r="GJA28" s="2"/>
+      <c r="GJG28" s="16"/>
+      <c r="GJI28" s="17"/>
+      <c r="GJJ28" s="17"/>
+      <c r="GJK28" s="13"/>
+      <c r="GJL28" s="2"/>
+      <c r="GJR28" s="16"/>
+      <c r="GJT28" s="17"/>
+      <c r="GJU28" s="17"/>
+      <c r="GJV28" s="13"/>
+      <c r="GJW28" s="2"/>
+      <c r="GKC28" s="16"/>
+      <c r="GKE28" s="17"/>
+      <c r="GKF28" s="17"/>
+      <c r="GKG28" s="13"/>
+      <c r="GKH28" s="2"/>
+      <c r="GKN28" s="16"/>
+      <c r="GKP28" s="17"/>
+      <c r="GKQ28" s="17"/>
+      <c r="GKR28" s="13"/>
+      <c r="GKS28" s="2"/>
+      <c r="GKY28" s="16"/>
+      <c r="GLA28" s="17"/>
+      <c r="GLB28" s="17"/>
+      <c r="GLC28" s="13"/>
+      <c r="GLD28" s="2"/>
+      <c r="GLJ28" s="16"/>
+      <c r="GLL28" s="17"/>
+      <c r="GLM28" s="17"/>
+      <c r="GLN28" s="13"/>
+      <c r="GLO28" s="2"/>
+      <c r="GLU28" s="16"/>
+      <c r="GLW28" s="17"/>
+      <c r="GLX28" s="17"/>
+      <c r="GLY28" s="13"/>
+      <c r="GLZ28" s="2"/>
+      <c r="GMF28" s="16"/>
+      <c r="GMH28" s="17"/>
+      <c r="GMI28" s="17"/>
+      <c r="GMJ28" s="13"/>
+      <c r="GMK28" s="2"/>
+      <c r="GMQ28" s="16"/>
+      <c r="GMS28" s="17"/>
+      <c r="GMT28" s="17"/>
+      <c r="GMU28" s="13"/>
+      <c r="GMV28" s="2"/>
+      <c r="GNB28" s="16"/>
+      <c r="GND28" s="17"/>
+      <c r="GNE28" s="17"/>
+      <c r="GNF28" s="13"/>
+      <c r="GNG28" s="2"/>
+      <c r="GNM28" s="16"/>
+      <c r="GNO28" s="17"/>
+      <c r="GNP28" s="17"/>
+      <c r="GNQ28" s="13"/>
+      <c r="GNR28" s="2"/>
+      <c r="GNX28" s="16"/>
+      <c r="GNZ28" s="17"/>
+      <c r="GOA28" s="17"/>
+      <c r="GOB28" s="13"/>
+      <c r="GOC28" s="2"/>
+      <c r="GOI28" s="16"/>
+      <c r="GOK28" s="17"/>
+      <c r="GOL28" s="17"/>
+      <c r="GOM28" s="13"/>
+      <c r="GON28" s="2"/>
+      <c r="GOT28" s="16"/>
+      <c r="GOV28" s="17"/>
+      <c r="GOW28" s="17"/>
+      <c r="GOX28" s="13"/>
+      <c r="GOY28" s="2"/>
+      <c r="GPE28" s="16"/>
+      <c r="GPG28" s="17"/>
+      <c r="GPH28" s="17"/>
+      <c r="GPI28" s="13"/>
+      <c r="GPJ28" s="2"/>
+      <c r="GPP28" s="16"/>
+      <c r="GPR28" s="17"/>
+      <c r="GPS28" s="17"/>
+      <c r="GPT28" s="13"/>
+      <c r="GPU28" s="2"/>
+      <c r="GQA28" s="16"/>
+      <c r="GQC28" s="17"/>
+      <c r="GQD28" s="17"/>
+      <c r="GQE28" s="13"/>
+      <c r="GQF28" s="2"/>
+      <c r="GQL28" s="16"/>
+      <c r="GQN28" s="17"/>
+      <c r="GQO28" s="17"/>
+      <c r="GQP28" s="13"/>
+      <c r="GQQ28" s="2"/>
+      <c r="GQW28" s="16"/>
+      <c r="GQY28" s="17"/>
+      <c r="GQZ28" s="17"/>
+      <c r="GRA28" s="13"/>
+      <c r="GRB28" s="2"/>
+      <c r="GRH28" s="16"/>
+      <c r="GRJ28" s="17"/>
+      <c r="GRK28" s="17"/>
+      <c r="GRL28" s="13"/>
+      <c r="GRM28" s="2"/>
+      <c r="GRS28" s="16"/>
+      <c r="GRU28" s="17"/>
+      <c r="GRV28" s="17"/>
+      <c r="GRW28" s="13"/>
+      <c r="GRX28" s="2"/>
+      <c r="GSD28" s="16"/>
+      <c r="GSF28" s="17"/>
+      <c r="GSG28" s="17"/>
+      <c r="GSH28" s="13"/>
+      <c r="GSI28" s="2"/>
+      <c r="GSO28" s="16"/>
+      <c r="GSQ28" s="17"/>
+      <c r="GSR28" s="17"/>
+      <c r="GSS28" s="13"/>
+      <c r="GST28" s="2"/>
+      <c r="GSZ28" s="16"/>
+      <c r="GTB28" s="17"/>
+      <c r="GTC28" s="17"/>
+      <c r="GTD28" s="13"/>
+      <c r="GTE28" s="2"/>
+      <c r="GTK28" s="16"/>
+      <c r="GTM28" s="17"/>
+      <c r="GTN28" s="17"/>
+      <c r="GTO28" s="13"/>
+      <c r="GTP28" s="2"/>
+      <c r="GTV28" s="16"/>
+      <c r="GTX28" s="17"/>
+      <c r="GTY28" s="17"/>
+      <c r="GTZ28" s="13"/>
+      <c r="GUA28" s="2"/>
+      <c r="GUG28" s="16"/>
+      <c r="GUI28" s="17"/>
+      <c r="GUJ28" s="17"/>
+      <c r="GUK28" s="13"/>
+      <c r="GUL28" s="2"/>
+      <c r="GUR28" s="16"/>
+      <c r="GUT28" s="17"/>
+      <c r="GUU28" s="17"/>
+      <c r="GUV28" s="13"/>
+      <c r="GUW28" s="2"/>
+      <c r="GVC28" s="16"/>
+      <c r="GVE28" s="17"/>
+      <c r="GVF28" s="17"/>
+      <c r="GVG28" s="13"/>
+      <c r="GVH28" s="2"/>
+      <c r="GVN28" s="16"/>
+      <c r="GVP28" s="17"/>
+      <c r="GVQ28" s="17"/>
+      <c r="GVR28" s="13"/>
+      <c r="GVS28" s="2"/>
+      <c r="GVY28" s="16"/>
+      <c r="GWA28" s="17"/>
+      <c r="GWB28" s="17"/>
+      <c r="GWC28" s="13"/>
+      <c r="GWD28" s="2"/>
+      <c r="GWJ28" s="16"/>
+      <c r="GWL28" s="17"/>
+      <c r="GWM28" s="17"/>
+      <c r="GWN28" s="13"/>
+      <c r="GWO28" s="2"/>
+      <c r="GWU28" s="16"/>
+      <c r="GWW28" s="17"/>
+      <c r="GWX28" s="17"/>
+      <c r="GWY28" s="13"/>
+      <c r="GWZ28" s="2"/>
+      <c r="GXF28" s="16"/>
+      <c r="GXH28" s="17"/>
+      <c r="GXI28" s="17"/>
+      <c r="GXJ28" s="13"/>
+      <c r="GXK28" s="2"/>
+      <c r="GXQ28" s="16"/>
+      <c r="GXS28" s="17"/>
+      <c r="GXT28" s="17"/>
+      <c r="GXU28" s="13"/>
+      <c r="GXV28" s="2"/>
+      <c r="GYB28" s="16"/>
+      <c r="GYD28" s="17"/>
+      <c r="GYE28" s="17"/>
+      <c r="GYF28" s="13"/>
+      <c r="GYG28" s="2"/>
+      <c r="GYM28" s="16"/>
+      <c r="GYO28" s="17"/>
+      <c r="GYP28" s="17"/>
+      <c r="GYQ28" s="13"/>
+      <c r="GYR28" s="2"/>
+      <c r="GYX28" s="16"/>
+      <c r="GYZ28" s="17"/>
+      <c r="GZA28" s="17"/>
+      <c r="GZB28" s="13"/>
+      <c r="GZC28" s="2"/>
+      <c r="GZI28" s="16"/>
+      <c r="GZK28" s="17"/>
+      <c r="GZL28" s="17"/>
+      <c r="GZM28" s="13"/>
+      <c r="GZN28" s="2"/>
+      <c r="GZT28" s="16"/>
+      <c r="GZV28" s="17"/>
+      <c r="GZW28" s="17"/>
+      <c r="GZX28" s="13"/>
+      <c r="GZY28" s="2"/>
+      <c r="HAE28" s="16"/>
+      <c r="HAG28" s="17"/>
+      <c r="HAH28" s="17"/>
+      <c r="HAI28" s="13"/>
+      <c r="HAJ28" s="2"/>
+      <c r="HAP28" s="16"/>
+      <c r="HAR28" s="17"/>
+      <c r="HAS28" s="17"/>
+      <c r="HAT28" s="13"/>
+      <c r="HAU28" s="2"/>
+      <c r="HBA28" s="16"/>
+      <c r="HBC28" s="17"/>
+      <c r="HBD28" s="17"/>
+      <c r="HBE28" s="13"/>
+      <c r="HBF28" s="2"/>
+      <c r="HBL28" s="16"/>
+      <c r="HBN28" s="17"/>
+      <c r="HBO28" s="17"/>
+      <c r="HBP28" s="13"/>
+      <c r="HBQ28" s="2"/>
+      <c r="HBW28" s="16"/>
+      <c r="HBY28" s="17"/>
+      <c r="HBZ28" s="17"/>
+      <c r="HCA28" s="13"/>
+      <c r="HCB28" s="2"/>
+      <c r="HCH28" s="16"/>
+      <c r="HCJ28" s="17"/>
+      <c r="HCK28" s="17"/>
+      <c r="HCL28" s="13"/>
+      <c r="HCM28" s="2"/>
+      <c r="HCS28" s="16"/>
+      <c r="HCU28" s="17"/>
+      <c r="HCV28" s="17"/>
+      <c r="HCW28" s="13"/>
+      <c r="HCX28" s="2"/>
+      <c r="HDD28" s="16"/>
+      <c r="HDF28" s="17"/>
+      <c r="HDG28" s="17"/>
+      <c r="HDH28" s="13"/>
+      <c r="HDI28" s="2"/>
+      <c r="HDO28" s="16"/>
+      <c r="HDQ28" s="17"/>
+      <c r="HDR28" s="17"/>
+      <c r="HDS28" s="13"/>
+      <c r="HDT28" s="2"/>
+      <c r="HDZ28" s="16"/>
+      <c r="HEB28" s="17"/>
+      <c r="HEC28" s="17"/>
+      <c r="HED28" s="13"/>
+      <c r="HEE28" s="2"/>
+      <c r="HEK28" s="16"/>
+      <c r="HEM28" s="17"/>
+      <c r="HEN28" s="17"/>
+      <c r="HEO28" s="13"/>
+      <c r="HEP28" s="2"/>
+      <c r="HEV28" s="16"/>
+      <c r="HEX28" s="17"/>
+      <c r="HEY28" s="17"/>
+      <c r="HEZ28" s="13"/>
+      <c r="HFA28" s="2"/>
+      <c r="HFG28" s="16"/>
+      <c r="HFI28" s="17"/>
+      <c r="HFJ28" s="17"/>
+      <c r="HFK28" s="13"/>
+      <c r="HFL28" s="2"/>
+      <c r="HFR28" s="16"/>
+      <c r="HFT28" s="17"/>
+      <c r="HFU28" s="17"/>
+      <c r="HFV28" s="13"/>
+      <c r="HFW28" s="2"/>
+      <c r="HGC28" s="16"/>
+      <c r="HGE28" s="17"/>
+      <c r="HGF28" s="17"/>
+      <c r="HGG28" s="13"/>
+      <c r="HGH28" s="2"/>
+      <c r="HGN28" s="16"/>
+      <c r="HGP28" s="17"/>
+      <c r="HGQ28" s="17"/>
+      <c r="HGR28" s="13"/>
+      <c r="HGS28" s="2"/>
+      <c r="HGY28" s="16"/>
+      <c r="HHA28" s="17"/>
+      <c r="HHB28" s="17"/>
+      <c r="HHC28" s="13"/>
+      <c r="HHD28" s="2"/>
+      <c r="HHJ28" s="16"/>
+      <c r="HHL28" s="17"/>
+      <c r="HHM28" s="17"/>
+      <c r="HHN28" s="13"/>
+      <c r="HHO28" s="2"/>
+      <c r="HHU28" s="16"/>
+      <c r="HHW28" s="17"/>
+      <c r="HHX28" s="17"/>
+      <c r="HHY28" s="13"/>
+      <c r="HHZ28" s="2"/>
+      <c r="HIF28" s="16"/>
+      <c r="HIH28" s="17"/>
+      <c r="HII28" s="17"/>
+      <c r="HIJ28" s="13"/>
+      <c r="HIK28" s="2"/>
+      <c r="HIQ28" s="16"/>
+      <c r="HIS28" s="17"/>
+      <c r="HIT28" s="17"/>
+      <c r="HIU28" s="13"/>
+      <c r="HIV28" s="2"/>
+      <c r="HJB28" s="16"/>
+      <c r="HJD28" s="17"/>
+      <c r="HJE28" s="17"/>
+      <c r="HJF28" s="13"/>
+      <c r="HJG28" s="2"/>
+      <c r="HJM28" s="16"/>
+      <c r="HJO28" s="17"/>
+      <c r="HJP28" s="17"/>
+      <c r="HJQ28" s="13"/>
+      <c r="HJR28" s="2"/>
+      <c r="HJX28" s="16"/>
+      <c r="HJZ28" s="17"/>
+      <c r="HKA28" s="17"/>
+      <c r="HKB28" s="13"/>
+      <c r="HKC28" s="2"/>
+      <c r="HKI28" s="16"/>
+      <c r="HKK28" s="17"/>
+      <c r="HKL28" s="17"/>
+      <c r="HKM28" s="13"/>
+      <c r="HKN28" s="2"/>
+      <c r="HKT28" s="16"/>
+      <c r="HKV28" s="17"/>
+      <c r="HKW28" s="17"/>
+      <c r="HKX28" s="13"/>
+      <c r="HKY28" s="2"/>
+      <c r="HLE28" s="16"/>
+      <c r="HLG28" s="17"/>
+      <c r="HLH28" s="17"/>
+      <c r="HLI28" s="13"/>
+      <c r="HLJ28" s="2"/>
+      <c r="HLP28" s="16"/>
+      <c r="HLR28" s="17"/>
+      <c r="HLS28" s="17"/>
+      <c r="HLT28" s="13"/>
+      <c r="HLU28" s="2"/>
+      <c r="HMA28" s="16"/>
+      <c r="HMC28" s="17"/>
+      <c r="HMD28" s="17"/>
+      <c r="HME28" s="13"/>
+      <c r="HMF28" s="2"/>
+      <c r="HML28" s="16"/>
+      <c r="HMN28" s="17"/>
+      <c r="HMO28" s="17"/>
+      <c r="HMP28" s="13"/>
+      <c r="HMQ28" s="2"/>
+      <c r="HMW28" s="16"/>
+      <c r="HMY28" s="17"/>
+      <c r="HMZ28" s="17"/>
+      <c r="HNA28" s="13"/>
+      <c r="HNB28" s="2"/>
+      <c r="HNH28" s="16"/>
+      <c r="HNJ28" s="17"/>
+      <c r="HNK28" s="17"/>
+      <c r="HNL28" s="13"/>
+      <c r="HNM28" s="2"/>
+      <c r="HNS28" s="16"/>
+      <c r="HNU28" s="17"/>
+      <c r="HNV28" s="17"/>
+      <c r="HNW28" s="13"/>
+      <c r="HNX28" s="2"/>
+      <c r="HOD28" s="16"/>
+      <c r="HOF28" s="17"/>
+      <c r="HOG28" s="17"/>
+      <c r="HOH28" s="13"/>
+      <c r="HOI28" s="2"/>
+      <c r="HOO28" s="16"/>
+      <c r="HOQ28" s="17"/>
+      <c r="HOR28" s="17"/>
+      <c r="HOS28" s="13"/>
+      <c r="HOT28" s="2"/>
+      <c r="HOZ28" s="16"/>
+      <c r="HPB28" s="17"/>
+      <c r="HPC28" s="17"/>
+      <c r="HPD28" s="13"/>
+      <c r="HPE28" s="2"/>
+      <c r="HPK28" s="16"/>
+      <c r="HPM28" s="17"/>
+      <c r="HPN28" s="17"/>
+      <c r="HPO28" s="13"/>
+      <c r="HPP28" s="2"/>
+      <c r="HPV28" s="16"/>
+      <c r="HPX28" s="17"/>
+      <c r="HPY28" s="17"/>
+      <c r="HPZ28" s="13"/>
+      <c r="HQA28" s="2"/>
+      <c r="HQG28" s="16"/>
+      <c r="HQI28" s="17"/>
+      <c r="HQJ28" s="17"/>
+      <c r="HQK28" s="13"/>
+      <c r="HQL28" s="2"/>
+      <c r="HQR28" s="16"/>
+      <c r="HQT28" s="17"/>
+      <c r="HQU28" s="17"/>
+      <c r="HQV28" s="13"/>
+      <c r="HQW28" s="2"/>
+      <c r="HRC28" s="16"/>
+      <c r="HRE28" s="17"/>
+      <c r="HRF28" s="17"/>
+      <c r="HRG28" s="13"/>
+      <c r="HRH28" s="2"/>
+      <c r="HRN28" s="16"/>
+      <c r="HRP28" s="17"/>
+      <c r="HRQ28" s="17"/>
+      <c r="HRR28" s="13"/>
+      <c r="HRS28" s="2"/>
+      <c r="HRY28" s="16"/>
+      <c r="HSA28" s="17"/>
+      <c r="HSB28" s="17"/>
+      <c r="HSC28" s="13"/>
+      <c r="HSD28" s="2"/>
+      <c r="HSJ28" s="16"/>
+      <c r="HSL28" s="17"/>
+      <c r="HSM28" s="17"/>
+      <c r="HSN28" s="13"/>
+      <c r="HSO28" s="2"/>
+      <c r="HSU28" s="16"/>
+      <c r="HSW28" s="17"/>
+      <c r="HSX28" s="17"/>
+      <c r="HSY28" s="13"/>
+      <c r="HSZ28" s="2"/>
+      <c r="HTF28" s="16"/>
+      <c r="HTH28" s="17"/>
+      <c r="HTI28" s="17"/>
+      <c r="HTJ28" s="13"/>
+      <c r="HTK28" s="2"/>
+      <c r="HTQ28" s="16"/>
+      <c r="HTS28" s="17"/>
+      <c r="HTT28" s="17"/>
+      <c r="HTU28" s="13"/>
+      <c r="HTV28" s="2"/>
+      <c r="HUB28" s="16"/>
+      <c r="HUD28" s="17"/>
+      <c r="HUE28" s="17"/>
+      <c r="HUF28" s="13"/>
+      <c r="HUG28" s="2"/>
+      <c r="HUM28" s="16"/>
+      <c r="HUO28" s="17"/>
+      <c r="HUP28" s="17"/>
+      <c r="HUQ28" s="13"/>
+      <c r="HUR28" s="2"/>
+      <c r="HUX28" s="16"/>
+      <c r="HUZ28" s="17"/>
+      <c r="HVA28" s="17"/>
+      <c r="HVB28" s="13"/>
+      <c r="HVC28" s="2"/>
+      <c r="HVI28" s="16"/>
+      <c r="HVK28" s="17"/>
+      <c r="HVL28" s="17"/>
+      <c r="HVM28" s="13"/>
+      <c r="HVN28" s="2"/>
+      <c r="HVT28" s="16"/>
+      <c r="HVV28" s="17"/>
+      <c r="HVW28" s="17"/>
+      <c r="HVX28" s="13"/>
+      <c r="HVY28" s="2"/>
+      <c r="HWE28" s="16"/>
+      <c r="HWG28" s="17"/>
+      <c r="HWH28" s="17"/>
+      <c r="HWI28" s="13"/>
+      <c r="HWJ28" s="2"/>
+      <c r="HWP28" s="16"/>
+      <c r="HWR28" s="17"/>
+      <c r="HWS28" s="17"/>
+      <c r="HWT28" s="13"/>
+      <c r="HWU28" s="2"/>
+      <c r="HXA28" s="16"/>
+      <c r="HXC28" s="17"/>
+      <c r="HXD28" s="17"/>
+      <c r="HXE28" s="13"/>
+      <c r="HXF28" s="2"/>
+      <c r="HXL28" s="16"/>
+      <c r="HXN28" s="17"/>
+      <c r="HXO28" s="17"/>
+      <c r="HXP28" s="13"/>
+      <c r="HXQ28" s="2"/>
+      <c r="HXW28" s="16"/>
+      <c r="HXY28" s="17"/>
+      <c r="HXZ28" s="17"/>
+      <c r="HYA28" s="13"/>
+      <c r="HYB28" s="2"/>
+      <c r="HYH28" s="16"/>
+      <c r="HYJ28" s="17"/>
+      <c r="HYK28" s="17"/>
+      <c r="HYL28" s="13"/>
+      <c r="HYM28" s="2"/>
+      <c r="HYS28" s="16"/>
+      <c r="HYU28" s="17"/>
+      <c r="HYV28" s="17"/>
+      <c r="HYW28" s="13"/>
+      <c r="HYX28" s="2"/>
+      <c r="HZD28" s="16"/>
+      <c r="HZF28" s="17"/>
+      <c r="HZG28" s="17"/>
+      <c r="HZH28" s="13"/>
+      <c r="HZI28" s="2"/>
+      <c r="HZO28" s="16"/>
+      <c r="HZQ28" s="17"/>
+      <c r="HZR28" s="17"/>
+      <c r="HZS28" s="13"/>
+      <c r="HZT28" s="2"/>
+      <c r="HZZ28" s="16"/>
+      <c r="IAB28" s="17"/>
+      <c r="IAC28" s="17"/>
+      <c r="IAD28" s="13"/>
+      <c r="IAE28" s="2"/>
+      <c r="IAK28" s="16"/>
+      <c r="IAM28" s="17"/>
+      <c r="IAN28" s="17"/>
+      <c r="IAO28" s="13"/>
+      <c r="IAP28" s="2"/>
+      <c r="IAV28" s="16"/>
+      <c r="IAX28" s="17"/>
+      <c r="IAY28" s="17"/>
+      <c r="IAZ28" s="13"/>
+      <c r="IBA28" s="2"/>
+      <c r="IBG28" s="16"/>
+      <c r="IBI28" s="17"/>
+      <c r="IBJ28" s="17"/>
+      <c r="IBK28" s="13"/>
+      <c r="IBL28" s="2"/>
+      <c r="IBR28" s="16"/>
+      <c r="IBT28" s="17"/>
+      <c r="IBU28" s="17"/>
+      <c r="IBV28" s="13"/>
+      <c r="IBW28" s="2"/>
+      <c r="ICC28" s="16"/>
+      <c r="ICE28" s="17"/>
+      <c r="ICF28" s="17"/>
+      <c r="ICG28" s="13"/>
+      <c r="ICH28" s="2"/>
+      <c r="ICN28" s="16"/>
+      <c r="ICP28" s="17"/>
+      <c r="ICQ28" s="17"/>
+      <c r="ICR28" s="13"/>
+      <c r="ICS28" s="2"/>
+      <c r="ICY28" s="16"/>
+      <c r="IDA28" s="17"/>
+      <c r="IDB28" s="17"/>
+      <c r="IDC28" s="13"/>
+      <c r="IDD28" s="2"/>
+      <c r="IDJ28" s="16"/>
+      <c r="IDL28" s="17"/>
+      <c r="IDM28" s="17"/>
+      <c r="IDN28" s="13"/>
+      <c r="IDO28" s="2"/>
+      <c r="IDU28" s="16"/>
+      <c r="IDW28" s="17"/>
+      <c r="IDX28" s="17"/>
+      <c r="IDY28" s="13"/>
+      <c r="IDZ28" s="2"/>
+      <c r="IEF28" s="16"/>
+      <c r="IEH28" s="17"/>
+      <c r="IEI28" s="17"/>
+      <c r="IEJ28" s="13"/>
+      <c r="IEK28" s="2"/>
+      <c r="IEQ28" s="16"/>
+      <c r="IES28" s="17"/>
+      <c r="IET28" s="17"/>
+      <c r="IEU28" s="13"/>
+      <c r="IEV28" s="2"/>
+      <c r="IFB28" s="16"/>
+      <c r="IFD28" s="17"/>
+      <c r="IFE28" s="17"/>
+      <c r="IFF28" s="13"/>
+      <c r="IFG28" s="2"/>
+      <c r="IFM28" s="16"/>
+      <c r="IFO28" s="17"/>
+      <c r="IFP28" s="17"/>
+      <c r="IFQ28" s="13"/>
+      <c r="IFR28" s="2"/>
+      <c r="IFX28" s="16"/>
+      <c r="IFZ28" s="17"/>
+      <c r="IGA28" s="17"/>
+      <c r="IGB28" s="13"/>
+      <c r="IGC28" s="2"/>
+      <c r="IGI28" s="16"/>
+      <c r="IGK28" s="17"/>
+      <c r="IGL28" s="17"/>
+      <c r="IGM28" s="13"/>
+      <c r="IGN28" s="2"/>
+      <c r="IGT28" s="16"/>
+      <c r="IGV28" s="17"/>
+      <c r="IGW28" s="17"/>
+      <c r="IGX28" s="13"/>
+      <c r="IGY28" s="2"/>
+      <c r="IHE28" s="16"/>
+      <c r="IHG28" s="17"/>
+      <c r="IHH28" s="17"/>
+      <c r="IHI28" s="13"/>
+      <c r="IHJ28" s="2"/>
+      <c r="IHP28" s="16"/>
+      <c r="IHR28" s="17"/>
+      <c r="IHS28" s="17"/>
+      <c r="IHT28" s="13"/>
+      <c r="IHU28" s="2"/>
+      <c r="IIA28" s="16"/>
+      <c r="IIC28" s="17"/>
+      <c r="IID28" s="17"/>
+      <c r="IIE28" s="13"/>
+      <c r="IIF28" s="2"/>
+      <c r="IIL28" s="16"/>
+      <c r="IIN28" s="17"/>
+      <c r="IIO28" s="17"/>
+      <c r="IIP28" s="13"/>
+      <c r="IIQ28" s="2"/>
+      <c r="IIW28" s="16"/>
+      <c r="IIY28" s="17"/>
+      <c r="IIZ28" s="17"/>
+      <c r="IJA28" s="13"/>
+      <c r="IJB28" s="2"/>
+      <c r="IJH28" s="16"/>
+      <c r="IJJ28" s="17"/>
+      <c r="IJK28" s="17"/>
+      <c r="IJL28" s="13"/>
+      <c r="IJM28" s="2"/>
+      <c r="IJS28" s="16"/>
+      <c r="IJU28" s="17"/>
+      <c r="IJV28" s="17"/>
+      <c r="IJW28" s="13"/>
+      <c r="IJX28" s="2"/>
+      <c r="IKD28" s="16"/>
+      <c r="IKF28" s="17"/>
+      <c r="IKG28" s="17"/>
+      <c r="IKH28" s="13"/>
+      <c r="IKI28" s="2"/>
+      <c r="IKO28" s="16"/>
+      <c r="IKQ28" s="17"/>
+      <c r="IKR28" s="17"/>
+      <c r="IKS28" s="13"/>
+      <c r="IKT28" s="2"/>
+      <c r="IKZ28" s="16"/>
+      <c r="ILB28" s="17"/>
+      <c r="ILC28" s="17"/>
+      <c r="ILD28" s="13"/>
+      <c r="ILE28" s="2"/>
+      <c r="ILK28" s="16"/>
+      <c r="ILM28" s="17"/>
+      <c r="ILN28" s="17"/>
+      <c r="ILO28" s="13"/>
+      <c r="ILP28" s="2"/>
+      <c r="ILV28" s="16"/>
+      <c r="ILX28" s="17"/>
+      <c r="ILY28" s="17"/>
+      <c r="ILZ28" s="13"/>
+      <c r="IMA28" s="2"/>
+      <c r="IMG28" s="16"/>
+      <c r="IMI28" s="17"/>
+      <c r="IMJ28" s="17"/>
+      <c r="IMK28" s="13"/>
+      <c r="IML28" s="2"/>
+      <c r="IMR28" s="16"/>
+      <c r="IMT28" s="17"/>
+      <c r="IMU28" s="17"/>
+      <c r="IMV28" s="13"/>
+      <c r="IMW28" s="2"/>
+      <c r="INC28" s="16"/>
+      <c r="INE28" s="17"/>
+      <c r="INF28" s="17"/>
+      <c r="ING28" s="13"/>
+      <c r="INH28" s="2"/>
+      <c r="INN28" s="16"/>
+      <c r="INP28" s="17"/>
+      <c r="INQ28" s="17"/>
+      <c r="INR28" s="13"/>
+      <c r="INS28" s="2"/>
+      <c r="INY28" s="16"/>
+      <c r="IOA28" s="17"/>
+      <c r="IOB28" s="17"/>
+      <c r="IOC28" s="13"/>
+      <c r="IOD28" s="2"/>
+      <c r="IOJ28" s="16"/>
+      <c r="IOL28" s="17"/>
+      <c r="IOM28" s="17"/>
+      <c r="ION28" s="13"/>
+      <c r="IOO28" s="2"/>
+      <c r="IOU28" s="16"/>
+      <c r="IOW28" s="17"/>
+      <c r="IOX28" s="17"/>
+      <c r="IOY28" s="13"/>
+      <c r="IOZ28" s="2"/>
+      <c r="IPF28" s="16"/>
+      <c r="IPH28" s="17"/>
+      <c r="IPI28" s="17"/>
+      <c r="IPJ28" s="13"/>
+      <c r="IPK28" s="2"/>
+      <c r="IPQ28" s="16"/>
+      <c r="IPS28" s="17"/>
+      <c r="IPT28" s="17"/>
+      <c r="IPU28" s="13"/>
+      <c r="IPV28" s="2"/>
+      <c r="IQB28" s="16"/>
+      <c r="IQD28" s="17"/>
+      <c r="IQE28" s="17"/>
+      <c r="IQF28" s="13"/>
+      <c r="IQG28" s="2"/>
+      <c r="IQM28" s="16"/>
+      <c r="IQO28" s="17"/>
+      <c r="IQP28" s="17"/>
+      <c r="IQQ28" s="13"/>
+      <c r="IQR28" s="2"/>
+      <c r="IQX28" s="16"/>
+      <c r="IQZ28" s="17"/>
+      <c r="IRA28" s="17"/>
+      <c r="IRB28" s="13"/>
+      <c r="IRC28" s="2"/>
+      <c r="IRI28" s="16"/>
+      <c r="IRK28" s="17"/>
+      <c r="IRL28" s="17"/>
+      <c r="IRM28" s="13"/>
+      <c r="IRN28" s="2"/>
+      <c r="IRT28" s="16"/>
+      <c r="IRV28" s="17"/>
+      <c r="IRW28" s="17"/>
+      <c r="IRX28" s="13"/>
+      <c r="IRY28" s="2"/>
+      <c r="ISE28" s="16"/>
+      <c r="ISG28" s="17"/>
+      <c r="ISH28" s="17"/>
+      <c r="ISI28" s="13"/>
+      <c r="ISJ28" s="2"/>
+      <c r="ISP28" s="16"/>
+      <c r="ISR28" s="17"/>
+      <c r="ISS28" s="17"/>
+      <c r="IST28" s="13"/>
+      <c r="ISU28" s="2"/>
+      <c r="ITA28" s="16"/>
+      <c r="ITC28" s="17"/>
+      <c r="ITD28" s="17"/>
+      <c r="ITE28" s="13"/>
+      <c r="ITF28" s="2"/>
+      <c r="ITL28" s="16"/>
+      <c r="ITN28" s="17"/>
+      <c r="ITO28" s="17"/>
+      <c r="ITP28" s="13"/>
+      <c r="ITQ28" s="2"/>
+      <c r="ITW28" s="16"/>
+      <c r="ITY28" s="17"/>
+      <c r="ITZ28" s="17"/>
+      <c r="IUA28" s="13"/>
+      <c r="IUB28" s="2"/>
+      <c r="IUH28" s="16"/>
+      <c r="IUJ28" s="17"/>
+      <c r="IUK28" s="17"/>
+      <c r="IUL28" s="13"/>
+      <c r="IUM28" s="2"/>
+      <c r="IUS28" s="16"/>
+      <c r="IUU28" s="17"/>
+      <c r="IUV28" s="17"/>
+      <c r="IUW28" s="13"/>
+      <c r="IUX28" s="2"/>
+      <c r="IVD28" s="16"/>
+      <c r="IVF28" s="17"/>
+      <c r="IVG28" s="17"/>
+      <c r="IVH28" s="13"/>
+      <c r="IVI28" s="2"/>
+      <c r="IVO28" s="16"/>
+      <c r="IVQ28" s="17"/>
+      <c r="IVR28" s="17"/>
+      <c r="IVS28" s="13"/>
+      <c r="IVT28" s="2"/>
+      <c r="IVZ28" s="16"/>
+      <c r="IWB28" s="17"/>
+      <c r="IWC28" s="17"/>
+      <c r="IWD28" s="13"/>
+      <c r="IWE28" s="2"/>
+      <c r="IWK28" s="16"/>
+      <c r="IWM28" s="17"/>
+      <c r="IWN28" s="17"/>
+      <c r="IWO28" s="13"/>
+      <c r="IWP28" s="2"/>
+      <c r="IWV28" s="16"/>
+      <c r="IWX28" s="17"/>
+      <c r="IWY28" s="17"/>
+      <c r="IWZ28" s="13"/>
+      <c r="IXA28" s="2"/>
+      <c r="IXG28" s="16"/>
+      <c r="IXI28" s="17"/>
+      <c r="IXJ28" s="17"/>
+      <c r="IXK28" s="13"/>
+      <c r="IXL28" s="2"/>
+      <c r="IXR28" s="16"/>
+      <c r="IXT28" s="17"/>
+      <c r="IXU28" s="17"/>
+      <c r="IXV28" s="13"/>
+      <c r="IXW28" s="2"/>
+      <c r="IYC28" s="16"/>
+      <c r="IYE28" s="17"/>
+      <c r="IYF28" s="17"/>
+      <c r="IYG28" s="13"/>
+      <c r="IYH28" s="2"/>
+      <c r="IYN28" s="16"/>
+      <c r="IYP28" s="17"/>
+      <c r="IYQ28" s="17"/>
+      <c r="IYR28" s="13"/>
+      <c r="IYS28" s="2"/>
+      <c r="IYY28" s="16"/>
+      <c r="IZA28" s="17"/>
+      <c r="IZB28" s="17"/>
+      <c r="IZC28" s="13"/>
+      <c r="IZD28" s="2"/>
+      <c r="IZJ28" s="16"/>
+      <c r="IZL28" s="17"/>
+      <c r="IZM28" s="17"/>
+      <c r="IZN28" s="13"/>
+      <c r="IZO28" s="2"/>
+      <c r="IZU28" s="16"/>
+      <c r="IZW28" s="17"/>
+      <c r="IZX28" s="17"/>
+      <c r="IZY28" s="13"/>
+      <c r="IZZ28" s="2"/>
+      <c r="JAF28" s="16"/>
+      <c r="JAH28" s="17"/>
+      <c r="JAI28" s="17"/>
+      <c r="JAJ28" s="13"/>
+      <c r="JAK28" s="2"/>
+      <c r="JAQ28" s="16"/>
+      <c r="JAS28" s="17"/>
+      <c r="JAT28" s="17"/>
+      <c r="JAU28" s="13"/>
+      <c r="JAV28" s="2"/>
+      <c r="JBB28" s="16"/>
+      <c r="JBD28" s="17"/>
+      <c r="JBE28" s="17"/>
+      <c r="JBF28" s="13"/>
+      <c r="JBG28" s="2"/>
+      <c r="JBM28" s="16"/>
+      <c r="JBO28" s="17"/>
+      <c r="JBP28" s="17"/>
+      <c r="JBQ28" s="13"/>
+      <c r="JBR28" s="2"/>
+      <c r="JBX28" s="16"/>
+      <c r="JBZ28" s="17"/>
+      <c r="JCA28" s="17"/>
+      <c r="JCB28" s="13"/>
+      <c r="JCC28" s="2"/>
+      <c r="JCI28" s="16"/>
+      <c r="JCK28" s="17"/>
+      <c r="JCL28" s="17"/>
+      <c r="JCM28" s="13"/>
+      <c r="JCN28" s="2"/>
+      <c r="JCT28" s="16"/>
+      <c r="JCV28" s="17"/>
+      <c r="JCW28" s="17"/>
+      <c r="JCX28" s="13"/>
+      <c r="JCY28" s="2"/>
+      <c r="JDE28" s="16"/>
+      <c r="JDG28" s="17"/>
+      <c r="JDH28" s="17"/>
+      <c r="JDI28" s="13"/>
+      <c r="JDJ28" s="2"/>
+      <c r="JDP28" s="16"/>
+      <c r="JDR28" s="17"/>
+      <c r="JDS28" s="17"/>
+      <c r="JDT28" s="13"/>
+      <c r="JDU28" s="2"/>
+      <c r="JEA28" s="16"/>
+      <c r="JEC28" s="17"/>
+      <c r="JED28" s="17"/>
+      <c r="JEE28" s="13"/>
+      <c r="JEF28" s="2"/>
+      <c r="JEL28" s="16"/>
+      <c r="JEN28" s="17"/>
+      <c r="JEO28" s="17"/>
+      <c r="JEP28" s="13"/>
+      <c r="JEQ28" s="2"/>
+      <c r="JEW28" s="16"/>
+      <c r="JEY28" s="17"/>
+      <c r="JEZ28" s="17"/>
+      <c r="JFA28" s="13"/>
+      <c r="JFB28" s="2"/>
+      <c r="JFH28" s="16"/>
+      <c r="JFJ28" s="17"/>
+      <c r="JFK28" s="17"/>
+      <c r="JFL28" s="13"/>
+      <c r="JFM28" s="2"/>
+      <c r="JFS28" s="16"/>
+      <c r="JFU28" s="17"/>
+      <c r="JFV28" s="17"/>
+      <c r="JFW28" s="13"/>
+      <c r="JFX28" s="2"/>
+      <c r="JGD28" s="16"/>
+      <c r="JGF28" s="17"/>
+      <c r="JGG28" s="17"/>
+      <c r="JGH28" s="13"/>
+      <c r="JGI28" s="2"/>
+      <c r="JGO28" s="16"/>
+      <c r="JGQ28" s="17"/>
+      <c r="JGR28" s="17"/>
+      <c r="JGS28" s="13"/>
+      <c r="JGT28" s="2"/>
+      <c r="JGZ28" s="16"/>
+      <c r="JHB28" s="17"/>
+      <c r="JHC28" s="17"/>
+      <c r="JHD28" s="13"/>
+      <c r="JHE28" s="2"/>
+      <c r="JHK28" s="16"/>
+      <c r="JHM28" s="17"/>
+      <c r="JHN28" s="17"/>
+      <c r="JHO28" s="13"/>
+      <c r="JHP28" s="2"/>
+      <c r="JHV28" s="16"/>
+      <c r="JHX28" s="17"/>
+      <c r="JHY28" s="17"/>
+      <c r="JHZ28" s="13"/>
+      <c r="JIA28" s="2"/>
+      <c r="JIG28" s="16"/>
+      <c r="JII28" s="17"/>
+      <c r="JIJ28" s="17"/>
+      <c r="JIK28" s="13"/>
+      <c r="JIL28" s="2"/>
+      <c r="JIR28" s="16"/>
+      <c r="JIT28" s="17"/>
+      <c r="JIU28" s="17"/>
+      <c r="JIV28" s="13"/>
+      <c r="JIW28" s="2"/>
+      <c r="JJC28" s="16"/>
+      <c r="JJE28" s="17"/>
+      <c r="JJF28" s="17"/>
+      <c r="JJG28" s="13"/>
+      <c r="JJH28" s="2"/>
+      <c r="JJN28" s="16"/>
+      <c r="JJP28" s="17"/>
+      <c r="JJQ28" s="17"/>
+      <c r="JJR28" s="13"/>
+      <c r="JJS28" s="2"/>
+      <c r="JJY28" s="16"/>
+      <c r="JKA28" s="17"/>
+      <c r="JKB28" s="17"/>
+      <c r="JKC28" s="13"/>
+      <c r="JKD28" s="2"/>
+      <c r="JKJ28" s="16"/>
+      <c r="JKL28" s="17"/>
+      <c r="JKM28" s="17"/>
+      <c r="JKN28" s="13"/>
+      <c r="JKO28" s="2"/>
+      <c r="JKU28" s="16"/>
+      <c r="JKW28" s="17"/>
+      <c r="JKX28" s="17"/>
+      <c r="JKY28" s="13"/>
+      <c r="JKZ28" s="2"/>
+      <c r="JLF28" s="16"/>
+      <c r="JLH28" s="17"/>
+      <c r="JLI28" s="17"/>
+      <c r="JLJ28" s="13"/>
+      <c r="JLK28" s="2"/>
+      <c r="JLQ28" s="16"/>
+      <c r="JLS28" s="17"/>
+      <c r="JLT28" s="17"/>
+      <c r="JLU28" s="13"/>
+      <c r="JLV28" s="2"/>
+      <c r="JMB28" s="16"/>
+      <c r="JMD28" s="17"/>
+      <c r="JME28" s="17"/>
+      <c r="JMF28" s="13"/>
+      <c r="JMG28" s="2"/>
+      <c r="JMM28" s="16"/>
+      <c r="JMO28" s="17"/>
+      <c r="JMP28" s="17"/>
+      <c r="JMQ28" s="13"/>
+      <c r="JMR28" s="2"/>
+      <c r="JMX28" s="16"/>
+      <c r="JMZ28" s="17"/>
+      <c r="JNA28" s="17"/>
+      <c r="JNB28" s="13"/>
+      <c r="JNC28" s="2"/>
+      <c r="JNI28" s="16"/>
+      <c r="JNK28" s="17"/>
+      <c r="JNL28" s="17"/>
+      <c r="JNM28" s="13"/>
+      <c r="JNN28" s="2"/>
+      <c r="JNT28" s="16"/>
+      <c r="JNV28" s="17"/>
+      <c r="JNW28" s="17"/>
+      <c r="JNX28" s="13"/>
+      <c r="JNY28" s="2"/>
+      <c r="JOE28" s="16"/>
+      <c r="JOG28" s="17"/>
+      <c r="JOH28" s="17"/>
+      <c r="JOI28" s="13"/>
+      <c r="JOJ28" s="2"/>
+      <c r="JOP28" s="16"/>
+      <c r="JOR28" s="17"/>
+      <c r="JOS28" s="17"/>
+      <c r="JOT28" s="13"/>
+      <c r="JOU28" s="2"/>
+      <c r="JPA28" s="16"/>
+      <c r="JPC28" s="17"/>
+      <c r="JPD28" s="17"/>
+      <c r="JPE28" s="13"/>
+      <c r="JPF28" s="2"/>
+      <c r="JPL28" s="16"/>
+      <c r="JPN28" s="17"/>
+      <c r="JPO28" s="17"/>
+      <c r="JPP28" s="13"/>
+      <c r="JPQ28" s="2"/>
+      <c r="JPW28" s="16"/>
+      <c r="JPY28" s="17"/>
+      <c r="JPZ28" s="17"/>
+      <c r="JQA28" s="13"/>
+      <c r="JQB28" s="2"/>
+      <c r="JQH28" s="16"/>
+      <c r="JQJ28" s="17"/>
+      <c r="JQK28" s="17"/>
+      <c r="JQL28" s="13"/>
+      <c r="JQM28" s="2"/>
+      <c r="JQS28" s="16"/>
+      <c r="JQU28" s="17"/>
+      <c r="JQV28" s="17"/>
+      <c r="JQW28" s="13"/>
+      <c r="JQX28" s="2"/>
+      <c r="JRD28" s="16"/>
+      <c r="JRF28" s="17"/>
+      <c r="JRG28" s="17"/>
+      <c r="JRH28" s="13"/>
+      <c r="JRI28" s="2"/>
+      <c r="JRO28" s="16"/>
+      <c r="JRQ28" s="17"/>
+      <c r="JRR28" s="17"/>
+      <c r="JRS28" s="13"/>
+      <c r="JRT28" s="2"/>
+      <c r="JRZ28" s="16"/>
+      <c r="JSB28" s="17"/>
+      <c r="JSC28" s="17"/>
+      <c r="JSD28" s="13"/>
+      <c r="JSE28" s="2"/>
+      <c r="JSK28" s="16"/>
+      <c r="JSM28" s="17"/>
+      <c r="JSN28" s="17"/>
+      <c r="JSO28" s="13"/>
+      <c r="JSP28" s="2"/>
+      <c r="JSV28" s="16"/>
+      <c r="JSX28" s="17"/>
+      <c r="JSY28" s="17"/>
+      <c r="JSZ28" s="13"/>
+      <c r="JTA28" s="2"/>
+      <c r="JTG28" s="16"/>
+      <c r="JTI28" s="17"/>
+      <c r="JTJ28" s="17"/>
+      <c r="JTK28" s="13"/>
+      <c r="JTL28" s="2"/>
+      <c r="JTR28" s="16"/>
+      <c r="JTT28" s="17"/>
+      <c r="JTU28" s="17"/>
+      <c r="JTV28" s="13"/>
+      <c r="JTW28" s="2"/>
+      <c r="JUC28" s="16"/>
+      <c r="JUE28" s="17"/>
+      <c r="JUF28" s="17"/>
+      <c r="JUG28" s="13"/>
+      <c r="JUH28" s="2"/>
+      <c r="JUN28" s="16"/>
+      <c r="JUP28" s="17"/>
+      <c r="JUQ28" s="17"/>
+      <c r="JUR28" s="13"/>
+      <c r="JUS28" s="2"/>
+      <c r="JUY28" s="16"/>
+      <c r="JVA28" s="17"/>
+      <c r="JVB28" s="17"/>
+      <c r="JVC28" s="13"/>
+      <c r="JVD28" s="2"/>
+      <c r="JVJ28" s="16"/>
+      <c r="JVL28" s="17"/>
+      <c r="JVM28" s="17"/>
+      <c r="JVN28" s="13"/>
+      <c r="JVO28" s="2"/>
+      <c r="JVU28" s="16"/>
+      <c r="JVW28" s="17"/>
+      <c r="JVX28" s="17"/>
+      <c r="JVY28" s="13"/>
+      <c r="JVZ28" s="2"/>
+      <c r="JWF28" s="16"/>
+      <c r="JWH28" s="17"/>
+      <c r="JWI28" s="17"/>
+      <c r="JWJ28" s="13"/>
+      <c r="JWK28" s="2"/>
+      <c r="JWQ28" s="16"/>
+      <c r="JWS28" s="17"/>
+      <c r="JWT28" s="17"/>
+      <c r="JWU28" s="13"/>
+      <c r="JWV28" s="2"/>
+      <c r="JXB28" s="16"/>
+      <c r="JXD28" s="17"/>
+      <c r="JXE28" s="17"/>
+      <c r="JXF28" s="13"/>
+      <c r="JXG28" s="2"/>
+      <c r="JXM28" s="16"/>
+      <c r="JXO28" s="17"/>
+      <c r="JXP28" s="17"/>
+      <c r="JXQ28" s="13"/>
+      <c r="JXR28" s="2"/>
+      <c r="JXX28" s="16"/>
+      <c r="JXZ28" s="17"/>
+      <c r="JYA28" s="17"/>
+      <c r="JYB28" s="13"/>
+      <c r="JYC28" s="2"/>
+      <c r="JYI28" s="16"/>
+      <c r="JYK28" s="17"/>
+      <c r="JYL28" s="17"/>
+      <c r="JYM28" s="13"/>
+      <c r="JYN28" s="2"/>
+      <c r="JYT28" s="16"/>
+      <c r="JYV28" s="17"/>
+      <c r="JYW28" s="17"/>
+      <c r="JYX28" s="13"/>
+      <c r="JYY28" s="2"/>
+      <c r="JZE28" s="16"/>
+      <c r="JZG28" s="17"/>
+      <c r="JZH28" s="17"/>
+      <c r="JZI28" s="13"/>
+      <c r="JZJ28" s="2"/>
+      <c r="JZP28" s="16"/>
+      <c r="JZR28" s="17"/>
+      <c r="JZS28" s="17"/>
+      <c r="JZT28" s="13"/>
+      <c r="JZU28" s="2"/>
+      <c r="KAA28" s="16"/>
+      <c r="KAC28" s="17"/>
+      <c r="KAD28" s="17"/>
+      <c r="KAE28" s="13"/>
+      <c r="KAF28" s="2"/>
+      <c r="KAL28" s="16"/>
+      <c r="KAN28" s="17"/>
+      <c r="KAO28" s="17"/>
+      <c r="KAP28" s="13"/>
+      <c r="KAQ28" s="2"/>
+      <c r="KAW28" s="16"/>
+      <c r="KAY28" s="17"/>
+      <c r="KAZ28" s="17"/>
+      <c r="KBA28" s="13"/>
+      <c r="KBB28" s="2"/>
+      <c r="KBH28" s="16"/>
+      <c r="KBJ28" s="17"/>
+      <c r="KBK28" s="17"/>
+      <c r="KBL28" s="13"/>
+      <c r="KBM28" s="2"/>
+      <c r="KBS28" s="16"/>
+      <c r="KBU28" s="17"/>
+      <c r="KBV28" s="17"/>
+      <c r="KBW28" s="13"/>
+      <c r="KBX28" s="2"/>
+      <c r="KCD28" s="16"/>
+      <c r="KCF28" s="17"/>
+      <c r="KCG28" s="17"/>
+      <c r="KCH28" s="13"/>
+      <c r="KCI28" s="2"/>
+      <c r="KCO28" s="16"/>
+      <c r="KCQ28" s="17"/>
+      <c r="KCR28" s="17"/>
+      <c r="KCS28" s="13"/>
+      <c r="KCT28" s="2"/>
+      <c r="KCZ28" s="16"/>
+      <c r="KDB28" s="17"/>
+      <c r="KDC28" s="17"/>
+      <c r="KDD28" s="13"/>
+      <c r="KDE28" s="2"/>
+      <c r="KDK28" s="16"/>
+      <c r="KDM28" s="17"/>
+      <c r="KDN28" s="17"/>
+      <c r="KDO28" s="13"/>
+      <c r="KDP28" s="2"/>
+      <c r="KDV28" s="16"/>
+      <c r="KDX28" s="17"/>
+      <c r="KDY28" s="17"/>
+      <c r="KDZ28" s="13"/>
+      <c r="KEA28" s="2"/>
+      <c r="KEG28" s="16"/>
+      <c r="KEI28" s="17"/>
+      <c r="KEJ28" s="17"/>
+      <c r="KEK28" s="13"/>
+      <c r="KEL28" s="2"/>
+      <c r="KER28" s="16"/>
+      <c r="KET28" s="17"/>
+      <c r="KEU28" s="17"/>
+      <c r="KEV28" s="13"/>
+      <c r="KEW28" s="2"/>
+      <c r="KFC28" s="16"/>
+      <c r="KFE28" s="17"/>
+      <c r="KFF28" s="17"/>
+      <c r="KFG28" s="13"/>
+      <c r="KFH28" s="2"/>
+      <c r="KFN28" s="16"/>
+      <c r="KFP28" s="17"/>
+      <c r="KFQ28" s="17"/>
+      <c r="KFR28" s="13"/>
+      <c r="KFS28" s="2"/>
+      <c r="KFY28" s="16"/>
+      <c r="KGA28" s="17"/>
+      <c r="KGB28" s="17"/>
+      <c r="KGC28" s="13"/>
+      <c r="KGD28" s="2"/>
+      <c r="KGJ28" s="16"/>
+      <c r="KGL28" s="17"/>
+      <c r="KGM28" s="17"/>
+      <c r="KGN28" s="13"/>
+      <c r="KGO28" s="2"/>
+      <c r="KGU28" s="16"/>
+      <c r="KGW28" s="17"/>
+      <c r="KGX28" s="17"/>
+      <c r="KGY28" s="13"/>
+      <c r="KGZ28" s="2"/>
+      <c r="KHF28" s="16"/>
+      <c r="KHH28" s="17"/>
+      <c r="KHI28" s="17"/>
+      <c r="KHJ28" s="13"/>
+      <c r="KHK28" s="2"/>
+      <c r="KHQ28" s="16"/>
+      <c r="KHS28" s="17"/>
+      <c r="KHT28" s="17"/>
+      <c r="KHU28" s="13"/>
+      <c r="KHV28" s="2"/>
+      <c r="KIB28" s="16"/>
+      <c r="KID28" s="17"/>
+      <c r="KIE28" s="17"/>
+      <c r="KIF28" s="13"/>
+      <c r="KIG28" s="2"/>
+      <c r="KIM28" s="16"/>
+      <c r="KIO28" s="17"/>
+      <c r="KIP28" s="17"/>
+      <c r="KIQ28" s="13"/>
+      <c r="KIR28" s="2"/>
+      <c r="KIX28" s="16"/>
+      <c r="KIZ28" s="17"/>
+      <c r="KJA28" s="17"/>
+      <c r="KJB28" s="13"/>
+      <c r="KJC28" s="2"/>
+      <c r="KJI28" s="16"/>
+      <c r="KJK28" s="17"/>
+      <c r="KJL28" s="17"/>
+      <c r="KJM28" s="13"/>
+      <c r="KJN28" s="2"/>
+      <c r="KJT28" s="16"/>
+      <c r="KJV28" s="17"/>
+      <c r="KJW28" s="17"/>
+      <c r="KJX28" s="13"/>
+      <c r="KJY28" s="2"/>
+      <c r="KKE28" s="16"/>
+      <c r="KKG28" s="17"/>
+      <c r="KKH28" s="17"/>
+      <c r="KKI28" s="13"/>
+      <c r="KKJ28" s="2"/>
+      <c r="KKP28" s="16"/>
+      <c r="KKR28" s="17"/>
+      <c r="KKS28" s="17"/>
+      <c r="KKT28" s="13"/>
+      <c r="KKU28" s="2"/>
+      <c r="KLA28" s="16"/>
+      <c r="KLC28" s="17"/>
+      <c r="KLD28" s="17"/>
+      <c r="KLE28" s="13"/>
+      <c r="KLF28" s="2"/>
+      <c r="KLL28" s="16"/>
+      <c r="KLN28" s="17"/>
+      <c r="KLO28" s="17"/>
+      <c r="KLP28" s="13"/>
+      <c r="KLQ28" s="2"/>
+      <c r="KLW28" s="16"/>
+      <c r="KLY28" s="17"/>
+      <c r="KLZ28" s="17"/>
+      <c r="KMA28" s="13"/>
+      <c r="KMB28" s="2"/>
+      <c r="KMH28" s="16"/>
+      <c r="KMJ28" s="17"/>
+      <c r="KMK28" s="17"/>
+      <c r="KML28" s="13"/>
+      <c r="KMM28" s="2"/>
+      <c r="KMS28" s="16"/>
+      <c r="KMU28" s="17"/>
+      <c r="KMV28" s="17"/>
+      <c r="KMW28" s="13"/>
+      <c r="KMX28" s="2"/>
+      <c r="KND28" s="16"/>
+      <c r="KNF28" s="17"/>
+      <c r="KNG28" s="17"/>
+      <c r="KNH28" s="13"/>
+      <c r="KNI28" s="2"/>
+      <c r="KNO28" s="16"/>
+      <c r="KNQ28" s="17"/>
+      <c r="KNR28" s="17"/>
+      <c r="KNS28" s="13"/>
+      <c r="KNT28" s="2"/>
+      <c r="KNZ28" s="16"/>
+      <c r="KOB28" s="17"/>
+      <c r="KOC28" s="17"/>
+      <c r="KOD28" s="13"/>
+      <c r="KOE28" s="2"/>
+      <c r="KOK28" s="16"/>
+      <c r="KOM28" s="17"/>
+      <c r="KON28" s="17"/>
+      <c r="KOO28" s="13"/>
+      <c r="KOP28" s="2"/>
+      <c r="KOV28" s="16"/>
+      <c r="KOX28" s="17"/>
+      <c r="KOY28" s="17"/>
+      <c r="KOZ28" s="13"/>
+      <c r="KPA28" s="2"/>
+      <c r="KPG28" s="16"/>
+      <c r="KPI28" s="17"/>
+      <c r="KPJ28" s="17"/>
+      <c r="KPK28" s="13"/>
+      <c r="KPL28" s="2"/>
+      <c r="KPR28" s="16"/>
+      <c r="KPT28" s="17"/>
+      <c r="KPU28" s="17"/>
+      <c r="KPV28" s="13"/>
+      <c r="KPW28" s="2"/>
+      <c r="KQC28" s="16"/>
+      <c r="KQE28" s="17"/>
+      <c r="KQF28" s="17"/>
+      <c r="KQG28" s="13"/>
+      <c r="KQH28" s="2"/>
+      <c r="KQN28" s="16"/>
+      <c r="KQP28" s="17"/>
+      <c r="KQQ28" s="17"/>
+      <c r="KQR28" s="13"/>
+      <c r="KQS28" s="2"/>
+      <c r="KQY28" s="16"/>
+      <c r="KRA28" s="17"/>
+      <c r="KRB28" s="17"/>
+      <c r="KRC28" s="13"/>
+      <c r="KRD28" s="2"/>
+      <c r="KRJ28" s="16"/>
+      <c r="KRL28" s="17"/>
+      <c r="KRM28" s="17"/>
+      <c r="KRN28" s="13"/>
+      <c r="KRO28" s="2"/>
+      <c r="KRU28" s="16"/>
+      <c r="KRW28" s="17"/>
+      <c r="KRX28" s="17"/>
+      <c r="KRY28" s="13"/>
+      <c r="KRZ28" s="2"/>
+      <c r="KSF28" s="16"/>
+      <c r="KSH28" s="17"/>
+      <c r="KSI28" s="17"/>
+      <c r="KSJ28" s="13"/>
+      <c r="KSK28" s="2"/>
+      <c r="KSQ28" s="16"/>
+      <c r="KSS28" s="17"/>
+      <c r="KST28" s="17"/>
+      <c r="KSU28" s="13"/>
+      <c r="KSV28" s="2"/>
+      <c r="KTB28" s="16"/>
+      <c r="KTD28" s="17"/>
+      <c r="KTE28" s="17"/>
+      <c r="KTF28" s="13"/>
+      <c r="KTG28" s="2"/>
+      <c r="KTM28" s="16"/>
+      <c r="KTO28" s="17"/>
+      <c r="KTP28" s="17"/>
+      <c r="KTQ28" s="13"/>
+      <c r="KTR28" s="2"/>
+      <c r="KTX28" s="16"/>
+      <c r="KTZ28" s="17"/>
+      <c r="KUA28" s="17"/>
+      <c r="KUB28" s="13"/>
+      <c r="KUC28" s="2"/>
+      <c r="KUI28" s="16"/>
+      <c r="KUK28" s="17"/>
+      <c r="KUL28" s="17"/>
+      <c r="KUM28" s="13"/>
+      <c r="KUN28" s="2"/>
+      <c r="KUT28" s="16"/>
+      <c r="KUV28" s="17"/>
+      <c r="KUW28" s="17"/>
+      <c r="KUX28" s="13"/>
+      <c r="KUY28" s="2"/>
+      <c r="KVE28" s="16"/>
+      <c r="KVG28" s="17"/>
+      <c r="KVH28" s="17"/>
+      <c r="KVI28" s="13"/>
+      <c r="KVJ28" s="2"/>
+      <c r="KVP28" s="16"/>
+      <c r="KVR28" s="17"/>
+      <c r="KVS28" s="17"/>
+      <c r="KVT28" s="13"/>
+      <c r="KVU28" s="2"/>
+      <c r="KWA28" s="16"/>
+      <c r="KWC28" s="17"/>
+      <c r="KWD28" s="17"/>
+      <c r="KWE28" s="13"/>
+      <c r="KWF28" s="2"/>
+      <c r="KWL28" s="16"/>
+      <c r="KWN28" s="17"/>
+      <c r="KWO28" s="17"/>
+      <c r="KWP28" s="13"/>
+      <c r="KWQ28" s="2"/>
+      <c r="KWW28" s="16"/>
+      <c r="KWY28" s="17"/>
+      <c r="KWZ28" s="17"/>
+      <c r="KXA28" s="13"/>
+      <c r="KXB28" s="2"/>
+      <c r="KXH28" s="16"/>
+      <c r="KXJ28" s="17"/>
+      <c r="KXK28" s="17"/>
+      <c r="KXL28" s="13"/>
+      <c r="KXM28" s="2"/>
+      <c r="KXS28" s="16"/>
+      <c r="KXU28" s="17"/>
+      <c r="KXV28" s="17"/>
+      <c r="KXW28" s="13"/>
+      <c r="KXX28" s="2"/>
+      <c r="KYD28" s="16"/>
+      <c r="KYF28" s="17"/>
+      <c r="KYG28" s="17"/>
+      <c r="KYH28" s="13"/>
+      <c r="KYI28" s="2"/>
+      <c r="KYO28" s="16"/>
+      <c r="KYQ28" s="17"/>
+      <c r="KYR28" s="17"/>
+      <c r="KYS28" s="13"/>
+      <c r="KYT28" s="2"/>
+      <c r="KYZ28" s="16"/>
+      <c r="KZB28" s="17"/>
+      <c r="KZC28" s="17"/>
+      <c r="KZD28" s="13"/>
+      <c r="KZE28" s="2"/>
+      <c r="KZK28" s="16"/>
+      <c r="KZM28" s="17"/>
+      <c r="KZN28" s="17"/>
+      <c r="KZO28" s="13"/>
+      <c r="KZP28" s="2"/>
+      <c r="KZV28" s="16"/>
+      <c r="KZX28" s="17"/>
+      <c r="KZY28" s="17"/>
+      <c r="KZZ28" s="13"/>
+      <c r="LAA28" s="2"/>
+      <c r="LAG28" s="16"/>
+      <c r="LAI28" s="17"/>
+      <c r="LAJ28" s="17"/>
+      <c r="LAK28" s="13"/>
+      <c r="LAL28" s="2"/>
+      <c r="LAR28" s="16"/>
+      <c r="LAT28" s="17"/>
+      <c r="LAU28" s="17"/>
+      <c r="LAV28" s="13"/>
+      <c r="LAW28" s="2"/>
+      <c r="LBC28" s="16"/>
+      <c r="LBE28" s="17"/>
+      <c r="LBF28" s="17"/>
+      <c r="LBG28" s="13"/>
+      <c r="LBH28" s="2"/>
+      <c r="LBN28" s="16"/>
+      <c r="LBP28" s="17"/>
+      <c r="LBQ28" s="17"/>
+      <c r="LBR28" s="13"/>
+      <c r="LBS28" s="2"/>
+      <c r="LBY28" s="16"/>
+      <c r="LCA28" s="17"/>
+      <c r="LCB28" s="17"/>
+      <c r="LCC28" s="13"/>
+      <c r="LCD28" s="2"/>
+      <c r="LCJ28" s="16"/>
+      <c r="LCL28" s="17"/>
+      <c r="LCM28" s="17"/>
+      <c r="LCN28" s="13"/>
+      <c r="LCO28" s="2"/>
+      <c r="LCU28" s="16"/>
+      <c r="LCW28" s="17"/>
+      <c r="LCX28" s="17"/>
+      <c r="LCY28" s="13"/>
+      <c r="LCZ28" s="2"/>
+      <c r="LDF28" s="16"/>
+      <c r="LDH28" s="17"/>
+      <c r="LDI28" s="17"/>
+      <c r="LDJ28" s="13"/>
+      <c r="LDK28" s="2"/>
+      <c r="LDQ28" s="16"/>
+      <c r="LDS28" s="17"/>
+      <c r="LDT28" s="17"/>
+      <c r="LDU28" s="13"/>
+      <c r="LDV28" s="2"/>
+      <c r="LEB28" s="16"/>
+      <c r="LED28" s="17"/>
+      <c r="LEE28" s="17"/>
+      <c r="LEF28" s="13"/>
+      <c r="LEG28" s="2"/>
+      <c r="LEM28" s="16"/>
+      <c r="LEO28" s="17"/>
+      <c r="LEP28" s="17"/>
+      <c r="LEQ28" s="13"/>
+      <c r="LER28" s="2"/>
+      <c r="LEX28" s="16"/>
+      <c r="LEZ28" s="17"/>
+      <c r="LFA28" s="17"/>
+      <c r="LFB28" s="13"/>
+      <c r="LFC28" s="2"/>
+      <c r="LFI28" s="16"/>
+      <c r="LFK28" s="17"/>
+      <c r="LFL28" s="17"/>
+      <c r="LFM28" s="13"/>
+      <c r="LFN28" s="2"/>
+      <c r="LFT28" s="16"/>
+      <c r="LFV28" s="17"/>
+      <c r="LFW28" s="17"/>
+      <c r="LFX28" s="13"/>
+      <c r="LFY28" s="2"/>
+      <c r="LGE28" s="16"/>
+      <c r="LGG28" s="17"/>
+      <c r="LGH28" s="17"/>
+      <c r="LGI28" s="13"/>
+      <c r="LGJ28" s="2"/>
+      <c r="LGP28" s="16"/>
+      <c r="LGR28" s="17"/>
+      <c r="LGS28" s="17"/>
+      <c r="LGT28" s="13"/>
+      <c r="LGU28" s="2"/>
+      <c r="LHA28" s="16"/>
+      <c r="LHC28" s="17"/>
+      <c r="LHD28" s="17"/>
+      <c r="LHE28" s="13"/>
+      <c r="LHF28" s="2"/>
+      <c r="LHL28" s="16"/>
+      <c r="LHN28" s="17"/>
+      <c r="LHO28" s="17"/>
+      <c r="LHP28" s="13"/>
+      <c r="LHQ28" s="2"/>
+      <c r="LHW28" s="16"/>
+      <c r="LHY28" s="17"/>
+      <c r="LHZ28" s="17"/>
+      <c r="LIA28" s="13"/>
+      <c r="LIB28" s="2"/>
+      <c r="LIH28" s="16"/>
+      <c r="LIJ28" s="17"/>
+      <c r="LIK28" s="17"/>
+      <c r="LIL28" s="13"/>
+      <c r="LIM28" s="2"/>
+      <c r="LIS28" s="16"/>
+      <c r="LIU28" s="17"/>
+      <c r="LIV28" s="17"/>
+      <c r="LIW28" s="13"/>
+      <c r="LIX28" s="2"/>
+      <c r="LJD28" s="16"/>
+      <c r="LJF28" s="17"/>
+      <c r="LJG28" s="17"/>
+      <c r="LJH28" s="13"/>
+      <c r="LJI28" s="2"/>
+      <c r="LJO28" s="16"/>
+      <c r="LJQ28" s="17"/>
+      <c r="LJR28" s="17"/>
+      <c r="LJS28" s="13"/>
+      <c r="LJT28" s="2"/>
+      <c r="LJZ28" s="16"/>
+      <c r="LKB28" s="17"/>
+      <c r="LKC28" s="17"/>
+      <c r="LKD28" s="13"/>
+      <c r="LKE28" s="2"/>
+      <c r="LKK28" s="16"/>
+      <c r="LKM28" s="17"/>
+      <c r="LKN28" s="17"/>
+      <c r="LKO28" s="13"/>
+      <c r="LKP28" s="2"/>
+      <c r="LKV28" s="16"/>
+      <c r="LKX28" s="17"/>
+      <c r="LKY28" s="17"/>
+      <c r="LKZ28" s="13"/>
+      <c r="LLA28" s="2"/>
+      <c r="LLG28" s="16"/>
+      <c r="LLI28" s="17"/>
+      <c r="LLJ28" s="17"/>
+      <c r="LLK28" s="13"/>
+      <c r="LLL28" s="2"/>
+      <c r="LLR28" s="16"/>
+      <c r="LLT28" s="17"/>
+      <c r="LLU28" s="17"/>
+      <c r="LLV28" s="13"/>
+      <c r="LLW28" s="2"/>
+      <c r="LMC28" s="16"/>
+      <c r="LME28" s="17"/>
+      <c r="LMF28" s="17"/>
+      <c r="LMG28" s="13"/>
+      <c r="LMH28" s="2"/>
+      <c r="LMN28" s="16"/>
+      <c r="LMP28" s="17"/>
+      <c r="LMQ28" s="17"/>
+      <c r="LMR28" s="13"/>
+      <c r="LMS28" s="2"/>
+      <c r="LMY28" s="16"/>
+      <c r="LNA28" s="17"/>
+      <c r="LNB28" s="17"/>
+      <c r="LNC28" s="13"/>
+      <c r="LND28" s="2"/>
+      <c r="LNJ28" s="16"/>
+      <c r="LNL28" s="17"/>
+      <c r="LNM28" s="17"/>
+      <c r="LNN28" s="13"/>
+      <c r="LNO28" s="2"/>
+      <c r="LNU28" s="16"/>
+      <c r="LNW28" s="17"/>
+      <c r="LNX28" s="17"/>
+      <c r="LNY28" s="13"/>
+      <c r="LNZ28" s="2"/>
+      <c r="LOF28" s="16"/>
+      <c r="LOH28" s="17"/>
+      <c r="LOI28" s="17"/>
+      <c r="LOJ28" s="13"/>
+      <c r="LOK28" s="2"/>
+      <c r="LOQ28" s="16"/>
+      <c r="LOS28" s="17"/>
+      <c r="LOT28" s="17"/>
+      <c r="LOU28" s="13"/>
+      <c r="LOV28" s="2"/>
+      <c r="LPB28" s="16"/>
+      <c r="LPD28" s="17"/>
+      <c r="LPE28" s="17"/>
+      <c r="LPF28" s="13"/>
+      <c r="LPG28" s="2"/>
+      <c r="LPM28" s="16"/>
+      <c r="LPO28" s="17"/>
+      <c r="LPP28" s="17"/>
+      <c r="LPQ28" s="13"/>
+      <c r="LPR28" s="2"/>
+      <c r="LPX28" s="16"/>
+      <c r="LPZ28" s="17"/>
+      <c r="LQA28" s="17"/>
+      <c r="LQB28" s="13"/>
+      <c r="LQC28" s="2"/>
+      <c r="LQI28" s="16"/>
+      <c r="LQK28" s="17"/>
+      <c r="LQL28" s="17"/>
+      <c r="LQM28" s="13"/>
+      <c r="LQN28" s="2"/>
+      <c r="LQT28" s="16"/>
+      <c r="LQV28" s="17"/>
+      <c r="LQW28" s="17"/>
+      <c r="LQX28" s="13"/>
+      <c r="LQY28" s="2"/>
+      <c r="LRE28" s="16"/>
+      <c r="LRG28" s="17"/>
+      <c r="LRH28" s="17"/>
+      <c r="LRI28" s="13"/>
+      <c r="LRJ28" s="2"/>
+      <c r="LRP28" s="16"/>
+      <c r="LRR28" s="17"/>
+      <c r="LRS28" s="17"/>
+      <c r="LRT28" s="13"/>
+      <c r="LRU28" s="2"/>
+      <c r="LSA28" s="16"/>
+      <c r="LSC28" s="17"/>
+      <c r="LSD28" s="17"/>
+      <c r="LSE28" s="13"/>
+      <c r="LSF28" s="2"/>
+      <c r="LSL28" s="16"/>
+      <c r="LSN28" s="17"/>
+      <c r="LSO28" s="17"/>
+      <c r="LSP28" s="13"/>
+      <c r="LSQ28" s="2"/>
+      <c r="LSW28" s="16"/>
+      <c r="LSY28" s="17"/>
+      <c r="LSZ28" s="17"/>
+      <c r="LTA28" s="13"/>
+      <c r="LTB28" s="2"/>
+      <c r="LTH28" s="16"/>
+      <c r="LTJ28" s="17"/>
+      <c r="LTK28" s="17"/>
+      <c r="LTL28" s="13"/>
+      <c r="LTM28" s="2"/>
+      <c r="LTS28" s="16"/>
+      <c r="LTU28" s="17"/>
+      <c r="LTV28" s="17"/>
+      <c r="LTW28" s="13"/>
+      <c r="LTX28" s="2"/>
+      <c r="LUD28" s="16"/>
+      <c r="LUF28" s="17"/>
+      <c r="LUG28" s="17"/>
+      <c r="LUH28" s="13"/>
+      <c r="LUI28" s="2"/>
+      <c r="LUO28" s="16"/>
+      <c r="LUQ28" s="17"/>
+      <c r="LUR28" s="17"/>
+      <c r="LUS28" s="13"/>
+      <c r="LUT28" s="2"/>
+      <c r="LUZ28" s="16"/>
+      <c r="LVB28" s="17"/>
+      <c r="LVC28" s="17"/>
+      <c r="LVD28" s="13"/>
+      <c r="LVE28" s="2"/>
+      <c r="LVK28" s="16"/>
+      <c r="LVM28" s="17"/>
+      <c r="LVN28" s="17"/>
+      <c r="LVO28" s="13"/>
+      <c r="LVP28" s="2"/>
+      <c r="LVV28" s="16"/>
+      <c r="LVX28" s="17"/>
+      <c r="LVY28" s="17"/>
+      <c r="LVZ28" s="13"/>
+      <c r="LWA28" s="2"/>
+      <c r="LWG28" s="16"/>
+      <c r="LWI28" s="17"/>
+      <c r="LWJ28" s="17"/>
+      <c r="LWK28" s="13"/>
+      <c r="LWL28" s="2"/>
+      <c r="LWR28" s="16"/>
+      <c r="LWT28" s="17"/>
+      <c r="LWU28" s="17"/>
+      <c r="LWV28" s="13"/>
+      <c r="LWW28" s="2"/>
+      <c r="LXC28" s="16"/>
+      <c r="LXE28" s="17"/>
+      <c r="LXF28" s="17"/>
+      <c r="LXG28" s="13"/>
+      <c r="LXH28" s="2"/>
+      <c r="LXN28" s="16"/>
+      <c r="LXP28" s="17"/>
+      <c r="LXQ28" s="17"/>
+      <c r="LXR28" s="13"/>
+      <c r="LXS28" s="2"/>
+      <c r="LXY28" s="16"/>
+      <c r="LYA28" s="17"/>
+      <c r="LYB28" s="17"/>
+      <c r="LYC28" s="13"/>
+      <c r="LYD28" s="2"/>
+      <c r="LYJ28" s="16"/>
+      <c r="LYL28" s="17"/>
+      <c r="LYM28" s="17"/>
+      <c r="LYN28" s="13"/>
+      <c r="LYO28" s="2"/>
+      <c r="LYU28" s="16"/>
+      <c r="LYW28" s="17"/>
+      <c r="LYX28" s="17"/>
+      <c r="LYY28" s="13"/>
+      <c r="LYZ28" s="2"/>
+      <c r="LZF28" s="16"/>
+      <c r="LZH28" s="17"/>
+      <c r="LZI28" s="17"/>
+      <c r="LZJ28" s="13"/>
+      <c r="LZK28" s="2"/>
+      <c r="LZQ28" s="16"/>
+      <c r="LZS28" s="17"/>
+      <c r="LZT28" s="17"/>
+      <c r="LZU28" s="13"/>
+      <c r="LZV28" s="2"/>
+      <c r="MAB28" s="16"/>
+      <c r="MAD28" s="17"/>
+      <c r="MAE28" s="17"/>
+      <c r="MAF28" s="13"/>
+      <c r="MAG28" s="2"/>
+      <c r="MAM28" s="16"/>
+      <c r="MAO28" s="17"/>
+      <c r="MAP28" s="17"/>
+      <c r="MAQ28" s="13"/>
+      <c r="MAR28" s="2"/>
+      <c r="MAX28" s="16"/>
+      <c r="MAZ28" s="17"/>
+      <c r="MBA28" s="17"/>
+      <c r="MBB28" s="13"/>
+      <c r="MBC28" s="2"/>
+      <c r="MBI28" s="16"/>
+      <c r="MBK28" s="17"/>
+      <c r="MBL28" s="17"/>
+      <c r="MBM28" s="13"/>
+      <c r="MBN28" s="2"/>
+      <c r="MBT28" s="16"/>
+      <c r="MBV28" s="17"/>
+      <c r="MBW28" s="17"/>
+      <c r="MBX28" s="13"/>
+      <c r="MBY28" s="2"/>
+      <c r="MCE28" s="16"/>
+      <c r="MCG28" s="17"/>
+      <c r="MCH28" s="17"/>
+      <c r="MCI28" s="13"/>
+      <c r="MCJ28" s="2"/>
+      <c r="MCP28" s="16"/>
+      <c r="MCR28" s="17"/>
+      <c r="MCS28" s="17"/>
+      <c r="MCT28" s="13"/>
+      <c r="MCU28" s="2"/>
+      <c r="MDA28" s="16"/>
+      <c r="MDC28" s="17"/>
+      <c r="MDD28" s="17"/>
+      <c r="MDE28" s="13"/>
+      <c r="MDF28" s="2"/>
+      <c r="MDL28" s="16"/>
+      <c r="MDN28" s="17"/>
+      <c r="MDO28" s="17"/>
+      <c r="MDP28" s="13"/>
+      <c r="MDQ28" s="2"/>
+      <c r="MDW28" s="16"/>
+      <c r="MDY28" s="17"/>
+      <c r="MDZ28" s="17"/>
+      <c r="MEA28" s="13"/>
+      <c r="MEB28" s="2"/>
+      <c r="MEH28" s="16"/>
+      <c r="MEJ28" s="17"/>
+      <c r="MEK28" s="17"/>
+      <c r="MEL28" s="13"/>
+      <c r="MEM28" s="2"/>
+      <c r="MES28" s="16"/>
+      <c r="MEU28" s="17"/>
+      <c r="MEV28" s="17"/>
+      <c r="MEW28" s="13"/>
+      <c r="MEX28" s="2"/>
+      <c r="MFD28" s="16"/>
+      <c r="MFF28" s="17"/>
+      <c r="MFG28" s="17"/>
+      <c r="MFH28" s="13"/>
+      <c r="MFI28" s="2"/>
+      <c r="MFO28" s="16"/>
+      <c r="MFQ28" s="17"/>
+      <c r="MFR28" s="17"/>
+      <c r="MFS28" s="13"/>
+      <c r="MFT28" s="2"/>
+      <c r="MFZ28" s="16"/>
+      <c r="MGB28" s="17"/>
+      <c r="MGC28" s="17"/>
+      <c r="MGD28" s="13"/>
+      <c r="MGE28" s="2"/>
+      <c r="MGK28" s="16"/>
+      <c r="MGM28" s="17"/>
+      <c r="MGN28" s="17"/>
+      <c r="MGO28" s="13"/>
+      <c r="MGP28" s="2"/>
+      <c r="MGV28" s="16"/>
+      <c r="MGX28" s="17"/>
+      <c r="MGY28" s="17"/>
+      <c r="MGZ28" s="13"/>
+      <c r="MHA28" s="2"/>
+      <c r="MHG28" s="16"/>
+      <c r="MHI28" s="17"/>
+      <c r="MHJ28" s="17"/>
+      <c r="MHK28" s="13"/>
+      <c r="MHL28" s="2"/>
+      <c r="MHR28" s="16"/>
+      <c r="MHT28" s="17"/>
+      <c r="MHU28" s="17"/>
+      <c r="MHV28" s="13"/>
+      <c r="MHW28" s="2"/>
+      <c r="MIC28" s="16"/>
+      <c r="MIE28" s="17"/>
+      <c r="MIF28" s="17"/>
+      <c r="MIG28" s="13"/>
+      <c r="MIH28" s="2"/>
+      <c r="MIN28" s="16"/>
+      <c r="MIP28" s="17"/>
+      <c r="MIQ28" s="17"/>
+      <c r="MIR28" s="13"/>
+      <c r="MIS28" s="2"/>
+      <c r="MIY28" s="16"/>
+      <c r="MJA28" s="17"/>
+      <c r="MJB28" s="17"/>
+      <c r="MJC28" s="13"/>
+      <c r="MJD28" s="2"/>
+      <c r="MJJ28" s="16"/>
+      <c r="MJL28" s="17"/>
+      <c r="MJM28" s="17"/>
+      <c r="MJN28" s="13"/>
+      <c r="MJO28" s="2"/>
+      <c r="MJU28" s="16"/>
+      <c r="MJW28" s="17"/>
+      <c r="MJX28" s="17"/>
+      <c r="MJY28" s="13"/>
+      <c r="MJZ28" s="2"/>
+      <c r="MKF28" s="16"/>
+      <c r="MKH28" s="17"/>
+      <c r="MKI28" s="17"/>
+      <c r="MKJ28" s="13"/>
+      <c r="MKK28" s="2"/>
+      <c r="MKQ28" s="16"/>
+      <c r="MKS28" s="17"/>
+      <c r="MKT28" s="17"/>
+      <c r="MKU28" s="13"/>
+      <c r="MKV28" s="2"/>
+      <c r="MLB28" s="16"/>
+      <c r="MLD28" s="17"/>
+      <c r="MLE28" s="17"/>
+      <c r="MLF28" s="13"/>
+      <c r="MLG28" s="2"/>
+      <c r="MLM28" s="16"/>
+      <c r="MLO28" s="17"/>
+      <c r="MLP28" s="17"/>
+      <c r="MLQ28" s="13"/>
+      <c r="MLR28" s="2"/>
+      <c r="MLX28" s="16"/>
+      <c r="MLZ28" s="17"/>
+      <c r="MMA28" s="17"/>
+      <c r="MMB28" s="13"/>
+      <c r="MMC28" s="2"/>
+      <c r="MMI28" s="16"/>
+      <c r="MMK28" s="17"/>
+      <c r="MML28" s="17"/>
+      <c r="MMM28" s="13"/>
+      <c r="MMN28" s="2"/>
+      <c r="MMT28" s="16"/>
+      <c r="MMV28" s="17"/>
+      <c r="MMW28" s="17"/>
+      <c r="MMX28" s="13"/>
+      <c r="MMY28" s="2"/>
+      <c r="MNE28" s="16"/>
+      <c r="MNG28" s="17"/>
+      <c r="MNH28" s="17"/>
+      <c r="MNI28" s="13"/>
+      <c r="MNJ28" s="2"/>
+      <c r="MNP28" s="16"/>
+      <c r="MNR28" s="17"/>
+      <c r="MNS28" s="17"/>
+      <c r="MNT28" s="13"/>
+      <c r="MNU28" s="2"/>
+      <c r="MOA28" s="16"/>
+      <c r="MOC28" s="17"/>
+      <c r="MOD28" s="17"/>
+      <c r="MOE28" s="13"/>
+      <c r="MOF28" s="2"/>
+      <c r="MOL28" s="16"/>
+      <c r="MON28" s="17"/>
+      <c r="MOO28" s="17"/>
+      <c r="MOP28" s="13"/>
+      <c r="MOQ28" s="2"/>
+      <c r="MOW28" s="16"/>
+      <c r="MOY28" s="17"/>
+      <c r="MOZ28" s="17"/>
+      <c r="MPA28" s="13"/>
+      <c r="MPB28" s="2"/>
+      <c r="MPH28" s="16"/>
+      <c r="MPJ28" s="17"/>
+      <c r="MPK28" s="17"/>
+      <c r="MPL28" s="13"/>
+      <c r="MPM28" s="2"/>
+      <c r="MPS28" s="16"/>
+      <c r="MPU28" s="17"/>
+      <c r="MPV28" s="17"/>
+      <c r="MPW28" s="13"/>
+      <c r="MPX28" s="2"/>
+      <c r="MQD28" s="16"/>
+      <c r="MQF28" s="17"/>
+      <c r="MQG28" s="17"/>
+      <c r="MQH28" s="13"/>
+      <c r="MQI28" s="2"/>
+      <c r="MQO28" s="16"/>
+      <c r="MQQ28" s="17"/>
+      <c r="MQR28" s="17"/>
+      <c r="MQS28" s="13"/>
+      <c r="MQT28" s="2"/>
+      <c r="MQZ28" s="16"/>
+      <c r="MRB28" s="17"/>
+      <c r="MRC28" s="17"/>
+      <c r="MRD28" s="13"/>
+      <c r="MRE28" s="2"/>
+      <c r="MRK28" s="16"/>
+      <c r="MRM28" s="17"/>
+      <c r="MRN28" s="17"/>
+      <c r="MRO28" s="13"/>
+      <c r="MRP28" s="2"/>
+      <c r="MRV28" s="16"/>
+      <c r="MRX28" s="17"/>
+      <c r="MRY28" s="17"/>
+      <c r="MRZ28" s="13"/>
+      <c r="MSA28" s="2"/>
+      <c r="MSG28" s="16"/>
+      <c r="MSI28" s="17"/>
+      <c r="MSJ28" s="17"/>
+      <c r="MSK28" s="13"/>
+      <c r="MSL28" s="2"/>
+      <c r="MSR28" s="16"/>
+      <c r="MST28" s="17"/>
+      <c r="MSU28" s="17"/>
+      <c r="MSV28" s="13"/>
+      <c r="MSW28" s="2"/>
+      <c r="MTC28" s="16"/>
+      <c r="MTE28" s="17"/>
+      <c r="MTF28" s="17"/>
+      <c r="MTG28" s="13"/>
+      <c r="MTH28" s="2"/>
+      <c r="MTN28" s="16"/>
+      <c r="MTP28" s="17"/>
+      <c r="MTQ28" s="17"/>
+      <c r="MTR28" s="13"/>
+      <c r="MTS28" s="2"/>
+      <c r="MTY28" s="16"/>
+      <c r="MUA28" s="17"/>
+      <c r="MUB28" s="17"/>
+      <c r="MUC28" s="13"/>
+      <c r="MUD28" s="2"/>
+      <c r="MUJ28" s="16"/>
+      <c r="MUL28" s="17"/>
+      <c r="MUM28" s="17"/>
+      <c r="MUN28" s="13"/>
+      <c r="MUO28" s="2"/>
+      <c r="MUU28" s="16"/>
+      <c r="MUW28" s="17"/>
+      <c r="MUX28" s="17"/>
+      <c r="MUY28" s="13"/>
+      <c r="MUZ28" s="2"/>
+      <c r="MVF28" s="16"/>
+      <c r="MVH28" s="17"/>
+      <c r="MVI28" s="17"/>
+      <c r="MVJ28" s="13"/>
+      <c r="MVK28" s="2"/>
+      <c r="MVQ28" s="16"/>
+      <c r="MVS28" s="17"/>
+      <c r="MVT28" s="17"/>
+      <c r="MVU28" s="13"/>
+      <c r="MVV28" s="2"/>
+      <c r="MWB28" s="16"/>
+      <c r="MWD28" s="17"/>
+      <c r="MWE28" s="17"/>
+      <c r="MWF28" s="13"/>
+      <c r="MWG28" s="2"/>
+      <c r="MWM28" s="16"/>
+      <c r="MWO28" s="17"/>
+      <c r="MWP28" s="17"/>
+      <c r="MWQ28" s="13"/>
+      <c r="MWR28" s="2"/>
+      <c r="MWX28" s="16"/>
+      <c r="MWZ28" s="17"/>
+      <c r="MXA28" s="17"/>
+      <c r="MXB28" s="13"/>
+      <c r="MXC28" s="2"/>
+      <c r="MXI28" s="16"/>
+      <c r="MXK28" s="17"/>
+      <c r="MXL28" s="17"/>
+      <c r="MXM28" s="13"/>
+      <c r="MXN28" s="2"/>
+      <c r="MXT28" s="16"/>
+      <c r="MXV28" s="17"/>
+      <c r="MXW28" s="17"/>
+      <c r="MXX28" s="13"/>
+      <c r="MXY28" s="2"/>
+      <c r="MYE28" s="16"/>
+      <c r="MYG28" s="17"/>
+      <c r="MYH28" s="17"/>
+      <c r="MYI28" s="13"/>
+      <c r="MYJ28" s="2"/>
+      <c r="MYP28" s="16"/>
+      <c r="MYR28" s="17"/>
+      <c r="MYS28" s="17"/>
+      <c r="MYT28" s="13"/>
+      <c r="MYU28" s="2"/>
+      <c r="MZA28" s="16"/>
+      <c r="MZC28" s="17"/>
+      <c r="MZD28" s="17"/>
+      <c r="MZE28" s="13"/>
+      <c r="MZF28" s="2"/>
+      <c r="MZL28" s="16"/>
+      <c r="MZN28" s="17"/>
+      <c r="MZO28" s="17"/>
+      <c r="MZP28" s="13"/>
+      <c r="MZQ28" s="2"/>
+      <c r="MZW28" s="16"/>
+      <c r="MZY28" s="17"/>
+      <c r="MZZ28" s="17"/>
+      <c r="NAA28" s="13"/>
+      <c r="NAB28" s="2"/>
+      <c r="NAH28" s="16"/>
+      <c r="NAJ28" s="17"/>
+      <c r="NAK28" s="17"/>
+      <c r="NAL28" s="13"/>
+      <c r="NAM28" s="2"/>
+      <c r="NAS28" s="16"/>
+      <c r="NAU28" s="17"/>
+      <c r="NAV28" s="17"/>
+      <c r="NAW28" s="13"/>
+      <c r="NAX28" s="2"/>
+      <c r="NBD28" s="16"/>
+      <c r="NBF28" s="17"/>
+      <c r="NBG28" s="17"/>
+      <c r="NBH28" s="13"/>
+      <c r="NBI28" s="2"/>
+      <c r="NBO28" s="16"/>
+      <c r="NBQ28" s="17"/>
+      <c r="NBR28" s="17"/>
+      <c r="NBS28" s="13"/>
+      <c r="NBT28" s="2"/>
+      <c r="NBZ28" s="16"/>
+      <c r="NCB28" s="17"/>
+      <c r="NCC28" s="17"/>
+      <c r="NCD28" s="13"/>
+      <c r="NCE28" s="2"/>
+      <c r="NCK28" s="16"/>
+      <c r="NCM28" s="17"/>
+      <c r="NCN28" s="17"/>
+      <c r="NCO28" s="13"/>
+      <c r="NCP28" s="2"/>
+      <c r="NCV28" s="16"/>
+      <c r="NCX28" s="17"/>
+      <c r="NCY28" s="17"/>
+      <c r="NCZ28" s="13"/>
+      <c r="NDA28" s="2"/>
+      <c r="NDG28" s="16"/>
+      <c r="NDI28" s="17"/>
+      <c r="NDJ28" s="17"/>
+      <c r="NDK28" s="13"/>
+      <c r="NDL28" s="2"/>
+      <c r="NDR28" s="16"/>
+      <c r="NDT28" s="17"/>
+      <c r="NDU28" s="17"/>
+      <c r="NDV28" s="13"/>
+      <c r="NDW28" s="2"/>
+      <c r="NEC28" s="16"/>
+      <c r="NEE28" s="17"/>
+      <c r="NEF28" s="17"/>
+      <c r="NEG28" s="13"/>
+      <c r="NEH28" s="2"/>
+      <c r="NEN28" s="16"/>
+      <c r="NEP28" s="17"/>
+      <c r="NEQ28" s="17"/>
+      <c r="NER28" s="13"/>
+      <c r="NES28" s="2"/>
+      <c r="NEY28" s="16"/>
+      <c r="NFA28" s="17"/>
+      <c r="NFB28" s="17"/>
+      <c r="NFC28" s="13"/>
+      <c r="NFD28" s="2"/>
+      <c r="NFJ28" s="16"/>
+      <c r="NFL28" s="17"/>
+      <c r="NFM28" s="17"/>
+      <c r="NFN28" s="13"/>
+      <c r="NFO28" s="2"/>
+      <c r="NFU28" s="16"/>
+      <c r="NFW28" s="17"/>
+      <c r="NFX28" s="17"/>
+      <c r="NFY28" s="13"/>
+      <c r="NFZ28" s="2"/>
+      <c r="NGF28" s="16"/>
+      <c r="NGH28" s="17"/>
+      <c r="NGI28" s="17"/>
+      <c r="NGJ28" s="13"/>
+      <c r="NGK28" s="2"/>
+      <c r="NGQ28" s="16"/>
+      <c r="NGS28" s="17"/>
+      <c r="NGT28" s="17"/>
+      <c r="NGU28" s="13"/>
+      <c r="NGV28" s="2"/>
+      <c r="NHB28" s="16"/>
+      <c r="NHD28" s="17"/>
+      <c r="NHE28" s="17"/>
+      <c r="NHF28" s="13"/>
+      <c r="NHG28" s="2"/>
+      <c r="NHM28" s="16"/>
+      <c r="NHO28" s="17"/>
+      <c r="NHP28" s="17"/>
+      <c r="NHQ28" s="13"/>
+      <c r="NHR28" s="2"/>
+      <c r="NHX28" s="16"/>
+      <c r="NHZ28" s="17"/>
+      <c r="NIA28" s="17"/>
+      <c r="NIB28" s="13"/>
+      <c r="NIC28" s="2"/>
+      <c r="NII28" s="16"/>
+      <c r="NIK28" s="17"/>
+      <c r="NIL28" s="17"/>
+      <c r="NIM28" s="13"/>
+      <c r="NIN28" s="2"/>
+      <c r="NIT28" s="16"/>
+      <c r="NIV28" s="17"/>
+      <c r="NIW28" s="17"/>
+      <c r="NIX28" s="13"/>
+      <c r="NIY28" s="2"/>
+      <c r="NJE28" s="16"/>
+      <c r="NJG28" s="17"/>
+      <c r="NJH28" s="17"/>
+      <c r="NJI28" s="13"/>
+      <c r="NJJ28" s="2"/>
+      <c r="NJP28" s="16"/>
+      <c r="NJR28" s="17"/>
+      <c r="NJS28" s="17"/>
+      <c r="NJT28" s="13"/>
+      <c r="NJU28" s="2"/>
+      <c r="NKA28" s="16"/>
+      <c r="NKC28" s="17"/>
+      <c r="NKD28" s="17"/>
+      <c r="NKE28" s="13"/>
+      <c r="NKF28" s="2"/>
+      <c r="NKL28" s="16"/>
+      <c r="NKN28" s="17"/>
+      <c r="NKO28" s="17"/>
+      <c r="NKP28" s="13"/>
+      <c r="NKQ28" s="2"/>
+      <c r="NKW28" s="16"/>
+      <c r="NKY28" s="17"/>
+      <c r="NKZ28" s="17"/>
+      <c r="NLA28" s="13"/>
+      <c r="NLB28" s="2"/>
+      <c r="NLH28" s="16"/>
+      <c r="NLJ28" s="17"/>
+      <c r="NLK28" s="17"/>
+      <c r="NLL28" s="13"/>
+      <c r="NLM28" s="2"/>
+      <c r="NLS28" s="16"/>
+      <c r="NLU28" s="17"/>
+      <c r="NLV28" s="17"/>
+      <c r="NLW28" s="13"/>
+      <c r="NLX28" s="2"/>
+      <c r="NMD28" s="16"/>
+      <c r="NMF28" s="17"/>
+      <c r="NMG28" s="17"/>
+      <c r="NMH28" s="13"/>
+      <c r="NMI28" s="2"/>
+      <c r="NMO28" s="16"/>
+      <c r="NMQ28" s="17"/>
+      <c r="NMR28" s="17"/>
+      <c r="NMS28" s="13"/>
+      <c r="NMT28" s="2"/>
+      <c r="NMZ28" s="16"/>
+      <c r="NNB28" s="17"/>
+      <c r="NNC28" s="17"/>
+      <c r="NND28" s="13"/>
+      <c r="NNE28" s="2"/>
+      <c r="NNK28" s="16"/>
+      <c r="NNM28" s="17"/>
+      <c r="NNN28" s="17"/>
+      <c r="NNO28" s="13"/>
+      <c r="NNP28" s="2"/>
+      <c r="NNV28" s="16"/>
+      <c r="NNX28" s="17"/>
+      <c r="NNY28" s="17"/>
+      <c r="NNZ28" s="13"/>
+      <c r="NOA28" s="2"/>
+      <c r="NOG28" s="16"/>
+      <c r="NOI28" s="17"/>
+      <c r="NOJ28" s="17"/>
+      <c r="NOK28" s="13"/>
+      <c r="NOL28" s="2"/>
+      <c r="NOR28" s="16"/>
+      <c r="NOT28" s="17"/>
+      <c r="NOU28" s="17"/>
+      <c r="NOV28" s="13"/>
+      <c r="NOW28" s="2"/>
+      <c r="NPC28" s="16"/>
+      <c r="NPE28" s="17"/>
+      <c r="NPF28" s="17"/>
+      <c r="NPG28" s="13"/>
+      <c r="NPH28" s="2"/>
+      <c r="NPN28" s="16"/>
+      <c r="NPP28" s="17"/>
+      <c r="NPQ28" s="17"/>
+      <c r="NPR28" s="13"/>
+      <c r="NPS28" s="2"/>
+      <c r="NPY28" s="16"/>
+      <c r="NQA28" s="17"/>
+      <c r="NQB28" s="17"/>
+      <c r="NQC28" s="13"/>
+      <c r="NQD28" s="2"/>
+      <c r="NQJ28" s="16"/>
+      <c r="NQL28" s="17"/>
+      <c r="NQM28" s="17"/>
+      <c r="NQN28" s="13"/>
+      <c r="NQO28" s="2"/>
+      <c r="NQU28" s="16"/>
+      <c r="NQW28" s="17"/>
+      <c r="NQX28" s="17"/>
+      <c r="NQY28" s="13"/>
+      <c r="NQZ28" s="2"/>
+      <c r="NRF28" s="16"/>
+      <c r="NRH28" s="17"/>
+      <c r="NRI28" s="17"/>
+      <c r="NRJ28" s="13"/>
+      <c r="NRK28" s="2"/>
+      <c r="NRQ28" s="16"/>
+      <c r="NRS28" s="17"/>
+      <c r="NRT28" s="17"/>
+      <c r="NRU28" s="13"/>
+      <c r="NRV28" s="2"/>
+      <c r="NSB28" s="16"/>
+      <c r="NSD28" s="17"/>
+      <c r="NSE28" s="17"/>
+      <c r="NSF28" s="13"/>
+      <c r="NSG28" s="2"/>
+      <c r="NSM28" s="16"/>
+      <c r="NSO28" s="17"/>
+      <c r="NSP28" s="17"/>
+      <c r="NSQ28" s="13"/>
+      <c r="NSR28" s="2"/>
+      <c r="NSX28" s="16"/>
+      <c r="NSZ28" s="17"/>
+      <c r="NTA28" s="17"/>
+      <c r="NTB28" s="13"/>
+      <c r="NTC28" s="2"/>
+      <c r="NTI28" s="16"/>
+      <c r="NTK28" s="17"/>
+      <c r="NTL28" s="17"/>
+      <c r="NTM28" s="13"/>
+      <c r="NTN28" s="2"/>
+      <c r="NTT28" s="16"/>
+      <c r="NTV28" s="17"/>
+      <c r="NTW28" s="17"/>
+      <c r="NTX28" s="13"/>
+      <c r="NTY28" s="2"/>
+      <c r="NUE28" s="16"/>
+      <c r="NUG28" s="17"/>
+      <c r="NUH28" s="17"/>
+      <c r="NUI28" s="13"/>
+      <c r="NUJ28" s="2"/>
+      <c r="NUP28" s="16"/>
+      <c r="NUR28" s="17"/>
+      <c r="NUS28" s="17"/>
+      <c r="NUT28" s="13"/>
+      <c r="NUU28" s="2"/>
+      <c r="NVA28" s="16"/>
+      <c r="NVC28" s="17"/>
+      <c r="NVD28" s="17"/>
+      <c r="NVE28" s="13"/>
+      <c r="NVF28" s="2"/>
+      <c r="NVL28" s="16"/>
+      <c r="NVN28" s="17"/>
+      <c r="NVO28" s="17"/>
+      <c r="NVP28" s="13"/>
+      <c r="NVQ28" s="2"/>
+      <c r="NVW28" s="16"/>
+      <c r="NVY28" s="17"/>
+      <c r="NVZ28" s="17"/>
+      <c r="NWA28" s="13"/>
+      <c r="NWB28" s="2"/>
+      <c r="NWH28" s="16"/>
+      <c r="NWJ28" s="17"/>
+      <c r="NWK28" s="17"/>
+      <c r="NWL28" s="13"/>
+      <c r="NWM28" s="2"/>
+      <c r="NWS28" s="16"/>
+      <c r="NWU28" s="17"/>
+      <c r="NWV28" s="17"/>
+      <c r="NWW28" s="13"/>
+      <c r="NWX28" s="2"/>
+      <c r="NXD28" s="16"/>
+      <c r="NXF28" s="17"/>
+      <c r="NXG28" s="17"/>
+      <c r="NXH28" s="13"/>
+      <c r="NXI28" s="2"/>
+      <c r="NXO28" s="16"/>
+      <c r="NXQ28" s="17"/>
+      <c r="NXR28" s="17"/>
+      <c r="NXS28" s="13"/>
+      <c r="NXT28" s="2"/>
+      <c r="NXZ28" s="16"/>
+      <c r="NYB28" s="17"/>
+      <c r="NYC28" s="17"/>
+      <c r="NYD28" s="13"/>
+      <c r="NYE28" s="2"/>
+      <c r="NYK28" s="16"/>
+      <c r="NYM28" s="17"/>
+      <c r="NYN28" s="17"/>
+      <c r="NYO28" s="13"/>
+      <c r="NYP28" s="2"/>
+      <c r="NYV28" s="16"/>
+      <c r="NYX28" s="17"/>
+      <c r="NYY28" s="17"/>
+      <c r="NYZ28" s="13"/>
+      <c r="NZA28" s="2"/>
+      <c r="NZG28" s="16"/>
+      <c r="NZI28" s="17"/>
+      <c r="NZJ28" s="17"/>
+      <c r="NZK28" s="13"/>
+      <c r="NZL28" s="2"/>
+      <c r="NZR28" s="16"/>
+      <c r="NZT28" s="17"/>
+      <c r="NZU28" s="17"/>
+      <c r="NZV28" s="13"/>
+      <c r="NZW28" s="2"/>
+      <c r="OAC28" s="16"/>
+      <c r="OAE28" s="17"/>
+      <c r="OAF28" s="17"/>
+      <c r="OAG28" s="13"/>
+      <c r="OAH28" s="2"/>
+      <c r="OAN28" s="16"/>
+      <c r="OAP28" s="17"/>
+      <c r="OAQ28" s="17"/>
+      <c r="OAR28" s="13"/>
+      <c r="OAS28" s="2"/>
+      <c r="OAY28" s="16"/>
+      <c r="OBA28" s="17"/>
+      <c r="OBB28" s="17"/>
+      <c r="OBC28" s="13"/>
+      <c r="OBD28" s="2"/>
+      <c r="OBJ28" s="16"/>
+      <c r="OBL28" s="17"/>
+      <c r="OBM28" s="17"/>
+      <c r="OBN28" s="13"/>
+      <c r="OBO28" s="2"/>
+      <c r="OBU28" s="16"/>
+      <c r="OBW28" s="17"/>
+      <c r="OBX28" s="17"/>
+      <c r="OBY28" s="13"/>
+      <c r="OBZ28" s="2"/>
+      <c r="OCF28" s="16"/>
+      <c r="OCH28" s="17"/>
+      <c r="OCI28" s="17"/>
+      <c r="OCJ28" s="13"/>
+      <c r="OCK28" s="2"/>
+      <c r="OCQ28" s="16"/>
+      <c r="OCS28" s="17"/>
+      <c r="OCT28" s="17"/>
+      <c r="OCU28" s="13"/>
+      <c r="OCV28" s="2"/>
+      <c r="ODB28" s="16"/>
+      <c r="ODD28" s="17"/>
+      <c r="ODE28" s="17"/>
+      <c r="ODF28" s="13"/>
+      <c r="ODG28" s="2"/>
+      <c r="ODM28" s="16"/>
+      <c r="ODO28" s="17"/>
+      <c r="ODP28" s="17"/>
+      <c r="ODQ28" s="13"/>
+      <c r="ODR28" s="2"/>
+      <c r="ODX28" s="16"/>
+      <c r="ODZ28" s="17"/>
+      <c r="OEA28" s="17"/>
+      <c r="OEB28" s="13"/>
+      <c r="OEC28" s="2"/>
+      <c r="OEI28" s="16"/>
+      <c r="OEK28" s="17"/>
+      <c r="OEL28" s="17"/>
+      <c r="OEM28" s="13"/>
+      <c r="OEN28" s="2"/>
+      <c r="OET28" s="16"/>
+      <c r="OEV28" s="17"/>
+      <c r="OEW28" s="17"/>
+      <c r="OEX28" s="13"/>
+      <c r="OEY28" s="2"/>
+      <c r="OFE28" s="16"/>
+      <c r="OFG28" s="17"/>
+      <c r="OFH28" s="17"/>
+      <c r="OFI28" s="13"/>
+      <c r="OFJ28" s="2"/>
+      <c r="OFP28" s="16"/>
+      <c r="OFR28" s="17"/>
+      <c r="OFS28" s="17"/>
+      <c r="OFT28" s="13"/>
+      <c r="OFU28" s="2"/>
+      <c r="OGA28" s="16"/>
+      <c r="OGC28" s="17"/>
+      <c r="OGD28" s="17"/>
+      <c r="OGE28" s="13"/>
+      <c r="OGF28" s="2"/>
+      <c r="OGL28" s="16"/>
+      <c r="OGN28" s="17"/>
+      <c r="OGO28" s="17"/>
+      <c r="OGP28" s="13"/>
+      <c r="OGQ28" s="2"/>
+      <c r="OGW28" s="16"/>
+      <c r="OGY28" s="17"/>
+      <c r="OGZ28" s="17"/>
+      <c r="OHA28" s="13"/>
+      <c r="OHB28" s="2"/>
+      <c r="OHH28" s="16"/>
+      <c r="OHJ28" s="17"/>
+      <c r="OHK28" s="17"/>
+      <c r="OHL28" s="13"/>
+      <c r="OHM28" s="2"/>
+      <c r="OHS28" s="16"/>
+      <c r="OHU28" s="17"/>
+      <c r="OHV28" s="17"/>
+      <c r="OHW28" s="13"/>
+      <c r="OHX28" s="2"/>
+      <c r="OID28" s="16"/>
+      <c r="OIF28" s="17"/>
+      <c r="OIG28" s="17"/>
+      <c r="OIH28" s="13"/>
+      <c r="OII28" s="2"/>
+      <c r="OIO28" s="16"/>
+      <c r="OIQ28" s="17"/>
+      <c r="OIR28" s="17"/>
+      <c r="OIS28" s="13"/>
+      <c r="OIT28" s="2"/>
+      <c r="OIZ28" s="16"/>
+      <c r="OJB28" s="17"/>
+      <c r="OJC28" s="17"/>
+      <c r="OJD28" s="13"/>
+      <c r="OJE28" s="2"/>
+      <c r="OJK28" s="16"/>
+      <c r="OJM28" s="17"/>
+      <c r="OJN28" s="17"/>
+      <c r="OJO28" s="13"/>
+      <c r="OJP28" s="2"/>
+      <c r="OJV28" s="16"/>
+      <c r="OJX28" s="17"/>
+      <c r="OJY28" s="17"/>
+      <c r="OJZ28" s="13"/>
+      <c r="OKA28" s="2"/>
+      <c r="OKG28" s="16"/>
+      <c r="OKI28" s="17"/>
+      <c r="OKJ28" s="17"/>
+      <c r="OKK28" s="13"/>
+      <c r="OKL28" s="2"/>
+      <c r="OKR28" s="16"/>
+      <c r="OKT28" s="17"/>
+      <c r="OKU28" s="17"/>
+      <c r="OKV28" s="13"/>
+      <c r="OKW28" s="2"/>
+      <c r="OLC28" s="16"/>
+      <c r="OLE28" s="17"/>
+      <c r="OLF28" s="17"/>
+      <c r="OLG28" s="13"/>
+      <c r="OLH28" s="2"/>
+      <c r="OLN28" s="16"/>
+      <c r="OLP28" s="17"/>
+      <c r="OLQ28" s="17"/>
+      <c r="OLR28" s="13"/>
+      <c r="OLS28" s="2"/>
+      <c r="OLY28" s="16"/>
+      <c r="OMA28" s="17"/>
+      <c r="OMB28" s="17"/>
+      <c r="OMC28" s="13"/>
+      <c r="OMD28" s="2"/>
+      <c r="OMJ28" s="16"/>
+      <c r="OML28" s="17"/>
+      <c r="OMM28" s="17"/>
+      <c r="OMN28" s="13"/>
+      <c r="OMO28" s="2"/>
+      <c r="OMU28" s="16"/>
+      <c r="OMW28" s="17"/>
+      <c r="OMX28" s="17"/>
+      <c r="OMY28" s="13"/>
+      <c r="OMZ28" s="2"/>
+      <c r="ONF28" s="16"/>
+      <c r="ONH28" s="17"/>
+      <c r="ONI28" s="17"/>
+      <c r="ONJ28" s="13"/>
+      <c r="ONK28" s="2"/>
+      <c r="ONQ28" s="16"/>
+      <c r="ONS28" s="17"/>
+      <c r="ONT28" s="17"/>
+      <c r="ONU28" s="13"/>
+      <c r="ONV28" s="2"/>
+      <c r="OOB28" s="16"/>
+      <c r="OOD28" s="17"/>
+      <c r="OOE28" s="17"/>
+      <c r="OOF28" s="13"/>
+      <c r="OOG28" s="2"/>
+      <c r="OOM28" s="16"/>
+      <c r="OOO28" s="17"/>
+      <c r="OOP28" s="17"/>
+      <c r="OOQ28" s="13"/>
+      <c r="OOR28" s="2"/>
+      <c r="OOX28" s="16"/>
+      <c r="OOZ28" s="17"/>
+      <c r="OPA28" s="17"/>
+      <c r="OPB28" s="13"/>
+      <c r="OPC28" s="2"/>
+      <c r="OPI28" s="16"/>
+      <c r="OPK28" s="17"/>
+      <c r="OPL28" s="17"/>
+      <c r="OPM28" s="13"/>
+      <c r="OPN28" s="2"/>
+      <c r="OPT28" s="16"/>
+      <c r="OPV28" s="17"/>
+      <c r="OPW28" s="17"/>
+      <c r="OPX28" s="13"/>
+      <c r="OPY28" s="2"/>
+      <c r="OQE28" s="16"/>
+      <c r="OQG28" s="17"/>
+      <c r="OQH28" s="17"/>
+      <c r="OQI28" s="13"/>
+      <c r="OQJ28" s="2"/>
+      <c r="OQP28" s="16"/>
+      <c r="OQR28" s="17"/>
+      <c r="OQS28" s="17"/>
+      <c r="OQT28" s="13"/>
+      <c r="OQU28" s="2"/>
+      <c r="ORA28" s="16"/>
+      <c r="ORC28" s="17"/>
+      <c r="ORD28" s="17"/>
+      <c r="ORE28" s="13"/>
+      <c r="ORF28" s="2"/>
+      <c r="ORL28" s="16"/>
+      <c r="ORN28" s="17"/>
+      <c r="ORO28" s="17"/>
+      <c r="ORP28" s="13"/>
+      <c r="ORQ28" s="2"/>
+      <c r="ORW28" s="16"/>
+      <c r="ORY28" s="17"/>
+      <c r="ORZ28" s="17"/>
+      <c r="OSA28" s="13"/>
+      <c r="OSB28" s="2"/>
+      <c r="OSH28" s="16"/>
+      <c r="OSJ28" s="17"/>
+      <c r="OSK28" s="17"/>
+      <c r="OSL28" s="13"/>
+      <c r="OSM28" s="2"/>
+      <c r="OSS28" s="16"/>
+      <c r="OSU28" s="17"/>
+      <c r="OSV28" s="17"/>
+      <c r="OSW28" s="13"/>
+      <c r="OSX28" s="2"/>
+      <c r="OTD28" s="16"/>
+      <c r="OTF28" s="17"/>
+      <c r="OTG28" s="17"/>
+      <c r="OTH28" s="13"/>
+      <c r="OTI28" s="2"/>
+      <c r="OTO28" s="16"/>
+      <c r="OTQ28" s="17"/>
+      <c r="OTR28" s="17"/>
+      <c r="OTS28" s="13"/>
+      <c r="OTT28" s="2"/>
+      <c r="OTZ28" s="16"/>
+      <c r="OUB28" s="17"/>
+      <c r="OUC28" s="17"/>
+      <c r="OUD28" s="13"/>
+      <c r="OUE28" s="2"/>
+      <c r="OUK28" s="16"/>
+      <c r="OUM28" s="17"/>
+      <c r="OUN28" s="17"/>
+      <c r="OUO28" s="13"/>
+      <c r="OUP28" s="2"/>
+      <c r="OUV28" s="16"/>
+      <c r="OUX28" s="17"/>
+      <c r="OUY28" s="17"/>
+      <c r="OUZ28" s="13"/>
+      <c r="OVA28" s="2"/>
+      <c r="OVG28" s="16"/>
+      <c r="OVI28" s="17"/>
+      <c r="OVJ28" s="17"/>
+      <c r="OVK28" s="13"/>
+      <c r="OVL28" s="2"/>
+      <c r="OVR28" s="16"/>
+      <c r="OVT28" s="17"/>
+      <c r="OVU28" s="17"/>
+      <c r="OVV28" s="13"/>
+      <c r="OVW28" s="2"/>
+      <c r="OWC28" s="16"/>
+      <c r="OWE28" s="17"/>
+      <c r="OWF28" s="17"/>
+      <c r="OWG28" s="13"/>
+      <c r="OWH28" s="2"/>
+      <c r="OWN28" s="16"/>
+      <c r="OWP28" s="17"/>
+      <c r="OWQ28" s="17"/>
+      <c r="OWR28" s="13"/>
+      <c r="OWS28" s="2"/>
+      <c r="OWY28" s="16"/>
+      <c r="OXA28" s="17"/>
+      <c r="OXB28" s="17"/>
+      <c r="OXC28" s="13"/>
+      <c r="OXD28" s="2"/>
+      <c r="OXJ28" s="16"/>
+      <c r="OXL28" s="17"/>
+      <c r="OXM28" s="17"/>
+      <c r="OXN28" s="13"/>
+      <c r="OXO28" s="2"/>
+      <c r="OXU28" s="16"/>
+      <c r="OXW28" s="17"/>
+      <c r="OXX28" s="17"/>
+      <c r="OXY28" s="13"/>
+      <c r="OXZ28" s="2"/>
+      <c r="OYF28" s="16"/>
+      <c r="OYH28" s="17"/>
+      <c r="OYI28" s="17"/>
+      <c r="OYJ28" s="13"/>
+      <c r="OYK28" s="2"/>
+      <c r="OYQ28" s="16"/>
+      <c r="OYS28" s="17"/>
+      <c r="OYT28" s="17"/>
+      <c r="OYU28" s="13"/>
+      <c r="OYV28" s="2"/>
+      <c r="OZB28" s="16"/>
+      <c r="OZD28" s="17"/>
+      <c r="OZE28" s="17"/>
+      <c r="OZF28" s="13"/>
+      <c r="OZG28" s="2"/>
+      <c r="OZM28" s="16"/>
+      <c r="OZO28" s="17"/>
+      <c r="OZP28" s="17"/>
+      <c r="OZQ28" s="13"/>
+      <c r="OZR28" s="2"/>
+      <c r="OZX28" s="16"/>
+      <c r="OZZ28" s="17"/>
+      <c r="PAA28" s="17"/>
+      <c r="PAB28" s="13"/>
+      <c r="PAC28" s="2"/>
+      <c r="PAI28" s="16"/>
+      <c r="PAK28" s="17"/>
+      <c r="PAL28" s="17"/>
+      <c r="PAM28" s="13"/>
+      <c r="PAN28" s="2"/>
+      <c r="PAT28" s="16"/>
+      <c r="PAV28" s="17"/>
+      <c r="PAW28" s="17"/>
+      <c r="PAX28" s="13"/>
+      <c r="PAY28" s="2"/>
+      <c r="PBE28" s="16"/>
+      <c r="PBG28" s="17"/>
+      <c r="PBH28" s="17"/>
+      <c r="PBI28" s="13"/>
+      <c r="PBJ28" s="2"/>
+      <c r="PBP28" s="16"/>
+      <c r="PBR28" s="17"/>
+      <c r="PBS28" s="17"/>
+      <c r="PBT28" s="13"/>
+      <c r="PBU28" s="2"/>
+      <c r="PCA28" s="16"/>
+      <c r="PCC28" s="17"/>
+      <c r="PCD28" s="17"/>
+      <c r="PCE28" s="13"/>
+      <c r="PCF28" s="2"/>
+      <c r="PCL28" s="16"/>
+      <c r="PCN28" s="17"/>
+      <c r="PCO28" s="17"/>
+      <c r="PCP28" s="13"/>
+      <c r="PCQ28" s="2"/>
+      <c r="PCW28" s="16"/>
+      <c r="PCY28" s="17"/>
+      <c r="PCZ28" s="17"/>
+      <c r="PDA28" s="13"/>
+      <c r="PDB28" s="2"/>
+      <c r="PDH28" s="16"/>
+      <c r="PDJ28" s="17"/>
+      <c r="PDK28" s="17"/>
+      <c r="PDL28" s="13"/>
+      <c r="PDM28" s="2"/>
+      <c r="PDS28" s="16"/>
+      <c r="PDU28" s="17"/>
+      <c r="PDV28" s="17"/>
+      <c r="PDW28" s="13"/>
+      <c r="PDX28" s="2"/>
+      <c r="PED28" s="16"/>
+      <c r="PEF28" s="17"/>
+      <c r="PEG28" s="17"/>
+      <c r="PEH28" s="13"/>
+      <c r="PEI28" s="2"/>
+      <c r="PEO28" s="16"/>
+      <c r="PEQ28" s="17"/>
+      <c r="PER28" s="17"/>
+      <c r="PES28" s="13"/>
+      <c r="PET28" s="2"/>
+      <c r="PEZ28" s="16"/>
+      <c r="PFB28" s="17"/>
+      <c r="PFC28" s="17"/>
+      <c r="PFD28" s="13"/>
+      <c r="PFE28" s="2"/>
+      <c r="PFK28" s="16"/>
+      <c r="PFM28" s="17"/>
+      <c r="PFN28" s="17"/>
+      <c r="PFO28" s="13"/>
+      <c r="PFP28" s="2"/>
+      <c r="PFV28" s="16"/>
+      <c r="PFX28" s="17"/>
+      <c r="PFY28" s="17"/>
+      <c r="PFZ28" s="13"/>
+      <c r="PGA28" s="2"/>
+      <c r="PGG28" s="16"/>
+      <c r="PGI28" s="17"/>
+      <c r="PGJ28" s="17"/>
+      <c r="PGK28" s="13"/>
+      <c r="PGL28" s="2"/>
+      <c r="PGR28" s="16"/>
+      <c r="PGT28" s="17"/>
+      <c r="PGU28" s="17"/>
+      <c r="PGV28" s="13"/>
+      <c r="PGW28" s="2"/>
+      <c r="PHC28" s="16"/>
+      <c r="PHE28" s="17"/>
+      <c r="PHF28" s="17"/>
+      <c r="PHG28" s="13"/>
+      <c r="PHH28" s="2"/>
+      <c r="PHN28" s="16"/>
+      <c r="PHP28" s="17"/>
+      <c r="PHQ28" s="17"/>
+      <c r="PHR28" s="13"/>
+      <c r="PHS28" s="2"/>
+      <c r="PHY28" s="16"/>
+      <c r="PIA28" s="17"/>
+      <c r="PIB28" s="17"/>
+      <c r="PIC28" s="13"/>
+      <c r="PID28" s="2"/>
+      <c r="PIJ28" s="16"/>
+      <c r="PIL28" s="17"/>
+      <c r="PIM28" s="17"/>
+      <c r="PIN28" s="13"/>
+      <c r="PIO28" s="2"/>
+      <c r="PIU28" s="16"/>
+      <c r="PIW28" s="17"/>
+      <c r="PIX28" s="17"/>
+      <c r="PIY28" s="13"/>
+      <c r="PIZ28" s="2"/>
+      <c r="PJF28" s="16"/>
+      <c r="PJH28" s="17"/>
+      <c r="PJI28" s="17"/>
+      <c r="PJJ28" s="13"/>
+      <c r="PJK28" s="2"/>
+      <c r="PJQ28" s="16"/>
+      <c r="PJS28" s="17"/>
+      <c r="PJT28" s="17"/>
+      <c r="PJU28" s="13"/>
+      <c r="PJV28" s="2"/>
+      <c r="PKB28" s="16"/>
+      <c r="PKD28" s="17"/>
+      <c r="PKE28" s="17"/>
+      <c r="PKF28" s="13"/>
+      <c r="PKG28" s="2"/>
+      <c r="PKM28" s="16"/>
+      <c r="PKO28" s="17"/>
+      <c r="PKP28" s="17"/>
+      <c r="PKQ28" s="13"/>
+      <c r="PKR28" s="2"/>
+      <c r="PKX28" s="16"/>
+      <c r="PKZ28" s="17"/>
+      <c r="PLA28" s="17"/>
+      <c r="PLB28" s="13"/>
+      <c r="PLC28" s="2"/>
+      <c r="PLI28" s="16"/>
+      <c r="PLK28" s="17"/>
+      <c r="PLL28" s="17"/>
+      <c r="PLM28" s="13"/>
+      <c r="PLN28" s="2"/>
+      <c r="PLT28" s="16"/>
+      <c r="PLV28" s="17"/>
+      <c r="PLW28" s="17"/>
+      <c r="PLX28" s="13"/>
+      <c r="PLY28" s="2"/>
+      <c r="PME28" s="16"/>
+      <c r="PMG28" s="17"/>
+      <c r="PMH28" s="17"/>
+      <c r="PMI28" s="13"/>
+      <c r="PMJ28" s="2"/>
+      <c r="PMP28" s="16"/>
+      <c r="PMR28" s="17"/>
+      <c r="PMS28" s="17"/>
+      <c r="PMT28" s="13"/>
+      <c r="PMU28" s="2"/>
+      <c r="PNA28" s="16"/>
+      <c r="PNC28" s="17"/>
+      <c r="PND28" s="17"/>
+      <c r="PNE28" s="13"/>
+      <c r="PNF28" s="2"/>
+      <c r="PNL28" s="16"/>
+      <c r="PNN28" s="17"/>
+      <c r="PNO28" s="17"/>
+      <c r="PNP28" s="13"/>
+      <c r="PNQ28" s="2"/>
+      <c r="PNW28" s="16"/>
+      <c r="PNY28" s="17"/>
+      <c r="PNZ28" s="17"/>
+      <c r="POA28" s="13"/>
+      <c r="POB28" s="2"/>
+      <c r="POH28" s="16"/>
+      <c r="POJ28" s="17"/>
+      <c r="POK28" s="17"/>
+      <c r="POL28" s="13"/>
+      <c r="POM28" s="2"/>
+      <c r="POS28" s="16"/>
+      <c r="POU28" s="17"/>
+      <c r="POV28" s="17"/>
+      <c r="POW28" s="13"/>
+      <c r="POX28" s="2"/>
+      <c r="PPD28" s="16"/>
+      <c r="PPF28" s="17"/>
+      <c r="PPG28" s="17"/>
+      <c r="PPH28" s="13"/>
+      <c r="PPI28" s="2"/>
+      <c r="PPO28" s="16"/>
+      <c r="PPQ28" s="17"/>
+      <c r="PPR28" s="17"/>
+      <c r="PPS28" s="13"/>
+      <c r="PPT28" s="2"/>
+      <c r="PPZ28" s="16"/>
+      <c r="PQB28" s="17"/>
+      <c r="PQC28" s="17"/>
+      <c r="PQD28" s="13"/>
+      <c r="PQE28" s="2"/>
+      <c r="PQK28" s="16"/>
+      <c r="PQM28" s="17"/>
+      <c r="PQN28" s="17"/>
+      <c r="PQO28" s="13"/>
+      <c r="PQP28" s="2"/>
+      <c r="PQV28" s="16"/>
+      <c r="PQX28" s="17"/>
+      <c r="PQY28" s="17"/>
+      <c r="PQZ28" s="13"/>
+      <c r="PRA28" s="2"/>
+      <c r="PRG28" s="16"/>
+      <c r="PRI28" s="17"/>
+      <c r="PRJ28" s="17"/>
+      <c r="PRK28" s="13"/>
+      <c r="PRL28" s="2"/>
+      <c r="PRR28" s="16"/>
+      <c r="PRT28" s="17"/>
+      <c r="PRU28" s="17"/>
+      <c r="PRV28" s="13"/>
+      <c r="PRW28" s="2"/>
+      <c r="PSC28" s="16"/>
+      <c r="PSE28" s="17"/>
+      <c r="PSF28" s="17"/>
+      <c r="PSG28" s="13"/>
+      <c r="PSH28" s="2"/>
+      <c r="PSN28" s="16"/>
+      <c r="PSP28" s="17"/>
+      <c r="PSQ28" s="17"/>
+      <c r="PSR28" s="13"/>
+      <c r="PSS28" s="2"/>
+      <c r="PSY28" s="16"/>
+      <c r="PTA28" s="17"/>
+      <c r="PTB28" s="17"/>
+      <c r="PTC28" s="13"/>
+      <c r="PTD28" s="2"/>
+      <c r="PTJ28" s="16"/>
+      <c r="PTL28" s="17"/>
+      <c r="PTM28" s="17"/>
+      <c r="PTN28" s="13"/>
+      <c r="PTO28" s="2"/>
+      <c r="PTU28" s="16"/>
+      <c r="PTW28" s="17"/>
+      <c r="PTX28" s="17"/>
+      <c r="PTY28" s="13"/>
+      <c r="PTZ28" s="2"/>
+      <c r="PUF28" s="16"/>
+      <c r="PUH28" s="17"/>
+      <c r="PUI28" s="17"/>
+      <c r="PUJ28" s="13"/>
+      <c r="PUK28" s="2"/>
+      <c r="PUQ28" s="16"/>
+      <c r="PUS28" s="17"/>
+      <c r="PUT28" s="17"/>
+      <c r="PUU28" s="13"/>
+      <c r="PUV28" s="2"/>
+      <c r="PVB28" s="16"/>
+      <c r="PVD28" s="17"/>
+      <c r="PVE28" s="17"/>
+      <c r="PVF28" s="13"/>
+      <c r="PVG28" s="2"/>
+      <c r="PVM28" s="16"/>
+      <c r="PVO28" s="17"/>
+      <c r="PVP28" s="17"/>
+      <c r="PVQ28" s="13"/>
+      <c r="PVR28" s="2"/>
+      <c r="PVX28" s="16"/>
+      <c r="PVZ28" s="17"/>
+      <c r="PWA28" s="17"/>
+      <c r="PWB28" s="13"/>
+      <c r="PWC28" s="2"/>
+      <c r="PWI28" s="16"/>
+      <c r="PWK28" s="17"/>
+      <c r="PWL28" s="17"/>
+      <c r="PWM28" s="13"/>
+      <c r="PWN28" s="2"/>
+      <c r="PWT28" s="16"/>
+      <c r="PWV28" s="17"/>
+      <c r="PWW28" s="17"/>
+      <c r="PWX28" s="13"/>
+      <c r="PWY28" s="2"/>
+      <c r="PXE28" s="16"/>
+      <c r="PXG28" s="17"/>
+      <c r="PXH28" s="17"/>
+      <c r="PXI28" s="13"/>
+      <c r="PXJ28" s="2"/>
+      <c r="PXP28" s="16"/>
+      <c r="PXR28" s="17"/>
+      <c r="PXS28" s="17"/>
+      <c r="PXT28" s="13"/>
+      <c r="PXU28" s="2"/>
+      <c r="PYA28" s="16"/>
+      <c r="PYC28" s="17"/>
+      <c r="PYD28" s="17"/>
+      <c r="PYE28" s="13"/>
+      <c r="PYF28" s="2"/>
+      <c r="PYL28" s="16"/>
+      <c r="PYN28" s="17"/>
+      <c r="PYO28" s="17"/>
+      <c r="PYP28" s="13"/>
+      <c r="PYQ28" s="2"/>
+      <c r="PYW28" s="16"/>
+      <c r="PYY28" s="17"/>
+      <c r="PYZ28" s="17"/>
+      <c r="PZA28" s="13"/>
+      <c r="PZB28" s="2"/>
+      <c r="PZH28" s="16"/>
+      <c r="PZJ28" s="17"/>
+      <c r="PZK28" s="17"/>
+      <c r="PZL28" s="13"/>
+      <c r="PZM28" s="2"/>
+      <c r="PZS28" s="16"/>
+      <c r="PZU28" s="17"/>
+      <c r="PZV28" s="17"/>
+      <c r="PZW28" s="13"/>
+      <c r="PZX28" s="2"/>
+      <c r="QAD28" s="16"/>
+      <c r="QAF28" s="17"/>
+      <c r="QAG28" s="17"/>
+      <c r="QAH28" s="13"/>
+      <c r="QAI28" s="2"/>
+      <c r="QAO28" s="16"/>
+      <c r="QAQ28" s="17"/>
+      <c r="QAR28" s="17"/>
+      <c r="QAS28" s="13"/>
+      <c r="QAT28" s="2"/>
+      <c r="QAZ28" s="16"/>
+      <c r="QBB28" s="17"/>
+      <c r="QBC28" s="17"/>
+      <c r="QBD28" s="13"/>
+      <c r="QBE28" s="2"/>
+      <c r="QBK28" s="16"/>
+      <c r="QBM28" s="17"/>
+      <c r="QBN28" s="17"/>
+      <c r="QBO28" s="13"/>
+      <c r="QBP28" s="2"/>
+      <c r="QBV28" s="16"/>
+      <c r="QBX28" s="17"/>
+      <c r="QBY28" s="17"/>
+      <c r="QBZ28" s="13"/>
+      <c r="QCA28" s="2"/>
+      <c r="QCG28" s="16"/>
+      <c r="QCI28" s="17"/>
+      <c r="QCJ28" s="17"/>
+      <c r="QCK28" s="13"/>
+      <c r="QCL28" s="2"/>
+      <c r="QCR28" s="16"/>
+      <c r="QCT28" s="17"/>
+      <c r="QCU28" s="17"/>
+      <c r="QCV28" s="13"/>
+      <c r="QCW28" s="2"/>
+      <c r="QDC28" s="16"/>
+      <c r="QDE28" s="17"/>
+      <c r="QDF28" s="17"/>
+      <c r="QDG28" s="13"/>
+      <c r="QDH28" s="2"/>
+      <c r="QDN28" s="16"/>
+      <c r="QDP28" s="17"/>
+      <c r="QDQ28" s="17"/>
+      <c r="QDR28" s="13"/>
+      <c r="QDS28" s="2"/>
+      <c r="QDY28" s="16"/>
+      <c r="QEA28" s="17"/>
+      <c r="QEB28" s="17"/>
+      <c r="QEC28" s="13"/>
+      <c r="QED28" s="2"/>
+      <c r="QEJ28" s="16"/>
+      <c r="QEL28" s="17"/>
+      <c r="QEM28" s="17"/>
+      <c r="QEN28" s="13"/>
+      <c r="QEO28" s="2"/>
+      <c r="QEU28" s="16"/>
+      <c r="QEW28" s="17"/>
+      <c r="QEX28" s="17"/>
+      <c r="QEY28" s="13"/>
+      <c r="QEZ28" s="2"/>
+      <c r="QFF28" s="16"/>
+      <c r="QFH28" s="17"/>
+      <c r="QFI28" s="17"/>
+      <c r="QFJ28" s="13"/>
+      <c r="QFK28" s="2"/>
+      <c r="QFQ28" s="16"/>
+      <c r="QFS28" s="17"/>
+      <c r="QFT28" s="17"/>
+      <c r="QFU28" s="13"/>
+      <c r="QFV28" s="2"/>
+      <c r="QGB28" s="16"/>
+      <c r="QGD28" s="17"/>
+      <c r="QGE28" s="17"/>
+      <c r="QGF28" s="13"/>
+      <c r="QGG28" s="2"/>
+      <c r="QGM28" s="16"/>
+      <c r="QGO28" s="17"/>
+      <c r="QGP28" s="17"/>
+      <c r="QGQ28" s="13"/>
+      <c r="QGR28" s="2"/>
+      <c r="QGX28" s="16"/>
+      <c r="QGZ28" s="17"/>
+      <c r="QHA28" s="17"/>
+      <c r="QHB28" s="13"/>
+      <c r="QHC28" s="2"/>
+      <c r="QHI28" s="16"/>
+      <c r="QHK28" s="17"/>
+      <c r="QHL28" s="17"/>
+      <c r="QHM28" s="13"/>
+      <c r="QHN28" s="2"/>
+      <c r="QHT28" s="16"/>
+      <c r="QHV28" s="17"/>
+      <c r="QHW28" s="17"/>
+      <c r="QHX28" s="13"/>
+      <c r="QHY28" s="2"/>
+      <c r="QIE28" s="16"/>
+      <c r="QIG28" s="17"/>
+      <c r="QIH28" s="17"/>
+      <c r="QII28" s="13"/>
+      <c r="QIJ28" s="2"/>
+      <c r="QIP28" s="16"/>
+      <c r="QIR28" s="17"/>
+      <c r="QIS28" s="17"/>
+      <c r="QIT28" s="13"/>
+      <c r="QIU28" s="2"/>
+      <c r="QJA28" s="16"/>
+      <c r="QJC28" s="17"/>
+      <c r="QJD28" s="17"/>
+      <c r="QJE28" s="13"/>
+      <c r="QJF28" s="2"/>
+      <c r="QJL28" s="16"/>
+      <c r="QJN28" s="17"/>
+      <c r="QJO28" s="17"/>
+      <c r="QJP28" s="13"/>
+      <c r="QJQ28" s="2"/>
+      <c r="QJW28" s="16"/>
+      <c r="QJY28" s="17"/>
+      <c r="QJZ28" s="17"/>
+      <c r="QKA28" s="13"/>
+      <c r="QKB28" s="2"/>
+      <c r="QKH28" s="16"/>
+      <c r="QKJ28" s="17"/>
+      <c r="QKK28" s="17"/>
+      <c r="QKL28" s="13"/>
+      <c r="QKM28" s="2"/>
+      <c r="QKS28" s="16"/>
+      <c r="QKU28" s="17"/>
+      <c r="QKV28" s="17"/>
+      <c r="QKW28" s="13"/>
+      <c r="QKX28" s="2"/>
+      <c r="QLD28" s="16"/>
+      <c r="QLF28" s="17"/>
+      <c r="QLG28" s="17"/>
+      <c r="QLH28" s="13"/>
+      <c r="QLI28" s="2"/>
+      <c r="QLO28" s="16"/>
+      <c r="QLQ28" s="17"/>
+      <c r="QLR28" s="17"/>
+      <c r="QLS28" s="13"/>
+      <c r="QLT28" s="2"/>
+      <c r="QLZ28" s="16"/>
+      <c r="QMB28" s="17"/>
+      <c r="QMC28" s="17"/>
+      <c r="QMD28" s="13"/>
+      <c r="QME28" s="2"/>
+      <c r="QMK28" s="16"/>
+      <c r="QMM28" s="17"/>
+      <c r="QMN28" s="17"/>
+      <c r="QMO28" s="13"/>
+      <c r="QMP28" s="2"/>
+      <c r="QMV28" s="16"/>
+      <c r="QMX28" s="17"/>
+      <c r="QMY28" s="17"/>
+      <c r="QMZ28" s="13"/>
+      <c r="QNA28" s="2"/>
+      <c r="QNG28" s="16"/>
+      <c r="QNI28" s="17"/>
+      <c r="QNJ28" s="17"/>
+      <c r="QNK28" s="13"/>
+      <c r="QNL28" s="2"/>
+      <c r="QNR28" s="16"/>
+      <c r="QNT28" s="17"/>
+      <c r="QNU28" s="17"/>
+      <c r="QNV28" s="13"/>
+      <c r="QNW28" s="2"/>
+      <c r="QOC28" s="16"/>
+      <c r="QOE28" s="17"/>
+      <c r="QOF28" s="17"/>
+      <c r="QOG28" s="13"/>
+      <c r="QOH28" s="2"/>
+      <c r="QON28" s="16"/>
+      <c r="QOP28" s="17"/>
+      <c r="QOQ28" s="17"/>
+      <c r="QOR28" s="13"/>
+      <c r="QOS28" s="2"/>
+      <c r="QOY28" s="16"/>
+      <c r="QPA28" s="17"/>
+      <c r="QPB28" s="17"/>
+      <c r="QPC28" s="13"/>
+      <c r="QPD28" s="2"/>
+      <c r="QPJ28" s="16"/>
+      <c r="QPL28" s="17"/>
+      <c r="QPM28" s="17"/>
+      <c r="QPN28" s="13"/>
+      <c r="QPO28" s="2"/>
+      <c r="QPU28" s="16"/>
+      <c r="QPW28" s="17"/>
+      <c r="QPX28" s="17"/>
+      <c r="QPY28" s="13"/>
+      <c r="QPZ28" s="2"/>
+      <c r="QQF28" s="16"/>
+      <c r="QQH28" s="17"/>
+      <c r="QQI28" s="17"/>
+      <c r="QQJ28" s="13"/>
+      <c r="QQK28" s="2"/>
+      <c r="QQQ28" s="16"/>
+      <c r="QQS28" s="17"/>
+      <c r="QQT28" s="17"/>
+      <c r="QQU28" s="13"/>
+      <c r="QQV28" s="2"/>
+      <c r="QRB28" s="16"/>
+      <c r="QRD28" s="17"/>
+      <c r="QRE28" s="17"/>
+      <c r="QRF28" s="13"/>
+      <c r="QRG28" s="2"/>
+      <c r="QRM28" s="16"/>
+      <c r="QRO28" s="17"/>
+      <c r="QRP28" s="17"/>
+      <c r="QRQ28" s="13"/>
+      <c r="QRR28" s="2"/>
+      <c r="QRX28" s="16"/>
+      <c r="QRZ28" s="17"/>
+      <c r="QSA28" s="17"/>
+      <c r="QSB28" s="13"/>
+      <c r="QSC28" s="2"/>
+      <c r="QSI28" s="16"/>
+      <c r="QSK28" s="17"/>
+      <c r="QSL28" s="17"/>
+      <c r="QSM28" s="13"/>
+      <c r="QSN28" s="2"/>
+      <c r="QST28" s="16"/>
+      <c r="QSV28" s="17"/>
+      <c r="QSW28" s="17"/>
+      <c r="QSX28" s="13"/>
+      <c r="QSY28" s="2"/>
+      <c r="QTE28" s="16"/>
+      <c r="QTG28" s="17"/>
+      <c r="QTH28" s="17"/>
+      <c r="QTI28" s="13"/>
+      <c r="QTJ28" s="2"/>
+      <c r="QTP28" s="16"/>
+      <c r="QTR28" s="17"/>
+      <c r="QTS28" s="17"/>
+      <c r="QTT28" s="13"/>
+      <c r="QTU28" s="2"/>
+      <c r="QUA28" s="16"/>
+      <c r="QUC28" s="17"/>
+      <c r="QUD28" s="17"/>
+      <c r="QUE28" s="13"/>
+      <c r="QUF28" s="2"/>
+      <c r="QUL28" s="16"/>
+      <c r="QUN28" s="17"/>
+      <c r="QUO28" s="17"/>
+      <c r="QUP28" s="13"/>
+      <c r="QUQ28" s="2"/>
+      <c r="QUW28" s="16"/>
+      <c r="QUY28" s="17"/>
+      <c r="QUZ28" s="17"/>
+      <c r="QVA28" s="13"/>
+      <c r="QVB28" s="2"/>
+      <c r="QVH28" s="16"/>
+      <c r="QVJ28" s="17"/>
+      <c r="QVK28" s="17"/>
+      <c r="QVL28" s="13"/>
+      <c r="QVM28" s="2"/>
+      <c r="QVS28" s="16"/>
+      <c r="QVU28" s="17"/>
+      <c r="QVV28" s="17"/>
+      <c r="QVW28" s="13"/>
+      <c r="QVX28" s="2"/>
+      <c r="QWD28" s="16"/>
+      <c r="QWF28" s="17"/>
+      <c r="QWG28" s="17"/>
+      <c r="QWH28" s="13"/>
+      <c r="QWI28" s="2"/>
+      <c r="QWO28" s="16"/>
+      <c r="QWQ28" s="17"/>
+      <c r="QWR28" s="17"/>
+      <c r="QWS28" s="13"/>
+      <c r="QWT28" s="2"/>
+      <c r="QWZ28" s="16"/>
+      <c r="QXB28" s="17"/>
+      <c r="QXC28" s="17"/>
+      <c r="QXD28" s="13"/>
+      <c r="QXE28" s="2"/>
+      <c r="QXK28" s="16"/>
+      <c r="QXM28" s="17"/>
+      <c r="QXN28" s="17"/>
+      <c r="QXO28" s="13"/>
+      <c r="QXP28" s="2"/>
+      <c r="QXV28" s="16"/>
+      <c r="QXX28" s="17"/>
+      <c r="QXY28" s="17"/>
+      <c r="QXZ28" s="13"/>
+      <c r="QYA28" s="2"/>
+      <c r="QYG28" s="16"/>
+      <c r="QYI28" s="17"/>
+      <c r="QYJ28" s="17"/>
+      <c r="QYK28" s="13"/>
+      <c r="QYL28" s="2"/>
+      <c r="QYR28" s="16"/>
+      <c r="QYT28" s="17"/>
+      <c r="QYU28" s="17"/>
+      <c r="QYV28" s="13"/>
+      <c r="QYW28" s="2"/>
+      <c r="QZC28" s="16"/>
+      <c r="QZE28" s="17"/>
+      <c r="QZF28" s="17"/>
+      <c r="QZG28" s="13"/>
+      <c r="QZH28" s="2"/>
+      <c r="QZN28" s="16"/>
+      <c r="QZP28" s="17"/>
+      <c r="QZQ28" s="17"/>
+      <c r="QZR28" s="13"/>
+      <c r="QZS28" s="2"/>
+      <c r="QZY28" s="16"/>
+      <c r="RAA28" s="17"/>
+      <c r="RAB28" s="17"/>
+      <c r="RAC28" s="13"/>
+      <c r="RAD28" s="2"/>
+      <c r="RAJ28" s="16"/>
+      <c r="RAL28" s="17"/>
+      <c r="RAM28" s="17"/>
+      <c r="RAN28" s="13"/>
+      <c r="RAO28" s="2"/>
+      <c r="RAU28" s="16"/>
+      <c r="RAW28" s="17"/>
+      <c r="RAX28" s="17"/>
+      <c r="RAY28" s="13"/>
+      <c r="RAZ28" s="2"/>
+      <c r="RBF28" s="16"/>
+      <c r="RBH28" s="17"/>
+      <c r="RBI28" s="17"/>
+      <c r="RBJ28" s="13"/>
+      <c r="RBK28" s="2"/>
+      <c r="RBQ28" s="16"/>
+      <c r="RBS28" s="17"/>
+      <c r="RBT28" s="17"/>
+      <c r="RBU28" s="13"/>
+      <c r="RBV28" s="2"/>
+      <c r="RCB28" s="16"/>
+      <c r="RCD28" s="17"/>
+      <c r="RCE28" s="17"/>
+      <c r="RCF28" s="13"/>
+      <c r="RCG28" s="2"/>
+      <c r="RCM28" s="16"/>
+      <c r="RCO28" s="17"/>
+      <c r="RCP28" s="17"/>
+      <c r="RCQ28" s="13"/>
+      <c r="RCR28" s="2"/>
+      <c r="RCX28" s="16"/>
+      <c r="RCZ28" s="17"/>
+      <c r="RDA28" s="17"/>
+      <c r="RDB28" s="13"/>
+      <c r="RDC28" s="2"/>
+      <c r="RDI28" s="16"/>
+      <c r="RDK28" s="17"/>
+      <c r="RDL28" s="17"/>
+      <c r="RDM28" s="13"/>
+      <c r="RDN28" s="2"/>
+      <c r="RDT28" s="16"/>
+      <c r="RDV28" s="17"/>
+      <c r="RDW28" s="17"/>
+      <c r="RDX28" s="13"/>
+      <c r="RDY28" s="2"/>
+      <c r="REE28" s="16"/>
+      <c r="REG28" s="17"/>
+      <c r="REH28" s="17"/>
+      <c r="REI28" s="13"/>
+      <c r="REJ28" s="2"/>
+      <c r="REP28" s="16"/>
+      <c r="RER28" s="17"/>
+      <c r="RES28" s="17"/>
+      <c r="RET28" s="13"/>
+      <c r="REU28" s="2"/>
+      <c r="RFA28" s="16"/>
+      <c r="RFC28" s="17"/>
+      <c r="RFD28" s="17"/>
+      <c r="RFE28" s="13"/>
+      <c r="RFF28" s="2"/>
+      <c r="RFL28" s="16"/>
+      <c r="RFN28" s="17"/>
+      <c r="RFO28" s="17"/>
+      <c r="RFP28" s="13"/>
+      <c r="RFQ28" s="2"/>
+      <c r="RFW28" s="16"/>
+      <c r="RFY28" s="17"/>
+      <c r="RFZ28" s="17"/>
+      <c r="RGA28" s="13"/>
+      <c r="RGB28" s="2"/>
+      <c r="RGH28" s="16"/>
+      <c r="RGJ28" s="17"/>
+      <c r="RGK28" s="17"/>
+      <c r="RGL28" s="13"/>
+      <c r="RGM28" s="2"/>
+      <c r="RGS28" s="16"/>
+      <c r="RGU28" s="17"/>
+      <c r="RGV28" s="17"/>
+      <c r="RGW28" s="13"/>
+      <c r="RGX28" s="2"/>
+      <c r="RHD28" s="16"/>
+      <c r="RHF28" s="17"/>
+      <c r="RHG28" s="17"/>
+      <c r="RHH28" s="13"/>
+      <c r="RHI28" s="2"/>
+      <c r="RHO28" s="16"/>
+      <c r="RHQ28" s="17"/>
+      <c r="RHR28" s="17"/>
+      <c r="RHS28" s="13"/>
+      <c r="RHT28" s="2"/>
+      <c r="RHZ28" s="16"/>
+      <c r="RIB28" s="17"/>
+      <c r="RIC28" s="17"/>
+      <c r="RID28" s="13"/>
+      <c r="RIE28" s="2"/>
+      <c r="RIK28" s="16"/>
+      <c r="RIM28" s="17"/>
+      <c r="RIN28" s="17"/>
+      <c r="RIO28" s="13"/>
+      <c r="RIP28" s="2"/>
+      <c r="RIV28" s="16"/>
+      <c r="RIX28" s="17"/>
+      <c r="RIY28" s="17"/>
+      <c r="RIZ28" s="13"/>
+      <c r="RJA28" s="2"/>
+      <c r="RJG28" s="16"/>
+      <c r="RJI28" s="17"/>
+      <c r="RJJ28" s="17"/>
+      <c r="RJK28" s="13"/>
+      <c r="RJL28" s="2"/>
+      <c r="RJR28" s="16"/>
+      <c r="RJT28" s="17"/>
+      <c r="RJU28" s="17"/>
+      <c r="RJV28" s="13"/>
+      <c r="RJW28" s="2"/>
+      <c r="RKC28" s="16"/>
+      <c r="RKE28" s="17"/>
+      <c r="RKF28" s="17"/>
+      <c r="RKG28" s="13"/>
+      <c r="RKH28" s="2"/>
+      <c r="RKN28" s="16"/>
+      <c r="RKP28" s="17"/>
+      <c r="RKQ28" s="17"/>
+      <c r="RKR28" s="13"/>
+      <c r="RKS28" s="2"/>
+      <c r="RKY28" s="16"/>
+      <c r="RLA28" s="17"/>
+      <c r="RLB28" s="17"/>
+      <c r="RLC28" s="13"/>
+      <c r="RLD28" s="2"/>
+      <c r="RLJ28" s="16"/>
+      <c r="RLL28" s="17"/>
+      <c r="RLM28" s="17"/>
+      <c r="RLN28" s="13"/>
+      <c r="RLO28" s="2"/>
+      <c r="RLU28" s="16"/>
+      <c r="RLW28" s="17"/>
+      <c r="RLX28" s="17"/>
+      <c r="RLY28" s="13"/>
+      <c r="RLZ28" s="2"/>
+      <c r="RMF28" s="16"/>
+      <c r="RMH28" s="17"/>
+      <c r="RMI28" s="17"/>
+      <c r="RMJ28" s="13"/>
+      <c r="RMK28" s="2"/>
+      <c r="RMQ28" s="16"/>
+      <c r="RMS28" s="17"/>
+      <c r="RMT28" s="17"/>
+      <c r="RMU28" s="13"/>
+      <c r="RMV28" s="2"/>
+      <c r="RNB28" s="16"/>
+      <c r="RND28" s="17"/>
+      <c r="RNE28" s="17"/>
+      <c r="RNF28" s="13"/>
+      <c r="RNG28" s="2"/>
+      <c r="RNM28" s="16"/>
+      <c r="RNO28" s="17"/>
+      <c r="RNP28" s="17"/>
+      <c r="RNQ28" s="13"/>
+      <c r="RNR28" s="2"/>
+      <c r="RNX28" s="16"/>
+      <c r="RNZ28" s="17"/>
+      <c r="ROA28" s="17"/>
+      <c r="ROB28" s="13"/>
+      <c r="ROC28" s="2"/>
+      <c r="ROI28" s="16"/>
+      <c r="ROK28" s="17"/>
+      <c r="ROL28" s="17"/>
+      <c r="ROM28" s="13"/>
+      <c r="RON28" s="2"/>
+      <c r="ROT28" s="16"/>
+      <c r="ROV28" s="17"/>
+      <c r="ROW28" s="17"/>
+      <c r="ROX28" s="13"/>
+      <c r="ROY28" s="2"/>
+      <c r="RPE28" s="16"/>
+      <c r="RPG28" s="17"/>
+      <c r="RPH28" s="17"/>
+      <c r="RPI28" s="13"/>
+      <c r="RPJ28" s="2"/>
+      <c r="RPP28" s="16"/>
+      <c r="RPR28" s="17"/>
+      <c r="RPS28" s="17"/>
+      <c r="RPT28" s="13"/>
+      <c r="RPU28" s="2"/>
+      <c r="RQA28" s="16"/>
+      <c r="RQC28" s="17"/>
+      <c r="RQD28" s="17"/>
+      <c r="RQE28" s="13"/>
+      <c r="RQF28" s="2"/>
+      <c r="RQL28" s="16"/>
+      <c r="RQN28" s="17"/>
+      <c r="RQO28" s="17"/>
+      <c r="RQP28" s="13"/>
+      <c r="RQQ28" s="2"/>
+      <c r="RQW28" s="16"/>
+      <c r="RQY28" s="17"/>
+      <c r="RQZ28" s="17"/>
+      <c r="RRA28" s="13"/>
+      <c r="RRB28" s="2"/>
+      <c r="RRH28" s="16"/>
+      <c r="RRJ28" s="17"/>
+      <c r="RRK28" s="17"/>
+      <c r="RRL28" s="13"/>
+      <c r="RRM28" s="2"/>
+      <c r="RRS28" s="16"/>
+      <c r="RRU28" s="17"/>
+      <c r="RRV28" s="17"/>
+      <c r="RRW28" s="13"/>
+      <c r="RRX28" s="2"/>
+      <c r="RSD28" s="16"/>
+      <c r="RSF28" s="17"/>
+      <c r="RSG28" s="17"/>
+      <c r="RSH28" s="13"/>
+      <c r="RSI28" s="2"/>
+      <c r="RSO28" s="16"/>
+      <c r="RSQ28" s="17"/>
+      <c r="RSR28" s="17"/>
+      <c r="RSS28" s="13"/>
+      <c r="RST28" s="2"/>
+      <c r="RSZ28" s="16"/>
+      <c r="RTB28" s="17"/>
+      <c r="RTC28" s="17"/>
+      <c r="RTD28" s="13"/>
+      <c r="RTE28" s="2"/>
+      <c r="RTK28" s="16"/>
+      <c r="RTM28" s="17"/>
+      <c r="RTN28" s="17"/>
+      <c r="RTO28" s="13"/>
+      <c r="RTP28" s="2"/>
+      <c r="RTV28" s="16"/>
+      <c r="RTX28" s="17"/>
+      <c r="RTY28" s="17"/>
+      <c r="RTZ28" s="13"/>
+      <c r="RUA28" s="2"/>
+      <c r="RUG28" s="16"/>
+      <c r="RUI28" s="17"/>
+      <c r="RUJ28" s="17"/>
+      <c r="RUK28" s="13"/>
+      <c r="RUL28" s="2"/>
+      <c r="RUR28" s="16"/>
+      <c r="RUT28" s="17"/>
+      <c r="RUU28" s="17"/>
+      <c r="RUV28" s="13"/>
+      <c r="RUW28" s="2"/>
+      <c r="RVC28" s="16"/>
+      <c r="RVE28" s="17"/>
+      <c r="RVF28" s="17"/>
+      <c r="RVG28" s="13"/>
+      <c r="RVH28" s="2"/>
+      <c r="RVN28" s="16"/>
+      <c r="RVP28" s="17"/>
+      <c r="RVQ28" s="17"/>
+      <c r="RVR28" s="13"/>
+      <c r="RVS28" s="2"/>
+      <c r="RVY28" s="16"/>
+      <c r="RWA28" s="17"/>
+      <c r="RWB28" s="17"/>
+      <c r="RWC28" s="13"/>
+      <c r="RWD28" s="2"/>
+      <c r="RWJ28" s="16"/>
+      <c r="RWL28" s="17"/>
+      <c r="RWM28" s="17"/>
+      <c r="RWN28" s="13"/>
+      <c r="RWO28" s="2"/>
+      <c r="RWU28" s="16"/>
+      <c r="RWW28" s="17"/>
+      <c r="RWX28" s="17"/>
+      <c r="RWY28" s="13"/>
+      <c r="RWZ28" s="2"/>
+      <c r="RXF28" s="16"/>
+      <c r="RXH28" s="17"/>
+      <c r="RXI28" s="17"/>
+      <c r="RXJ28" s="13"/>
+      <c r="RXK28" s="2"/>
+      <c r="RXQ28" s="16"/>
+      <c r="RXS28" s="17"/>
+      <c r="RXT28" s="17"/>
+      <c r="RXU28" s="13"/>
+      <c r="RXV28" s="2"/>
+      <c r="RYB28" s="16"/>
+      <c r="RYD28" s="17"/>
+      <c r="RYE28" s="17"/>
+      <c r="RYF28" s="13"/>
+      <c r="RYG28" s="2"/>
+      <c r="RYM28" s="16"/>
+      <c r="RYO28" s="17"/>
+      <c r="RYP28" s="17"/>
+      <c r="RYQ28" s="13"/>
+      <c r="RYR28" s="2"/>
+      <c r="RYX28" s="16"/>
+      <c r="RYZ28" s="17"/>
+      <c r="RZA28" s="17"/>
+      <c r="RZB28" s="13"/>
+      <c r="RZC28" s="2"/>
+      <c r="RZI28" s="16"/>
+      <c r="RZK28" s="17"/>
+      <c r="RZL28" s="17"/>
+      <c r="RZM28" s="13"/>
+      <c r="RZN28" s="2"/>
+      <c r="RZT28" s="16"/>
+      <c r="RZV28" s="17"/>
+      <c r="RZW28" s="17"/>
+      <c r="RZX28" s="13"/>
+      <c r="RZY28" s="2"/>
+      <c r="SAE28" s="16"/>
+      <c r="SAG28" s="17"/>
+      <c r="SAH28" s="17"/>
+      <c r="SAI28" s="13"/>
+      <c r="SAJ28" s="2"/>
+      <c r="SAP28" s="16"/>
+      <c r="SAR28" s="17"/>
+      <c r="SAS28" s="17"/>
+      <c r="SAT28" s="13"/>
+      <c r="SAU28" s="2"/>
+      <c r="SBA28" s="16"/>
+      <c r="SBC28" s="17"/>
+      <c r="SBD28" s="17"/>
+      <c r="SBE28" s="13"/>
+      <c r="SBF28" s="2"/>
+      <c r="SBL28" s="16"/>
+      <c r="SBN28" s="17"/>
+      <c r="SBO28" s="17"/>
+      <c r="SBP28" s="13"/>
+      <c r="SBQ28" s="2"/>
+      <c r="SBW28" s="16"/>
+      <c r="SBY28" s="17"/>
+      <c r="SBZ28" s="17"/>
+      <c r="SCA28" s="13"/>
+      <c r="SCB28" s="2"/>
+      <c r="SCH28" s="16"/>
+      <c r="SCJ28" s="17"/>
+      <c r="SCK28" s="17"/>
+      <c r="SCL28" s="13"/>
+      <c r="SCM28" s="2"/>
+      <c r="SCS28" s="16"/>
+      <c r="SCU28" s="17"/>
+      <c r="SCV28" s="17"/>
+      <c r="SCW28" s="13"/>
+      <c r="SCX28" s="2"/>
+      <c r="SDD28" s="16"/>
+      <c r="SDF28" s="17"/>
+      <c r="SDG28" s="17"/>
+      <c r="SDH28" s="13"/>
+      <c r="SDI28" s="2"/>
+      <c r="SDO28" s="16"/>
+      <c r="SDQ28" s="17"/>
+      <c r="SDR28" s="17"/>
+      <c r="SDS28" s="13"/>
+      <c r="SDT28" s="2"/>
+      <c r="SDZ28" s="16"/>
+      <c r="SEB28" s="17"/>
+      <c r="SEC28" s="17"/>
+      <c r="SED28" s="13"/>
+      <c r="SEE28" s="2"/>
+      <c r="SEK28" s="16"/>
+      <c r="SEM28" s="17"/>
+      <c r="SEN28" s="17"/>
+      <c r="SEO28" s="13"/>
+      <c r="SEP28" s="2"/>
+      <c r="SEV28" s="16"/>
+      <c r="SEX28" s="17"/>
+      <c r="SEY28" s="17"/>
+      <c r="SEZ28" s="13"/>
+      <c r="SFA28" s="2"/>
+      <c r="SFG28" s="16"/>
+      <c r="SFI28" s="17"/>
+      <c r="SFJ28" s="17"/>
+      <c r="SFK28" s="13"/>
+      <c r="SFL28" s="2"/>
+      <c r="SFR28" s="16"/>
+      <c r="SFT28" s="17"/>
+      <c r="SFU28" s="17"/>
+      <c r="SFV28" s="13"/>
+      <c r="SFW28" s="2"/>
+      <c r="SGC28" s="16"/>
+      <c r="SGE28" s="17"/>
+      <c r="SGF28" s="17"/>
+      <c r="SGG28" s="13"/>
+      <c r="SGH28" s="2"/>
+      <c r="SGN28" s="16"/>
+      <c r="SGP28" s="17"/>
+      <c r="SGQ28" s="17"/>
+      <c r="SGR28" s="13"/>
+      <c r="SGS28" s="2"/>
+      <c r="SGY28" s="16"/>
+      <c r="SHA28" s="17"/>
+      <c r="SHB28" s="17"/>
+      <c r="SHC28" s="13"/>
+      <c r="SHD28" s="2"/>
+      <c r="SHJ28" s="16"/>
+      <c r="SHL28" s="17"/>
+      <c r="SHM28" s="17"/>
+      <c r="SHN28" s="13"/>
+      <c r="SHO28" s="2"/>
+      <c r="SHU28" s="16"/>
+      <c r="SHW28" s="17"/>
+      <c r="SHX28" s="17"/>
+      <c r="SHY28" s="13"/>
+      <c r="SHZ28" s="2"/>
+      <c r="SIF28" s="16"/>
+      <c r="SIH28" s="17"/>
+      <c r="SII28" s="17"/>
+      <c r="SIJ28" s="13"/>
+      <c r="SIK28" s="2"/>
+      <c r="SIQ28" s="16"/>
+      <c r="SIS28" s="17"/>
+      <c r="SIT28" s="17"/>
+      <c r="SIU28" s="13"/>
+      <c r="SIV28" s="2"/>
+      <c r="SJB28" s="16"/>
+      <c r="SJD28" s="17"/>
+      <c r="SJE28" s="17"/>
+      <c r="SJF28" s="13"/>
+      <c r="SJG28" s="2"/>
+      <c r="SJM28" s="16"/>
+      <c r="SJO28" s="17"/>
+      <c r="SJP28" s="17"/>
+      <c r="SJQ28" s="13"/>
+      <c r="SJR28" s="2"/>
+      <c r="SJX28" s="16"/>
+      <c r="SJZ28" s="17"/>
+      <c r="SKA28" s="17"/>
+      <c r="SKB28" s="13"/>
+      <c r="SKC28" s="2"/>
+      <c r="SKI28" s="16"/>
+      <c r="SKK28" s="17"/>
+      <c r="SKL28" s="17"/>
+      <c r="SKM28" s="13"/>
+      <c r="SKN28" s="2"/>
+      <c r="SKT28" s="16"/>
+      <c r="SKV28" s="17"/>
+      <c r="SKW28" s="17"/>
+      <c r="SKX28" s="13"/>
+      <c r="SKY28" s="2"/>
+      <c r="SLE28" s="16"/>
+      <c r="SLG28" s="17"/>
+      <c r="SLH28" s="17"/>
+      <c r="SLI28" s="13"/>
+      <c r="SLJ28" s="2"/>
+      <c r="SLP28" s="16"/>
+      <c r="SLR28" s="17"/>
+      <c r="SLS28" s="17"/>
+      <c r="SLT28" s="13"/>
+      <c r="SLU28" s="2"/>
+      <c r="SMA28" s="16"/>
+      <c r="SMC28" s="17"/>
+      <c r="SMD28" s="17"/>
+      <c r="SME28" s="13"/>
+      <c r="SMF28" s="2"/>
+      <c r="SML28" s="16"/>
+      <c r="SMN28" s="17"/>
+      <c r="SMO28" s="17"/>
+      <c r="SMP28" s="13"/>
+      <c r="SMQ28" s="2"/>
+      <c r="SMW28" s="16"/>
+      <c r="SMY28" s="17"/>
+      <c r="SMZ28" s="17"/>
+      <c r="SNA28" s="13"/>
+      <c r="SNB28" s="2"/>
+      <c r="SNH28" s="16"/>
+      <c r="SNJ28" s="17"/>
+      <c r="SNK28" s="17"/>
+      <c r="SNL28" s="13"/>
+      <c r="SNM28" s="2"/>
+      <c r="SNS28" s="16"/>
+      <c r="SNU28" s="17"/>
+      <c r="SNV28" s="17"/>
+      <c r="SNW28" s="13"/>
+      <c r="SNX28" s="2"/>
+      <c r="SOD28" s="16"/>
+      <c r="SOF28" s="17"/>
+      <c r="SOG28" s="17"/>
+      <c r="SOH28" s="13"/>
+      <c r="SOI28" s="2"/>
+      <c r="SOO28" s="16"/>
+      <c r="SOQ28" s="17"/>
+      <c r="SOR28" s="17"/>
+      <c r="SOS28" s="13"/>
+      <c r="SOT28" s="2"/>
+      <c r="SOZ28" s="16"/>
+      <c r="SPB28" s="17"/>
+      <c r="SPC28" s="17"/>
+      <c r="SPD28" s="13"/>
+      <c r="SPE28" s="2"/>
+      <c r="SPK28" s="16"/>
+      <c r="SPM28" s="17"/>
+      <c r="SPN28" s="17"/>
+      <c r="SPO28" s="13"/>
+      <c r="SPP28" s="2"/>
+      <c r="SPV28" s="16"/>
+      <c r="SPX28" s="17"/>
+      <c r="SPY28" s="17"/>
+      <c r="SPZ28" s="13"/>
+      <c r="SQA28" s="2"/>
+      <c r="SQG28" s="16"/>
+      <c r="SQI28" s="17"/>
+      <c r="SQJ28" s="17"/>
+      <c r="SQK28" s="13"/>
+      <c r="SQL28" s="2"/>
+      <c r="SQR28" s="16"/>
+      <c r="SQT28" s="17"/>
+      <c r="SQU28" s="17"/>
+      <c r="SQV28" s="13"/>
+      <c r="SQW28" s="2"/>
+      <c r="SRC28" s="16"/>
+      <c r="SRE28" s="17"/>
+      <c r="SRF28" s="17"/>
+      <c r="SRG28" s="13"/>
+      <c r="SRH28" s="2"/>
+      <c r="SRN28" s="16"/>
+      <c r="SRP28" s="17"/>
+      <c r="SRQ28" s="17"/>
+      <c r="SRR28" s="13"/>
+      <c r="SRS28" s="2"/>
+      <c r="SRY28" s="16"/>
+      <c r="SSA28" s="17"/>
+      <c r="SSB28" s="17"/>
+      <c r="SSC28" s="13"/>
+      <c r="SSD28" s="2"/>
+      <c r="SSJ28" s="16"/>
+      <c r="SSL28" s="17"/>
+      <c r="SSM28" s="17"/>
+      <c r="SSN28" s="13"/>
+      <c r="SSO28" s="2"/>
+      <c r="SSU28" s="16"/>
+      <c r="SSW28" s="17"/>
+      <c r="SSX28" s="17"/>
+      <c r="SSY28" s="13"/>
+      <c r="SSZ28" s="2"/>
+      <c r="STF28" s="16"/>
+      <c r="STH28" s="17"/>
+      <c r="STI28" s="17"/>
+      <c r="STJ28" s="13"/>
+      <c r="STK28" s="2"/>
+      <c r="STQ28" s="16"/>
+      <c r="STS28" s="17"/>
+      <c r="STT28" s="17"/>
+      <c r="STU28" s="13"/>
+      <c r="STV28" s="2"/>
+      <c r="SUB28" s="16"/>
+      <c r="SUD28" s="17"/>
+      <c r="SUE28" s="17"/>
+      <c r="SUF28" s="13"/>
+      <c r="SUG28" s="2"/>
+      <c r="SUM28" s="16"/>
+      <c r="SUO28" s="17"/>
+      <c r="SUP28" s="17"/>
+      <c r="SUQ28" s="13"/>
+      <c r="SUR28" s="2"/>
+      <c r="SUX28" s="16"/>
+      <c r="SUZ28" s="17"/>
+      <c r="SVA28" s="17"/>
+      <c r="SVB28" s="13"/>
+      <c r="SVC28" s="2"/>
+      <c r="SVI28" s="16"/>
+      <c r="SVK28" s="17"/>
+      <c r="SVL28" s="17"/>
+      <c r="SVM28" s="13"/>
+      <c r="SVN28" s="2"/>
+      <c r="SVT28" s="16"/>
+      <c r="SVV28" s="17"/>
+      <c r="SVW28" s="17"/>
+      <c r="SVX28" s="13"/>
+      <c r="SVY28" s="2"/>
+      <c r="SWE28" s="16"/>
+      <c r="SWG28" s="17"/>
+      <c r="SWH28" s="17"/>
+      <c r="SWI28" s="13"/>
+      <c r="SWJ28" s="2"/>
+      <c r="SWP28" s="16"/>
+      <c r="SWR28" s="17"/>
+      <c r="SWS28" s="17"/>
+      <c r="SWT28" s="13"/>
+      <c r="SWU28" s="2"/>
+      <c r="SXA28" s="16"/>
+      <c r="SXC28" s="17"/>
+      <c r="SXD28" s="17"/>
+      <c r="SXE28" s="13"/>
+      <c r="SXF28" s="2"/>
+      <c r="SXL28" s="16"/>
+      <c r="SXN28" s="17"/>
+      <c r="SXO28" s="17"/>
+      <c r="SXP28" s="13"/>
+      <c r="SXQ28" s="2"/>
+      <c r="SXW28" s="16"/>
+      <c r="SXY28" s="17"/>
+      <c r="SXZ28" s="17"/>
+      <c r="SYA28" s="13"/>
+      <c r="SYB28" s="2"/>
+      <c r="SYH28" s="16"/>
+      <c r="SYJ28" s="17"/>
+      <c r="SYK28" s="17"/>
+      <c r="SYL28" s="13"/>
+      <c r="SYM28" s="2"/>
+      <c r="SYS28" s="16"/>
+      <c r="SYU28" s="17"/>
+      <c r="SYV28" s="17"/>
+      <c r="SYW28" s="13"/>
+      <c r="SYX28" s="2"/>
+      <c r="SZD28" s="16"/>
+      <c r="SZF28" s="17"/>
+      <c r="SZG28" s="17"/>
+      <c r="SZH28" s="13"/>
+      <c r="SZI28" s="2"/>
+      <c r="SZO28" s="16"/>
+      <c r="SZQ28" s="17"/>
+      <c r="SZR28" s="17"/>
+      <c r="SZS28" s="13"/>
+      <c r="SZT28" s="2"/>
+      <c r="SZZ28" s="16"/>
+      <c r="TAB28" s="17"/>
+      <c r="TAC28" s="17"/>
+      <c r="TAD28" s="13"/>
+      <c r="TAE28" s="2"/>
+      <c r="TAK28" s="16"/>
+      <c r="TAM28" s="17"/>
+      <c r="TAN28" s="17"/>
+      <c r="TAO28" s="13"/>
+      <c r="TAP28" s="2"/>
+      <c r="TAV28" s="16"/>
+      <c r="TAX28" s="17"/>
+      <c r="TAY28" s="17"/>
+      <c r="TAZ28" s="13"/>
+      <c r="TBA28" s="2"/>
+      <c r="TBG28" s="16"/>
+      <c r="TBI28" s="17"/>
+      <c r="TBJ28" s="17"/>
+      <c r="TBK28" s="13"/>
+      <c r="TBL28" s="2"/>
+      <c r="TBR28" s="16"/>
+      <c r="TBT28" s="17"/>
+      <c r="TBU28" s="17"/>
+      <c r="TBV28" s="13"/>
+      <c r="TBW28" s="2"/>
+      <c r="TCC28" s="16"/>
+      <c r="TCE28" s="17"/>
+      <c r="TCF28" s="17"/>
+      <c r="TCG28" s="13"/>
+      <c r="TCH28" s="2"/>
+      <c r="TCN28" s="16"/>
+      <c r="TCP28" s="17"/>
+      <c r="TCQ28" s="17"/>
+      <c r="TCR28" s="13"/>
+      <c r="TCS28" s="2"/>
+      <c r="TCY28" s="16"/>
+      <c r="TDA28" s="17"/>
+      <c r="TDB28" s="17"/>
+      <c r="TDC28" s="13"/>
+      <c r="TDD28" s="2"/>
+      <c r="TDJ28" s="16"/>
+      <c r="TDL28" s="17"/>
+      <c r="TDM28" s="17"/>
+      <c r="TDN28" s="13"/>
+      <c r="TDO28" s="2"/>
+      <c r="TDU28" s="16"/>
+      <c r="TDW28" s="17"/>
+      <c r="TDX28" s="17"/>
+      <c r="TDY28" s="13"/>
+      <c r="TDZ28" s="2"/>
+      <c r="TEF28" s="16"/>
+      <c r="TEH28" s="17"/>
+      <c r="TEI28" s="17"/>
+      <c r="TEJ28" s="13"/>
+      <c r="TEK28" s="2"/>
+      <c r="TEQ28" s="16"/>
+      <c r="TES28" s="17"/>
+      <c r="TET28" s="17"/>
+      <c r="TEU28" s="13"/>
+      <c r="TEV28" s="2"/>
+      <c r="TFB28" s="16"/>
+      <c r="TFD28" s="17"/>
+      <c r="TFE28" s="17"/>
+      <c r="TFF28" s="13"/>
+      <c r="TFG28" s="2"/>
+      <c r="TFM28" s="16"/>
+      <c r="TFO28" s="17"/>
+      <c r="TFP28" s="17"/>
+      <c r="TFQ28" s="13"/>
+      <c r="TFR28" s="2"/>
+      <c r="TFX28" s="16"/>
+      <c r="TFZ28" s="17"/>
+      <c r="TGA28" s="17"/>
+      <c r="TGB28" s="13"/>
+      <c r="TGC28" s="2"/>
+      <c r="TGI28" s="16"/>
+      <c r="TGK28" s="17"/>
+      <c r="TGL28" s="17"/>
+      <c r="TGM28" s="13"/>
+      <c r="TGN28" s="2"/>
+      <c r="TGT28" s="16"/>
+      <c r="TGV28" s="17"/>
+      <c r="TGW28" s="17"/>
+      <c r="TGX28" s="13"/>
+      <c r="TGY28" s="2"/>
+      <c r="THE28" s="16"/>
+      <c r="THG28" s="17"/>
+      <c r="THH28" s="17"/>
+      <c r="THI28" s="13"/>
+      <c r="THJ28" s="2"/>
+      <c r="THP28" s="16"/>
+      <c r="THR28" s="17"/>
+      <c r="THS28" s="17"/>
+      <c r="THT28" s="13"/>
+      <c r="THU28" s="2"/>
+      <c r="TIA28" s="16"/>
+      <c r="TIC28" s="17"/>
+      <c r="TID28" s="17"/>
+      <c r="TIE28" s="13"/>
+      <c r="TIF28" s="2"/>
+      <c r="TIL28" s="16"/>
+      <c r="TIN28" s="17"/>
+      <c r="TIO28" s="17"/>
+      <c r="TIP28" s="13"/>
+      <c r="TIQ28" s="2"/>
+      <c r="TIW28" s="16"/>
+      <c r="TIY28" s="17"/>
+      <c r="TIZ28" s="17"/>
+      <c r="TJA28" s="13"/>
+      <c r="TJB28" s="2"/>
+      <c r="TJH28" s="16"/>
+      <c r="TJJ28" s="17"/>
+      <c r="TJK28" s="17"/>
+      <c r="TJL28" s="13"/>
+      <c r="TJM28" s="2"/>
+      <c r="TJS28" s="16"/>
+      <c r="TJU28" s="17"/>
+      <c r="TJV28" s="17"/>
+      <c r="TJW28" s="13"/>
+      <c r="TJX28" s="2"/>
+      <c r="TKD28" s="16"/>
+      <c r="TKF28" s="17"/>
+      <c r="TKG28" s="17"/>
+      <c r="TKH28" s="13"/>
+      <c r="TKI28" s="2"/>
+      <c r="TKO28" s="16"/>
+      <c r="TKQ28" s="17"/>
+      <c r="TKR28" s="17"/>
+      <c r="TKS28" s="13"/>
+      <c r="TKT28" s="2"/>
+      <c r="TKZ28" s="16"/>
+      <c r="TLB28" s="17"/>
+      <c r="TLC28" s="17"/>
+      <c r="TLD28" s="13"/>
+      <c r="TLE28" s="2"/>
+      <c r="TLK28" s="16"/>
+      <c r="TLM28" s="17"/>
+      <c r="TLN28" s="17"/>
+      <c r="TLO28" s="13"/>
+      <c r="TLP28" s="2"/>
+      <c r="TLV28" s="16"/>
+      <c r="TLX28" s="17"/>
+      <c r="TLY28" s="17"/>
+      <c r="TLZ28" s="13"/>
+      <c r="TMA28" s="2"/>
+      <c r="TMG28" s="16"/>
+      <c r="TMI28" s="17"/>
+      <c r="TMJ28" s="17"/>
+      <c r="TMK28" s="13"/>
+      <c r="TML28" s="2"/>
+      <c r="TMR28" s="16"/>
+      <c r="TMT28" s="17"/>
+      <c r="TMU28" s="17"/>
+      <c r="TMV28" s="13"/>
+      <c r="TMW28" s="2"/>
+      <c r="TNC28" s="16"/>
+      <c r="TNE28" s="17"/>
+      <c r="TNF28" s="17"/>
+      <c r="TNG28" s="13"/>
+      <c r="TNH28" s="2"/>
+      <c r="TNN28" s="16"/>
+      <c r="TNP28" s="17"/>
+      <c r="TNQ28" s="17"/>
+      <c r="TNR28" s="13"/>
+      <c r="TNS28" s="2"/>
+      <c r="TNY28" s="16"/>
+      <c r="TOA28" s="17"/>
+      <c r="TOB28" s="17"/>
+      <c r="TOC28" s="13"/>
+      <c r="TOD28" s="2"/>
+      <c r="TOJ28" s="16"/>
+      <c r="TOL28" s="17"/>
+      <c r="TOM28" s="17"/>
+      <c r="TON28" s="13"/>
+      <c r="TOO28" s="2"/>
+      <c r="TOU28" s="16"/>
+      <c r="TOW28" s="17"/>
+      <c r="TOX28" s="17"/>
+      <c r="TOY28" s="13"/>
+      <c r="TOZ28" s="2"/>
+      <c r="TPF28" s="16"/>
+      <c r="TPH28" s="17"/>
+      <c r="TPI28" s="17"/>
+      <c r="TPJ28" s="13"/>
+      <c r="TPK28" s="2"/>
+      <c r="TPQ28" s="16"/>
+      <c r="TPS28" s="17"/>
+      <c r="TPT28" s="17"/>
+      <c r="TPU28" s="13"/>
+      <c r="TPV28" s="2"/>
+      <c r="TQB28" s="16"/>
+      <c r="TQD28" s="17"/>
+      <c r="TQE28" s="17"/>
+      <c r="TQF28" s="13"/>
+      <c r="TQG28" s="2"/>
+      <c r="TQM28" s="16"/>
+      <c r="TQO28" s="17"/>
+      <c r="TQP28" s="17"/>
+      <c r="TQQ28" s="13"/>
+      <c r="TQR28" s="2"/>
+      <c r="TQX28" s="16"/>
+      <c r="TQZ28" s="17"/>
+      <c r="TRA28" s="17"/>
+      <c r="TRB28" s="13"/>
+      <c r="TRC28" s="2"/>
+      <c r="TRI28" s="16"/>
+      <c r="TRK28" s="17"/>
+      <c r="TRL28" s="17"/>
+      <c r="TRM28" s="13"/>
+      <c r="TRN28" s="2"/>
+      <c r="TRT28" s="16"/>
+      <c r="TRV28" s="17"/>
+      <c r="TRW28" s="17"/>
+      <c r="TRX28" s="13"/>
+      <c r="TRY28" s="2"/>
+      <c r="TSE28" s="16"/>
+      <c r="TSG28" s="17"/>
+      <c r="TSH28" s="17"/>
+      <c r="TSI28" s="13"/>
+      <c r="TSJ28" s="2"/>
+      <c r="TSP28" s="16"/>
+      <c r="TSR28" s="17"/>
+      <c r="TSS28" s="17"/>
+      <c r="TST28" s="13"/>
+      <c r="TSU28" s="2"/>
+      <c r="TTA28" s="16"/>
+      <c r="TTC28" s="17"/>
+      <c r="TTD28" s="17"/>
+      <c r="TTE28" s="13"/>
+      <c r="TTF28" s="2"/>
+      <c r="TTL28" s="16"/>
+      <c r="TTN28" s="17"/>
+      <c r="TTO28" s="17"/>
+      <c r="TTP28" s="13"/>
+      <c r="TTQ28" s="2"/>
+      <c r="TTW28" s="16"/>
+      <c r="TTY28" s="17"/>
+      <c r="TTZ28" s="17"/>
+      <c r="TUA28" s="13"/>
+      <c r="TUB28" s="2"/>
+      <c r="TUH28" s="16"/>
+      <c r="TUJ28" s="17"/>
+      <c r="TUK28" s="17"/>
+      <c r="TUL28" s="13"/>
+      <c r="TUM28" s="2"/>
+      <c r="TUS28" s="16"/>
+      <c r="TUU28" s="17"/>
+      <c r="TUV28" s="17"/>
+      <c r="TUW28" s="13"/>
+      <c r="TUX28" s="2"/>
+      <c r="TVD28" s="16"/>
+      <c r="TVF28" s="17"/>
+      <c r="TVG28" s="17"/>
+      <c r="TVH28" s="13"/>
+      <c r="TVI28" s="2"/>
+      <c r="TVO28" s="16"/>
+      <c r="TVQ28" s="17"/>
+      <c r="TVR28" s="17"/>
+      <c r="TVS28" s="13"/>
+      <c r="TVT28" s="2"/>
+      <c r="TVZ28" s="16"/>
+      <c r="TWB28" s="17"/>
+      <c r="TWC28" s="17"/>
+      <c r="TWD28" s="13"/>
+      <c r="TWE28" s="2"/>
+      <c r="TWK28" s="16"/>
+      <c r="TWM28" s="17"/>
+      <c r="TWN28" s="17"/>
+      <c r="TWO28" s="13"/>
+      <c r="TWP28" s="2"/>
+      <c r="TWV28" s="16"/>
+      <c r="TWX28" s="17"/>
+      <c r="TWY28" s="17"/>
+      <c r="TWZ28" s="13"/>
+      <c r="TXA28" s="2"/>
+      <c r="TXG28" s="16"/>
+      <c r="TXI28" s="17"/>
+      <c r="TXJ28" s="17"/>
+      <c r="TXK28" s="13"/>
+      <c r="TXL28" s="2"/>
+      <c r="TXR28" s="16"/>
+      <c r="TXT28" s="17"/>
+      <c r="TXU28" s="17"/>
+      <c r="TXV28" s="13"/>
+      <c r="TXW28" s="2"/>
+      <c r="TYC28" s="16"/>
+      <c r="TYE28" s="17"/>
+      <c r="TYF28" s="17"/>
+      <c r="TYG28" s="13"/>
+      <c r="TYH28" s="2"/>
+      <c r="TYN28" s="16"/>
+      <c r="TYP28" s="17"/>
+      <c r="TYQ28" s="17"/>
+      <c r="TYR28" s="13"/>
+      <c r="TYS28" s="2"/>
+      <c r="TYY28" s="16"/>
+      <c r="TZA28" s="17"/>
+      <c r="TZB28" s="17"/>
+      <c r="TZC28" s="13"/>
+      <c r="TZD28" s="2"/>
+      <c r="TZJ28" s="16"/>
+      <c r="TZL28" s="17"/>
+      <c r="TZM28" s="17"/>
+      <c r="TZN28" s="13"/>
+      <c r="TZO28" s="2"/>
+      <c r="TZU28" s="16"/>
+      <c r="TZW28" s="17"/>
+      <c r="TZX28" s="17"/>
+      <c r="TZY28" s="13"/>
+      <c r="TZZ28" s="2"/>
+      <c r="UAF28" s="16"/>
+      <c r="UAH28" s="17"/>
+      <c r="UAI28" s="17"/>
+      <c r="UAJ28" s="13"/>
+      <c r="UAK28" s="2"/>
+      <c r="UAQ28" s="16"/>
+      <c r="UAS28" s="17"/>
+      <c r="UAT28" s="17"/>
+      <c r="UAU28" s="13"/>
+      <c r="UAV28" s="2"/>
+      <c r="UBB28" s="16"/>
+      <c r="UBD28" s="17"/>
+      <c r="UBE28" s="17"/>
+      <c r="UBF28" s="13"/>
+      <c r="UBG28" s="2"/>
+      <c r="UBM28" s="16"/>
+      <c r="UBO28" s="17"/>
+      <c r="UBP28" s="17"/>
+      <c r="UBQ28" s="13"/>
+      <c r="UBR28" s="2"/>
+      <c r="UBX28" s="16"/>
+      <c r="UBZ28" s="17"/>
+      <c r="UCA28" s="17"/>
+      <c r="UCB28" s="13"/>
+      <c r="UCC28" s="2"/>
+      <c r="UCI28" s="16"/>
+      <c r="UCK28" s="17"/>
+      <c r="UCL28" s="17"/>
+      <c r="UCM28" s="13"/>
+      <c r="UCN28" s="2"/>
+      <c r="UCT28" s="16"/>
+      <c r="UCV28" s="17"/>
+      <c r="UCW28" s="17"/>
+      <c r="UCX28" s="13"/>
+      <c r="UCY28" s="2"/>
+      <c r="UDE28" s="16"/>
+      <c r="UDG28" s="17"/>
+      <c r="UDH28" s="17"/>
+      <c r="UDI28" s="13"/>
+      <c r="UDJ28" s="2"/>
+      <c r="UDP28" s="16"/>
+      <c r="UDR28" s="17"/>
+      <c r="UDS28" s="17"/>
+      <c r="UDT28" s="13"/>
+      <c r="UDU28" s="2"/>
+      <c r="UEA28" s="16"/>
+      <c r="UEC28" s="17"/>
+      <c r="UED28" s="17"/>
+      <c r="UEE28" s="13"/>
+      <c r="UEF28" s="2"/>
+      <c r="UEL28" s="16"/>
+      <c r="UEN28" s="17"/>
+      <c r="UEO28" s="17"/>
+      <c r="UEP28" s="13"/>
+      <c r="UEQ28" s="2"/>
+      <c r="UEW28" s="16"/>
+      <c r="UEY28" s="17"/>
+      <c r="UEZ28" s="17"/>
+      <c r="UFA28" s="13"/>
+      <c r="UFB28" s="2"/>
+      <c r="UFH28" s="16"/>
+      <c r="UFJ28" s="17"/>
+      <c r="UFK28" s="17"/>
+      <c r="UFL28" s="13"/>
+      <c r="UFM28" s="2"/>
+      <c r="UFS28" s="16"/>
+      <c r="UFU28" s="17"/>
+      <c r="UFV28" s="17"/>
+      <c r="UFW28" s="13"/>
+      <c r="UFX28" s="2"/>
+      <c r="UGD28" s="16"/>
+      <c r="UGF28" s="17"/>
+      <c r="UGG28" s="17"/>
+      <c r="UGH28" s="13"/>
+      <c r="UGI28" s="2"/>
+      <c r="UGO28" s="16"/>
+      <c r="UGQ28" s="17"/>
+      <c r="UGR28" s="17"/>
+      <c r="UGS28" s="13"/>
+      <c r="UGT28" s="2"/>
+      <c r="UGZ28" s="16"/>
+      <c r="UHB28" s="17"/>
+      <c r="UHC28" s="17"/>
+      <c r="UHD28" s="13"/>
+      <c r="UHE28" s="2"/>
+      <c r="UHK28" s="16"/>
+      <c r="UHM28" s="17"/>
+      <c r="UHN28" s="17"/>
+      <c r="UHO28" s="13"/>
+      <c r="UHP28" s="2"/>
+      <c r="UHV28" s="16"/>
+      <c r="UHX28" s="17"/>
+      <c r="UHY28" s="17"/>
+      <c r="UHZ28" s="13"/>
+      <c r="UIA28" s="2"/>
+      <c r="UIG28" s="16"/>
+      <c r="UII28" s="17"/>
+      <c r="UIJ28" s="17"/>
+      <c r="UIK28" s="13"/>
+      <c r="UIL28" s="2"/>
+      <c r="UIR28" s="16"/>
+      <c r="UIT28" s="17"/>
+      <c r="UIU28" s="17"/>
+      <c r="UIV28" s="13"/>
+      <c r="UIW28" s="2"/>
+      <c r="UJC28" s="16"/>
+      <c r="UJE28" s="17"/>
+      <c r="UJF28" s="17"/>
+      <c r="UJG28" s="13"/>
+      <c r="UJH28" s="2"/>
+      <c r="UJN28" s="16"/>
+      <c r="UJP28" s="17"/>
+      <c r="UJQ28" s="17"/>
+      <c r="UJR28" s="13"/>
+      <c r="UJS28" s="2"/>
+      <c r="UJY28" s="16"/>
+      <c r="UKA28" s="17"/>
+      <c r="UKB28" s="17"/>
+      <c r="UKC28" s="13"/>
+      <c r="UKD28" s="2"/>
+      <c r="UKJ28" s="16"/>
+      <c r="UKL28" s="17"/>
+      <c r="UKM28" s="17"/>
+      <c r="UKN28" s="13"/>
+      <c r="UKO28" s="2"/>
+      <c r="UKU28" s="16"/>
+      <c r="UKW28" s="17"/>
+      <c r="UKX28" s="17"/>
+      <c r="UKY28" s="13"/>
+      <c r="UKZ28" s="2"/>
+      <c r="ULF28" s="16"/>
+      <c r="ULH28" s="17"/>
+      <c r="ULI28" s="17"/>
+      <c r="ULJ28" s="13"/>
+      <c r="ULK28" s="2"/>
+      <c r="ULQ28" s="16"/>
+      <c r="ULS28" s="17"/>
+      <c r="ULT28" s="17"/>
+      <c r="ULU28" s="13"/>
+      <c r="ULV28" s="2"/>
+      <c r="UMB28" s="16"/>
+      <c r="UMD28" s="17"/>
+      <c r="UME28" s="17"/>
+      <c r="UMF28" s="13"/>
+      <c r="UMG28" s="2"/>
+      <c r="UMM28" s="16"/>
+      <c r="UMO28" s="17"/>
+      <c r="UMP28" s="17"/>
+      <c r="UMQ28" s="13"/>
+      <c r="UMR28" s="2"/>
+      <c r="UMX28" s="16"/>
+      <c r="UMZ28" s="17"/>
+      <c r="UNA28" s="17"/>
+      <c r="UNB28" s="13"/>
+      <c r="UNC28" s="2"/>
+      <c r="UNI28" s="16"/>
+      <c r="UNK28" s="17"/>
+      <c r="UNL28" s="17"/>
+      <c r="UNM28" s="13"/>
+      <c r="UNN28" s="2"/>
+      <c r="UNT28" s="16"/>
+      <c r="UNV28" s="17"/>
+      <c r="UNW28" s="17"/>
+      <c r="UNX28" s="13"/>
+      <c r="UNY28" s="2"/>
+      <c r="UOE28" s="16"/>
+      <c r="UOG28" s="17"/>
+      <c r="UOH28" s="17"/>
+      <c r="UOI28" s="13"/>
+      <c r="UOJ28" s="2"/>
+      <c r="UOP28" s="16"/>
+      <c r="UOR28" s="17"/>
+      <c r="UOS28" s="17"/>
+      <c r="UOT28" s="13"/>
+      <c r="UOU28" s="2"/>
+      <c r="UPA28" s="16"/>
+      <c r="UPC28" s="17"/>
+      <c r="UPD28" s="17"/>
+      <c r="UPE28" s="13"/>
+      <c r="UPF28" s="2"/>
+      <c r="UPL28" s="16"/>
+      <c r="UPN28" s="17"/>
+      <c r="UPO28" s="17"/>
+      <c r="UPP28" s="13"/>
+      <c r="UPQ28" s="2"/>
+      <c r="UPW28" s="16"/>
+      <c r="UPY28" s="17"/>
+      <c r="UPZ28" s="17"/>
+      <c r="UQA28" s="13"/>
+      <c r="UQB28" s="2"/>
+      <c r="UQH28" s="16"/>
+      <c r="UQJ28" s="17"/>
+      <c r="UQK28" s="17"/>
+      <c r="UQL28" s="13"/>
+      <c r="UQM28" s="2"/>
+      <c r="UQS28" s="16"/>
+      <c r="UQU28" s="17"/>
+      <c r="UQV28" s="17"/>
+      <c r="UQW28" s="13"/>
+      <c r="UQX28" s="2"/>
+      <c r="URD28" s="16"/>
+      <c r="URF28" s="17"/>
+      <c r="URG28" s="17"/>
+      <c r="URH28" s="13"/>
+      <c r="URI28" s="2"/>
+      <c r="URO28" s="16"/>
+      <c r="URQ28" s="17"/>
+      <c r="URR28" s="17"/>
+      <c r="URS28" s="13"/>
+      <c r="URT28" s="2"/>
+      <c r="URZ28" s="16"/>
+      <c r="USB28" s="17"/>
+      <c r="USC28" s="17"/>
+      <c r="USD28" s="13"/>
+      <c r="USE28" s="2"/>
+      <c r="USK28" s="16"/>
+      <c r="USM28" s="17"/>
+      <c r="USN28" s="17"/>
+      <c r="USO28" s="13"/>
+      <c r="USP28" s="2"/>
+      <c r="USV28" s="16"/>
+      <c r="USX28" s="17"/>
+      <c r="USY28" s="17"/>
+      <c r="USZ28" s="13"/>
+      <c r="UTA28" s="2"/>
+      <c r="UTG28" s="16"/>
+      <c r="UTI28" s="17"/>
+      <c r="UTJ28" s="17"/>
+      <c r="UTK28" s="13"/>
+      <c r="UTL28" s="2"/>
+      <c r="UTR28" s="16"/>
+      <c r="UTT28" s="17"/>
+      <c r="UTU28" s="17"/>
+      <c r="UTV28" s="13"/>
+      <c r="UTW28" s="2"/>
+      <c r="UUC28" s="16"/>
+      <c r="UUE28" s="17"/>
+      <c r="UUF28" s="17"/>
+      <c r="UUG28" s="13"/>
+      <c r="UUH28" s="2"/>
+      <c r="UUN28" s="16"/>
+      <c r="UUP28" s="17"/>
+      <c r="UUQ28" s="17"/>
+      <c r="UUR28" s="13"/>
+      <c r="UUS28" s="2"/>
+      <c r="UUY28" s="16"/>
+      <c r="UVA28" s="17"/>
+      <c r="UVB28" s="17"/>
+      <c r="UVC28" s="13"/>
+      <c r="UVD28" s="2"/>
+      <c r="UVJ28" s="16"/>
+      <c r="UVL28" s="17"/>
+      <c r="UVM28" s="17"/>
+      <c r="UVN28" s="13"/>
+      <c r="UVO28" s="2"/>
+      <c r="UVU28" s="16"/>
+      <c r="UVW28" s="17"/>
+      <c r="UVX28" s="17"/>
+      <c r="UVY28" s="13"/>
+      <c r="UVZ28" s="2"/>
+      <c r="UWF28" s="16"/>
+      <c r="UWH28" s="17"/>
+      <c r="UWI28" s="17"/>
+      <c r="UWJ28" s="13"/>
+      <c r="UWK28" s="2"/>
+      <c r="UWQ28" s="16"/>
+      <c r="UWS28" s="17"/>
+      <c r="UWT28" s="17"/>
+      <c r="UWU28" s="13"/>
+      <c r="UWV28" s="2"/>
+      <c r="UXB28" s="16"/>
+      <c r="UXD28" s="17"/>
+      <c r="UXE28" s="17"/>
+      <c r="UXF28" s="13"/>
+      <c r="UXG28" s="2"/>
+      <c r="UXM28" s="16"/>
+      <c r="UXO28" s="17"/>
+      <c r="UXP28" s="17"/>
+      <c r="UXQ28" s="13"/>
+      <c r="UXR28" s="2"/>
+      <c r="UXX28" s="16"/>
+      <c r="UXZ28" s="17"/>
+      <c r="UYA28" s="17"/>
+      <c r="UYB28" s="13"/>
+      <c r="UYC28" s="2"/>
+      <c r="UYI28" s="16"/>
+      <c r="UYK28" s="17"/>
+      <c r="UYL28" s="17"/>
+      <c r="UYM28" s="13"/>
+      <c r="UYN28" s="2"/>
+      <c r="UYT28" s="16"/>
+      <c r="UYV28" s="17"/>
+      <c r="UYW28" s="17"/>
+      <c r="UYX28" s="13"/>
+      <c r="UYY28" s="2"/>
+      <c r="UZE28" s="16"/>
+      <c r="UZG28" s="17"/>
+      <c r="UZH28" s="17"/>
+      <c r="UZI28" s="13"/>
+      <c r="UZJ28" s="2"/>
+      <c r="UZP28" s="16"/>
+      <c r="UZR28" s="17"/>
+      <c r="UZS28" s="17"/>
+      <c r="UZT28" s="13"/>
+      <c r="UZU28" s="2"/>
+      <c r="VAA28" s="16"/>
+      <c r="VAC28" s="17"/>
+      <c r="VAD28" s="17"/>
+      <c r="VAE28" s="13"/>
+      <c r="VAF28" s="2"/>
+      <c r="VAL28" s="16"/>
+      <c r="VAN28" s="17"/>
+      <c r="VAO28" s="17"/>
+      <c r="VAP28" s="13"/>
+      <c r="VAQ28" s="2"/>
+      <c r="VAW28" s="16"/>
+      <c r="VAY28" s="17"/>
+      <c r="VAZ28" s="17"/>
+      <c r="VBA28" s="13"/>
+      <c r="VBB28" s="2"/>
+      <c r="VBH28" s="16"/>
+      <c r="VBJ28" s="17"/>
+      <c r="VBK28" s="17"/>
+      <c r="VBL28" s="13"/>
+      <c r="VBM28" s="2"/>
+      <c r="VBS28" s="16"/>
+      <c r="VBU28" s="17"/>
+      <c r="VBV28" s="17"/>
+      <c r="VBW28" s="13"/>
+      <c r="VBX28" s="2"/>
+      <c r="VCD28" s="16"/>
+      <c r="VCF28" s="17"/>
+      <c r="VCG28" s="17"/>
+      <c r="VCH28" s="13"/>
+      <c r="VCI28" s="2"/>
+      <c r="VCO28" s="16"/>
+      <c r="VCQ28" s="17"/>
+      <c r="VCR28" s="17"/>
+      <c r="VCS28" s="13"/>
+      <c r="VCT28" s="2"/>
+      <c r="VCZ28" s="16"/>
+      <c r="VDB28" s="17"/>
+      <c r="VDC28" s="17"/>
+      <c r="VDD28" s="13"/>
+      <c r="VDE28" s="2"/>
+      <c r="VDK28" s="16"/>
+      <c r="VDM28" s="17"/>
+      <c r="VDN28" s="17"/>
+      <c r="VDO28" s="13"/>
+      <c r="VDP28" s="2"/>
+      <c r="VDV28" s="16"/>
+      <c r="VDX28" s="17"/>
+      <c r="VDY28" s="17"/>
+      <c r="VDZ28" s="13"/>
+      <c r="VEA28" s="2"/>
+      <c r="VEG28" s="16"/>
+      <c r="VEI28" s="17"/>
+      <c r="VEJ28" s="17"/>
+      <c r="VEK28" s="13"/>
+      <c r="VEL28" s="2"/>
+      <c r="VER28" s="16"/>
+      <c r="VET28" s="17"/>
+      <c r="VEU28" s="17"/>
+      <c r="VEV28" s="13"/>
+      <c r="VEW28" s="2"/>
+      <c r="VFC28" s="16"/>
+      <c r="VFE28" s="17"/>
+      <c r="VFF28" s="17"/>
+      <c r="VFG28" s="13"/>
+      <c r="VFH28" s="2"/>
+      <c r="VFN28" s="16"/>
+      <c r="VFP28" s="17"/>
+      <c r="VFQ28" s="17"/>
+      <c r="VFR28" s="13"/>
+      <c r="VFS28" s="2"/>
+      <c r="VFY28" s="16"/>
+      <c r="VGA28" s="17"/>
+      <c r="VGB28" s="17"/>
+      <c r="VGC28" s="13"/>
+      <c r="VGD28" s="2"/>
+      <c r="VGJ28" s="16"/>
+      <c r="VGL28" s="17"/>
+      <c r="VGM28" s="17"/>
+      <c r="VGN28" s="13"/>
+      <c r="VGO28" s="2"/>
+      <c r="VGU28" s="16"/>
+      <c r="VGW28" s="17"/>
+      <c r="VGX28" s="17"/>
+      <c r="VGY28" s="13"/>
+      <c r="VGZ28" s="2"/>
+      <c r="VHF28" s="16"/>
+      <c r="VHH28" s="17"/>
+      <c r="VHI28" s="17"/>
+      <c r="VHJ28" s="13"/>
+      <c r="VHK28" s="2"/>
+      <c r="VHQ28" s="16"/>
+      <c r="VHS28" s="17"/>
+      <c r="VHT28" s="17"/>
+      <c r="VHU28" s="13"/>
+      <c r="VHV28" s="2"/>
+      <c r="VIB28" s="16"/>
+      <c r="VID28" s="17"/>
+      <c r="VIE28" s="17"/>
+      <c r="VIF28" s="13"/>
+      <c r="VIG28" s="2"/>
+      <c r="VIM28" s="16"/>
+      <c r="VIO28" s="17"/>
+      <c r="VIP28" s="17"/>
+      <c r="VIQ28" s="13"/>
+      <c r="VIR28" s="2"/>
+      <c r="VIX28" s="16"/>
+      <c r="VIZ28" s="17"/>
+      <c r="VJA28" s="17"/>
+      <c r="VJB28" s="13"/>
+      <c r="VJC28" s="2"/>
+      <c r="VJI28" s="16"/>
+      <c r="VJK28" s="17"/>
+      <c r="VJL28" s="17"/>
+      <c r="VJM28" s="13"/>
+      <c r="VJN28" s="2"/>
+      <c r="VJT28" s="16"/>
+      <c r="VJV28" s="17"/>
+      <c r="VJW28" s="17"/>
+      <c r="VJX28" s="13"/>
+      <c r="VJY28" s="2"/>
+      <c r="VKE28" s="16"/>
+      <c r="VKG28" s="17"/>
+      <c r="VKH28" s="17"/>
+      <c r="VKI28" s="13"/>
+      <c r="VKJ28" s="2"/>
+      <c r="VKP28" s="16"/>
+      <c r="VKR28" s="17"/>
+      <c r="VKS28" s="17"/>
+      <c r="VKT28" s="13"/>
+      <c r="VKU28" s="2"/>
+      <c r="VLA28" s="16"/>
+      <c r="VLC28" s="17"/>
+      <c r="VLD28" s="17"/>
+      <c r="VLE28" s="13"/>
+      <c r="VLF28" s="2"/>
+      <c r="VLL28" s="16"/>
+      <c r="VLN28" s="17"/>
+      <c r="VLO28" s="17"/>
+      <c r="VLP28" s="13"/>
+      <c r="VLQ28" s="2"/>
+      <c r="VLW28" s="16"/>
+      <c r="VLY28" s="17"/>
+      <c r="VLZ28" s="17"/>
+      <c r="VMA28" s="13"/>
+      <c r="VMB28" s="2"/>
+      <c r="VMH28" s="16"/>
+      <c r="VMJ28" s="17"/>
+      <c r="VMK28" s="17"/>
+      <c r="VML28" s="13"/>
+      <c r="VMM28" s="2"/>
+      <c r="VMS28" s="16"/>
+      <c r="VMU28" s="17"/>
+      <c r="VMV28" s="17"/>
+      <c r="VMW28" s="13"/>
+      <c r="VMX28" s="2"/>
+      <c r="VND28" s="16"/>
+      <c r="VNF28" s="17"/>
+      <c r="VNG28" s="17"/>
+      <c r="VNH28" s="13"/>
+      <c r="VNI28" s="2"/>
+      <c r="VNO28" s="16"/>
+      <c r="VNQ28" s="17"/>
+      <c r="VNR28" s="17"/>
+      <c r="VNS28" s="13"/>
+      <c r="VNT28" s="2"/>
+      <c r="VNZ28" s="16"/>
+      <c r="VOB28" s="17"/>
+      <c r="VOC28" s="17"/>
+      <c r="VOD28" s="13"/>
+      <c r="VOE28" s="2"/>
+      <c r="VOK28" s="16"/>
+      <c r="VOM28" s="17"/>
+      <c r="VON28" s="17"/>
+      <c r="VOO28" s="13"/>
+      <c r="VOP28" s="2"/>
+      <c r="VOV28" s="16"/>
+      <c r="VOX28" s="17"/>
+      <c r="VOY28" s="17"/>
+      <c r="VOZ28" s="13"/>
+      <c r="VPA28" s="2"/>
+      <c r="VPG28" s="16"/>
+      <c r="VPI28" s="17"/>
+      <c r="VPJ28" s="17"/>
+      <c r="VPK28" s="13"/>
+      <c r="VPL28" s="2"/>
+      <c r="VPR28" s="16"/>
+      <c r="VPT28" s="17"/>
+      <c r="VPU28" s="17"/>
+      <c r="VPV28" s="13"/>
+      <c r="VPW28" s="2"/>
+      <c r="VQC28" s="16"/>
+      <c r="VQE28" s="17"/>
+      <c r="VQF28" s="17"/>
+      <c r="VQG28" s="13"/>
+      <c r="VQH28" s="2"/>
+      <c r="VQN28" s="16"/>
+      <c r="VQP28" s="17"/>
+      <c r="VQQ28" s="17"/>
+      <c r="VQR28" s="13"/>
+      <c r="VQS28" s="2"/>
+      <c r="VQY28" s="16"/>
+      <c r="VRA28" s="17"/>
+      <c r="VRB28" s="17"/>
+      <c r="VRC28" s="13"/>
+      <c r="VRD28" s="2"/>
+      <c r="VRJ28" s="16"/>
+      <c r="VRL28" s="17"/>
+      <c r="VRM28" s="17"/>
+      <c r="VRN28" s="13"/>
+      <c r="VRO28" s="2"/>
+      <c r="VRU28" s="16"/>
+      <c r="VRW28" s="17"/>
+      <c r="VRX28" s="17"/>
+      <c r="VRY28" s="13"/>
+      <c r="VRZ28" s="2"/>
+      <c r="VSF28" s="16"/>
+      <c r="VSH28" s="17"/>
+      <c r="VSI28" s="17"/>
+      <c r="VSJ28" s="13"/>
+      <c r="VSK28" s="2"/>
+      <c r="VSQ28" s="16"/>
+      <c r="VSS28" s="17"/>
+      <c r="VST28" s="17"/>
+      <c r="VSU28" s="13"/>
+      <c r="VSV28" s="2"/>
+      <c r="VTB28" s="16"/>
+      <c r="VTD28" s="17"/>
+      <c r="VTE28" s="17"/>
+      <c r="VTF28" s="13"/>
+      <c r="VTG28" s="2"/>
+      <c r="VTM28" s="16"/>
+      <c r="VTO28" s="17"/>
+      <c r="VTP28" s="17"/>
+      <c r="VTQ28" s="13"/>
+      <c r="VTR28" s="2"/>
+      <c r="VTX28" s="16"/>
+      <c r="VTZ28" s="17"/>
+      <c r="VUA28" s="17"/>
+      <c r="VUB28" s="13"/>
+      <c r="VUC28" s="2"/>
+      <c r="VUI28" s="16"/>
+      <c r="VUK28" s="17"/>
+      <c r="VUL28" s="17"/>
+      <c r="VUM28" s="13"/>
+      <c r="VUN28" s="2"/>
+      <c r="VUT28" s="16"/>
+      <c r="VUV28" s="17"/>
+      <c r="VUW28" s="17"/>
+      <c r="VUX28" s="13"/>
+      <c r="VUY28" s="2"/>
+      <c r="VVE28" s="16"/>
+      <c r="VVG28" s="17"/>
+      <c r="VVH28" s="17"/>
+      <c r="VVI28" s="13"/>
+      <c r="VVJ28" s="2"/>
+      <c r="VVP28" s="16"/>
+      <c r="VVR28" s="17"/>
+      <c r="VVS28" s="17"/>
+      <c r="VVT28" s="13"/>
+      <c r="VVU28" s="2"/>
+      <c r="VWA28" s="16"/>
+      <c r="VWC28" s="17"/>
+      <c r="VWD28" s="17"/>
+      <c r="VWE28" s="13"/>
+      <c r="VWF28" s="2"/>
+      <c r="VWL28" s="16"/>
+      <c r="VWN28" s="17"/>
+      <c r="VWO28" s="17"/>
+      <c r="VWP28" s="13"/>
+      <c r="VWQ28" s="2"/>
+      <c r="VWW28" s="16"/>
+      <c r="VWY28" s="17"/>
+      <c r="VWZ28" s="17"/>
+      <c r="VXA28" s="13"/>
+      <c r="VXB28" s="2"/>
+      <c r="VXH28" s="16"/>
+      <c r="VXJ28" s="17"/>
+      <c r="VXK28" s="17"/>
+      <c r="VXL28" s="13"/>
+      <c r="VXM28" s="2"/>
+      <c r="VXS28" s="16"/>
+      <c r="VXU28" s="17"/>
+      <c r="VXV28" s="17"/>
+      <c r="VXW28" s="13"/>
+      <c r="VXX28" s="2"/>
+      <c r="VYD28" s="16"/>
+      <c r="VYF28" s="17"/>
+      <c r="VYG28" s="17"/>
+      <c r="VYH28" s="13"/>
+      <c r="VYI28" s="2"/>
+      <c r="VYO28" s="16"/>
+      <c r="VYQ28" s="17"/>
+      <c r="VYR28" s="17"/>
+      <c r="VYS28" s="13"/>
+      <c r="VYT28" s="2"/>
+      <c r="VYZ28" s="16"/>
+      <c r="VZB28" s="17"/>
+      <c r="VZC28" s="17"/>
+      <c r="VZD28" s="13"/>
+      <c r="VZE28" s="2"/>
+      <c r="VZK28" s="16"/>
+      <c r="VZM28" s="17"/>
+      <c r="VZN28" s="17"/>
+      <c r="VZO28" s="13"/>
+      <c r="VZP28" s="2"/>
+      <c r="VZV28" s="16"/>
+      <c r="VZX28" s="17"/>
+      <c r="VZY28" s="17"/>
+      <c r="VZZ28" s="13"/>
+      <c r="WAA28" s="2"/>
+      <c r="WAG28" s="16"/>
+      <c r="WAI28" s="17"/>
+      <c r="WAJ28" s="17"/>
+      <c r="WAK28" s="13"/>
+      <c r="WAL28" s="2"/>
+      <c r="WAR28" s="16"/>
+      <c r="WAT28" s="17"/>
+      <c r="WAU28" s="17"/>
+      <c r="WAV28" s="13"/>
+      <c r="WAW28" s="2"/>
+      <c r="WBC28" s="16"/>
+      <c r="WBE28" s="17"/>
+      <c r="WBF28" s="17"/>
+      <c r="WBG28" s="13"/>
+      <c r="WBH28" s="2"/>
+      <c r="WBN28" s="16"/>
+      <c r="WBP28" s="17"/>
+      <c r="WBQ28" s="17"/>
+      <c r="WBR28" s="13"/>
+      <c r="WBS28" s="2"/>
+      <c r="WBY28" s="16"/>
+      <c r="WCA28" s="17"/>
+      <c r="WCB28" s="17"/>
+      <c r="WCC28" s="13"/>
+      <c r="WCD28" s="2"/>
+      <c r="WCJ28" s="16"/>
+      <c r="WCL28" s="17"/>
+      <c r="WCM28" s="17"/>
+      <c r="WCN28" s="13"/>
+      <c r="WCO28" s="2"/>
+      <c r="WCU28" s="16"/>
+      <c r="WCW28" s="17"/>
+      <c r="WCX28" s="17"/>
+      <c r="WCY28" s="13"/>
+      <c r="WCZ28" s="2"/>
+      <c r="WDF28" s="16"/>
+      <c r="WDH28" s="17"/>
+      <c r="WDI28" s="17"/>
+      <c r="WDJ28" s="13"/>
+      <c r="WDK28" s="2"/>
+      <c r="WDQ28" s="16"/>
+      <c r="WDS28" s="17"/>
+      <c r="WDT28" s="17"/>
+      <c r="WDU28" s="13"/>
+      <c r="WDV28" s="2"/>
+      <c r="WEB28" s="16"/>
+      <c r="WED28" s="17"/>
+      <c r="WEE28" s="17"/>
+      <c r="WEF28" s="13"/>
+      <c r="WEG28" s="2"/>
+      <c r="WEM28" s="16"/>
+      <c r="WEO28" s="17"/>
+      <c r="WEP28" s="17"/>
+      <c r="WEQ28" s="13"/>
+      <c r="WER28" s="2"/>
+      <c r="WEX28" s="16"/>
+      <c r="WEZ28" s="17"/>
+      <c r="WFA28" s="17"/>
+      <c r="WFB28" s="13"/>
+      <c r="WFC28" s="2"/>
+      <c r="WFI28" s="16"/>
+      <c r="WFK28" s="17"/>
+      <c r="WFL28" s="17"/>
+      <c r="WFM28" s="13"/>
+      <c r="WFN28" s="2"/>
+      <c r="WFT28" s="16"/>
+      <c r="WFV28" s="17"/>
+      <c r="WFW28" s="17"/>
+      <c r="WFX28" s="13"/>
+      <c r="WFY28" s="2"/>
+      <c r="WGE28" s="16"/>
+      <c r="WGG28" s="17"/>
+      <c r="WGH28" s="17"/>
+      <c r="WGI28" s="13"/>
+      <c r="WGJ28" s="2"/>
+      <c r="WGP28" s="16"/>
+      <c r="WGR28" s="17"/>
+      <c r="WGS28" s="17"/>
+      <c r="WGT28" s="13"/>
+      <c r="WGU28" s="2"/>
+      <c r="WHA28" s="16"/>
+      <c r="WHC28" s="17"/>
+      <c r="WHD28" s="17"/>
+      <c r="WHE28" s="13"/>
+      <c r="WHF28" s="2"/>
+      <c r="WHL28" s="16"/>
+      <c r="WHN28" s="17"/>
+      <c r="WHO28" s="17"/>
+      <c r="WHP28" s="13"/>
+      <c r="WHQ28" s="2"/>
+      <c r="WHW28" s="16"/>
+      <c r="WHY28" s="17"/>
+      <c r="WHZ28" s="17"/>
+      <c r="WIA28" s="13"/>
+      <c r="WIB28" s="2"/>
+      <c r="WIH28" s="16"/>
+      <c r="WIJ28" s="17"/>
+      <c r="WIK28" s="17"/>
+      <c r="WIL28" s="13"/>
+      <c r="WIM28" s="2"/>
+      <c r="WIS28" s="16"/>
+      <c r="WIU28" s="17"/>
+      <c r="WIV28" s="17"/>
+      <c r="WIW28" s="13"/>
+      <c r="WIX28" s="2"/>
+      <c r="WJD28" s="16"/>
+      <c r="WJF28" s="17"/>
+      <c r="WJG28" s="17"/>
+      <c r="WJH28" s="13"/>
+      <c r="WJI28" s="2"/>
+      <c r="WJO28" s="16"/>
+      <c r="WJQ28" s="17"/>
+      <c r="WJR28" s="17"/>
+      <c r="WJS28" s="13"/>
+      <c r="WJT28" s="2"/>
+      <c r="WJZ28" s="16"/>
+      <c r="WKB28" s="17"/>
+      <c r="WKC28" s="17"/>
+      <c r="WKD28" s="13"/>
+      <c r="WKE28" s="2"/>
+      <c r="WKK28" s="16"/>
+      <c r="WKM28" s="17"/>
+      <c r="WKN28" s="17"/>
+      <c r="WKO28" s="13"/>
+      <c r="WKP28" s="2"/>
+      <c r="WKV28" s="16"/>
+      <c r="WKX28" s="17"/>
+      <c r="WKY28" s="17"/>
+      <c r="WKZ28" s="13"/>
+      <c r="WLA28" s="2"/>
+      <c r="WLG28" s="16"/>
+      <c r="WLI28" s="17"/>
+      <c r="WLJ28" s="17"/>
+      <c r="WLK28" s="13"/>
+      <c r="WLL28" s="2"/>
+      <c r="WLR28" s="16"/>
+      <c r="WLT28" s="17"/>
+      <c r="WLU28" s="17"/>
+      <c r="WLV28" s="13"/>
+      <c r="WLW28" s="2"/>
+      <c r="WMC28" s="16"/>
+      <c r="WME28" s="17"/>
+      <c r="WMF28" s="17"/>
+      <c r="WMG28" s="13"/>
+      <c r="WMH28" s="2"/>
+      <c r="WMN28" s="16"/>
+      <c r="WMP28" s="17"/>
+      <c r="WMQ28" s="17"/>
+      <c r="WMR28" s="13"/>
+      <c r="WMS28" s="2"/>
+      <c r="WMY28" s="16"/>
+      <c r="WNA28" s="17"/>
+      <c r="WNB28" s="17"/>
+      <c r="WNC28" s="13"/>
+      <c r="WND28" s="2"/>
+      <c r="WNJ28" s="16"/>
+      <c r="WNL28" s="17"/>
+      <c r="WNM28" s="17"/>
+      <c r="WNN28" s="13"/>
+      <c r="WNO28" s="2"/>
+      <c r="WNU28" s="16"/>
+      <c r="WNW28" s="17"/>
+      <c r="WNX28" s="17"/>
+      <c r="WNY28" s="13"/>
+      <c r="WNZ28" s="2"/>
+      <c r="WOF28" s="16"/>
+      <c r="WOH28" s="17"/>
+      <c r="WOI28" s="17"/>
+      <c r="WOJ28" s="13"/>
+      <c r="WOK28" s="2"/>
+      <c r="WOQ28" s="16"/>
+      <c r="WOS28" s="17"/>
+      <c r="WOT28" s="17"/>
+      <c r="WOU28" s="13"/>
+      <c r="WOV28" s="2"/>
+      <c r="WPB28" s="16"/>
+      <c r="WPD28" s="17"/>
+      <c r="WPE28" s="17"/>
+      <c r="WPF28" s="13"/>
+      <c r="WPG28" s="2"/>
+      <c r="WPM28" s="16"/>
+      <c r="WPO28" s="17"/>
+      <c r="WPP28" s="17"/>
+      <c r="WPQ28" s="13"/>
+      <c r="WPR28" s="2"/>
+      <c r="WPX28" s="16"/>
+      <c r="WPZ28" s="17"/>
+      <c r="WQA28" s="17"/>
+      <c r="WQB28" s="13"/>
+      <c r="WQC28" s="2"/>
+      <c r="WQI28" s="16"/>
+      <c r="WQK28" s="17"/>
+      <c r="WQL28" s="17"/>
+      <c r="WQM28" s="13"/>
+      <c r="WQN28" s="2"/>
+      <c r="WQT28" s="16"/>
+      <c r="WQV28" s="17"/>
+      <c r="WQW28" s="17"/>
+      <c r="WQX28" s="13"/>
+      <c r="WQY28" s="2"/>
+      <c r="WRE28" s="16"/>
+      <c r="WRG28" s="17"/>
+      <c r="WRH28" s="17"/>
+      <c r="WRI28" s="13"/>
+      <c r="WRJ28" s="2"/>
+      <c r="WRP28" s="16"/>
+      <c r="WRR28" s="17"/>
+      <c r="WRS28" s="17"/>
+      <c r="WRT28" s="13"/>
+      <c r="WRU28" s="2"/>
+      <c r="WSA28" s="16"/>
+      <c r="WSC28" s="17"/>
+      <c r="WSD28" s="17"/>
+      <c r="WSE28" s="13"/>
+      <c r="WSF28" s="2"/>
+      <c r="WSL28" s="16"/>
+      <c r="WSN28" s="17"/>
+      <c r="WSO28" s="17"/>
+      <c r="WSP28" s="13"/>
+      <c r="WSQ28" s="2"/>
+      <c r="WSW28" s="16"/>
+      <c r="WSY28" s="17"/>
+      <c r="WSZ28" s="17"/>
+      <c r="WTA28" s="13"/>
+      <c r="WTB28" s="2"/>
+      <c r="WTH28" s="16"/>
+      <c r="WTJ28" s="17"/>
+      <c r="WTK28" s="17"/>
+      <c r="WTL28" s="13"/>
+      <c r="WTM28" s="2"/>
+      <c r="WTS28" s="16"/>
+      <c r="WTU28" s="17"/>
+      <c r="WTV28" s="17"/>
+      <c r="WTW28" s="13"/>
+      <c r="WTX28" s="2"/>
+      <c r="WUD28" s="16"/>
+      <c r="WUF28" s="17"/>
+      <c r="WUG28" s="17"/>
+      <c r="WUH28" s="13"/>
+      <c r="WUI28" s="2"/>
+      <c r="WUO28" s="16"/>
+      <c r="WUQ28" s="17"/>
+      <c r="WUR28" s="17"/>
+      <c r="WUS28" s="13"/>
+      <c r="WUT28" s="2"/>
+      <c r="WUZ28" s="16"/>
+      <c r="WVB28" s="17"/>
+      <c r="WVC28" s="17"/>
+      <c r="WVD28" s="13"/>
+      <c r="WVE28" s="2"/>
+      <c r="WVK28" s="16"/>
+      <c r="WVM28" s="17"/>
+      <c r="WVN28" s="17"/>
+      <c r="WVO28" s="13"/>
+      <c r="WVP28" s="2"/>
+      <c r="WVV28" s="16"/>
+      <c r="WVX28" s="17"/>
+      <c r="WVY28" s="17"/>
+      <c r="WVZ28" s="13"/>
+      <c r="WWA28" s="2"/>
+      <c r="WWG28" s="16"/>
+      <c r="WWI28" s="17"/>
+      <c r="WWJ28" s="17"/>
+      <c r="WWK28" s="13"/>
+      <c r="WWL28" s="2"/>
+      <c r="WWR28" s="16"/>
+      <c r="WWT28" s="17"/>
+      <c r="WWU28" s="17"/>
+      <c r="WWV28" s="13"/>
+      <c r="WWW28" s="2"/>
+      <c r="WXC28" s="16"/>
+      <c r="WXE28" s="17"/>
+      <c r="WXF28" s="17"/>
+      <c r="WXG28" s="13"/>
+      <c r="WXH28" s="2"/>
+      <c r="WXN28" s="16"/>
+      <c r="WXP28" s="17"/>
+      <c r="WXQ28" s="17"/>
+      <c r="WXR28" s="13"/>
+      <c r="WXS28" s="2"/>
+      <c r="WXY28" s="16"/>
+      <c r="WYA28" s="17"/>
+      <c r="WYB28" s="17"/>
+      <c r="WYC28" s="13"/>
+      <c r="WYD28" s="2"/>
+      <c r="WYJ28" s="16"/>
+      <c r="WYL28" s="17"/>
+      <c r="WYM28" s="17"/>
+      <c r="WYN28" s="13"/>
+      <c r="WYO28" s="2"/>
+      <c r="WYU28" s="16"/>
+      <c r="WYW28" s="17"/>
+      <c r="WYX28" s="17"/>
+      <c r="WYY28" s="13"/>
+      <c r="WYZ28" s="2"/>
+      <c r="WZF28" s="16"/>
+      <c r="WZH28" s="17"/>
+      <c r="WZI28" s="17"/>
+      <c r="WZJ28" s="13"/>
+      <c r="WZK28" s="2"/>
+      <c r="WZQ28" s="16"/>
+      <c r="WZS28" s="17"/>
+      <c r="WZT28" s="17"/>
+      <c r="WZU28" s="13"/>
+      <c r="WZV28" s="2"/>
+      <c r="XAB28" s="16"/>
+      <c r="XAD28" s="17"/>
+      <c r="XAE28" s="17"/>
+      <c r="XAF28" s="13"/>
+      <c r="XAG28" s="2"/>
+      <c r="XAM28" s="16"/>
+      <c r="XAO28" s="17"/>
+      <c r="XAP28" s="17"/>
+      <c r="XAQ28" s="13"/>
+      <c r="XAR28" s="2"/>
+      <c r="XAX28" s="16"/>
+      <c r="XAZ28" s="17"/>
+      <c r="XBA28" s="17"/>
+      <c r="XBB28" s="13"/>
+      <c r="XBC28" s="2"/>
+      <c r="XBI28" s="16"/>
+      <c r="XBK28" s="17"/>
+      <c r="XBL28" s="17"/>
+      <c r="XBM28" s="13"/>
+      <c r="XBN28" s="2"/>
+      <c r="XBT28" s="16"/>
+      <c r="XBV28" s="17"/>
+      <c r="XBW28" s="17"/>
+      <c r="XBX28" s="13"/>
+      <c r="XBY28" s="2"/>
+      <c r="XCE28" s="16"/>
+      <c r="XCG28" s="17"/>
+      <c r="XCH28" s="17"/>
+      <c r="XCI28" s="13"/>
+      <c r="XCJ28" s="2"/>
+      <c r="XCP28" s="16"/>
+      <c r="XCR28" s="17"/>
+      <c r="XCS28" s="17"/>
+      <c r="XCT28" s="13"/>
+      <c r="XCU28" s="2"/>
+      <c r="XDA28" s="16"/>
+      <c r="XDC28" s="17"/>
+      <c r="XDD28" s="17"/>
+      <c r="XDE28" s="13"/>
+      <c r="XDF28" s="2"/>
+      <c r="XDL28" s="16"/>
+      <c r="XDN28" s="17"/>
+      <c r="XDO28" s="17"/>
+      <c r="XDP28" s="13"/>
+      <c r="XDQ28" s="2"/>
+      <c r="XDW28" s="16"/>
+      <c r="XDY28" s="17"/>
+      <c r="XDZ28" s="17"/>
+      <c r="XEA28" s="13"/>
+      <c r="XEB28" s="2"/>
+      <c r="XEH28" s="16"/>
+      <c r="XEJ28" s="17"/>
+      <c r="XEK28" s="17"/>
+      <c r="XEL28" s="13"/>
+      <c r="XEM28" s="2"/>
+      <c r="XES28" s="16"/>
+      <c r="XEU28" s="17"/>
+      <c r="XEV28" s="17"/>
+      <c r="XEW28" s="13"/>
+      <c r="XEX28" s="2"/>
+      <c r="XFD28" s="16"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:12">
+    <row r="29" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2474,7 +9915,7 @@
       <c r="D29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F29" s="2">
@@ -2494,7 +9935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:12">
+    <row r="30" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2505,7 +9946,7 @@
       <c r="D30" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="18" t="s">
         <v>82</v>
       </c>
       <c r="F30" s="2">
@@ -2525,7 +9966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:12">
+    <row r="31" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2536,7 +9977,7 @@
       <c r="D31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="18" t="s">
         <v>84</v>
       </c>
       <c r="F31" s="2">
@@ -2556,7 +9997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:12">
+    <row r="32" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2567,7 +10008,7 @@
       <c r="D32" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>86</v>
       </c>
       <c r="F32" s="2">
@@ -2597,16 +10038,16 @@
       <c r="D33" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>88</v>
       </c>
       <c r="F33" s="3">
         <v>21</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="18"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="13" t="s">
         <v>27</v>
       </c>
@@ -2634,7 +10075,7 @@
       <c r="F34" s="3">
         <v>22</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
@@ -2642,7 +10083,7 @@
         <v>27</v>
       </c>
       <c r="J34" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -10082,8 +10082,8 @@
       <c r="I34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J34" s="3" t="b">
-        <v>0</v>
+      <c r="J34" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -10082,8 +10082,8 @@
       <c r="I34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J34" s="13" t="b">
-        <v>1</v>
+      <c r="J34" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -10082,8 +10082,8 @@
       <c r="I34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J34" s="2" t="b">
-        <v>0</v>
+      <c r="J34" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2256,7 +2256,7 @@
         <v>63</v>
       </c>
       <c r="F22" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
@@ -2288,7 +2288,7 @@
         <v>65</v>
       </c>
       <c r="F23" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
@@ -2320,7 +2320,7 @@
         <v>67</v>
       </c>
       <c r="F24" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="14">
         <v>1</v>
@@ -2352,7 +2352,7 @@
         <v>69</v>
       </c>
       <c r="F25" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>70</v>
@@ -2384,7 +2384,7 @@
         <v>73</v>
       </c>
       <c r="F26" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" s="14">
         <v>1</v>
@@ -2416,7 +2416,7 @@
         <v>75</v>
       </c>
       <c r="F27" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>26</v>
@@ -2447,7 +2447,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="17">
         <v>1</v>
@@ -9919,7 +9919,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
@@ -9950,7 +9950,7 @@
         <v>82</v>
       </c>
       <c r="F30" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         <v>84</v>
       </c>
       <c r="F31" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
@@ -10012,7 +10012,7 @@
         <v>86</v>
       </c>
       <c r="F32" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" s="15">
         <v>1</v>
@@ -10042,7 +10042,7 @@
         <v>88</v>
       </c>
       <c r="F33" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
@@ -10073,7 +10073,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -1933,7 +1933,7 @@
       <c r="I12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="11" t="b">
+      <c r="J12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="11"/>
@@ -1992,7 +1992,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E1AA58-00E9-4E79-B466-F396374A1558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -24,23 +30,27 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -49,6 +59,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +67,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -71,6 +83,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -80,13 +93,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -95,6 +109,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,13 +118,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -118,6 +134,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -125,13 +142,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -140,6 +158,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -148,13 +167,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -163,6 +183,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -173,13 +194,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -188,6 +210,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -197,13 +220,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -212,6 +236,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -222,13 +247,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -237,6 +263,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -244,13 +271,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -259,6 +287,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -552,14 +581,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,194 +595,65 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,198 +662,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -967,251 +681,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1274,61 +746,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1578,31 +1006,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XFD35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="4" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="4" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
+    <col min="8" max="8" width="19.75" style="5" customWidth="1"/>
     <col min="9" max="9" width="11.875" style="4" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="26" style="4" customWidth="1"/>
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
@@ -1673,7 +1101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1706,7 +1134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1719,7 +1147,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -1745,7 +1173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6" s="11">
         <v>2</v>
       </c>
@@ -1773,7 +1201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" s="11">
         <v>3</v>
       </c>
@@ -1801,7 +1229,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" s="11">
         <v>4</v>
       </c>
@@ -1833,7 +1261,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" s="11">
         <v>5</v>
       </c>
@@ -1861,7 +1289,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" s="11">
         <v>6</v>
       </c>
@@ -1889,7 +1317,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" s="11">
         <v>7</v>
       </c>
@@ -1915,7 +1343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12" s="11">
         <v>8</v>
       </c>
@@ -1933,15 +1361,15 @@
       <c r="I12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="2" t="b">
-        <v>0</v>
+      <c r="J12" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13" s="11">
         <v>9</v>
       </c>
@@ -1967,7 +1395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14" s="11">
         <v>10</v>
       </c>
@@ -1999,7 +1427,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15" s="13">
         <v>101</v>
       </c>
@@ -2035,7 +1463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16" s="13">
         <v>102</v>
       </c>
@@ -2069,7 +1497,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="17" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A17" s="13">
         <v>103</v>
       </c>
@@ -2105,7 +1533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="18" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A18" s="13">
         <v>104</v>
       </c>
@@ -2139,7 +1567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="19" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A19" s="13">
         <v>105</v>
       </c>
@@ -2171,7 +1599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="20" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A20" s="13">
         <v>106</v>
       </c>
@@ -2205,7 +1633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="21" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A21" s="13">
         <v>107</v>
       </c>
@@ -2239,7 +1667,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="22" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A22" s="13">
         <v>108</v>
       </c>
@@ -2273,7 +1701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="23" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A23" s="13">
         <v>109</v>
       </c>
@@ -2305,7 +1733,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="24" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A24" s="13">
         <v>110</v>
       </c>
@@ -2337,7 +1765,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="25" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A25" s="13">
         <v>111</v>
       </c>
@@ -2369,7 +1797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="26" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" x14ac:dyDescent="0.15">
       <c r="A26" s="13">
         <v>112</v>
       </c>
@@ -2401,14 +1829,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="27" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>113</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
       </c>
-      <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
         <v>74</v>
       </c>
@@ -2432,14 +1859,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="28" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3">
         <v>114</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
       </c>
-      <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
         <v>77</v>
       </c>
@@ -9904,14 +9330,13 @@
       <c r="XEX28" s="2"/>
       <c r="XFD28" s="16"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="29" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
         <v>115</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
       </c>
-      <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
         <v>79</v>
       </c>
@@ -9935,14 +9360,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="30" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>116</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
       </c>
-      <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
         <v>81</v>
       </c>
@@ -9966,14 +9390,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="31" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>117</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
-      <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
         <v>83</v>
       </c>
@@ -9997,14 +9420,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384">
+    <row r="32" spans="1:1022 1028:2045 2051:3068 3074:4091 4097:5120 5122:6143 6145:10240 10246:11263 11269:12286 12292:13309 13315:14332 14338:15355 15361:16384" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
         <v>118</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
       </c>
-      <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
         <v>85</v>
       </c>
@@ -10028,7 +9450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:12">
+    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -10058,7 +9480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -10090,7 +9512,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -10118,33 +9540,31 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -1934,7 +1934,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -1934,7 +1934,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -547,6 +547,9 @@
   </si>
   <si>
     <t>买一送七</t>
+  </si>
+  <si>
+    <t>新手赠送</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1602,7 +1605,7 @@
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
@@ -1673,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -2674,6 +2677,21 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="4">
+        <v>122</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -318,6 +318,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>map&lt;int{_}int&gt;{;}</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -396,7 +399,7 @@
     <t>私人房间</t>
   </si>
   <si>
-    <t>1_15</t>
+    <t>1_15;3_1</t>
   </si>
   <si>
     <t>商城界面</t>
@@ -1598,7 +1601,7 @@
     <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="4" customWidth="1"/>
     <col min="11" max="11" width="11.9083333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="26" style="4" customWidth="1"/>
@@ -1667,10 +1670,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>12</v>
@@ -1681,32 +1684,32 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1729,23 +1732,23 @@
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1757,23 +1760,23 @@
         <v>3</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1785,7 +1788,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1794,14 +1797,14 @@
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1813,10 +1816,10 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="11">
         <v>5</v>
@@ -1826,14 +1829,14 @@
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1845,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -1854,14 +1857,14 @@
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1871,10 +1874,10 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="12">
@@ -1882,14 +1885,14 @@
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1899,7 +1902,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -1908,14 +1911,14 @@
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1925,7 +1928,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -1934,14 +1937,14 @@
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="2" t="b">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="J12" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1951,23 +1954,23 @@
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1979,10 +1982,10 @@
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" s="11">
         <v>4</v>
@@ -1992,14 +1995,14 @@
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2011,22 +2014,22 @@
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="14">
         <v>1</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" s="2" t="b">
         <v>0</v>
@@ -2035,7 +2038,7 @@
         <v>47061</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2049,10 +2052,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="13">
         <v>2</v>
@@ -2062,14 +2065,14 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2083,29 +2086,29 @@
         <v>5</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="13">
         <v>9</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
         <v>2</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2119,27 +2122,27 @@
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K18" s="13"/>
       <c r="L18" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2151,27 +2154,27 @@
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="13">
         <v>6</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K19" s="13"/>
       <c r="L19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2185,10 +2188,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="13">
         <v>7</v>
@@ -2198,14 +2201,14 @@
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2219,10 +2222,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" s="13">
         <v>8</v>
@@ -2232,14 +2235,14 @@
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K21" s="13"/>
       <c r="L21" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2253,10 +2256,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="13">
         <v>11</v>
@@ -2266,14 +2269,14 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K22" s="13"/>
       <c r="L22" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2285,10 +2288,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" s="13">
         <v>12</v>
@@ -2298,14 +2301,14 @@
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J23" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2317,10 +2320,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="13">
         <v>13</v>
@@ -2330,14 +2333,14 @@
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J24" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K24" s="13"/>
       <c r="L24" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2349,27 +2352,27 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F25" s="13">
         <v>14</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2381,10 +2384,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2394,14 +2397,14 @@
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K26" s="13"/>
       <c r="L26" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:12">
@@ -2413,26 +2416,26 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:12">
@@ -2444,10 +2447,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2457,13 +2460,13 @@
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:12">
@@ -2475,10 +2478,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2488,13 +2491,13 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:12">
@@ -2506,10 +2509,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2519,13 +2522,13 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:12">
@@ -2537,10 +2540,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2550,13 +2553,13 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:12">
@@ -2568,10 +2571,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2581,13 +2584,13 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:12">
@@ -2598,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2611,13 +2614,13 @@
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2629,10 +2632,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2642,14 +2645,14 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" s="13" t="b">
         <v>1</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2660,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2669,26 +2672,25 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="4">
         <v>122</v>
       </c>
-      <c r="B36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J36" s="2" t="b">
         <v>0</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -430,9 +430,6 @@
   </si>
   <si>
     <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>1_25</t>
   </si>
   <si>
     <t>储钱罐</t>
@@ -1997,8 +1994,8 @@
       <c r="I14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
+      <c r="J14" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
@@ -2101,10 +2098,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="2" t="b">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="J17" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="4" t="s">
@@ -2122,10 +2119,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
@@ -2154,10 +2151,10 @@
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="F19" s="13">
         <v>6</v>
@@ -2167,7 +2164,7 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J19" s="2" t="b">
         <v>0</v>
@@ -2188,10 +2185,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="F20" s="13">
         <v>7</v>
@@ -2222,10 +2219,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="F21" s="13">
         <v>8</v>
@@ -2256,10 +2253,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="F22" s="13">
         <v>11</v>
@@ -2288,10 +2285,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="F23" s="13">
         <v>12</v>
@@ -2320,10 +2317,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>68</v>
       </c>
       <c r="F24" s="13">
         <v>13</v>
@@ -2352,16 +2349,16 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="F25" s="13">
         <v>14</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
@@ -2372,7 +2369,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2384,10 +2381,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2416,10 +2413,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2429,7 +2426,7 @@
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2447,10 +2444,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>78</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2478,10 +2475,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>80</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>81</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2491,7 +2488,7 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2509,10 +2506,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>82</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2522,7 +2519,7 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2540,10 +2537,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>85</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2553,7 +2550,7 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2571,10 +2568,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>87</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2584,7 +2581,7 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
@@ -2601,10 +2598,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>88</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2632,10 +2629,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2663,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2687,7 +2684,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>28</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>1_25</t>
   </si>
   <si>
     <t>储钱罐</t>
@@ -1994,8 +1997,8 @@
       <c r="I14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="11" t="b">
-        <v>1</v>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
@@ -2098,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="11" t="b">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="4" t="s">
@@ -2119,10 +2122,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
@@ -2151,10 +2154,10 @@
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="13">
         <v>6</v>
@@ -2164,7 +2167,7 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" s="2" t="b">
         <v>0</v>
@@ -2185,10 +2188,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="13">
         <v>7</v>
@@ -2219,10 +2222,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" s="13">
         <v>8</v>
@@ -2253,10 +2256,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="13">
         <v>11</v>
@@ -2285,10 +2288,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" s="13">
         <v>12</v>
@@ -2317,10 +2320,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="13">
         <v>13</v>
@@ -2349,16 +2352,16 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F25" s="13">
         <v>14</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
@@ -2369,7 +2372,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2381,10 +2384,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2413,10 +2416,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2426,7 +2429,7 @@
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2444,10 +2447,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2475,10 +2478,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2488,7 +2491,7 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2506,10 +2509,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2519,7 +2522,7 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2537,10 +2540,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2550,7 +2553,7 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2568,10 +2571,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2581,7 +2584,7 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
@@ -2598,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2629,10 +2632,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2660,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2684,7 +2687,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>28</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -481,9 +481,6 @@
   </si>
   <si>
     <t>Grid (6)</t>
-  </si>
-  <si>
-    <t>1_3</t>
   </si>
   <si>
     <t>显示位置：大厅+登陆界面</t>
@@ -2019,12 +2016,10 @@
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="14">
-        <v>1</v>
-      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14"/>
       <c r="I15" s="13" t="s">
         <v>48</v>
       </c>
@@ -2091,12 +2086,10 @@
       <c r="F17" s="13">
         <v>9</v>
       </c>
-      <c r="G17" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="14">
-        <v>2</v>
-      </c>
+      <c r="G17" s="14">
+        <v>1</v>
+      </c>
+      <c r="H17" s="14"/>
       <c r="I17" s="13" t="s">
         <v>28</v>
       </c>
@@ -2127,8 +2120,8 @@
       <c r="F18" s="13">
         <v>3</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>27</v>
+      <c r="G18" s="14">
+        <v>1</v>
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="13" t="s">
@@ -2159,8 +2152,8 @@
       <c r="F19" s="13">
         <v>6</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>27</v>
+      <c r="G19" s="14">
+        <v>1</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
@@ -2357,8 +2350,8 @@
       <c r="F25" s="13">
         <v>14</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>70</v>
+      <c r="G25" s="14">
+        <v>1</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
@@ -2369,7 +2362,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2381,10 +2374,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>73</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2413,20 +2406,20 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>27</v>
+      <c r="G27" s="15">
+        <v>1</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2444,10 +2437,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>78</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2475,10 +2468,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>80</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2488,7 +2481,7 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2506,10 +2499,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>82</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2519,7 +2512,7 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2537,10 +2530,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>84</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2550,7 +2543,7 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2568,10 +2561,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>85</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2581,7 +2574,7 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
@@ -2598,10 +2591,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>87</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>88</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2629,10 +2622,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2660,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2684,7 +2677,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>28</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -432,9 +432,6 @@
     <t>Grid (10)</t>
   </si>
   <si>
-    <t>1_25</t>
-  </si>
-  <si>
     <t>储钱罐</t>
   </si>
   <si>
@@ -484,9 +481,6 @@
   </si>
   <si>
     <t>Grid (6)</t>
-  </si>
-  <si>
-    <t>1_3</t>
   </si>
   <si>
     <t>显示位置：大厅+登陆界面</t>
@@ -1997,8 +1991,8 @@
       <c r="I14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
+      <c r="J14" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="4" t="s">
@@ -2022,12 +2016,10 @@
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="14">
-        <v>1</v>
-      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14"/>
       <c r="I15" s="13" t="s">
         <v>48</v>
       </c>
@@ -2094,17 +2086,15 @@
       <c r="F17" s="13">
         <v>9</v>
       </c>
-      <c r="G17" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="14">
-        <v>2</v>
-      </c>
+      <c r="G17" s="14">
+        <v>1</v>
+      </c>
+      <c r="H17" s="14"/>
       <c r="I17" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="2" t="b">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="J17" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="4" t="s">
@@ -2122,16 +2112,16 @@
         <v>4</v>
       </c>
       <c r="D18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>27</v>
+      <c r="G18" s="14">
+        <v>1</v>
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="13" t="s">
@@ -2154,20 +2144,20 @@
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="F19" s="13">
         <v>6</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>27</v>
+      <c r="G19" s="14">
+        <v>1</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J19" s="2" t="b">
         <v>0</v>
@@ -2188,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="F20" s="13">
         <v>7</v>
@@ -2222,10 +2212,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="F21" s="13">
         <v>8</v>
@@ -2256,10 +2246,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="F22" s="13">
         <v>11</v>
@@ -2288,10 +2278,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="F23" s="13">
         <v>12</v>
@@ -2320,10 +2310,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>68</v>
       </c>
       <c r="F24" s="13">
         <v>13</v>
@@ -2352,16 +2342,16 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="F25" s="13">
         <v>14</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>71</v>
+      <c r="G25" s="14">
+        <v>1</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
@@ -2372,7 +2362,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2384,10 +2374,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2416,20 +2406,20 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>27</v>
+      <c r="G27" s="15">
+        <v>1</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2447,10 +2437,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2478,10 +2468,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2491,7 +2481,7 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2509,10 +2499,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2522,7 +2512,7 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2540,10 +2530,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2553,7 +2543,7 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2571,10 +2561,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2584,7 +2574,7 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
@@ -2601,10 +2591,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2632,10 +2622,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2663,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2687,7 +2677,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>28</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2093,8 +2093,8 @@
       <c r="I17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="11" t="b">
-        <v>1</v>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2261,8 +2261,8 @@
       <c r="I22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="2" t="b">
-        <v>0</v>
+      <c r="J22" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="K22" s="13"/>
       <c r="L22" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>Grid (3)</t>
+  </si>
+  <si>
+    <t>4_1</t>
   </si>
   <si>
     <t>邮箱</t>
@@ -2259,7 +2262,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="13" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="J22" s="13" t="b">
         <v>1</v>
@@ -2278,10 +2281,10 @@
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" s="13">
         <v>12</v>
@@ -2310,10 +2313,10 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="13">
         <v>13</v>
@@ -2342,10 +2345,10 @@
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F25" s="13">
         <v>14</v>
@@ -2362,7 +2365,7 @@
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2374,10 +2377,10 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F26" s="13">
         <v>15</v>
@@ -2406,10 +2409,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2419,7 +2422,7 @@
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2437,10 +2440,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2468,10 +2471,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2481,7 +2484,7 @@
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J29" s="2" t="b">
         <v>0</v>
@@ -2499,10 +2502,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2512,7 +2515,7 @@
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J30" s="2" t="b">
         <v>0</v>
@@ -2530,10 +2533,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2543,7 +2546,7 @@
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2" t="b">
         <v>0</v>
@@ -2561,10 +2564,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2574,7 +2577,7 @@
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J32" s="2" t="b">
         <v>0</v>
@@ -2591,10 +2594,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2622,10 +2625,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2653,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2677,7 +2680,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>28</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -240,11 +240,36 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+条件类型_条件参数
+condition表中条件类型
+注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -345,12 +370,21 @@
     <t>vipLevel</t>
   </si>
   <si>
+    <t>condition</t>
+  </si>
+  <si>
     <t>isOpen</t>
   </si>
   <si>
     <t>tips</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>server</t>
+  </si>
+  <si>
     <t>小游戏</t>
   </si>
   <si>
@@ -360,6 +394,9 @@
     <t>1_1</t>
   </si>
   <si>
+    <t>playerLevel(1)</t>
+  </si>
+  <si>
     <t>显示位置：大厅 + 各游戏区</t>
   </si>
   <si>
@@ -369,12 +406,18 @@
     <t>1_5</t>
   </si>
   <si>
+    <t>playerLevel(5)</t>
+  </si>
+  <si>
     <t>官方派奖</t>
   </si>
   <si>
     <t>1_10</t>
   </si>
   <si>
+    <t>playerLevel(10)</t>
+  </si>
+  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -402,6 +445,9 @@
     <t>1_15;3_1</t>
   </si>
   <si>
+    <t>AND(playerLevel(15),playerVipLevel(1))</t>
+  </si>
+  <si>
     <t>商城界面</t>
   </si>
   <si>
@@ -420,6 +466,9 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
     <t>每日奖金</t>
   </si>
   <si>
@@ -447,6 +496,9 @@
     <t>1_30</t>
   </si>
   <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
     <t>首充礼包</t>
   </si>
   <si>
@@ -468,6 +520,9 @@
     <t>4_1</t>
   </si>
   <si>
+    <t>bindPhone()</t>
+  </si>
+  <si>
     <t>邮箱</t>
   </si>
   <si>
@@ -502,6 +557,9 @@
   </si>
   <si>
     <t>1_999</t>
+  </si>
+  <si>
+    <t>playerLevel(999)</t>
   </si>
   <si>
     <t>每日充值</t>
@@ -562,7 +620,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,7 +654,32 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -751,18 +834,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,6 +855,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1088,137 +1177,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1237,13 +1326,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1252,17 +1347,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1587,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1599,808 +1703,889 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="12" max="12" width="26" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="10" max="10" width="40.375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="13" max="13" width="26" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="11">
-        <v>1</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11" t="s">
+      <c r="L3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11" t="s">
+      <c r="J4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="2" t="b">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="14">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="11">
+      <c r="L5" s="14"/>
+      <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14">
         <v>3</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="11" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="14"/>
+      <c r="M6" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="14">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14">
+        <v>9</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="14">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="14">
+        <v>5</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="11">
+      <c r="J8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="14">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14">
+        <v>6</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="14">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="14">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="14">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="14">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="14"/>
+      <c r="M13" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="14">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="14">
+        <v>4</v>
+      </c>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="17">
+        <v>101</v>
+      </c>
+      <c r="B15" s="17">
+        <v>1</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="17">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="17">
+        <v>47061</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="17">
+        <v>102</v>
+      </c>
+      <c r="B16" s="17">
+        <v>1</v>
+      </c>
+      <c r="C16" s="17">
+        <v>2</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2</v>
+      </c>
+      <c r="G16" s="18">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17"/>
+      <c r="M16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="17">
+        <v>103</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17">
+        <v>5</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="17">
+        <v>9</v>
+      </c>
+      <c r="G17" s="18">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="17"/>
+      <c r="M17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="17">
+        <v>104</v>
+      </c>
+      <c r="B18" s="17">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17">
+        <v>4</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11">
-        <v>9</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="G18" s="18">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="11" t="s">
+      <c r="K18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="17"/>
+      <c r="M18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="11">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>1</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="17">
+        <v>105</v>
+      </c>
+      <c r="B19" s="17">
+        <v>1</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="17">
+        <v>6</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="17"/>
+      <c r="M19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="17">
+        <v>106</v>
+      </c>
+      <c r="B20" s="17">
+        <v>1</v>
+      </c>
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="17">
+        <v>7</v>
+      </c>
+      <c r="G20" s="18">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="J20" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="11">
-        <v>5</v>
-      </c>
-      <c r="G8" s="12">
-        <v>1</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="11">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11">
-        <v>6</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="11">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11" t="s">
+      <c r="K20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17"/>
+      <c r="M20" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="17">
+        <v>107</v>
+      </c>
+      <c r="B21" s="17">
+        <v>1</v>
+      </c>
+      <c r="C21" s="17">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="17">
+        <v>8</v>
+      </c>
+      <c r="G21" s="18">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="J21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12">
-        <v>1</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="11">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="s">
+      <c r="K21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="17"/>
+      <c r="M21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12">
-        <v>1</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="11">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="11">
-        <v>9</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="11">
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="17">
+        <v>108</v>
+      </c>
+      <c r="B22" s="17">
+        <v>1</v>
+      </c>
+      <c r="C22" s="17">
         <v>10</v>
       </c>
-      <c r="B14" s="11">
-        <v>1</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="11">
-        <v>4</v>
-      </c>
-      <c r="G14" s="12">
-        <v>1</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="13">
-        <v>101</v>
-      </c>
-      <c r="B15" s="13">
-        <v>1</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="13">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="13">
-        <v>47061</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="13">
-        <v>102</v>
-      </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="13">
-        <v>2</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="13">
-        <v>103</v>
-      </c>
-      <c r="B17" s="13">
-        <v>1</v>
-      </c>
-      <c r="C17" s="13">
-        <v>5</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="13">
-        <v>9</v>
-      </c>
-      <c r="G17" s="14">
-        <v>1</v>
-      </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13"/>
-      <c r="L17" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="13">
-        <v>104</v>
-      </c>
-      <c r="B18" s="13">
-        <v>1</v>
-      </c>
-      <c r="C18" s="13">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="13">
-        <v>3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>1</v>
-      </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13"/>
-      <c r="L18" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="13">
-        <v>105</v>
-      </c>
-      <c r="B19" s="13">
-        <v>1</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="13">
-        <v>6</v>
-      </c>
-      <c r="G19" s="14">
-        <v>1</v>
-      </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="13"/>
-      <c r="L19" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="13">
-        <v>106</v>
-      </c>
-      <c r="B20" s="13">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13">
+      <c r="D22" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="17">
         <v>11</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="13">
-        <v>7</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="13" t="s">
+      <c r="G22" s="18">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="17"/>
+      <c r="M22" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="17">
+        <v>109</v>
+      </c>
+      <c r="B23" s="17">
+        <v>1</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="17">
+        <v>12</v>
+      </c>
+      <c r="G23" s="18">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13"/>
-      <c r="L20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="13">
-        <v>107</v>
-      </c>
-      <c r="B21" s="13">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13">
+      <c r="J23" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17"/>
+      <c r="M23" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="17">
+        <v>110</v>
+      </c>
+      <c r="B24" s="17">
+        <v>1</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="17">
+        <v>13</v>
+      </c>
+      <c r="G24" s="18">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="17"/>
+      <c r="M24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="17">
+        <v>111</v>
+      </c>
+      <c r="B25" s="17">
+        <v>1</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="17">
+        <v>14</v>
+      </c>
+      <c r="G25" s="18">
+        <v>1</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="17"/>
+      <c r="M25" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="17">
+        <v>112</v>
+      </c>
+      <c r="B26" s="17">
+        <v>1</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="17">
         <v>15</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="13">
-        <v>8</v>
-      </c>
-      <c r="G21" s="14">
-        <v>1</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="13"/>
-      <c r="L21" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="13">
-        <v>108</v>
-      </c>
-      <c r="B22" s="13">
-        <v>1</v>
-      </c>
-      <c r="C22" s="13">
-        <v>10</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="13">
-        <v>11</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="13"/>
-      <c r="L22" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="13">
-        <v>109</v>
-      </c>
-      <c r="B23" s="13">
-        <v>1</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="13">
-        <v>12</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="13"/>
-      <c r="L23" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="13">
-        <v>110</v>
-      </c>
-      <c r="B24" s="13">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="13">
-        <v>13</v>
-      </c>
-      <c r="G24" s="14">
-        <v>1</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="13"/>
-      <c r="L24" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="13">
-        <v>111</v>
-      </c>
-      <c r="B25" s="13">
-        <v>1</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="13">
-        <v>14</v>
-      </c>
-      <c r="G25" s="14">
-        <v>1</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="13"/>
-      <c r="L25" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="13">
-        <v>112</v>
-      </c>
-      <c r="B26" s="13">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="13">
-        <v>15</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1</v>
-      </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="13"/>
-      <c r="L26" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:12">
+      <c r="G26" s="18">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="17"/>
+      <c r="M26" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:13">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2409,29 +2594,32 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15"/>
+      <c r="G27" s="20">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20"/>
       <c r="I27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:12">
+      <c r="M27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:13">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2440,29 +2628,32 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="17">
-        <v>1</v>
-      </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="2" t="b">
+      <c r="G28" s="22">
+        <v>1</v>
+      </c>
+      <c r="H28" s="22"/>
+      <c r="I28" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:12">
+      <c r="M28" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:13">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2471,29 +2662,32 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>80</v>
+        <v>90</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>91</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15"/>
+      <c r="G29" s="20">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20"/>
       <c r="I29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J29" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:12">
+      <c r="M29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:13">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2502,29 +2696,32 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>82</v>
+        <v>92</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15"/>
+      <c r="G30" s="20">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20"/>
       <c r="I30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J30" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:12">
+      <c r="M30" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:13">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2533,29 +2730,32 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>84</v>
+        <v>94</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15"/>
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20"/>
       <c r="I31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:12">
+      <c r="M31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:13">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2564,29 +2764,32 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>86</v>
+        <v>96</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>97</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="15">
-        <v>1</v>
-      </c>
-      <c r="H32" s="15"/>
+      <c r="G32" s="20">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20"/>
       <c r="I32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J32" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:12">
+      <c r="M32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:13">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2594,29 +2797,32 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>88</v>
+        <v>98</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="17">
-        <v>1</v>
-      </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="2" t="b">
+      <c r="G33" s="22">
+        <v>1</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2625,30 +2831,33 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="22">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>31</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2656,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2665,27 +2874,33 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="2" t="b">
+        <v>31</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="L35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="2" t="b">
+        <v>31</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -296,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -412,115 +412,109 @@
     <t>官方派奖</t>
   </si>
   <si>
+    <t>显示位置：大厅</t>
+  </si>
+  <si>
+    <t>积分大奖</t>
+  </si>
+  <si>
+    <t>Grid (19)</t>
+  </si>
+  <si>
+    <t>分享推广</t>
+  </si>
+  <si>
+    <t>VIP功能</t>
+  </si>
+  <si>
+    <t>Grid (20)</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>私人房间</t>
+  </si>
+  <si>
+    <t>1_15;3_1</t>
+  </si>
+  <si>
+    <t>AND(playerLevel(15),playerVipLevel(1))</t>
+  </si>
+  <si>
+    <t>商城界面</t>
+  </si>
+  <si>
+    <t>幸运夺宝</t>
+  </si>
+  <si>
+    <t>Grid (21)</t>
+  </si>
+  <si>
+    <t>我的赌场</t>
+  </si>
+  <si>
+    <t>Grid (8)</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>刮刮乐</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>等级礼包</t>
+  </si>
+  <si>
+    <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>首充礼包</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>成长基金</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
     <t>1_10</t>
   </si>
   <si>
     <t>playerLevel(10)</t>
   </si>
   <si>
-    <t>显示位置：大厅</t>
-  </si>
-  <si>
-    <t>积分大奖</t>
-  </si>
-  <si>
-    <t>Grid (19)</t>
-  </si>
-  <si>
-    <t>分享推广</t>
-  </si>
-  <si>
-    <t>VIP功能</t>
-  </si>
-  <si>
-    <t>Grid (20)</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>私人房间</t>
-  </si>
-  <si>
-    <t>1_15;3_1</t>
-  </si>
-  <si>
-    <t>AND(playerLevel(15),playerVipLevel(1))</t>
-  </si>
-  <si>
-    <t>商城界面</t>
-  </si>
-  <si>
-    <t>幸运夺宝</t>
-  </si>
-  <si>
-    <t>Grid (21)</t>
-  </si>
-  <si>
-    <t>我的赌场</t>
-  </si>
-  <si>
-    <t>Grid (8)</t>
-  </si>
-  <si>
-    <t>1_20</t>
-  </si>
-  <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包</t>
-  </si>
-  <si>
-    <t>Grid (2)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>首充礼包</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>成长基金</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
     <t>签到奖励</t>
   </si>
   <si>
     <t>Grid (3)</t>
-  </si>
-  <si>
-    <t>4_1</t>
-  </si>
-  <si>
-    <t>bindPhone()</t>
   </si>
   <si>
     <t>邮箱</t>
@@ -620,7 +614,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -654,32 +648,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -834,18 +803,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,12 +824,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1177,137 +1140,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,19 +1289,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1347,26 +1304,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1703,7 +1654,7 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="40.375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
     <col min="13" max="13" width="26" style="4" customWidth="1"/>
@@ -1711,40 +1662,40 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1752,436 +1703,436 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="11" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="14">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14" t="s">
+      <c r="A5" s="12">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="14" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="12" t="s">
         <v>32</v>
       </c>
       <c r="K5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="14"/>
+      <c r="L5" s="12"/>
       <c r="M5" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="14">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12">
         <v>3</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15" t="s">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="14" t="s">
+      <c r="H6" s="13"/>
+      <c r="I6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="14"/>
+      <c r="K6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="12"/>
       <c r="M6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="14">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12">
         <v>9</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="16" t="s">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="12">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="4" t="s">
+      <c r="E8" s="12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="14">
-        <v>4</v>
-      </c>
-      <c r="B8" s="14">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="12">
+        <v>5</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="12">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="12">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="14">
-        <v>5</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14" t="s">
+      <c r="E10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="14">
-        <v>5</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14">
-        <v>6</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15">
-        <v>1</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14" t="s">
+      <c r="K10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="12">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="14">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="K11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15">
-        <v>1</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="14" t="s">
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="12">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="14">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15">
-        <v>1</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="14">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15">
-        <v>1</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="14"/>
-      <c r="M12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="14">
-        <v>9</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="14"/>
+      <c r="K13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12"/>
       <c r="M13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="14">
+      <c r="A14" s="12">
         <v>10</v>
       </c>
-      <c r="B14" s="14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14" t="s">
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="12">
+        <v>4</v>
+      </c>
+      <c r="G14" s="13">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="14">
+        <v>101</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E15" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="14">
-        <v>4</v>
-      </c>
-      <c r="G14" s="15">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="14"/>
-      <c r="M14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="17">
-        <v>101</v>
-      </c>
-      <c r="B15" s="17">
-        <v>1</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17" t="s">
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="J15" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="F15" s="17">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18">
-        <v>1</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="14">
         <v>47061</v>
       </c>
       <c r="M15" s="4" t="s">
@@ -2189,400 +2140,400 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="17">
+      <c r="A16" s="14">
         <v>102</v>
       </c>
-      <c r="B16" s="17">
-        <v>1</v>
-      </c>
-      <c r="C16" s="17">
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="17">
+      <c r="D16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="G16" s="18">
-        <v>1</v>
-      </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="17" t="s">
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="17"/>
+      <c r="L16" s="14"/>
       <c r="M16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="17">
+      <c r="A17" s="14">
         <v>103</v>
       </c>
-      <c r="B17" s="17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="17">
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+      <c r="C17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="17">
+      <c r="D17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="14">
         <v>9</v>
       </c>
-      <c r="G17" s="18">
-        <v>1</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="17" t="s">
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K17" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="17"/>
+      <c r="L17" s="14"/>
       <c r="M17" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="17">
+      <c r="A18" s="14">
         <v>104</v>
       </c>
-      <c r="B18" s="17">
-        <v>1</v>
-      </c>
-      <c r="C18" s="17">
+      <c r="B18" s="14">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="17">
+      <c r="D18" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="G18" s="18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="17" t="s">
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K18" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="17"/>
+      <c r="L18" s="14"/>
       <c r="M18" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="17">
+      <c r="A19" s="14">
         <v>105</v>
       </c>
-      <c r="B19" s="17">
-        <v>1</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17" t="s">
+      <c r="B19" s="14">
+        <v>1</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="14">
+        <v>6</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="J19" s="14" t="s">
         <v>64</v>
-      </c>
-      <c r="F19" s="17">
-        <v>6</v>
-      </c>
-      <c r="G19" s="18">
-        <v>1</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>66</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L19" s="17"/>
+      <c r="L19" s="14"/>
       <c r="M19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="17">
+      <c r="A20" s="14">
         <v>106</v>
       </c>
-      <c r="B20" s="17">
-        <v>1</v>
-      </c>
-      <c r="C20" s="17">
+      <c r="B20" s="14">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14">
         <v>11</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="17">
+      <c r="D20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="14">
         <v>7</v>
       </c>
-      <c r="G20" s="18">
-        <v>1</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="17" t="s">
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="14" t="s">
         <v>36</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="17"/>
+      <c r="L20" s="14"/>
       <c r="M20" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="17">
+      <c r="A21" s="14">
         <v>107</v>
       </c>
-      <c r="B21" s="17">
-        <v>1</v>
-      </c>
-      <c r="C21" s="17">
+      <c r="B21" s="14">
+        <v>1</v>
+      </c>
+      <c r="C21" s="14">
         <v>15</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="14">
+        <v>8</v>
+      </c>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="J21" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="F21" s="17">
-        <v>8</v>
-      </c>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>39</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L21" s="17"/>
+      <c r="L21" s="14"/>
       <c r="M21" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="17">
+      <c r="A22" s="14">
         <v>108</v>
       </c>
-      <c r="B22" s="17">
-        <v>1</v>
-      </c>
-      <c r="C22" s="17">
+      <c r="B22" s="14">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14">
         <v>10</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="14">
         <v>11</v>
       </c>
-      <c r="G22" s="18">
-        <v>1</v>
-      </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="17" t="s">
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14"/>
+      <c r="M22" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="14">
+        <v>109</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="E23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K22" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="17">
-        <v>109</v>
-      </c>
-      <c r="B23" s="17">
-        <v>1</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17" t="s">
+      <c r="F23" s="14">
+        <v>12</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="14">
+        <v>110</v>
+      </c>
+      <c r="B24" s="14">
+        <v>1</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E24" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="17">
-        <v>12</v>
-      </c>
-      <c r="G23" s="18">
-        <v>1</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="17" t="s">
+      <c r="F24" s="14">
+        <v>13</v>
+      </c>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="19" t="s">
+      <c r="J24" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="17"/>
-      <c r="M23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="17">
-        <v>110</v>
-      </c>
-      <c r="B24" s="17">
-        <v>1</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17" t="s">
+      <c r="K24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="14">
+        <v>111</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E25" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="17">
-        <v>13</v>
-      </c>
-      <c r="G24" s="18">
-        <v>1</v>
-      </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="17" t="s">
+      <c r="F25" s="14">
+        <v>14</v>
+      </c>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J25" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K24" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="17"/>
-      <c r="M24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="17">
-        <v>111</v>
-      </c>
-      <c r="B25" s="17">
-        <v>1</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17" t="s">
+      <c r="K25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="14"/>
+      <c r="M25" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="17" t="s">
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="14">
+        <v>112</v>
+      </c>
+      <c r="B26" s="14">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="17">
-        <v>14</v>
-      </c>
-      <c r="G25" s="18">
-        <v>1</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="17" t="s">
+      <c r="E26" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="14">
+        <v>15</v>
+      </c>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="19" t="s">
+      <c r="J26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K25" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="17"/>
-      <c r="M25" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="17">
-        <v>112</v>
-      </c>
-      <c r="B26" s="17">
-        <v>1</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="17">
-        <v>15</v>
-      </c>
-      <c r="G26" s="18">
-        <v>1</v>
-      </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" s="17"/>
+      <c r="K26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="14"/>
       <c r="M26" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:13">
@@ -2594,23 +2545,23 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="20">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20"/>
+      <c r="G27" s="16">
+        <v>1</v>
+      </c>
+      <c r="H27" s="16"/>
       <c r="I27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
@@ -2628,29 +2579,29 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>89</v>
+        <v>86</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="22">
-        <v>1</v>
-      </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="17" t="s">
+      <c r="G28" s="18">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J28" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:13">
@@ -2662,29 +2613,29 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="20">
-        <v>1</v>
-      </c>
-      <c r="H29" s="20"/>
+      <c r="G29" s="16">
+        <v>1</v>
+      </c>
+      <c r="H29" s="16"/>
       <c r="I29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="K29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:13">
@@ -2696,29 +2647,29 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>91</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="20">
-        <v>1</v>
-      </c>
-      <c r="H30" s="20"/>
+      <c r="G30" s="16">
+        <v>1</v>
+      </c>
+      <c r="H30" s="16"/>
       <c r="I30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="K30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:13">
@@ -2730,29 +2681,29 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>93</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="20">
-        <v>1</v>
-      </c>
-      <c r="H31" s="20"/>
+      <c r="G31" s="16">
+        <v>1</v>
+      </c>
+      <c r="H31" s="16"/>
       <c r="I31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:13">
@@ -2764,29 +2715,29 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>95</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="20">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20"/>
+      <c r="G32" s="16">
+        <v>1</v>
+      </c>
+      <c r="H32" s="16"/>
       <c r="I32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:13">
@@ -2797,29 +2748,29 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="22">
-        <v>1</v>
-      </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="17" t="s">
+      <c r="G33" s="18">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J33" s="19" t="s">
+      <c r="J33" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2831,30 +2782,30 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="18">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K34" s="17" t="b">
+      <c r="K34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2865,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2876,7 +2827,7 @@
       <c r="I35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J35" s="19" t="s">
+      <c r="J35" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K35" s="2" t="b">
@@ -2884,7 +2835,7 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2892,12 +2843,12 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K36" s="2" t="b">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2030,8 +2030,8 @@
       <c r="J12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="12" t="b">
-        <v>1</v>
+      <c r="K12" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="4" t="s">
@@ -2129,8 +2129,8 @@
       <c r="J15" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="2" t="b">
-        <v>0</v>
+      <c r="K15" s="12" t="b">
+        <v>1</v>
       </c>
       <c r="L15" s="14">
         <v>47061</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -2030,8 +2030,8 @@
       <c r="J12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="2" t="b">
-        <v>0</v>
+      <c r="K12" s="12" t="b">
+        <v>1</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="4" t="s">
@@ -2094,8 +2094,8 @@
       <c r="J14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="12" t="b">
-        <v>1</v>
+      <c r="K14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -296,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -325,6 +325,9 @@
     <t>解锁条件</t>
   </si>
   <si>
+    <t>可看见的解锁条件</t>
+  </si>
+  <si>
     <t>开启状态</t>
   </si>
   <si>
@@ -497,6 +500,9 @@
   </si>
   <si>
     <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1)</t>
   </si>
   <si>
     <t>成长基金</t>
@@ -1654,7 +1660,7 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
     <col min="13" max="13" width="26" style="4" customWidth="1"/>
@@ -1690,52 +1696,52 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
@@ -1743,35 +1749,35 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1784,10 +1790,10 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1799,26 +1805,26 @@
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1830,26 +1836,26 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1861,7 +1867,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1870,17 +1876,17 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1892,10 +1898,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1905,17 +1911,17 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1927,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1936,17 +1942,17 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1956,10 +1962,10 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -1967,17 +1973,17 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K10" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1987,7 +1993,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1996,17 +2002,17 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2016,7 +2022,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2025,17 +2031,17 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2045,26 +2051,26 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2076,10 +2082,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2089,17 +2095,17 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2111,10 +2117,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2124,10 +2130,10 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="12" t="b">
         <v>1</v>
@@ -2136,7 +2142,7 @@
         <v>47061</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2150,10 +2156,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2163,17 +2169,17 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="14"/>
       <c r="M16" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2187,10 +2193,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2200,17 +2206,17 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2224,10 +2230,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2237,17 +2243,17 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="14"/>
       <c r="M18" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2259,10 +2265,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2272,17 +2278,17 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="14"/>
       <c r="M19" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2296,10 +2302,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2309,17 +2315,17 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" s="2" t="b">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="K20" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L20" s="14"/>
       <c r="M20" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2333,10 +2339,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2346,17 +2352,17 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2370,10 +2376,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2383,17 +2389,17 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K22" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2405,10 +2411,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2418,17 +2424,17 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2440,10 +2446,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2453,17 +2459,17 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K24" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2475,10 +2481,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2488,17 +2494,17 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K25" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="14"/>
       <c r="M25" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2510,10 +2516,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2523,17 +2529,17 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K26" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="14"/>
       <c r="M26" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:13">
@@ -2545,10 +2551,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2558,16 +2564,16 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:13">
@@ -2579,10 +2585,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2592,16 +2598,16 @@
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:13">
@@ -2613,10 +2619,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2626,16 +2632,16 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:13">
@@ -2647,10 +2653,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2660,16 +2666,16 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:13">
@@ -2681,10 +2687,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2694,16 +2700,16 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:13">
@@ -2715,10 +2721,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2728,16 +2734,16 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:13">
@@ -2748,10 +2754,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2761,16 +2767,16 @@
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2782,10 +2788,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2795,17 +2801,17 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2816,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2825,17 +2831,17 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2843,13 +2849,13 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K36" s="2" t="b">
         <v>0</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -502,7 +502,7 @@
     <t>Grid (13)</t>
   </si>
   <si>
-    <t>remainingAttempts(57011,1)</t>
+    <t>remainingAttempts(57011,1,1)</t>
   </si>
   <si>
     <t>成长基金</t>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -2174,8 +2174,8 @@
       <c r="J16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K16" s="2" t="b">
-        <v>0</v>
+      <c r="K16" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L16" s="14"/>
       <c r="M16" s="4" t="s">
@@ -2211,8 +2211,8 @@
       <c r="J17" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K17" s="2" t="b">
-        <v>0</v>
+      <c r="K17" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="4" t="s">
@@ -2248,8 +2248,8 @@
       <c r="J18" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K18" s="2" t="b">
-        <v>0</v>
+      <c r="K18" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L18" s="14"/>
       <c r="M18" s="4" t="s">
@@ -2283,8 +2283,8 @@
       <c r="J19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="2" t="b">
-        <v>0</v>
+      <c r="K19" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L19" s="14"/>
       <c r="M19" s="4" t="s">
@@ -2357,8 +2357,8 @@
       <c r="J21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="K21" s="2" t="b">
-        <v>0</v>
+      <c r="K21" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -296,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -325,9 +325,6 @@
     <t>解锁条件</t>
   </si>
   <si>
-    <t>可看见的解锁条件</t>
-  </si>
-  <si>
     <t>开启状态</t>
   </si>
   <si>
@@ -500,9 +497,6 @@
   </si>
   <si>
     <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
   </si>
   <si>
     <t>成长基金</t>
@@ -1660,7 +1654,7 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
+    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
     <col min="13" max="13" width="26" style="4" customWidth="1"/>
@@ -1696,52 +1690,52 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
@@ -1749,35 +1743,35 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1790,10 +1784,10 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1805,26 +1799,26 @@
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1836,26 +1830,26 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="K6" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1867,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1876,17 +1870,17 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K7" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1898,10 +1892,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>40</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1911,17 +1905,17 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K8" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1933,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1942,17 +1936,17 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K9" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1962,10 +1956,10 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -1973,17 +1967,17 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K10" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1993,7 +1987,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -2002,17 +1996,17 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K11" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2022,7 +2016,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2031,17 +2025,17 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="K12" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2051,26 +2045,26 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="K13" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2082,10 +2076,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2095,17 +2089,17 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="2" t="b">
-        <v>0</v>
+      <c r="K14" s="12" t="b">
+        <v>1</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2117,10 +2111,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>53</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2130,19 +2124,19 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="12" t="b">
+      <c r="K15" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="14">
         <v>47061</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2156,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>57</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2169,17 +2163,17 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K16" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="14"/>
       <c r="M16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2193,10 +2187,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>59</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2206,17 +2200,17 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K17" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2230,10 +2224,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>61</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2243,17 +2237,17 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K18" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="14"/>
       <c r="M18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2265,10 +2259,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>62</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>63</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2278,17 +2272,17 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="14" t="s">
         <v>64</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>65</v>
       </c>
       <c r="K19" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="14"/>
       <c r="M19" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2302,10 +2296,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2315,17 +2309,17 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>68</v>
       </c>
       <c r="K20" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="14"/>
       <c r="M20" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2339,10 +2333,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2352,17 +2346,17 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K21" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2376,10 +2370,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2389,17 +2383,17 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K22" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2411,10 +2405,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2424,17 +2418,17 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K23" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2446,10 +2440,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2459,17 +2453,17 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K24" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2481,10 +2475,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2494,17 +2488,17 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K25" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="14"/>
       <c r="M25" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2516,10 +2510,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2529,17 +2523,17 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K26" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="14"/>
       <c r="M26" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:13">
@@ -2551,10 +2545,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2564,16 +2558,16 @@
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:13">
@@ -2585,10 +2579,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2598,16 +2592,16 @@
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K28" s="2" t="b">
-        <v>0</v>
+      <c r="K28" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:13">
@@ -2619,10 +2613,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2632,16 +2626,16 @@
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:13">
@@ -2653,10 +2647,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2666,16 +2660,16 @@
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:13">
@@ -2687,10 +2681,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2700,16 +2694,16 @@
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:13">
@@ -2721,10 +2715,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2734,16 +2728,16 @@
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:13">
@@ -2754,10 +2748,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2767,16 +2761,16 @@
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2788,10 +2782,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2801,17 +2795,17 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2822,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2831,17 +2825,17 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2849,13 +2843,13 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="K36" s="2" t="b">
         <v>0</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -265,11 +265,36 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+条件类型_条件参数
+condition表中条件类型
+注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -296,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -325,6 +350,9 @@
     <t>解锁条件</t>
   </si>
   <si>
+    <t>可看见的解锁条件</t>
+  </si>
+  <si>
     <t>开启状态</t>
   </si>
   <si>
@@ -370,6 +398,9 @@
     <t>vipLevel</t>
   </si>
   <si>
+    <t>showCondition</t>
+  </si>
+  <si>
     <t>condition</t>
   </si>
   <si>
@@ -460,6 +491,9 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(10)</t>
+  </si>
+  <si>
     <t>playerLevel(20)</t>
   </si>
   <si>
@@ -499,6 +533,9 @@
     <t>Grid (13)</t>
   </si>
   <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
     <t>成长基金</t>
   </si>
   <si>
@@ -506,9 +543,6 @@
   </si>
   <si>
     <t>1_10</t>
-  </si>
-  <si>
-    <t>playerLevel(10)</t>
   </si>
   <si>
     <t>签到奖励</t>
@@ -614,7 +648,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,6 +689,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -814,7 +854,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -830,6 +870,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,55 +1186,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1203,74 +1246,77 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1318,6 +1364,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1642,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1654,14 +1703,15 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="4"/>
+    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="14" max="14" width="26" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1690,91 +1740,100 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="K3" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1784,44 +1843,50 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="M5" s="12"/>
+      <c r="N5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1830,29 +1895,32 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1861,7 +1929,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1870,20 +1938,23 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1892,10 +1963,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1905,20 +1976,23 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -1927,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1936,30 +2010,33 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -1967,27 +2044,30 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1996,27 +2076,30 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="12">
         <v>8</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2025,49 +2108,55 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>49</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="12">
         <v>9</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2076,10 +2165,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2089,20 +2178,23 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="14">
         <v>101</v>
       </c>
@@ -2111,10 +2203,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2124,22 +2216,25 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="14">
+        <v>55</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
         <v>47061</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="14">
         <v>102</v>
       </c>
@@ -2150,10 +2245,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2163,20 +2258,23 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="14"/>
+      <c r="N16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="14">
         <v>103</v>
       </c>
@@ -2187,10 +2285,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2200,20 +2298,23 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="14">
         <v>104</v>
       </c>
@@ -2224,10 +2325,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2237,20 +2338,23 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="14"/>
+      <c r="N18" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -2259,10 +2363,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2272,20 +2376,23 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="K19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>67</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="14"/>
+      <c r="N19" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="14">
         <v>106</v>
       </c>
@@ -2296,10 +2403,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2309,20 +2416,23 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>70</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="14"/>
+      <c r="N20" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="14">
         <v>107</v>
       </c>
@@ -2333,10 +2443,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2346,20 +2456,23 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="14"/>
-      <c r="M21" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>56</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="14"/>
+      <c r="N21" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="14">
         <v>108</v>
       </c>
@@ -2370,10 +2483,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2383,20 +2496,23 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="14">
         <v>109</v>
       </c>
@@ -2405,10 +2521,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2418,20 +2534,23 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="14"/>
+      <c r="N23" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="14">
         <v>110</v>
       </c>
@@ -2440,10 +2559,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2453,20 +2572,23 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="14">
         <v>111</v>
       </c>
@@ -2475,10 +2597,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2488,20 +2610,23 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="14">
         <v>112</v>
       </c>
@@ -2510,10 +2635,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2523,20 +2648,23 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="14"/>
+      <c r="N26" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:14">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2545,32 +2673,35 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="16">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K27" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:13">
+      <c r="N27" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:14">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2579,32 +2710,35 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="18">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18"/>
+      <c r="G28" s="19">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19"/>
       <c r="I28" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:14">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2613,32 +2747,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="16">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:13">
+      <c r="N29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:14">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2647,32 +2784,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="16">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:13">
+      <c r="N30" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:14">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2681,32 +2821,35 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="16">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:13">
+      <c r="N31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:14">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2715,32 +2858,35 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="16">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:13">
+      <c r="N32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:14">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2748,32 +2894,35 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="18">
-        <v>1</v>
-      </c>
-      <c r="H33" s="18"/>
+      <c r="G33" s="19">
+        <v>1</v>
+      </c>
+      <c r="H33" s="19"/>
       <c r="I33" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2782,33 +2931,36 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="19">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2816,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2825,33 +2977,39 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -636,6 +636,9 @@
   </si>
   <si>
     <t>新手赠送</t>
+  </si>
+  <si>
+    <t>充值活动：福利</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1694,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -3010,6 +3013,35 @@
         <v>34</v>
       </c>
       <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="4">
+        <v>123</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="4">
+        <v>24</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -265,36 +265,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-条件类型_条件参数
-condition表中条件类型
-注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
-</t>
+如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
         </r>
       </text>
     </comment>
     <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -321,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -350,9 +325,6 @@
     <t>解锁条件</t>
   </si>
   <si>
-    <t>可看见的解锁条件</t>
-  </si>
-  <si>
     <t>开启状态</t>
   </si>
   <si>
@@ -398,9 +370,6 @@
     <t>vipLevel</t>
   </si>
   <si>
-    <t>showCondition</t>
-  </si>
-  <si>
     <t>condition</t>
   </si>
   <si>
@@ -491,60 +460,57 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>刮刮乐</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>等级礼包</t>
+  </si>
+  <si>
+    <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>首充礼包</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>成长基金</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
     <t>playerLevel(10)</t>
   </si>
   <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包</t>
-  </si>
-  <si>
-    <t>Grid (2)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>首充礼包</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
-  </si>
-  <si>
     <t>签到奖励</t>
   </si>
   <si>
@@ -636,9 +602,6 @@
   </si>
   <si>
     <t>新手赠送</t>
-  </si>
-  <si>
-    <t>充值活动：福利</t>
   </si>
 </sst>
 </file>
@@ -651,7 +614,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,12 +655,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -857,7 +814,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -873,12 +830,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1189,52 +1140,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1249,77 +1203,74 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1367,9 +1318,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1694,7 +1642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1706,15 +1654,14 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="14" max="14" width="26" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="4"/>
+    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="13" max="13" width="26" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1743,100 +1690,91 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1846,50 +1784,44 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>30</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="K4" s="9"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1898,32 +1830,29 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="K6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1932,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1941,23 +1870,20 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1966,10 +1892,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1979,23 +1905,20 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2004,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -2013,33 +1936,30 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -2047,30 +1967,27 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -2079,30 +1996,27 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="12">
         <v>8</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2111,55 +2025,49 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>47</v>
+      </c>
+      <c r="K12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="12">
         <v>9</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2168,10 +2076,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2181,23 +2089,20 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="14">
         <v>101</v>
       </c>
@@ -2206,10 +2111,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2219,25 +2124,22 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="L15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="14">
+        <v>53</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="14">
         <v>47061</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="14">
         <v>102</v>
       </c>
@@ -2248,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2261,23 +2163,20 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="14"/>
+      <c r="M16" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="14">
         <v>103</v>
       </c>
@@ -2288,10 +2187,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2301,23 +2200,20 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="14"/>
+      <c r="M17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="14">
         <v>104</v>
       </c>
@@ -2328,10 +2224,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2341,23 +2237,20 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="14"/>
+      <c r="M18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -2366,10 +2259,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2379,23 +2272,20 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>64</v>
+      </c>
+      <c r="K19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="14"/>
+      <c r="M19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="14">
         <v>106</v>
       </c>
@@ -2406,10 +2296,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2419,23 +2309,20 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="N20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="K20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="14"/>
+      <c r="M20" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="14">
         <v>107</v>
       </c>
@@ -2446,10 +2333,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2459,23 +2346,20 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="N21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>70</v>
+      </c>
+      <c r="K21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="14"/>
+      <c r="M21" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="14">
         <v>108</v>
       </c>
@@ -2486,10 +2370,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2499,23 +2383,20 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14"/>
+      <c r="M22" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="14">
         <v>109</v>
       </c>
@@ -2524,10 +2405,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2537,23 +2418,20 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="14">
         <v>110</v>
       </c>
@@ -2562,10 +2440,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2575,23 +2453,20 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="14">
         <v>111</v>
       </c>
@@ -2600,10 +2475,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2613,23 +2488,20 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="14"/>
+      <c r="M25" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="14">
         <v>112</v>
       </c>
@@ -2638,10 +2510,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2651,23 +2523,20 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="14"/>
+      <c r="M26" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:13">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2676,35 +2545,32 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="17">
-        <v>1</v>
-      </c>
-      <c r="H27" s="17"/>
+      <c r="G27" s="16">
+        <v>1</v>
+      </c>
+      <c r="H27" s="16"/>
       <c r="I27" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27" s="2" t="b">
+        <v>85</v>
+      </c>
+      <c r="K27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:14">
+      <c r="M27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:13">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2713,35 +2579,32 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="19">
-        <v>1</v>
-      </c>
-      <c r="H28" s="19"/>
+      <c r="G28" s="18">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
       <c r="I28" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K28" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:13">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2750,35 +2613,32 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="17">
-        <v>1</v>
-      </c>
-      <c r="H29" s="17"/>
+      <c r="G29" s="16">
+        <v>1</v>
+      </c>
+      <c r="H29" s="16"/>
       <c r="I29" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L29" s="2" t="b">
+        <v>85</v>
+      </c>
+      <c r="K29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:14">
+      <c r="M29" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:13">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2787,35 +2647,32 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>91</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="17">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17"/>
+      <c r="G30" s="16">
+        <v>1</v>
+      </c>
+      <c r="H30" s="16"/>
       <c r="I30" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L30" s="2" t="b">
+        <v>85</v>
+      </c>
+      <c r="K30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:14">
+      <c r="M30" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:13">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2824,35 +2681,32 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>93</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="17">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17"/>
+      <c r="G31" s="16">
+        <v>1</v>
+      </c>
+      <c r="H31" s="16"/>
       <c r="I31" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L31" s="2" t="b">
+        <v>85</v>
+      </c>
+      <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:14">
+      <c r="M31" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:13">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2861,35 +2715,32 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>95</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="17">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
+      <c r="G32" s="16">
+        <v>1</v>
+      </c>
+      <c r="H32" s="16"/>
       <c r="I32" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L32" s="2" t="b">
+        <v>85</v>
+      </c>
+      <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:14">
+      <c r="M32" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:13">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2897,35 +2748,32 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19"/>
+      <c r="G33" s="18">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18"/>
       <c r="I33" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="2" t="b">
+        <v>32</v>
+      </c>
+      <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="M33" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2934,36 +2782,33 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="18">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L34" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="K34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2971,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2980,68 +2825,33 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L35" s="2" t="b">
+        <v>32</v>
+      </c>
+      <c r="K35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="L35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L36" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="4">
-        <v>123</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="4">
-        <v>24</v>
-      </c>
-      <c r="G37" s="5">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L37" s="2" t="b">
+        <v>32</v>
+      </c>
+      <c r="K36" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -265,11 +265,36 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+条件类型_条件参数
+condition表中条件类型
+注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启状态保持一致</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -296,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -325,6 +350,9 @@
     <t>解锁条件</t>
   </si>
   <si>
+    <t>可看见的解锁条件</t>
+  </si>
+  <si>
     <t>开启状态</t>
   </si>
   <si>
@@ -370,6 +398,9 @@
     <t>vipLevel</t>
   </si>
   <si>
+    <t>showCondition</t>
+  </si>
+  <si>
     <t>condition</t>
   </si>
   <si>
@@ -460,6 +491,9 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(10)</t>
+  </si>
+  <si>
     <t>playerLevel(20)</t>
   </si>
   <si>
@@ -499,6 +533,9 @@
     <t>Grid (13)</t>
   </si>
   <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
     <t>成长基金</t>
   </si>
   <si>
@@ -508,9 +545,6 @@
     <t>1_10</t>
   </si>
   <si>
-    <t>playerLevel(10)</t>
-  </si>
-  <si>
     <t>签到奖励</t>
   </si>
   <si>
@@ -602,6 +636,9 @@
   </si>
   <si>
     <t>新手赠送</t>
+  </si>
+  <si>
+    <t>充值活动：福利</t>
   </si>
 </sst>
 </file>
@@ -614,7 +651,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,6 +692,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -814,7 +857,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -830,6 +873,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,55 +1189,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1203,74 +1249,77 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1318,6 +1367,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1642,7 +1694,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1654,14 +1706,15 @@
     <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
     <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="40.375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="4"/>
+    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="14" max="14" width="26" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1690,91 +1743,100 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="K3" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1784,44 +1846,50 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="M5" s="12"/>
+      <c r="N5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1830,29 +1898,32 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1861,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1870,20 +1941,23 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1892,10 +1966,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1905,20 +1979,23 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -1927,7 +2004,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1936,30 +2013,33 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -1967,27 +2047,30 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1996,27 +2079,30 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="12">
         <v>8</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2025,49 +2111,55 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>49</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="12">
         <v>9</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2076,10 +2168,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2089,20 +2181,23 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="14">
         <v>101</v>
       </c>
@@ -2111,10 +2206,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2124,22 +2219,25 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="14">
+        <v>55</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
         <v>47061</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="14">
         <v>102</v>
       </c>
@@ -2150,10 +2248,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2163,20 +2261,23 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="14"/>
+      <c r="N16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="14">
         <v>103</v>
       </c>
@@ -2187,10 +2288,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2200,20 +2301,23 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="14">
         <v>104</v>
       </c>
@@ -2224,10 +2328,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2237,20 +2341,23 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="14"/>
+      <c r="N18" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -2259,10 +2366,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2272,20 +2379,23 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="K19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>67</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="14"/>
+      <c r="N19" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="14">
         <v>106</v>
       </c>
@@ -2296,10 +2406,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2309,20 +2419,23 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>70</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="14"/>
+      <c r="N20" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="14">
         <v>107</v>
       </c>
@@ -2333,10 +2446,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2346,20 +2459,23 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="14"/>
-      <c r="M21" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>56</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="14"/>
+      <c r="N21" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="14">
         <v>108</v>
       </c>
@@ -2370,10 +2486,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2383,20 +2499,23 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="14">
         <v>109</v>
       </c>
@@ -2405,10 +2524,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2418,20 +2537,23 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="14"/>
+      <c r="N23" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="14">
         <v>110</v>
       </c>
@@ -2440,10 +2562,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2453,20 +2575,23 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="14">
         <v>111</v>
       </c>
@@ -2475,10 +2600,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2488,20 +2613,23 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="14">
         <v>112</v>
       </c>
@@ -2510,10 +2638,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2523,20 +2651,23 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="14"/>
+      <c r="N26" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:14">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2545,32 +2676,35 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="16">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K27" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:13">
+      <c r="N27" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:14">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2579,32 +2713,35 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="18">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18"/>
+      <c r="G28" s="19">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19"/>
       <c r="I28" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:14">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2613,32 +2750,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="16">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:13">
+      <c r="N29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:14">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2647,32 +2787,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="16">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:13">
+      <c r="N30" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:14">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2681,32 +2824,35 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="16">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:13">
+      <c r="N31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:14">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2715,32 +2861,35 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="16">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="2" t="b">
+        <v>88</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:13">
+      <c r="N32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:14">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2748,32 +2897,35 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="18">
-        <v>1</v>
-      </c>
-      <c r="H33" s="18"/>
+      <c r="G33" s="19">
+        <v>1</v>
+      </c>
+      <c r="H33" s="19"/>
       <c r="I33" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2782,33 +2934,36 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="19">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2816,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2825,33 +2980,68 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="4">
+        <v>123</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="4">
+        <v>24</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -639,6 +639,9 @@
   </si>
   <si>
     <t>充值活动：福利</t>
+  </si>
+  <si>
+    <t>礼包码</t>
   </si>
 </sst>
 </file>
@@ -1694,7 +1697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -3043,6 +3046,35 @@
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="4">
+        <v>124</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -296,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="110">
   <si>
     <t>id</t>
   </si>
@@ -608,6 +608,24 @@
   </si>
   <si>
     <t>新手赠送</t>
+  </si>
+  <si>
+    <t>充值活动：福利</t>
+  </si>
+  <si>
+    <t>Grid (24)</t>
+  </si>
+  <si>
+    <t>礼包码</t>
+  </si>
+  <si>
+    <t>Grid (25)</t>
+  </si>
+  <si>
+    <t>新游期待榜</t>
+  </si>
+  <si>
+    <t>Grid (26)</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1666,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -2859,6 +2877,102 @@
       </c>
       <c r="K36" s="2" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="4">
+        <v>123</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="4">
+        <v>24</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="4">
+        <v>124</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="4">
+        <v>25</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="4">
+        <v>125</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="4">
+        <v>26</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -642,6 +642,9 @@
   </si>
   <si>
     <t>礼包码</t>
+  </si>
+  <si>
+    <t>新游期待榜</t>
   </si>
 </sst>
 </file>
@@ -1697,7 +1700,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -3058,6 +3061,9 @@
       <c r="D38" s="4" t="s">
         <v>106</v>
       </c>
+      <c r="F38" s="4">
+        <v>25</v>
+      </c>
       <c r="G38" s="5">
         <v>1</v>
       </c>
@@ -3074,6 +3080,38 @@
         <v>0</v>
       </c>
       <c r="N38" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="4">
+        <v>125</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="4">
+        <v>26</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2" t="s">
         <v>40</v>
       </c>
     </row>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -2118,8 +2118,8 @@
       <c r="J14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="2" t="b">
-        <v>0</v>
+      <c r="K14" s="12" t="b">
+        <v>1</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="4" t="s">

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -2904,8 +2904,8 @@
       <c r="J37" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="14" t="b">
-        <v>1</v>
+      <c r="K37" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>39</v>
@@ -2936,8 +2936,8 @@
       <c r="J38" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="14" t="b">
-        <v>1</v>
+      <c r="K38" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>39</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="111">
   <si>
     <t>id</t>
   </si>
@@ -641,10 +641,19 @@
     <t>充值活动：福利</t>
   </si>
   <si>
+    <t>Grid (24)</t>
+  </si>
+  <si>
     <t>礼包码</t>
   </si>
   <si>
+    <t>Grid (25)</t>
+  </si>
+  <si>
     <t>新游期待榜</t>
+  </si>
+  <si>
+    <t>Grid (26)</t>
   </si>
 </sst>
 </file>
@@ -3032,6 +3041,9 @@
       <c r="D37" s="4" t="s">
         <v>105</v>
       </c>
+      <c r="E37" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="F37" s="4">
         <v>24</v>
       </c>
@@ -3059,7 +3071,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="F38" s="4">
         <v>25</v>
@@ -3091,7 +3106,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F39" s="4">
         <v>26</v>

--- a/slots/resources/sample/GameFunction.xlsx
+++ b/slots/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -2749,8 +2749,8 @@
       <c r="K28" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L28" s="14" t="b">
-        <v>1</v>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>40</v>
@@ -3091,8 +3091,8 @@
       <c r="K38" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="2" t="b">
-        <v>0</v>
+      <c r="L38" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>40</v>
@@ -3126,8 +3126,8 @@
       <c r="K39" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L39" s="2" t="b">
-        <v>0</v>
+      <c r="L39" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>40</v>
